--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3323</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3331</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13428" uniqueCount="6299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13440" uniqueCount="6303">
   <si>
     <t>名称</t>
   </si>
@@ -20363,6 +20363,18 @@
   </si>
   <si>
     <t>交换元素后的最大交替和</t>
+  </si>
+  <si>
+    <t>LCR 057</t>
+  </si>
+  <si>
+    <t>同220题</t>
+  </si>
+  <si>
+    <t>操作后字符串的最短长度</t>
+  </si>
+  <si>
+    <t>查找具有有效序列号的产品</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22028,16 +22040,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22989,7 +23001,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3336"/>
+  <dimension ref="A1:N3338"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92131,94 +92143,149 @@
       </c>
     </row>
     <row r="3325" spans="1:8">
-      <c r="A3325">
-        <v>3465</v>
+      <c r="A3325" t="s">
+        <v>5910</v>
+      </c>
+      <c r="B3325" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3325" s="2">
+        <v>46083</v>
+      </c>
+      <c r="D3325" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3325" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3325" s="1" t="s">
+        <v>5911</v>
       </c>
     </row>
     <row r="3326" spans="1:8">
       <c r="A3326">
-        <v>3570</v>
+        <v>3223</v>
+      </c>
+      <c r="B3326" t="s">
+        <v>5912</v>
+      </c>
+      <c r="C3326" s="2">
+        <v>46083</v>
+      </c>
+      <c r="D3326" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3326" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3326">
+        <v>1445</v>
+      </c>
+      <c r="G3326" s="1" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="3327" spans="1:8">
       <c r="A3327">
-        <v>3580</v>
+        <v>3465</v>
+      </c>
+      <c r="B3327" t="s">
+        <v>5913</v>
+      </c>
+      <c r="C3327" s="2">
+        <v>46083</v>
+      </c>
+      <c r="D3327" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3327" s="1" t="s">
+        <v>2951</v>
       </c>
     </row>
     <row r="3328" spans="1:8">
       <c r="A3328">
-        <v>3586</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="3329" spans="1:7">
       <c r="A3329">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="3330" spans="1:7">
+      <c r="A3330">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="3331" spans="1:7">
+      <c r="A3331">
         <v>3601</v>
       </c>
     </row>
-    <row r="3333" spans="1:7">
-      <c r="A3333">
+    <row r="3335" spans="1:7">
+      <c r="A3335">
         <v>3454</v>
       </c>
-      <c r="B3333" t="s">
-        <v>5910</v>
-      </c>
-      <c r="D3333" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3333" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3333">
-        <v>2671</v>
-      </c>
-      <c r="G3333" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3334" spans="1:7">
-      <c r="A3334">
-        <v>3562</v>
-      </c>
-      <c r="B3334" t="s">
-        <v>5911</v>
-      </c>
-      <c r="D3334" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3334">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="3335" spans="1:7">
-      <c r="A3335" t="s">
-        <v>5912</v>
-      </c>
       <c r="B3335" t="s">
-        <v>5913</v>
+        <v>5914</v>
       </c>
       <c r="D3335" t="s">
         <v>135</v>
       </c>
+      <c r="E3335" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3335">
+        <v>2671</v>
+      </c>
+      <c r="G3335" s="1" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="3336" spans="1:7">
       <c r="A3336">
-        <v>3721</v>
+        <v>3562</v>
       </c>
       <c r="B3336" t="s">
-        <v>5914</v>
+        <v>5915</v>
       </c>
       <c r="D3336" t="s">
         <v>135</v>
       </c>
-      <c r="E3336" t="s">
+      <c r="F3336">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="3337" spans="1:7">
+      <c r="A3337" t="s">
+        <v>5916</v>
+      </c>
+      <c r="B3337" t="s">
+        <v>5917</v>
+      </c>
+      <c r="D3337" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:7">
+      <c r="A3338">
+        <v>3721</v>
+      </c>
+      <c r="B3338" t="s">
+        <v>5918</v>
+      </c>
+      <c r="D3338" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3338" t="s">
         <v>73</v>
       </c>
-      <c r="F3336">
+      <c r="F3338">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3323" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3331" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92265,10 +92332,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5915</v>
+        <v>5919</v>
       </c>
       <c r="D5" t="s">
-        <v>5916</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92279,13 +92346,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5917</v>
+        <v>5921</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5918</v>
+        <v>5922</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92294,7 +92361,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5919</v>
+        <v>5923</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92309,16 +92376,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5920</v>
+        <v>5924</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5921</v>
+        <v>5925</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5922</v>
+        <v>5926</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92332,10 +92399,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5923</v>
+        <v>5927</v>
       </c>
       <c r="H14" t="s">
-        <v>5924</v>
+        <v>5928</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92350,16 +92417,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5925</v>
+        <v>5929</v>
       </c>
       <c r="W14" t="s">
-        <v>5926</v>
+        <v>5930</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5927</v>
+        <v>5931</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92371,158 +92438,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5929</v>
+        <v>5933</v>
       </c>
       <c r="AL14" t="s">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="AO14" t="s">
-        <v>5931</v>
+        <v>5935</v>
       </c>
       <c r="AR14" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="AU14" t="s">
-        <v>5933</v>
+        <v>5937</v>
       </c>
       <c r="AX14" t="s">
-        <v>5934</v>
+        <v>5938</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5936</v>
+        <v>5940</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5938</v>
+        <v>5942</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="T15" t="s">
-        <v>5940</v>
+        <v>5944</v>
       </c>
       <c r="W15" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="Z15" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="AF15" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
       <c r="AI15" t="s">
-        <v>5945</v>
+        <v>5949</v>
       </c>
       <c r="AL15" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="AU15" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="AX15" t="s">
-        <v>5949</v>
+        <v>5953</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5951</v>
+        <v>5955</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5953</v>
+        <v>5957</v>
       </c>
       <c r="H16" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="N16" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="T16" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="W16" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="Z16" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="AC16" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="AF16" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="AI16" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="AL16" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="AR16" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
       <c r="AU16" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="AX16" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92530,43 +92597,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="D17" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="H17" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="N17" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="T17" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="W17" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="Z17" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="AC17" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="AF17" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="AI17" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="AR17" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="AU17" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="BA17" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92574,37 +92641,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="H18" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="N18" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="T18" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="W18" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="Z18" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="AC18" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="AF18" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AI18" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="AU18" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="BA18" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92612,37 +92679,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="H19" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="N19" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="T19" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="W19" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="Z19" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="AC19" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="AF19" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="AI19" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="AU19" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="BA19" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92650,37 +92717,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>5999</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6001</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6002</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6003</v>
+      </c>
+      <c r="W20" t="s">
         <v>5995</v>
       </c>
-      <c r="D20" t="s">
-        <v>5996</v>
-      </c>
-      <c r="H20" t="s">
-        <v>5997</v>
-      </c>
-      <c r="N20" t="s">
-        <v>5998</v>
-      </c>
-      <c r="T20" t="s">
-        <v>5999</v>
-      </c>
-      <c r="W20" t="s">
-        <v>5991</v>
-      </c>
       <c r="Z20" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="AC20" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="AF20" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="AU20" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="BA20" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -92688,37 +92755,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="D21" t="s">
+        <v>6009</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6010</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6011</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6012</v>
+      </c>
+      <c r="W21" t="s">
         <v>6005</v>
       </c>
-      <c r="H21" t="s">
-        <v>6006</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6007</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6008</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6001</v>
-      </c>
       <c r="Z21" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="AC21" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="AF21" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="AU21" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="BA21" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -92729,13 +92796,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -92744,16 +92811,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="AC22" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AF22" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="AU22" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -92761,25 +92828,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="H23" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="T23" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="Z23" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="AC23" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="AF23" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AU23" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -92787,89 +92854,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="T24" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="Z24" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="AC24" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="AF24" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="D25" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="T25" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="AC25" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="AF25" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="AC26" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AF26" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="AC27" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AF27" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="AC28" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AF28" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -92879,22 +92946,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -92904,7 +92971,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -92912,7 +92979,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -92927,7 +92994,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -92945,227 +93012,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="Q41" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="T41" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="W41" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="AL41" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="AO41" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="AR41" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="Q42" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="T42" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="W42" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AC42" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AL42" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AO42" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AR42" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="K43" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="N43" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="Q43" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="T43" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="W43" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="Z43" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AC43" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AF43" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AL43" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AO43" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AR43" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="F44" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="N44" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="Q44" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="W44" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="Z44" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="AC44" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AF44" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AL44" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AO44" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AR44" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="F45" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="N45" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="Q45" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93174,103 +93241,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AF45" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AO45" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AR45" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="F46" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="N46" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="AC46" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AF46" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AO46" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AR46" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="F47" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AC47" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="AF47" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AO47" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AR47" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="F48" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93282,141 +93349,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AF48" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AO48" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AR48" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AF49" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AR49" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="F50" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AR50" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="F51" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AR51" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AR52" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="F53" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="F54" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="F55" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93424,10 +93491,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="F56" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93435,18 +93502,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="F57" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="F58" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93454,42 +93521,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="F59" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="F60" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="F61" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="F62" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="F63" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93497,181 +93564,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="F64" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="F65" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="F66" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="F67" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="F68" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="F69" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
   </sheetData>
@@ -93698,10 +93765,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -93710,13 +93777,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -93724,13 +93791,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -93742,13 +93809,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -93759,19 +93826,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="S10" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="T10" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -93785,15 +93852,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="S11" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -93802,18 +93869,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -93822,7 +93889,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -93833,13 +93900,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -93850,7 +93917,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -93859,10 +93926,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="T15" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -93873,12 +93940,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -93886,22 +93953,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -93912,39 +93979,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="H32" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="K32" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="N32" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="Q32" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="S32" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -93953,13 +94020,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="K33" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="N33" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -93967,153 +94034,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="K34" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="N34" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="N35" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="N36" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="N37" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="N38" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94121,7 +94188,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94137,7 +94204,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94153,21 +94220,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="J68" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94176,52 +94243,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5917</v>
+        <v>5921</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94283,7 +94350,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94291,10 +94358,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94302,7 +94369,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94315,15 +94382,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="F17" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3333</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13440" uniqueCount="6303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13452" uniqueCount="6307">
   <si>
     <t>名称</t>
   </si>
@@ -20375,6 +20375,18 @@
   </si>
   <si>
     <t>查找具有有效序列号的产品</t>
+  </si>
+  <si>
+    <t>查找无可用副本的书籍</t>
+  </si>
+  <si>
+    <t>LCR 059</t>
+  </si>
+  <si>
+    <t>同703题</t>
+  </si>
+  <si>
+    <t>移除相邻字符</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22034,18 +22046,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -23001,7 +23013,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3338"/>
+  <dimension ref="A1:N3340"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92206,86 +92218,141 @@
       <c r="A3328">
         <v>3570</v>
       </c>
-    </row>
-    <row r="3329" spans="1:7">
-      <c r="A3329">
+      <c r="B3328" t="s">
+        <v>5914</v>
+      </c>
+      <c r="C3328" s="2">
+        <v>46084</v>
+      </c>
+      <c r="D3328" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3328" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3329" spans="1:8">
+      <c r="A3329" t="s">
+        <v>5915</v>
+      </c>
+      <c r="B3329" t="s">
+        <v>5276</v>
+      </c>
+      <c r="C3329" s="2">
+        <v>46084</v>
+      </c>
+      <c r="D3329" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3329" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3329" s="1" t="s">
+        <v>5916</v>
+      </c>
+    </row>
+    <row r="3330" spans="1:8">
+      <c r="A3330">
+        <v>3561</v>
+      </c>
+      <c r="B3330" t="s">
+        <v>5917</v>
+      </c>
+      <c r="C3330" s="2">
+        <v>46084</v>
+      </c>
+      <c r="D3330" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3330" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3330">
+        <v>1397</v>
+      </c>
+      <c r="G3330" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3331" spans="1:8">
+      <c r="A3331">
         <v>3580</v>
       </c>
     </row>
-    <row r="3330" spans="1:7">
-      <c r="A3330">
+    <row r="3332" spans="1:8">
+      <c r="A3332">
         <v>3586</v>
       </c>
     </row>
-    <row r="3331" spans="1:7">
-      <c r="A3331">
+    <row r="3333" spans="1:8">
+      <c r="A3333">
         <v>3601</v>
       </c>
     </row>
-    <row r="3335" spans="1:7">
-      <c r="A3335">
+    <row r="3337" spans="1:8">
+      <c r="A3337">
         <v>3454</v>
       </c>
-      <c r="B3335" t="s">
-        <v>5914</v>
-      </c>
-      <c r="D3335" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3335" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3335">
-        <v>2671</v>
-      </c>
-      <c r="G3335" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3336" spans="1:7">
-      <c r="A3336">
-        <v>3562</v>
-      </c>
-      <c r="B3336" t="s">
-        <v>5915</v>
-      </c>
-      <c r="D3336" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3336">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="3337" spans="1:7">
-      <c r="A3337" t="s">
-        <v>5916</v>
-      </c>
       <c r="B3337" t="s">
-        <v>5917</v>
+        <v>5918</v>
       </c>
       <c r="D3337" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="3338" spans="1:7">
+      <c r="E3337" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3337">
+        <v>2671</v>
+      </c>
+      <c r="G3337" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:8">
       <c r="A3338">
-        <v>3721</v>
+        <v>3562</v>
       </c>
       <c r="B3338" t="s">
-        <v>5918</v>
+        <v>5919</v>
       </c>
       <c r="D3338" t="s">
         <v>135</v>
       </c>
-      <c r="E3338" t="s">
+      <c r="F3338">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="3339" spans="1:8">
+      <c r="A3339" t="s">
+        <v>5920</v>
+      </c>
+      <c r="B3339" t="s">
+        <v>5921</v>
+      </c>
+      <c r="D3339" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3340" spans="1:8">
+      <c r="A3340">
+        <v>3721</v>
+      </c>
+      <c r="B3340" t="s">
+        <v>5922</v>
+      </c>
+      <c r="D3340" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3340" t="s">
         <v>73</v>
       </c>
-      <c r="F3338">
+      <c r="F3340">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3331" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3333" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92332,10 +92399,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5919</v>
+        <v>5923</v>
       </c>
       <c r="D5" t="s">
-        <v>5920</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92346,13 +92413,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5921</v>
+        <v>5925</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5922</v>
+        <v>5926</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92361,7 +92428,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5923</v>
+        <v>5927</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92376,16 +92443,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5924</v>
+        <v>5928</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5925</v>
+        <v>5929</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5926</v>
+        <v>5930</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92399,10 +92466,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5927</v>
+        <v>5931</v>
       </c>
       <c r="H14" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92417,16 +92484,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5929</v>
+        <v>5933</v>
       </c>
       <c r="W14" t="s">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5931</v>
+        <v>5935</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92438,158 +92505,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5933</v>
+        <v>5937</v>
       </c>
       <c r="AL14" t="s">
-        <v>5934</v>
+        <v>5938</v>
       </c>
       <c r="AO14" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="AR14" t="s">
-        <v>5936</v>
+        <v>5940</v>
       </c>
       <c r="AU14" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
       <c r="AX14" t="s">
-        <v>5938</v>
+        <v>5942</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5940</v>
+        <v>5944</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="T15" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
       <c r="W15" t="s">
-        <v>5945</v>
+        <v>5949</v>
       </c>
       <c r="Z15" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="AF15" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="AI15" t="s">
-        <v>5949</v>
+        <v>5953</v>
       </c>
       <c r="AL15" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5951</v>
+        <v>5955</v>
       </c>
       <c r="AU15" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="AX15" t="s">
-        <v>5953</v>
+        <v>5957</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="H16" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="N16" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="T16" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="W16" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
       <c r="Z16" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="AC16" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="AF16" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="AI16" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="AL16" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="AR16" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="AU16" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="AX16" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92597,43 +92664,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="D17" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="H17" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="N17" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="T17" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="W17" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="Z17" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="AC17" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="AF17" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AI17" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="AR17" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="AU17" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="BA17" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92641,37 +92708,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="H18" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="N18" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="T18" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="W18" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="Z18" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="AC18" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="AF18" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="AI18" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="AU18" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="BA18" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92679,37 +92746,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="H19" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="N19" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="T19" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="W19" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="Z19" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="AC19" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="AF19" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AI19" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AU19" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="BA19" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92717,37 +92784,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6004</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6005</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6006</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6007</v>
+      </c>
+      <c r="W20" t="s">
         <v>5999</v>
       </c>
-      <c r="D20" t="s">
-        <v>6000</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6001</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6002</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6003</v>
-      </c>
-      <c r="W20" t="s">
-        <v>5995</v>
-      </c>
       <c r="Z20" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AC20" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="AF20" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="AU20" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="BA20" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -92755,37 +92822,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="D21" t="s">
+        <v>6013</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6014</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6015</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6016</v>
+      </c>
+      <c r="W21" t="s">
         <v>6009</v>
       </c>
-      <c r="H21" t="s">
-        <v>6010</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6011</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6012</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6005</v>
-      </c>
       <c r="Z21" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="AC21" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="AF21" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="AU21" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="BA21" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -92796,13 +92863,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -92811,16 +92878,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="AC22" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="AF22" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="AU22" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -92828,25 +92895,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="H23" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="T23" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="Z23" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="AC23" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AF23" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="AU23" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -92854,89 +92921,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="T24" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="Z24" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="AC24" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="AF24" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="D25" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="T25" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AC25" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="AF25" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AC26" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AF26" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AC27" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AF27" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="AC28" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AF28" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -92946,22 +93013,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -92971,7 +93038,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -92979,7 +93046,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -92994,7 +93061,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93012,227 +93079,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="Q41" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="T41" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="W41" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="AL41" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="AO41" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AR41" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="Q42" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="T42" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="W42" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AC42" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="AL42" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="AO42" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AR42" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="K43" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="N43" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="Q43" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="T43" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="W43" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="Z43" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AC43" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AF43" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="AL43" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="AO43" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AR43" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="F44" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="N44" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="Q44" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="W44" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="Z44" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AC44" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AF44" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="AL44" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="AO44" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AR44" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="F45" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="N45" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="Q45" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93241,103 +93308,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AF45" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AO45" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AR45" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="F46" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="N46" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AC46" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AF46" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AO46" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AR46" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="F47" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AC47" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AF47" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AO47" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AR47" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="F48" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93349,141 +93416,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AF48" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AO48" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AR48" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="AF49" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AR49" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="F50" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AR50" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="F51" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AR51" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AR52" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="F53" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="F54" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="F55" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93491,10 +93558,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="F56" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93502,18 +93569,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="F57" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="F58" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93521,42 +93588,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="F59" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="F60" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="F61" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="F62" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="F63" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93564,181 +93631,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="F64" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="F65" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="F66" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="F67" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="F68" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="F69" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
   </sheetData>
@@ -93765,10 +93832,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -93777,13 +93844,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -93791,13 +93858,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -93809,13 +93876,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -93826,19 +93893,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="S10" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="T10" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -93852,15 +93919,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="S11" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -93869,18 +93936,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -93889,7 +93956,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -93900,13 +93967,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -93917,7 +93984,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -93926,10 +93993,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="T15" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -93940,12 +94007,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -93953,22 +94020,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -93979,39 +94046,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="H32" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="K32" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="N32" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="Q32" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="S32" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94020,13 +94087,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="K33" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="N33" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94034,153 +94101,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="K34" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="N34" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="N35" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="N36" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="N37" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="N38" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94188,7 +94255,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94204,7 +94271,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94220,21 +94287,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="J68" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94243,52 +94310,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5921</v>
+        <v>5925</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94350,7 +94417,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94358,10 +94425,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94369,7 +94436,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94382,15 +94449,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="F17" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3335</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13452" uniqueCount="6307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13464" uniqueCount="6312">
   <si>
     <t>名称</t>
   </si>
@@ -20387,6 +20387,21 @@
   </si>
   <si>
     <t>移除相邻字符</t>
+  </si>
+  <si>
+    <t>寻找持续进步的员工</t>
+  </si>
+  <si>
+    <t>LCR 060</t>
+  </si>
+  <si>
+    <t>前 K 个高频元素</t>
+  </si>
+  <si>
+    <t>同347题</t>
+  </si>
+  <si>
+    <t>判断一个数是否迷人</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22046,9 +22061,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22060,8 +22074,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23013,7 +23028,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3340"/>
+  <dimension ref="A1:N3342"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92278,81 +92293,136 @@
       <c r="A3331">
         <v>3580</v>
       </c>
+      <c r="B3331" t="s">
+        <v>5918</v>
+      </c>
+      <c r="C3331" s="2">
+        <v>46086</v>
+      </c>
+      <c r="D3331" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3331" s="1" t="s">
+        <v>2951</v>
+      </c>
     </row>
     <row r="3332" spans="1:8">
-      <c r="A3332">
-        <v>3586</v>
+      <c r="A3332" t="s">
+        <v>5919</v>
+      </c>
+      <c r="B3332" t="s">
+        <v>5920</v>
+      </c>
+      <c r="C3332" s="2">
+        <v>46086</v>
+      </c>
+      <c r="D3332" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3332" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3332" s="1" t="s">
+        <v>5921</v>
       </c>
     </row>
     <row r="3333" spans="1:8">
       <c r="A3333">
+        <v>2729</v>
+      </c>
+      <c r="B3333" t="s">
+        <v>5922</v>
+      </c>
+      <c r="C3333" s="2">
+        <v>46086</v>
+      </c>
+      <c r="D3333" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3333" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3333">
+        <v>1227</v>
+      </c>
+      <c r="G3333" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="3334" spans="1:8">
+      <c r="A3334">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="3335" spans="1:8">
+      <c r="A3335">
         <v>3601</v>
       </c>
     </row>
-    <row r="3337" spans="1:8">
-      <c r="A3337">
+    <row r="3339" spans="1:8">
+      <c r="A3339">
         <v>3454</v>
       </c>
-      <c r="B3337" t="s">
-        <v>5918</v>
-      </c>
-      <c r="D3337" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3337" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3337">
-        <v>2671</v>
-      </c>
-      <c r="G3337" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3338" spans="1:8">
-      <c r="A3338">
-        <v>3562</v>
-      </c>
-      <c r="B3338" t="s">
-        <v>5919</v>
-      </c>
-      <c r="D3338" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3338">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="3339" spans="1:8">
-      <c r="A3339" t="s">
-        <v>5920</v>
-      </c>
       <c r="B3339" t="s">
-        <v>5921</v>
+        <v>5923</v>
       </c>
       <c r="D3339" t="s">
         <v>135</v>
       </c>
+      <c r="E3339" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3339">
+        <v>2671</v>
+      </c>
+      <c r="G3339" s="1" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="3340" spans="1:8">
       <c r="A3340">
-        <v>3721</v>
+        <v>3562</v>
       </c>
       <c r="B3340" t="s">
-        <v>5922</v>
+        <v>5924</v>
       </c>
       <c r="D3340" t="s">
         <v>135</v>
       </c>
-      <c r="E3340" t="s">
+      <c r="F3340">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="3341" spans="1:8">
+      <c r="A3341" t="s">
+        <v>5925</v>
+      </c>
+      <c r="B3341" t="s">
+        <v>5926</v>
+      </c>
+      <c r="D3341" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3342" spans="1:8">
+      <c r="A3342">
+        <v>3721</v>
+      </c>
+      <c r="B3342" t="s">
+        <v>5927</v>
+      </c>
+      <c r="D3342" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3342" t="s">
         <v>73</v>
       </c>
-      <c r="F3340">
+      <c r="F3342">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3333" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3335" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92399,10 +92469,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5923</v>
+        <v>5928</v>
       </c>
       <c r="D5" t="s">
-        <v>5924</v>
+        <v>5929</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92413,13 +92483,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5925</v>
+        <v>5930</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5926</v>
+        <v>5931</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92428,7 +92498,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5927</v>
+        <v>5932</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92443,16 +92513,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5928</v>
+        <v>5933</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5929</v>
+        <v>5934</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5930</v>
+        <v>5935</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92466,10 +92536,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5931</v>
+        <v>5936</v>
       </c>
       <c r="H14" t="s">
-        <v>5932</v>
+        <v>5937</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92484,16 +92554,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5933</v>
+        <v>5938</v>
       </c>
       <c r="W14" t="s">
-        <v>5934</v>
+        <v>5939</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5935</v>
+        <v>5940</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92505,158 +92575,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5936</v>
+        <v>5941</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5937</v>
+        <v>5942</v>
       </c>
       <c r="AL14" t="s">
-        <v>5938</v>
+        <v>5943</v>
       </c>
       <c r="AO14" t="s">
-        <v>5939</v>
+        <v>5944</v>
       </c>
       <c r="AR14" t="s">
-        <v>5940</v>
+        <v>5945</v>
       </c>
       <c r="AU14" t="s">
-        <v>5941</v>
+        <v>5946</v>
       </c>
       <c r="AX14" t="s">
-        <v>5942</v>
+        <v>5947</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5943</v>
+        <v>5948</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5944</v>
+        <v>5949</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5945</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5946</v>
+        <v>5951</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5947</v>
+        <v>5952</v>
       </c>
       <c r="T15" t="s">
-        <v>5948</v>
+        <v>5953</v>
       </c>
       <c r="W15" t="s">
-        <v>5949</v>
+        <v>5954</v>
       </c>
       <c r="Z15" t="s">
-        <v>5950</v>
+        <v>5955</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5951</v>
+        <v>5956</v>
       </c>
       <c r="AF15" t="s">
-        <v>5952</v>
+        <v>5957</v>
       </c>
       <c r="AI15" t="s">
-        <v>5953</v>
+        <v>5958</v>
       </c>
       <c r="AL15" t="s">
-        <v>5954</v>
+        <v>5959</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5955</v>
+        <v>5960</v>
       </c>
       <c r="AU15" t="s">
-        <v>5956</v>
+        <v>5961</v>
       </c>
       <c r="AX15" t="s">
-        <v>5957</v>
+        <v>5962</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5958</v>
+        <v>5963</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5959</v>
+        <v>5964</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5960</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5961</v>
+        <v>5966</v>
       </c>
       <c r="H16" t="s">
-        <v>5962</v>
+        <v>5967</v>
       </c>
       <c r="N16" t="s">
-        <v>5963</v>
+        <v>5968</v>
       </c>
       <c r="T16" t="s">
-        <v>5964</v>
+        <v>5969</v>
       </c>
       <c r="W16" t="s">
-        <v>5965</v>
+        <v>5970</v>
       </c>
       <c r="Z16" t="s">
-        <v>5966</v>
+        <v>5971</v>
       </c>
       <c r="AC16" t="s">
-        <v>5954</v>
+        <v>5959</v>
       </c>
       <c r="AF16" t="s">
-        <v>5936</v>
+        <v>5941</v>
       </c>
       <c r="AI16" t="s">
-        <v>5967</v>
+        <v>5972</v>
       </c>
       <c r="AL16" t="s">
-        <v>5968</v>
+        <v>5973</v>
       </c>
       <c r="AR16" t="s">
-        <v>5969</v>
+        <v>5974</v>
       </c>
       <c r="AU16" t="s">
-        <v>5970</v>
+        <v>5975</v>
       </c>
       <c r="AX16" t="s">
-        <v>5971</v>
+        <v>5976</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5972</v>
+        <v>5977</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92664,43 +92734,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5973</v>
+        <v>5978</v>
       </c>
       <c r="D17" t="s">
-        <v>5974</v>
+        <v>5979</v>
       </c>
       <c r="H17" t="s">
-        <v>5975</v>
+        <v>5980</v>
       </c>
       <c r="N17" t="s">
-        <v>5976</v>
+        <v>5981</v>
       </c>
       <c r="T17" t="s">
-        <v>5977</v>
+        <v>5982</v>
       </c>
       <c r="W17" t="s">
-        <v>5936</v>
+        <v>5941</v>
       </c>
       <c r="Z17" t="s">
-        <v>5947</v>
+        <v>5952</v>
       </c>
       <c r="AC17" t="s">
-        <v>5978</v>
+        <v>5983</v>
       </c>
       <c r="AF17" t="s">
-        <v>5979</v>
+        <v>5984</v>
       </c>
       <c r="AI17" t="s">
-        <v>5980</v>
+        <v>5985</v>
       </c>
       <c r="AR17" t="s">
-        <v>5981</v>
+        <v>5986</v>
       </c>
       <c r="AU17" t="s">
-        <v>5982</v>
+        <v>5987</v>
       </c>
       <c r="BA17" t="s">
-        <v>5983</v>
+        <v>5988</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92708,37 +92778,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5984</v>
+        <v>5989</v>
       </c>
       <c r="H18" t="s">
-        <v>5985</v>
+        <v>5990</v>
       </c>
       <c r="N18" t="s">
-        <v>5986</v>
+        <v>5991</v>
       </c>
       <c r="T18" t="s">
-        <v>5987</v>
+        <v>5992</v>
       </c>
       <c r="W18" t="s">
-        <v>5988</v>
+        <v>5993</v>
       </c>
       <c r="Z18" t="s">
-        <v>5963</v>
+        <v>5968</v>
       </c>
       <c r="AC18" t="s">
-        <v>5989</v>
+        <v>5994</v>
       </c>
       <c r="AF18" t="s">
-        <v>5990</v>
+        <v>5995</v>
       </c>
       <c r="AI18" t="s">
-        <v>5991</v>
+        <v>5996</v>
       </c>
       <c r="AU18" t="s">
-        <v>5992</v>
+        <v>5997</v>
       </c>
       <c r="BA18" t="s">
-        <v>5993</v>
+        <v>5998</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92746,37 +92816,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>5994</v>
+        <v>5999</v>
       </c>
       <c r="H19" t="s">
-        <v>5995</v>
+        <v>6000</v>
       </c>
       <c r="N19" t="s">
-        <v>5996</v>
+        <v>6001</v>
       </c>
       <c r="T19" t="s">
-        <v>5997</v>
+        <v>6002</v>
       </c>
       <c r="W19" t="s">
-        <v>5971</v>
+        <v>5976</v>
       </c>
       <c r="Z19" t="s">
-        <v>5976</v>
+        <v>5981</v>
       </c>
       <c r="AC19" t="s">
-        <v>5998</v>
+        <v>6003</v>
       </c>
       <c r="AF19" t="s">
-        <v>5999</v>
+        <v>6004</v>
       </c>
       <c r="AI19" t="s">
-        <v>6000</v>
+        <v>6005</v>
       </c>
       <c r="AU19" t="s">
-        <v>6001</v>
+        <v>6006</v>
       </c>
       <c r="BA19" t="s">
-        <v>6002</v>
+        <v>6007</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92784,37 +92854,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6003</v>
+        <v>6008</v>
       </c>
       <c r="D20" t="s">
+        <v>6009</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6010</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6011</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6012</v>
+      </c>
+      <c r="W20" t="s">
         <v>6004</v>
       </c>
-      <c r="H20" t="s">
-        <v>6005</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6006</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6007</v>
-      </c>
-      <c r="W20" t="s">
-        <v>5999</v>
-      </c>
       <c r="Z20" t="s">
-        <v>5986</v>
+        <v>5991</v>
       </c>
       <c r="AC20" t="s">
-        <v>6008</v>
+        <v>6013</v>
       </c>
       <c r="AF20" t="s">
-        <v>6009</v>
+        <v>6014</v>
       </c>
       <c r="AU20" t="s">
-        <v>6010</v>
+        <v>6015</v>
       </c>
       <c r="BA20" t="s">
-        <v>6011</v>
+        <v>6016</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -92822,37 +92892,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6012</v>
+        <v>6017</v>
       </c>
       <c r="D21" t="s">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="H21" t="s">
+        <v>6019</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6020</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6021</v>
+      </c>
+      <c r="W21" t="s">
         <v>6014</v>
       </c>
-      <c r="N21" t="s">
-        <v>6015</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6016</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6009</v>
-      </c>
       <c r="Z21" t="s">
-        <v>5996</v>
+        <v>6001</v>
       </c>
       <c r="AC21" t="s">
-        <v>6017</v>
+        <v>6022</v>
       </c>
       <c r="AF21" t="s">
-        <v>6018</v>
+        <v>6023</v>
       </c>
       <c r="AU21" t="s">
-        <v>6019</v>
+        <v>6024</v>
       </c>
       <c r="BA21" t="s">
-        <v>6020</v>
+        <v>6025</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -92863,13 +92933,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6021</v>
+        <v>6026</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6022</v>
+        <v>6027</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -92878,16 +92948,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6006</v>
+        <v>6011</v>
       </c>
       <c r="AC22" t="s">
-        <v>6023</v>
+        <v>6028</v>
       </c>
       <c r="AF22" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="AU22" t="s">
-        <v>6025</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -92895,25 +92965,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6026</v>
+        <v>6031</v>
       </c>
       <c r="H23" t="s">
-        <v>6027</v>
+        <v>6032</v>
       </c>
       <c r="T23" t="s">
-        <v>6028</v>
+        <v>6033</v>
       </c>
       <c r="Z23" t="s">
-        <v>6015</v>
+        <v>6020</v>
       </c>
       <c r="AC23" t="s">
-        <v>6029</v>
+        <v>6034</v>
       </c>
       <c r="AF23" t="s">
-        <v>6030</v>
+        <v>6035</v>
       </c>
       <c r="AU23" t="s">
-        <v>6031</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -92921,89 +92991,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="T24" t="s">
-        <v>6033</v>
+        <v>6038</v>
       </c>
       <c r="Z24" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="AC24" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="AF24" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6037</v>
+        <v>6042</v>
       </c>
       <c r="D25" t="s">
-        <v>6038</v>
+        <v>6043</v>
       </c>
       <c r="T25" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="AC25" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="AF25" t="s">
-        <v>6041</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="AC26" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
       <c r="AF26" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="AC27" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="AF27" t="s">
-        <v>6047</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6048</v>
+        <v>6053</v>
       </c>
       <c r="AC28" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="AF28" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6054</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93013,22 +93083,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6055</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93038,7 +93108,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93046,7 +93116,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93061,7 +93131,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93079,227 +93149,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="Q41" t="s">
-        <v>6055</v>
+        <v>6060</v>
       </c>
       <c r="T41" t="s">
-        <v>5951</v>
+        <v>5956</v>
       </c>
       <c r="W41" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="AL41" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="AO41" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="AR41" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="Q42" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
       <c r="T42" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="W42" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="AC42" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="AL42" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="AO42" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="AR42" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="K43" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="N43" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="Q43" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
       <c r="T43" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="W43" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="Z43" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="AC43" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
       <c r="AF43" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AL43" t="s">
-        <v>6003</v>
+        <v>6008</v>
       </c>
       <c r="AO43" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="AR43" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="F44" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="N44" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="Q44" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
       <c r="W44" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="Z44" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
       <c r="AC44" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="AF44" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="AL44" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="AO44" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="AR44" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="F45" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="N45" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="Q45" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93308,103 +93378,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="AF45" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="AO45" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="AR45" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="F46" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="N46" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="AC46" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AF46" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="AO46" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="AR46" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="F47" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="AC47" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AF47" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="AO47" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="AR47" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="F48" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93416,141 +93486,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AF48" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="AO48" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="AR48" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AF49" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="AR49" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="F50" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="AR50" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="F51" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="AR51" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="AR52" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="F53" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="F54" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="F55" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93558,10 +93628,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="F56" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93569,18 +93639,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="F57" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="F58" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93588,42 +93658,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="F59" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="F60" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="F61" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="F62" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="F63" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93631,181 +93701,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="F64" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="F65" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="F66" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="F67" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="F68" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="F69" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5952</v>
+        <v>5957</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
     </row>
   </sheetData>
@@ -93832,10 +93902,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -93844,13 +93914,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -93858,13 +93928,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -93876,13 +93946,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -93893,19 +93963,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="S10" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="T10" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -93919,15 +93989,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="S11" t="s">
-        <v>5956</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -93936,18 +94006,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -93956,7 +94026,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -93967,13 +94037,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -93984,7 +94054,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -93993,10 +94063,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="T15" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94007,12 +94077,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94020,22 +94090,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94046,39 +94116,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="H32" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="K32" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="N32" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="Q32" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="S32" t="s">
-        <v>5980</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94087,13 +94157,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
       <c r="K33" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="N33" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94101,153 +94171,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="K34" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
       <c r="N34" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="N35" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="N36" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="N37" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="N38" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>5993</v>
+        <v>5998</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94255,7 +94325,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94271,7 +94341,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94287,21 +94357,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="J68" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94310,52 +94380,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5925</v>
+        <v>5930</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94417,7 +94487,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94425,10 +94495,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94436,7 +94506,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94449,15 +94519,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="F17" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3337</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13464" uniqueCount="6312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13476" uniqueCount="6316">
   <si>
     <t>名称</t>
   </si>
@@ -20402,6 +20402,18 @@
   </si>
   <si>
     <t>判断一个数是否迷人</t>
+  </si>
+  <si>
+    <t>寻找 COVID 康复患者</t>
+  </si>
+  <si>
+    <t>LCR 061</t>
+  </si>
+  <si>
+    <t>同373题</t>
+  </si>
+  <si>
+    <t>木材运输的最小成本</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22061,13 +22073,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22077,6 +22082,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23028,7 +23040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3342"/>
+  <dimension ref="A1:N3344"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92353,76 +92365,131 @@
       <c r="A3334">
         <v>3586</v>
       </c>
+      <c r="B3334" t="s">
+        <v>5923</v>
+      </c>
+      <c r="C3334" s="2">
+        <v>46087</v>
+      </c>
+      <c r="D3334" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3334" s="1" t="s">
+        <v>2951</v>
+      </c>
     </row>
     <row r="3335" spans="1:8">
-      <c r="A3335">
+      <c r="A3335" t="s">
+        <v>5924</v>
+      </c>
+      <c r="B3335" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C3335" s="2">
+        <v>46087</v>
+      </c>
+      <c r="D3335" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3335" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3335" s="1" t="s">
+        <v>5925</v>
+      </c>
+    </row>
+    <row r="3336" spans="1:8">
+      <c r="A3336">
+        <v>3560</v>
+      </c>
+      <c r="B3336" t="s">
+        <v>5926</v>
+      </c>
+      <c r="C3336" s="2">
+        <v>46087</v>
+      </c>
+      <c r="D3336" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3336" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3336">
+        <v>1339</v>
+      </c>
+      <c r="G3336" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3337" spans="1:8">
+      <c r="A3337">
         <v>3601</v>
       </c>
     </row>
-    <row r="3339" spans="1:8">
-      <c r="A3339">
+    <row r="3341" spans="1:8">
+      <c r="A3341">
         <v>3454</v>
       </c>
-      <c r="B3339" t="s">
-        <v>5923</v>
-      </c>
-      <c r="D3339" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3339" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3339">
-        <v>2671</v>
-      </c>
-      <c r="G3339" s="1" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="3340" spans="1:8">
-      <c r="A3340">
-        <v>3562</v>
-      </c>
-      <c r="B3340" t="s">
-        <v>5924</v>
-      </c>
-      <c r="D3340" t="s">
-        <v>135</v>
-      </c>
-      <c r="F3340">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="3341" spans="1:8">
-      <c r="A3341" t="s">
-        <v>5925</v>
-      </c>
       <c r="B3341" t="s">
-        <v>5926</v>
+        <v>5927</v>
       </c>
       <c r="D3341" t="s">
         <v>135</v>
       </c>
+      <c r="E3341" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3341">
+        <v>2671</v>
+      </c>
+      <c r="G3341" s="1" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="3342" spans="1:8">
       <c r="A3342">
-        <v>3721</v>
+        <v>3562</v>
       </c>
       <c r="B3342" t="s">
-        <v>5927</v>
+        <v>5928</v>
       </c>
       <c r="D3342" t="s">
         <v>135</v>
       </c>
-      <c r="E3342" t="s">
+      <c r="F3342">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="3343" spans="1:8">
+      <c r="A3343" t="s">
+        <v>5929</v>
+      </c>
+      <c r="B3343" t="s">
+        <v>5930</v>
+      </c>
+      <c r="D3343" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3344" spans="1:8">
+      <c r="A3344">
+        <v>3721</v>
+      </c>
+      <c r="B3344" t="s">
+        <v>5931</v>
+      </c>
+      <c r="D3344" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3344" t="s">
         <v>73</v>
       </c>
-      <c r="F3342">
+      <c r="F3344">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3335" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3337" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92469,10 +92536,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5928</v>
+        <v>5932</v>
       </c>
       <c r="D5" t="s">
-        <v>5929</v>
+        <v>5933</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92483,13 +92550,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5931</v>
+        <v>5935</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92498,7 +92565,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5932</v>
+        <v>5936</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92513,16 +92580,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5933</v>
+        <v>5937</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5934</v>
+        <v>5938</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92536,10 +92603,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5936</v>
+        <v>5940</v>
       </c>
       <c r="H14" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92554,16 +92621,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5938</v>
+        <v>5942</v>
       </c>
       <c r="W14" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5940</v>
+        <v>5944</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92575,158 +92642,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="AL14" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="AO14" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
       <c r="AR14" t="s">
-        <v>5945</v>
+        <v>5949</v>
       </c>
       <c r="AU14" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="AX14" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5949</v>
+        <v>5953</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5951</v>
+        <v>5955</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="T15" t="s">
-        <v>5953</v>
+        <v>5957</v>
       </c>
       <c r="W15" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="Z15" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="AF15" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="AI15" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="AL15" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="AU15" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
       <c r="AX15" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="H16" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="N16" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="T16" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="W16" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="Z16" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="AC16" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="AF16" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="AI16" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="AL16" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="AR16" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="AU16" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AX16" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92734,43 +92801,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="D17" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="H17" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="N17" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="T17" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="W17" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="Z17" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="AC17" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="AF17" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="AI17" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="AR17" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="AU17" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="BA17" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92778,37 +92845,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="H18" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="N18" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="T18" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="W18" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="Z18" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="AC18" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="AF18" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AI18" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AU18" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="BA18" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92816,37 +92883,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="H19" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="N19" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="T19" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="W19" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="Z19" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="AC19" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="AF19" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="AI19" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="AU19" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="BA19" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92854,37 +92921,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6012</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6013</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6014</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6015</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6016</v>
+      </c>
+      <c r="W20" t="s">
         <v>6008</v>
       </c>
-      <c r="D20" t="s">
-        <v>6009</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6010</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6011</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6012</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6004</v>
-      </c>
       <c r="Z20" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="AC20" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="AF20" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="AU20" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="BA20" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -92892,37 +92959,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="D21" t="s">
+        <v>6022</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6023</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6024</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6025</v>
+      </c>
+      <c r="W21" t="s">
         <v>6018</v>
       </c>
-      <c r="H21" t="s">
-        <v>6019</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6020</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6021</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6014</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="AC21" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AF21" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="AU21" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="BA21" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -92933,13 +93000,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -92948,16 +93015,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="AC22" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="AF22" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="AU22" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -92965,25 +93032,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="H23" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="T23" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="Z23" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="AC23" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="AF23" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AU23" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -92991,89 +93058,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="T24" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="Z24" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AC24" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="AF24" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="D25" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="T25" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="AC25" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AF25" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="AC26" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="AF26" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="AC27" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="AF27" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="AC28" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AF28" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93083,22 +93150,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93108,7 +93175,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93116,7 +93183,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93131,7 +93198,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93149,227 +93216,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="Q41" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="T41" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="W41" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AL41" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AO41" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="AR41" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="Q42" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="T42" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="W42" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AC42" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AL42" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AO42" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AR42" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="K43" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="N43" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="Q43" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="T43" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="W43" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="Z43" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AC43" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AF43" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AL43" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AO43" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="AR43" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="F44" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="N44" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="Q44" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="W44" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="Z44" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AC44" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AF44" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AL44" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AO44" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AR44" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="F45" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="N45" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="Q45" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93378,103 +93445,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AF45" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AO45" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AR45" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="F46" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="N46" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AC46" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AF46" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AO46" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AR46" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="F47" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AC47" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AF47" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AO47" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="AR47" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="F48" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93486,141 +93553,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AF48" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AO48" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AR48" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AF49" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AR49" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="F50" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="AR50" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="F51" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AR51" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AR52" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="F53" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="F54" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="F55" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93628,10 +93695,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="F56" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93639,18 +93706,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="F57" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="F58" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93658,42 +93725,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="F59" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="F60" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="F61" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="F62" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="F63" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93701,181 +93768,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="F64" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="F65" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="F66" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="F67" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="F68" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="F69" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
   </sheetData>
@@ -93902,10 +93969,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -93914,13 +93981,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -93928,13 +93995,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -93946,13 +94013,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -93963,19 +94030,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="S10" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="T10" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -93989,15 +94056,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="S11" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94006,18 +94073,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94026,7 +94093,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94037,13 +94104,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94054,7 +94121,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94063,10 +94130,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="T15" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94077,12 +94144,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94090,22 +94157,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94116,39 +94183,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="H32" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="K32" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="N32" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="Q32" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="S32" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94157,13 +94224,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="K33" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="N33" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94171,153 +94238,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="K34" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="N34" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="N35" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="N36" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="N37" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="N38" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94325,7 +94392,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94341,7 +94408,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94357,21 +94424,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="J68" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94380,52 +94447,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5930</v>
+        <v>5934</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94487,7 +94554,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94495,10 +94562,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94506,7 +94573,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94519,15 +94586,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="F17" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3338</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13476" uniqueCount="6316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13487" uniqueCount="6319">
   <si>
     <t>名称</t>
   </si>
@@ -20414,6 +20414,15 @@
   </si>
   <si>
     <t>木材运输的最小成本</t>
+  </si>
+  <si>
+    <t>统计镜子反射路径数目</t>
+  </si>
+  <si>
+    <t>寻找燃油效率提升的驾驶员</t>
+  </si>
+  <si>
+    <t>十六进制和三十六进制转化</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22079,16 +22088,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23040,7 +23049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3344"/>
+  <dimension ref="A1:N3345"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92423,73 +92432,131 @@
     </row>
     <row r="3337" spans="1:8">
       <c r="A3337">
+        <v>3665</v>
+      </c>
+      <c r="B3337" t="s">
+        <v>5927</v>
+      </c>
+      <c r="C3337" s="2">
+        <v>46088</v>
+      </c>
+      <c r="D3337" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3337" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3337">
+        <v>1883</v>
+      </c>
+      <c r="G3337" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3338" spans="1:8">
+      <c r="A3338">
         <v>3601</v>
       </c>
-    </row>
-    <row r="3341" spans="1:8">
-      <c r="A3341">
-        <v>3454</v>
-      </c>
-      <c r="B3341" t="s">
-        <v>5927</v>
-      </c>
-      <c r="D3341" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3341" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3341">
-        <v>2671</v>
-      </c>
-      <c r="G3341" s="1" t="s">
-        <v>927</v>
+      <c r="B3338" t="s">
+        <v>5928</v>
+      </c>
+      <c r="C3338" s="2">
+        <v>46088</v>
+      </c>
+      <c r="D3338" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3338" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3339" spans="1:8">
+      <c r="A3339">
+        <v>3602</v>
+      </c>
+      <c r="B3339" t="s">
+        <v>5929</v>
+      </c>
+      <c r="C3339" s="2">
+        <v>46088</v>
+      </c>
+      <c r="D3339" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3339" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3339">
+        <v>1305</v>
+      </c>
+      <c r="G3339" s="1" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="3342" spans="1:8">
       <c r="A3342">
-        <v>3562</v>
+        <v>3454</v>
       </c>
       <c r="B3342" t="s">
-        <v>5928</v>
+        <v>5930</v>
       </c>
       <c r="D3342" t="s">
         <v>135</v>
       </c>
+      <c r="E3342" t="s">
+        <v>73</v>
+      </c>
       <c r="F3342">
-        <v>2458</v>
+        <v>2671</v>
+      </c>
+      <c r="G3342" s="1" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="3343" spans="1:8">
-      <c r="A3343" t="s">
-        <v>5929</v>
+      <c r="A3343">
+        <v>3562</v>
       </c>
       <c r="B3343" t="s">
-        <v>5930</v>
+        <v>5931</v>
       </c>
       <c r="D3343" t="s">
         <v>135</v>
       </c>
+      <c r="F3343">
+        <v>2458</v>
+      </c>
     </row>
     <row r="3344" spans="1:8">
-      <c r="A3344">
-        <v>3721</v>
+      <c r="A3344" t="s">
+        <v>5932</v>
       </c>
       <c r="B3344" t="s">
-        <v>5931</v>
+        <v>5933</v>
       </c>
       <c r="D3344" t="s">
         <v>135</v>
       </c>
-      <c r="E3344" t="s">
+    </row>
+    <row r="3345" spans="1:6">
+      <c r="A3345">
+        <v>3721</v>
+      </c>
+      <c r="B3345" t="s">
+        <v>5934</v>
+      </c>
+      <c r="D3345" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3345" t="s">
         <v>73</v>
       </c>
-      <c r="F3344">
+      <c r="F3345">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3337" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3338" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92536,10 +92603,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5932</v>
+        <v>5935</v>
       </c>
       <c r="D5" t="s">
-        <v>5933</v>
+        <v>5936</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92550,13 +92617,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5934</v>
+        <v>5937</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5935</v>
+        <v>5938</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92565,7 +92632,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5936</v>
+        <v>5939</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92580,16 +92647,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5937</v>
+        <v>5940</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5938</v>
+        <v>5941</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5939</v>
+        <v>5942</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92603,10 +92670,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5940</v>
+        <v>5943</v>
       </c>
       <c r="H14" t="s">
-        <v>5941</v>
+        <v>5944</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92621,16 +92688,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5942</v>
+        <v>5945</v>
       </c>
       <c r="W14" t="s">
-        <v>5943</v>
+        <v>5946</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5944</v>
+        <v>5947</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92642,158 +92709,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5945</v>
+        <v>5948</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5946</v>
+        <v>5949</v>
       </c>
       <c r="AL14" t="s">
-        <v>5947</v>
+        <v>5950</v>
       </c>
       <c r="AO14" t="s">
-        <v>5948</v>
+        <v>5951</v>
       </c>
       <c r="AR14" t="s">
-        <v>5949</v>
+        <v>5952</v>
       </c>
       <c r="AU14" t="s">
-        <v>5950</v>
+        <v>5953</v>
       </c>
       <c r="AX14" t="s">
-        <v>5951</v>
+        <v>5954</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5952</v>
+        <v>5955</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5953</v>
+        <v>5956</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5954</v>
+        <v>5957</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5955</v>
+        <v>5958</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5956</v>
+        <v>5959</v>
       </c>
       <c r="T15" t="s">
-        <v>5957</v>
+        <v>5960</v>
       </c>
       <c r="W15" t="s">
-        <v>5958</v>
+        <v>5961</v>
       </c>
       <c r="Z15" t="s">
-        <v>5959</v>
+        <v>5962</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5960</v>
+        <v>5963</v>
       </c>
       <c r="AF15" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
       <c r="AI15" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="AL15" t="s">
-        <v>5963</v>
+        <v>5966</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5964</v>
+        <v>5967</v>
       </c>
       <c r="AU15" t="s">
-        <v>5965</v>
+        <v>5968</v>
       </c>
       <c r="AX15" t="s">
-        <v>5966</v>
+        <v>5969</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5967</v>
+        <v>5970</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5968</v>
+        <v>5971</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5969</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5970</v>
+        <v>5973</v>
       </c>
       <c r="H16" t="s">
-        <v>5971</v>
+        <v>5974</v>
       </c>
       <c r="N16" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="T16" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="W16" t="s">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="Z16" t="s">
-        <v>5975</v>
+        <v>5978</v>
       </c>
       <c r="AC16" t="s">
-        <v>5963</v>
+        <v>5966</v>
       </c>
       <c r="AF16" t="s">
-        <v>5945</v>
+        <v>5948</v>
       </c>
       <c r="AI16" t="s">
-        <v>5976</v>
+        <v>5979</v>
       </c>
       <c r="AL16" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="AR16" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
       <c r="AU16" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="AX16" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5981</v>
+        <v>5984</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92801,43 +92868,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
       <c r="D17" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="H17" t="s">
-        <v>5984</v>
+        <v>5987</v>
       </c>
       <c r="N17" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="T17" t="s">
-        <v>5986</v>
+        <v>5989</v>
       </c>
       <c r="W17" t="s">
-        <v>5945</v>
+        <v>5948</v>
       </c>
       <c r="Z17" t="s">
-        <v>5956</v>
+        <v>5959</v>
       </c>
       <c r="AC17" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="AF17" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
       <c r="AI17" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="AR17" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="AU17" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="BA17" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92845,37 +92912,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="H18" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="N18" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="T18" t="s">
-        <v>5996</v>
+        <v>5999</v>
       </c>
       <c r="W18" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="Z18" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="AC18" t="s">
-        <v>5998</v>
+        <v>6001</v>
       </c>
       <c r="AF18" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="AI18" t="s">
-        <v>6000</v>
+        <v>6003</v>
       </c>
       <c r="AU18" t="s">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="BA18" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92883,37 +92950,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="H19" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
       <c r="N19" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="T19" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="W19" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="Z19" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="AC19" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AF19" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="AI19" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="AU19" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="BA19" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92921,37 +92988,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="D20" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="H20" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="N20" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="T20" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="W20" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="Z20" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="AC20" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="AF20" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="AU20" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="BA20" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -92959,37 +93026,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6024</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6025</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6026</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6027</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6028</v>
+      </c>
+      <c r="W21" t="s">
         <v>6021</v>
       </c>
-      <c r="D21" t="s">
-        <v>6022</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6023</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6024</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6025</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6018</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="AC21" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="AF21" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="AU21" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="BA21" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93000,13 +93067,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93015,16 +93082,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="AC22" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AF22" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="AU22" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93032,25 +93099,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="H23" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="T23" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="Z23" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="AC23" t="s">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="AF23" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="AU23" t="s">
-        <v>6040</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93058,89 +93125,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="T24" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="Z24" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="AC24" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="AF24" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="D25" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="T25" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="AC25" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="AF25" t="s">
-        <v>6050</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="AC26" t="s">
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="AF26" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="AC27" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="AF27" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="AC28" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="AF28" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93150,22 +93217,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93175,7 +93242,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93183,7 +93250,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93198,7 +93265,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93216,227 +93283,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6071</v>
+        <v>6074</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="Q41" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="T41" t="s">
-        <v>5960</v>
+        <v>5963</v>
       </c>
       <c r="W41" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
       <c r="AL41" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
       <c r="AO41" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="AR41" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="Q42" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="T42" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="W42" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="AC42" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
       <c r="AL42" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="AO42" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="AR42" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="K43" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
       <c r="N43" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="Q43" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="T43" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="W43" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="Z43" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="AC43" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="AF43" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="AL43" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="AO43" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="AR43" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="F44" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="N44" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="Q44" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
       <c r="W44" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="Z44" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="AC44" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="AF44" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="AL44" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="AO44" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="AR44" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="F45" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
       <c r="N45" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="Q45" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93445,103 +93512,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="AF45" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="AO45" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="AR45" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
       <c r="F46" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="N46" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="AC46" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="AF46" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
       <c r="AO46" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="AR46" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="F47" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
       <c r="AC47" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="AF47" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="AO47" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
       <c r="AR47" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="F48" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93553,141 +93620,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="AF48" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="AO48" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AR48" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="AF49" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="AR49" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="F50" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="AR50" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="F51" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="AR51" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="AR52" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="F53" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="F54" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="F55" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93695,10 +93762,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="F56" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93706,18 +93773,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="F57" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="F58" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93725,42 +93792,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="F59" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="F60" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="F61" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
       <c r="F62" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
       <c r="F63" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93768,181 +93835,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="F64" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="F65" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
       <c r="F66" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="F67" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="F68" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="F69" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
   </sheetData>
@@ -93969,10 +94036,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -93981,13 +94048,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -93995,13 +94062,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94013,13 +94080,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94030,19 +94097,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
       <c r="S10" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
       <c r="T10" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94056,15 +94123,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
       <c r="S11" t="s">
-        <v>5965</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94073,18 +94140,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94093,7 +94160,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94104,13 +94171,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94121,7 +94188,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94130,10 +94197,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="T15" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94144,12 +94211,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94157,22 +94224,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94183,39 +94250,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
       <c r="H32" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
       <c r="K32" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="N32" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="Q32" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="S32" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94224,13 +94291,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="K33" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="N33" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94238,153 +94305,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="K34" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="N34" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="N35" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
       <c r="N36" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="N37" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
       <c r="N38" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94392,7 +94459,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94408,7 +94475,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94424,21 +94491,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
       <c r="J68" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94447,52 +94514,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5934</v>
+        <v>5937</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94554,7 +94621,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94562,10 +94629,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94573,7 +94640,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94586,15 +94653,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
       <c r="F17" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3341</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13487" uniqueCount="6319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13498" uniqueCount="6323">
   <si>
     <t>名称</t>
   </si>
@@ -20423,6 +20423,18 @@
   </si>
   <si>
     <t>十六进制和三十六进制转化</t>
+  </si>
+  <si>
+    <t>最长相邻绝对差递减子序列</t>
+  </si>
+  <si>
+    <t>优化的写法是定义更好的状态，可以避免使用前缀和，使得状态转移更加方便</t>
+  </si>
+  <si>
+    <t>查找超预订员工</t>
+  </si>
+  <si>
+    <t>查找具有螺旋学习模式的学生</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22088,16 +22100,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23049,7 +23061,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3345"/>
+  <dimension ref="A1:N3355"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92493,70 +92505,130 @@
         <v>685</v>
       </c>
     </row>
+    <row r="3340" spans="1:8">
+      <c r="A3340">
+        <v>3409</v>
+      </c>
+      <c r="B3340" t="s">
+        <v>5930</v>
+      </c>
+      <c r="C3340" s="2">
+        <v>46089</v>
+      </c>
+      <c r="D3340" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3340" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3340">
+        <v>2500</v>
+      </c>
+      <c r="G3340" s="1" t="s">
+        <v>3574</v>
+      </c>
+      <c r="H3340" s="1" t="s">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="3341" spans="1:8">
+      <c r="A3341">
+        <v>3611</v>
+      </c>
+      <c r="B3341" t="s">
+        <v>5932</v>
+      </c>
+      <c r="C3341" s="2">
+        <v>46089</v>
+      </c>
+      <c r="D3341" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3341" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
     <row r="3342" spans="1:8">
       <c r="A3342">
-        <v>3454</v>
+        <v>3617</v>
       </c>
       <c r="B3342" t="s">
-        <v>5930</v>
+        <v>5933</v>
+      </c>
+      <c r="C3342" s="2">
+        <v>46089</v>
       </c>
       <c r="D3342" t="s">
         <v>135</v>
       </c>
-      <c r="E3342" t="s">
+      <c r="H3342" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3352" spans="1:7">
+      <c r="A3352">
+        <v>3454</v>
+      </c>
+      <c r="B3352" t="s">
+        <v>5934</v>
+      </c>
+      <c r="D3352" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3352" t="s">
         <v>73</v>
       </c>
-      <c r="F3342">
+      <c r="F3352">
         <v>2671</v>
       </c>
-      <c r="G3342" s="1" t="s">
+      <c r="G3352" s="1" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="3343" spans="1:8">
-      <c r="A3343">
+    <row r="3353" spans="1:7">
+      <c r="A3353">
         <v>3562</v>
       </c>
-      <c r="B3343" t="s">
-        <v>5931</v>
-      </c>
-      <c r="D3343" t="s">
+      <c r="B3353" t="s">
+        <v>5935</v>
+      </c>
+      <c r="D3353" t="s">
         <v>135</v>
       </c>
-      <c r="F3343">
+      <c r="F3353">
         <v>2458</v>
       </c>
     </row>
-    <row r="3344" spans="1:8">
-      <c r="A3344" t="s">
-        <v>5932</v>
-      </c>
-      <c r="B3344" t="s">
-        <v>5933</v>
-      </c>
-      <c r="D3344" t="s">
+    <row r="3354" spans="1:7">
+      <c r="A3354" t="s">
+        <v>5936</v>
+      </c>
+      <c r="B3354" t="s">
+        <v>5937</v>
+      </c>
+      <c r="D3354" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3345" spans="1:6">
-      <c r="A3345">
+    <row r="3355" spans="1:7">
+      <c r="A3355">
         <v>3721</v>
       </c>
-      <c r="B3345" t="s">
-        <v>5934</v>
-      </c>
-      <c r="D3345" t="s">
+      <c r="B3355" t="s">
+        <v>5938</v>
+      </c>
+      <c r="D3355" t="s">
         <v>135</v>
       </c>
-      <c r="E3345" t="s">
+      <c r="E3355" t="s">
         <v>73</v>
       </c>
-      <c r="F3345">
+      <c r="F3355">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3338" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3341" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92603,10 +92675,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="D5" t="s">
-        <v>5936</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92617,13 +92689,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5938</v>
+        <v>5942</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92632,7 +92704,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92647,16 +92719,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5940</v>
+        <v>5944</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92670,10 +92742,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="H14" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92688,16 +92760,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5945</v>
+        <v>5949</v>
       </c>
       <c r="W14" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92709,158 +92781,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5949</v>
+        <v>5953</v>
       </c>
       <c r="AL14" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="AO14" t="s">
-        <v>5951</v>
+        <v>5955</v>
       </c>
       <c r="AR14" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="AU14" t="s">
-        <v>5953</v>
+        <v>5957</v>
       </c>
       <c r="AX14" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="T15" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="W15" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
       <c r="Z15" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="AF15" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="AI15" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="AL15" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="AU15" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="AX15" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="H16" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="N16" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="T16" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="W16" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="Z16" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="AC16" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="AF16" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="AI16" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="AL16" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="AR16" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="AU16" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AX16" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92868,43 +92940,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="D17" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="H17" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="N17" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="T17" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="W17" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="Z17" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="AC17" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="AF17" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="AI17" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="AR17" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="AU17" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="BA17" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92912,37 +92984,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="H18" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="N18" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="T18" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="W18" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="Z18" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AC18" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="AF18" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="AI18" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="AU18" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="BA18" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -92950,37 +93022,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="H19" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="N19" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="T19" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="W19" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="Z19" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="AC19" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="AF19" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="AI19" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="AU19" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="BA19" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -92988,37 +93060,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6019</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6020</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6021</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6022</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6023</v>
+      </c>
+      <c r="W20" t="s">
         <v>6015</v>
       </c>
-      <c r="D20" t="s">
-        <v>6016</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6017</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6018</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6019</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6011</v>
-      </c>
       <c r="Z20" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="AC20" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="AF20" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="AU20" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="BA20" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93026,37 +93098,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="D21" t="s">
+        <v>6029</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6030</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6031</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6032</v>
+      </c>
+      <c r="W21" t="s">
         <v>6025</v>
       </c>
-      <c r="H21" t="s">
-        <v>6026</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6027</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6028</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6021</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AC21" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="AF21" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="AU21" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="BA21" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93067,13 +93139,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93082,16 +93154,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="AC22" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AF22" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="AU22" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93099,25 +93171,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="H23" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="T23" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="Z23" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="AC23" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AF23" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AU23" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93125,89 +93197,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="T24" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="Z24" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="AC24" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="AF24" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="D25" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="T25" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="AC25" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="AF25" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AC26" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AF26" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AC27" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AF27" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="AC28" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AF28" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93217,22 +93289,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93242,7 +93314,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93250,7 +93322,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93265,7 +93337,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93283,227 +93355,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="Q41" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="T41" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="W41" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AL41" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AO41" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AR41" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="Q42" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="T42" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="W42" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AC42" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="AL42" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="AO42" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AR42" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="K43" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="N43" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="Q43" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="T43" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="W43" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="Z43" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="AC43" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="AF43" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AL43" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AO43" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AR43" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="F44" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="N44" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="Q44" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="W44" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="Z44" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AC44" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AF44" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AL44" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AO44" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AR44" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="F45" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="N45" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="Q45" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93512,103 +93584,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AF45" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AO45" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AR45" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="F46" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="N46" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AC46" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AF46" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AO46" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AR46" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="F47" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AC47" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AF47" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AO47" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AR47" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="F48" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93620,141 +93692,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AF48" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AO48" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AR48" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="AF49" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AR49" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="F50" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AR50" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="F51" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AR51" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AR52" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="F53" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="F54" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="F55" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93762,10 +93834,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="F56" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93773,18 +93845,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="F57" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="F58" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93792,42 +93864,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="F59" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="F60" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="F61" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="F62" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="F63" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93835,181 +93907,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="F64" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="F65" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="F66" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="F67" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="F68" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="F69" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
   </sheetData>
@@ -94036,10 +94108,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94048,13 +94120,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94062,13 +94134,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94080,13 +94152,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94097,19 +94169,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="S10" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="T10" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94123,15 +94195,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="S11" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94140,18 +94212,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94160,7 +94232,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94171,13 +94243,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94188,7 +94260,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94197,10 +94269,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="T15" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94211,12 +94283,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94224,22 +94296,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94250,39 +94322,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="H32" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="K32" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="N32" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="Q32" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="S32" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94291,13 +94363,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="K33" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="N33" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94305,153 +94377,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="K34" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="N34" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="N35" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="N36" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="N37" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="N38" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94459,7 +94531,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94475,7 +94547,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94491,21 +94563,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="J68" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94514,52 +94586,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94621,7 +94693,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94629,10 +94701,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94640,7 +94712,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94653,15 +94725,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="F17" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3342</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13498" uniqueCount="6323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13510" uniqueCount="6327">
   <si>
     <t>名称</t>
   </si>
@@ -20435,6 +20435,18 @@
   </si>
   <si>
     <t>查找具有螺旋学习模式的学生</t>
+  </si>
+  <si>
+    <t>LCR 062</t>
+  </si>
+  <si>
+    <t>同208题</t>
+  </si>
+  <si>
+    <t>总价值可以被 K 整除的岛屿数目</t>
+  </si>
+  <si>
+    <t>查找库存不平衡的店铺</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -92565,12 +92577,72 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="3352" spans="1:7">
+    <row r="3343" spans="1:8">
+      <c r="A3343" t="s">
+        <v>5934</v>
+      </c>
+      <c r="B3343" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3343" s="2">
+        <v>46090</v>
+      </c>
+      <c r="D3343" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3343" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3343" s="1" t="s">
+        <v>5935</v>
+      </c>
+    </row>
+    <row r="3344" spans="1:8">
+      <c r="A3344">
+        <v>3619</v>
+      </c>
+      <c r="B3344" t="s">
+        <v>5936</v>
+      </c>
+      <c r="C3344" s="2">
+        <v>46090</v>
+      </c>
+      <c r="D3344" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3344" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3344">
+        <v>1461</v>
+      </c>
+      <c r="G3344" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3345" spans="1:8">
+      <c r="A3345">
+        <v>3626</v>
+      </c>
+      <c r="B3345" t="s">
+        <v>5937</v>
+      </c>
+      <c r="C3345" s="2">
+        <v>46090</v>
+      </c>
+      <c r="D3345" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3345" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3352" spans="1:8">
       <c r="A3352">
         <v>3454</v>
       </c>
       <c r="B3352" t="s">
-        <v>5934</v>
+        <v>5938</v>
       </c>
       <c r="D3352" t="s">
         <v>135</v>
@@ -92585,12 +92657,12 @@
         <v>927</v>
       </c>
     </row>
-    <row r="3353" spans="1:7">
+    <row r="3353" spans="1:8">
       <c r="A3353">
         <v>3562</v>
       </c>
       <c r="B3353" t="s">
-        <v>5935</v>
+        <v>5939</v>
       </c>
       <c r="D3353" t="s">
         <v>135</v>
@@ -92599,23 +92671,23 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="3354" spans="1:7">
+    <row r="3354" spans="1:8">
       <c r="A3354" t="s">
-        <v>5936</v>
+        <v>5940</v>
       </c>
       <c r="B3354" t="s">
-        <v>5937</v>
+        <v>5941</v>
       </c>
       <c r="D3354" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3355" spans="1:7">
+    <row r="3355" spans="1:8">
       <c r="A3355">
         <v>3721</v>
       </c>
       <c r="B3355" t="s">
-        <v>5938</v>
+        <v>5942</v>
       </c>
       <c r="D3355" t="s">
         <v>135</v>
@@ -92628,7 +92700,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3341" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3342" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92675,10 +92747,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5939</v>
+        <v>5943</v>
       </c>
       <c r="D5" t="s">
-        <v>5940</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92689,13 +92761,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5942</v>
+        <v>5946</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92704,7 +92776,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5943</v>
+        <v>5947</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92719,16 +92791,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5944</v>
+        <v>5948</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5945</v>
+        <v>5949</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5946</v>
+        <v>5950</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92742,10 +92814,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5947</v>
+        <v>5951</v>
       </c>
       <c r="H14" t="s">
-        <v>5948</v>
+        <v>5952</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92760,16 +92832,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5949</v>
+        <v>5953</v>
       </c>
       <c r="W14" t="s">
-        <v>5950</v>
+        <v>5954</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5951</v>
+        <v>5955</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92781,158 +92853,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5953</v>
+        <v>5957</v>
       </c>
       <c r="AL14" t="s">
-        <v>5954</v>
+        <v>5958</v>
       </c>
       <c r="AO14" t="s">
-        <v>5955</v>
+        <v>5959</v>
       </c>
       <c r="AR14" t="s">
-        <v>5956</v>
+        <v>5960</v>
       </c>
       <c r="AU14" t="s">
-        <v>5957</v>
+        <v>5961</v>
       </c>
       <c r="AX14" t="s">
-        <v>5958</v>
+        <v>5962</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5959</v>
+        <v>5963</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5960</v>
+        <v>5964</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5961</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="T15" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="W15" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="Z15" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="AF15" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="AI15" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="AL15" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="AU15" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="AX15" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="H16" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="N16" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="T16" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="W16" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="Z16" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AC16" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="AF16" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="AI16" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="AL16" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="AR16" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="AU16" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="AX16" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -92940,43 +93012,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="D17" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="H17" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="N17" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="T17" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="W17" t="s">
-        <v>5952</v>
+        <v>5956</v>
       </c>
       <c r="Z17" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
       <c r="AC17" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="AF17" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AI17" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AR17" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="AU17" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="BA17" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -92984,37 +93056,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="H18" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="N18" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="T18" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="W18" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="Z18" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="AC18" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="AF18" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="AI18" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="AU18" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="BA18" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93022,37 +93094,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="H19" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="N19" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="T19" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="W19" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="Z19" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="AC19" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="AF19" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AI19" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="AU19" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="BA19" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93060,37 +93132,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6023</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6024</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6025</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6026</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6027</v>
+      </c>
+      <c r="W20" t="s">
         <v>6019</v>
       </c>
-      <c r="D20" t="s">
-        <v>6020</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6021</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6022</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6023</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6015</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="AC20" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="AF20" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AU20" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="BA20" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93098,37 +93170,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="D21" t="s">
+        <v>6033</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6034</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6035</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6036</v>
+      </c>
+      <c r="W21" t="s">
         <v>6029</v>
       </c>
-      <c r="H21" t="s">
-        <v>6030</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6031</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6032</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6025</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="AC21" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="AF21" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="AU21" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="BA21" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93139,13 +93211,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93154,16 +93226,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AC22" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AF22" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="AU22" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93171,25 +93243,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="H23" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="T23" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="Z23" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="AC23" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AF23" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="AU23" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93197,89 +93269,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="T24" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="Z24" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="AC24" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="AF24" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="D25" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="T25" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AC25" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AF25" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AC26" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="AF26" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AC27" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="AF27" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="AC28" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="AF28" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93289,22 +93361,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93314,7 +93386,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93322,7 +93394,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93337,7 +93409,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93355,227 +93427,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="Q41" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="T41" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="W41" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AL41" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AO41" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AR41" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="Q42" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="T42" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="W42" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AC42" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AL42" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AO42" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AR42" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="K43" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="N43" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="Q43" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="T43" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="W43" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="Z43" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AC43" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AF43" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AL43" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="AO43" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AR43" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="F44" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="N44" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="Q44" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="W44" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="Z44" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AC44" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AF44" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AL44" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AO44" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AR44" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="F45" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="N45" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="Q45" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93584,103 +93656,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AF45" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AO45" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AR45" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="F46" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="N46" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AC46" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AF46" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="AO46" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AR46" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="F47" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AC47" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AF47" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AO47" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AR47" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="F48" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93692,141 +93764,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AF48" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AO48" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="AR48" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AF49" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AR49" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="F50" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AR50" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="F51" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AR51" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="AR52" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="F53" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="F54" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="F55" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93834,10 +93906,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="F56" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93845,18 +93917,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="F57" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="F58" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93864,42 +93936,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="F59" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="F60" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="F61" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="F62" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="F63" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93907,181 +93979,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="F64" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="F65" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="F66" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="F67" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="F68" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="F69" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
     </row>
   </sheetData>
@@ -94108,10 +94180,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94120,13 +94192,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94134,13 +94206,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94152,13 +94224,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94169,19 +94241,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="S10" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="T10" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94195,15 +94267,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="S11" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94212,18 +94284,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94232,7 +94304,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94243,13 +94315,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94260,7 +94332,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94269,10 +94341,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="T15" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94283,12 +94355,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94296,22 +94368,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94322,39 +94394,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="H32" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="K32" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="N32" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="Q32" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="S32" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94363,13 +94435,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="K33" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="N33" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94377,153 +94449,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="K34" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="N34" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="N35" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="N36" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="N37" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="N38" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94531,7 +94603,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94547,7 +94619,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94563,21 +94635,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="J68" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94586,52 +94658,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5941</v>
+        <v>5945</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94693,7 +94765,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94701,10 +94773,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94712,7 +94784,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94725,15 +94797,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
       <c r="F17" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13510" uniqueCount="6327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13525" uniqueCount="6333">
   <si>
     <t>名称</t>
   </si>
@@ -20447,6 +20447,24 @@
   </si>
   <si>
     <t>查找库存不平衡的店铺</t>
+  </si>
+  <si>
+    <t>根据质数下标分割数组</t>
+  </si>
+  <si>
+    <t>质数筛</t>
+  </si>
+  <si>
+    <t>LCR 064</t>
+  </si>
+  <si>
+    <t>同676题</t>
+  </si>
+  <si>
+    <t>查找有两极分化观点的书籍</t>
+  </si>
+  <si>
+    <t>最早完成陆地和水上游乐设施的时间 I</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -92637,12 +92655,89 @@
         <v>2951</v>
       </c>
     </row>
+    <row r="3346" spans="1:8">
+      <c r="A3346">
+        <v>3618</v>
+      </c>
+      <c r="B3346" t="s">
+        <v>5938</v>
+      </c>
+      <c r="C3346" s="2">
+        <v>46091</v>
+      </c>
+      <c r="D3346" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3346" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3346">
+        <v>1227</v>
+      </c>
+      <c r="G3346" s="1" t="s">
+        <v>5939</v>
+      </c>
+    </row>
+    <row r="3347" spans="1:8">
+      <c r="A3347" t="s">
+        <v>5940</v>
+      </c>
+      <c r="B3347" t="s">
+        <v>972</v>
+      </c>
+      <c r="C3347" s="2">
+        <v>46091</v>
+      </c>
+      <c r="D3347" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3347" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3347" s="1" t="s">
+        <v>5941</v>
+      </c>
+    </row>
+    <row r="3348" spans="1:8">
+      <c r="A3348">
+        <v>3642</v>
+      </c>
+      <c r="B3348" t="s">
+        <v>5942</v>
+      </c>
+      <c r="C3348" s="2">
+        <v>46091</v>
+      </c>
+      <c r="D3348" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3348" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3349" spans="1:8">
+      <c r="A3349">
+        <v>3633</v>
+      </c>
+      <c r="B3349" t="s">
+        <v>5943</v>
+      </c>
+      <c r="D3349" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3349" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3349">
+        <v>1342</v>
+      </c>
+    </row>
     <row r="3352" spans="1:8">
       <c r="A3352">
         <v>3454</v>
       </c>
       <c r="B3352" t="s">
-        <v>5938</v>
+        <v>5944</v>
       </c>
       <c r="D3352" t="s">
         <v>135</v>
@@ -92662,7 +92757,7 @@
         <v>3562</v>
       </c>
       <c r="B3353" t="s">
-        <v>5939</v>
+        <v>5945</v>
       </c>
       <c r="D3353" t="s">
         <v>135</v>
@@ -92673,10 +92768,10 @@
     </row>
     <row r="3354" spans="1:8">
       <c r="A3354" t="s">
-        <v>5940</v>
+        <v>5946</v>
       </c>
       <c r="B3354" t="s">
-        <v>5941</v>
+        <v>5947</v>
       </c>
       <c r="D3354" t="s">
         <v>135</v>
@@ -92687,7 +92782,7 @@
         <v>3721</v>
       </c>
       <c r="B3355" t="s">
-        <v>5942</v>
+        <v>5948</v>
       </c>
       <c r="D3355" t="s">
         <v>135</v>
@@ -92700,7 +92795,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3342" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3347" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92747,10 +92842,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5943</v>
+        <v>5949</v>
       </c>
       <c r="D5" t="s">
-        <v>5944</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92761,13 +92856,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5945</v>
+        <v>5951</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5946</v>
+        <v>5952</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92776,7 +92871,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5947</v>
+        <v>5953</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92791,16 +92886,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5948</v>
+        <v>5954</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5949</v>
+        <v>5955</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5950</v>
+        <v>5956</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92814,10 +92909,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5951</v>
+        <v>5957</v>
       </c>
       <c r="H14" t="s">
-        <v>5952</v>
+        <v>5958</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92832,16 +92927,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5953</v>
+        <v>5959</v>
       </c>
       <c r="W14" t="s">
-        <v>5954</v>
+        <v>5960</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5955</v>
+        <v>5961</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92853,158 +92948,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5956</v>
+        <v>5962</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5957</v>
+        <v>5963</v>
       </c>
       <c r="AL14" t="s">
-        <v>5958</v>
+        <v>5964</v>
       </c>
       <c r="AO14" t="s">
-        <v>5959</v>
+        <v>5965</v>
       </c>
       <c r="AR14" t="s">
-        <v>5960</v>
+        <v>5966</v>
       </c>
       <c r="AU14" t="s">
-        <v>5961</v>
+        <v>5967</v>
       </c>
       <c r="AX14" t="s">
-        <v>5962</v>
+        <v>5968</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5963</v>
+        <v>5969</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5964</v>
+        <v>5970</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5965</v>
+        <v>5971</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5966</v>
+        <v>5972</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5967</v>
+        <v>5973</v>
       </c>
       <c r="T15" t="s">
-        <v>5968</v>
+        <v>5974</v>
       </c>
       <c r="W15" t="s">
-        <v>5969</v>
+        <v>5975</v>
       </c>
       <c r="Z15" t="s">
-        <v>5970</v>
+        <v>5976</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5971</v>
+        <v>5977</v>
       </c>
       <c r="AF15" t="s">
-        <v>5972</v>
+        <v>5978</v>
       </c>
       <c r="AI15" t="s">
-        <v>5973</v>
+        <v>5979</v>
       </c>
       <c r="AL15" t="s">
-        <v>5974</v>
+        <v>5980</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5975</v>
+        <v>5981</v>
       </c>
       <c r="AU15" t="s">
-        <v>5976</v>
+        <v>5982</v>
       </c>
       <c r="AX15" t="s">
-        <v>5977</v>
+        <v>5983</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5978</v>
+        <v>5984</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5979</v>
+        <v>5985</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5980</v>
+        <v>5986</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5981</v>
+        <v>5987</v>
       </c>
       <c r="H16" t="s">
-        <v>5982</v>
+        <v>5988</v>
       </c>
       <c r="N16" t="s">
-        <v>5983</v>
+        <v>5989</v>
       </c>
       <c r="T16" t="s">
-        <v>5984</v>
+        <v>5990</v>
       </c>
       <c r="W16" t="s">
-        <v>5985</v>
+        <v>5991</v>
       </c>
       <c r="Z16" t="s">
-        <v>5986</v>
+        <v>5992</v>
       </c>
       <c r="AC16" t="s">
-        <v>5974</v>
+        <v>5980</v>
       </c>
       <c r="AF16" t="s">
-        <v>5956</v>
+        <v>5962</v>
       </c>
       <c r="AI16" t="s">
-        <v>5987</v>
+        <v>5993</v>
       </c>
       <c r="AL16" t="s">
-        <v>5988</v>
+        <v>5994</v>
       </c>
       <c r="AR16" t="s">
-        <v>5989</v>
+        <v>5995</v>
       </c>
       <c r="AU16" t="s">
-        <v>5990</v>
+        <v>5996</v>
       </c>
       <c r="AX16" t="s">
-        <v>5991</v>
+        <v>5997</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5992</v>
+        <v>5998</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93012,43 +93107,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5993</v>
+        <v>5999</v>
       </c>
       <c r="D17" t="s">
-        <v>5994</v>
+        <v>6000</v>
       </c>
       <c r="H17" t="s">
-        <v>5995</v>
+        <v>6001</v>
       </c>
       <c r="N17" t="s">
-        <v>5996</v>
+        <v>6002</v>
       </c>
       <c r="T17" t="s">
-        <v>5997</v>
+        <v>6003</v>
       </c>
       <c r="W17" t="s">
-        <v>5956</v>
+        <v>5962</v>
       </c>
       <c r="Z17" t="s">
-        <v>5967</v>
+        <v>5973</v>
       </c>
       <c r="AC17" t="s">
-        <v>5998</v>
+        <v>6004</v>
       </c>
       <c r="AF17" t="s">
-        <v>5999</v>
+        <v>6005</v>
       </c>
       <c r="AI17" t="s">
-        <v>6000</v>
+        <v>6006</v>
       </c>
       <c r="AR17" t="s">
-        <v>6001</v>
+        <v>6007</v>
       </c>
       <c r="AU17" t="s">
-        <v>6002</v>
+        <v>6008</v>
       </c>
       <c r="BA17" t="s">
-        <v>6003</v>
+        <v>6009</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93056,37 +93151,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6004</v>
+        <v>6010</v>
       </c>
       <c r="H18" t="s">
-        <v>6005</v>
+        <v>6011</v>
       </c>
       <c r="N18" t="s">
-        <v>6006</v>
+        <v>6012</v>
       </c>
       <c r="T18" t="s">
-        <v>6007</v>
+        <v>6013</v>
       </c>
       <c r="W18" t="s">
-        <v>6008</v>
+        <v>6014</v>
       </c>
       <c r="Z18" t="s">
-        <v>5983</v>
+        <v>5989</v>
       </c>
       <c r="AC18" t="s">
-        <v>6009</v>
+        <v>6015</v>
       </c>
       <c r="AF18" t="s">
-        <v>6010</v>
+        <v>6016</v>
       </c>
       <c r="AI18" t="s">
-        <v>6011</v>
+        <v>6017</v>
       </c>
       <c r="AU18" t="s">
-        <v>6012</v>
+        <v>6018</v>
       </c>
       <c r="BA18" t="s">
-        <v>6013</v>
+        <v>6019</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93094,37 +93189,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6014</v>
+        <v>6020</v>
       </c>
       <c r="H19" t="s">
-        <v>6015</v>
+        <v>6021</v>
       </c>
       <c r="N19" t="s">
-        <v>6016</v>
+        <v>6022</v>
       </c>
       <c r="T19" t="s">
-        <v>6017</v>
+        <v>6023</v>
       </c>
       <c r="W19" t="s">
-        <v>5991</v>
+        <v>5997</v>
       </c>
       <c r="Z19" t="s">
-        <v>5996</v>
+        <v>6002</v>
       </c>
       <c r="AC19" t="s">
-        <v>6018</v>
+        <v>6024</v>
       </c>
       <c r="AF19" t="s">
-        <v>6019</v>
+        <v>6025</v>
       </c>
       <c r="AI19" t="s">
-        <v>6020</v>
+        <v>6026</v>
       </c>
       <c r="AU19" t="s">
-        <v>6021</v>
+        <v>6027</v>
       </c>
       <c r="BA19" t="s">
-        <v>6022</v>
+        <v>6028</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93132,37 +93227,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6023</v>
+        <v>6029</v>
       </c>
       <c r="D20" t="s">
-        <v>6024</v>
+        <v>6030</v>
       </c>
       <c r="H20" t="s">
+        <v>6031</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6032</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6033</v>
+      </c>
+      <c r="W20" t="s">
         <v>6025</v>
       </c>
-      <c r="N20" t="s">
-        <v>6026</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6027</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6019</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6006</v>
+        <v>6012</v>
       </c>
       <c r="AC20" t="s">
-        <v>6028</v>
+        <v>6034</v>
       </c>
       <c r="AF20" t="s">
-        <v>6029</v>
+        <v>6035</v>
       </c>
       <c r="AU20" t="s">
-        <v>6030</v>
+        <v>6036</v>
       </c>
       <c r="BA20" t="s">
-        <v>6031</v>
+        <v>6037</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93170,37 +93265,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6032</v>
+        <v>6038</v>
       </c>
       <c r="D21" t="s">
-        <v>6033</v>
+        <v>6039</v>
       </c>
       <c r="H21" t="s">
-        <v>6034</v>
+        <v>6040</v>
       </c>
       <c r="N21" t="s">
+        <v>6041</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6042</v>
+      </c>
+      <c r="W21" t="s">
         <v>6035</v>
       </c>
-      <c r="T21" t="s">
-        <v>6036</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6029</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6016</v>
+        <v>6022</v>
       </c>
       <c r="AC21" t="s">
-        <v>6037</v>
+        <v>6043</v>
       </c>
       <c r="AF21" t="s">
-        <v>6038</v>
+        <v>6044</v>
       </c>
       <c r="AU21" t="s">
-        <v>6039</v>
+        <v>6045</v>
       </c>
       <c r="BA21" t="s">
-        <v>6040</v>
+        <v>6046</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93211,13 +93306,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6041</v>
+        <v>6047</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6042</v>
+        <v>6048</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93226,16 +93321,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6026</v>
+        <v>6032</v>
       </c>
       <c r="AC22" t="s">
-        <v>6043</v>
+        <v>6049</v>
       </c>
       <c r="AF22" t="s">
-        <v>6044</v>
+        <v>6050</v>
       </c>
       <c r="AU22" t="s">
-        <v>6045</v>
+        <v>6051</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93243,25 +93338,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6046</v>
+        <v>6052</v>
       </c>
       <c r="H23" t="s">
-        <v>6047</v>
+        <v>6053</v>
       </c>
       <c r="T23" t="s">
-        <v>6048</v>
+        <v>6054</v>
       </c>
       <c r="Z23" t="s">
-        <v>6035</v>
+        <v>6041</v>
       </c>
       <c r="AC23" t="s">
-        <v>6049</v>
+        <v>6055</v>
       </c>
       <c r="AF23" t="s">
-        <v>6050</v>
+        <v>6056</v>
       </c>
       <c r="AU23" t="s">
-        <v>6051</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93269,89 +93364,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6052</v>
+        <v>6058</v>
       </c>
       <c r="T24" t="s">
-        <v>6053</v>
+        <v>6059</v>
       </c>
       <c r="Z24" t="s">
-        <v>6054</v>
+        <v>6060</v>
       </c>
       <c r="AC24" t="s">
-        <v>6055</v>
+        <v>6061</v>
       </c>
       <c r="AF24" t="s">
-        <v>6056</v>
+        <v>6062</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6057</v>
+        <v>6063</v>
       </c>
       <c r="D25" t="s">
-        <v>6058</v>
+        <v>6064</v>
       </c>
       <c r="T25" t="s">
-        <v>6059</v>
+        <v>6065</v>
       </c>
       <c r="AC25" t="s">
-        <v>6060</v>
+        <v>6066</v>
       </c>
       <c r="AF25" t="s">
-        <v>6061</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6062</v>
+        <v>6068</v>
       </c>
       <c r="AC26" t="s">
-        <v>6063</v>
+        <v>6069</v>
       </c>
       <c r="AF26" t="s">
-        <v>6064</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6065</v>
+        <v>6071</v>
       </c>
       <c r="AC27" t="s">
-        <v>6066</v>
+        <v>6072</v>
       </c>
       <c r="AF27" t="s">
-        <v>6067</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6068</v>
+        <v>6074</v>
       </c>
       <c r="AC28" t="s">
-        <v>6069</v>
+        <v>6075</v>
       </c>
       <c r="AF28" t="s">
-        <v>6070</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6071</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6072</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6073</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93361,22 +93456,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6075</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6076</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6078</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93386,7 +93481,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6079</v>
+        <v>6085</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93394,7 +93489,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6080</v>
+        <v>6086</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93409,7 +93504,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6081</v>
+        <v>6087</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93427,227 +93522,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6082</v>
+        <v>6088</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6083</v>
+        <v>6089</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6084</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6086</v>
+        <v>6092</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6087</v>
+        <v>6093</v>
       </c>
       <c r="Q41" t="s">
-        <v>6075</v>
+        <v>6081</v>
       </c>
       <c r="T41" t="s">
-        <v>5971</v>
+        <v>5977</v>
       </c>
       <c r="W41" t="s">
-        <v>6088</v>
+        <v>6094</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6089</v>
+        <v>6095</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6090</v>
+        <v>6096</v>
       </c>
       <c r="AL41" t="s">
-        <v>6091</v>
+        <v>6097</v>
       </c>
       <c r="AO41" t="s">
-        <v>6092</v>
+        <v>6098</v>
       </c>
       <c r="AR41" t="s">
-        <v>6093</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6095</v>
+        <v>6101</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6096</v>
+        <v>6102</v>
       </c>
       <c r="Q42" t="s">
-        <v>6076</v>
+        <v>6082</v>
       </c>
       <c r="T42" t="s">
-        <v>6097</v>
+        <v>6103</v>
       </c>
       <c r="W42" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6099</v>
+        <v>6105</v>
       </c>
       <c r="AC42" t="s">
-        <v>6100</v>
+        <v>6106</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6101</v>
+        <v>6107</v>
       </c>
       <c r="AL42" t="s">
-        <v>6102</v>
+        <v>6108</v>
       </c>
       <c r="AO42" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
       <c r="AR42" t="s">
-        <v>6104</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6105</v>
+        <v>6111</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6106</v>
+        <v>6112</v>
       </c>
       <c r="K43" t="s">
-        <v>6107</v>
+        <v>6113</v>
       </c>
       <c r="N43" t="s">
-        <v>6108</v>
+        <v>6114</v>
       </c>
       <c r="Q43" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
       <c r="T43" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
       <c r="W43" t="s">
-        <v>6110</v>
+        <v>6116</v>
       </c>
       <c r="Z43" t="s">
-        <v>6111</v>
+        <v>6117</v>
       </c>
       <c r="AC43" t="s">
-        <v>6112</v>
+        <v>6118</v>
       </c>
       <c r="AF43" t="s">
-        <v>6113</v>
+        <v>6119</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6114</v>
+        <v>6120</v>
       </c>
       <c r="AL43" t="s">
-        <v>6023</v>
+        <v>6029</v>
       </c>
       <c r="AO43" t="s">
-        <v>6115</v>
+        <v>6121</v>
       </c>
       <c r="AR43" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6117</v>
+        <v>6123</v>
       </c>
       <c r="F44" t="s">
-        <v>6118</v>
+        <v>6124</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6119</v>
+        <v>6125</v>
       </c>
       <c r="N44" t="s">
-        <v>6120</v>
+        <v>6126</v>
       </c>
       <c r="Q44" t="s">
-        <v>6078</v>
+        <v>6084</v>
       </c>
       <c r="W44" t="s">
-        <v>6121</v>
+        <v>6127</v>
       </c>
       <c r="Z44" t="s">
-        <v>6122</v>
+        <v>6128</v>
       </c>
       <c r="AC44" t="s">
-        <v>6123</v>
+        <v>6129</v>
       </c>
       <c r="AF44" t="s">
-        <v>6060</v>
+        <v>6066</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6124</v>
+        <v>6130</v>
       </c>
       <c r="AL44" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="AO44" t="s">
-        <v>6126</v>
+        <v>6132</v>
       </c>
       <c r="AR44" t="s">
-        <v>6127</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6128</v>
+        <v>6134</v>
       </c>
       <c r="F45" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6130</v>
+        <v>6136</v>
       </c>
       <c r="N45" t="s">
-        <v>6131</v>
+        <v>6137</v>
       </c>
       <c r="Q45" t="s">
-        <v>6132</v>
+        <v>6138</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93656,103 +93751,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
       <c r="AF45" t="s">
-        <v>6134</v>
+        <v>6140</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="AO45" t="s">
-        <v>6136</v>
+        <v>6142</v>
       </c>
       <c r="AR45" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
       <c r="F46" t="s">
-        <v>6139</v>
+        <v>6145</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6140</v>
+        <v>6146</v>
       </c>
       <c r="N46" t="s">
-        <v>6141</v>
+        <v>6147</v>
       </c>
       <c r="AC46" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="AF46" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6144</v>
+        <v>6150</v>
       </c>
       <c r="AO46" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="AR46" t="s">
-        <v>6146</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6147</v>
+        <v>6153</v>
       </c>
       <c r="F47" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6149</v>
+        <v>6155</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="AC47" t="s">
-        <v>6151</v>
+        <v>6157</v>
       </c>
       <c r="AF47" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6153</v>
+        <v>6159</v>
       </c>
       <c r="AO47" t="s">
-        <v>6154</v>
+        <v>6160</v>
       </c>
       <c r="AR47" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6156</v>
+        <v>6162</v>
       </c>
       <c r="F48" t="s">
-        <v>6157</v>
+        <v>6163</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93764,141 +93859,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
       <c r="AF48" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
       <c r="AO48" t="s">
-        <v>6160</v>
+        <v>6166</v>
       </c>
       <c r="AR48" t="s">
-        <v>6161</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6162</v>
+        <v>6168</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6164</v>
+        <v>6170</v>
       </c>
       <c r="AF49" t="s">
-        <v>6165</v>
+        <v>6171</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6166</v>
+        <v>6172</v>
       </c>
       <c r="AR49" t="s">
-        <v>6167</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="F50" t="s">
-        <v>6169</v>
+        <v>6175</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6170</v>
+        <v>6176</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6171</v>
+        <v>6177</v>
       </c>
       <c r="AR50" t="s">
-        <v>6172</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6173</v>
+        <v>6179</v>
       </c>
       <c r="F51" t="s">
-        <v>6174</v>
+        <v>6180</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
       <c r="AR51" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6177</v>
+        <v>6183</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6178</v>
+        <v>6184</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
       <c r="AR52" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
       <c r="F53" t="s">
-        <v>6182</v>
+        <v>6188</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6183</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6184</v>
+        <v>6190</v>
       </c>
       <c r="F54" t="s">
-        <v>6185</v>
+        <v>6191</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6186</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6187</v>
+        <v>6193</v>
       </c>
       <c r="F55" t="s">
-        <v>6188</v>
+        <v>6194</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -93906,10 +94001,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6189</v>
+        <v>6195</v>
       </c>
       <c r="F56" t="s">
-        <v>6190</v>
+        <v>6196</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -93917,18 +94012,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6191</v>
+        <v>6197</v>
       </c>
       <c r="F57" t="s">
-        <v>6192</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6193</v>
+        <v>6199</v>
       </c>
       <c r="F58" t="s">
-        <v>6194</v>
+        <v>6200</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -93936,42 +94031,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6195</v>
+        <v>6201</v>
       </c>
       <c r="F59" t="s">
-        <v>6196</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6197</v>
+        <v>6203</v>
       </c>
       <c r="F60" t="s">
-        <v>6198</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6199</v>
+        <v>6205</v>
       </c>
       <c r="F61" t="s">
-        <v>6200</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6201</v>
+        <v>6207</v>
       </c>
       <c r="F62" t="s">
-        <v>6202</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6203</v>
+        <v>6209</v>
       </c>
       <c r="F63" t="s">
-        <v>6204</v>
+        <v>6210</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -93979,181 +94074,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6205</v>
+        <v>6211</v>
       </c>
       <c r="F64" t="s">
-        <v>6206</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="F65" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6207</v>
+        <v>6213</v>
       </c>
       <c r="F66" t="s">
-        <v>6208</v>
+        <v>6214</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6209</v>
+        <v>6215</v>
       </c>
       <c r="F67" t="s">
-        <v>6210</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6211</v>
+        <v>6217</v>
       </c>
       <c r="F68" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6212</v>
+        <v>6218</v>
       </c>
       <c r="F69" t="s">
-        <v>6213</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6214</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6215</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6216</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6218</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6219</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6220</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6221</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6222</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6223</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6224</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6225</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6226</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6228</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6229</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6231</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6232</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6233</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5972</v>
+        <v>5978</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6234</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
     </row>
   </sheetData>
@@ -94180,10 +94275,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94192,13 +94287,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6241</v>
+        <v>6247</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6242</v>
+        <v>6248</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94206,13 +94301,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6244</v>
+        <v>6250</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6245</v>
+        <v>6251</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94224,13 +94319,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6246</v>
+        <v>6252</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6247</v>
+        <v>6253</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94241,19 +94336,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6248</v>
+        <v>6254</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6249</v>
+        <v>6255</v>
       </c>
       <c r="S10" t="s">
-        <v>6250</v>
+        <v>6256</v>
       </c>
       <c r="T10" t="s">
-        <v>6251</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94267,15 +94362,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6252</v>
+        <v>6258</v>
       </c>
       <c r="S11" t="s">
-        <v>5976</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6253</v>
+        <v>6259</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94284,18 +94379,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6254</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6255</v>
+        <v>6261</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6256</v>
+        <v>6262</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94304,7 +94399,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6257</v>
+        <v>6263</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94315,13 +94410,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6258</v>
+        <v>6264</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6259</v>
+        <v>6265</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94332,7 +94427,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6260</v>
+        <v>6266</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94341,10 +94436,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
       <c r="T15" t="s">
-        <v>6261</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94355,12 +94450,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6262</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6263</v>
+        <v>6269</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94368,22 +94463,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6264</v>
+        <v>6270</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6265</v>
+        <v>6271</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6266</v>
+        <v>6272</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6267</v>
+        <v>6273</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6268</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94394,39 +94489,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6269</v>
+        <v>6275</v>
       </c>
       <c r="H32" t="s">
-        <v>6270</v>
+        <v>6276</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="K32" t="s">
-        <v>6272</v>
+        <v>6278</v>
       </c>
       <c r="N32" t="s">
-        <v>6273</v>
+        <v>6279</v>
       </c>
       <c r="Q32" t="s">
-        <v>6274</v>
+        <v>6280</v>
       </c>
       <c r="S32" t="s">
-        <v>6000</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6275</v>
+        <v>6281</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6276</v>
+        <v>6282</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94435,13 +94530,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6277</v>
+        <v>6283</v>
       </c>
       <c r="K33" t="s">
-        <v>6278</v>
+        <v>6284</v>
       </c>
       <c r="N33" t="s">
-        <v>6279</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94449,153 +94544,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6280</v>
+        <v>6286</v>
       </c>
       <c r="K34" t="s">
-        <v>6281</v>
+        <v>6287</v>
       </c>
       <c r="N34" t="s">
-        <v>6282</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6283</v>
+        <v>6289</v>
       </c>
       <c r="N35" t="s">
-        <v>6284</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6285</v>
+        <v>6291</v>
       </c>
       <c r="N36" t="s">
-        <v>6286</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6287</v>
+        <v>6293</v>
       </c>
       <c r="N37" t="s">
-        <v>6288</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="N38" t="s">
-        <v>6290</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6013</v>
+        <v>6019</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6291</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6292</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6293</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6294</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6295</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6296</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6297</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6298</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6299</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6300</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6190</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6301</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6302</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6188</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6303</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6304</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6305</v>
+        <v>6311</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6306</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6307</v>
+        <v>6313</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6308</v>
+        <v>6314</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94603,7 +94698,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6309</v>
+        <v>6315</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94619,7 +94714,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6310</v>
+        <v>6316</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94635,21 +94730,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6311</v>
+        <v>6317</v>
       </c>
       <c r="J68" t="s">
-        <v>6312</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6313</v>
+        <v>6319</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6314</v>
+        <v>6320</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94658,52 +94753,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6088</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6315</v>
+        <v>6321</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5945</v>
+        <v>5951</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6121</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6316</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6110</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6318</v>
+        <v>6324</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6319</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94765,7 +94860,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6320</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94773,10 +94868,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6321</v>
+        <v>6327</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6322</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94784,7 +94879,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6323</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94797,15 +94892,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6324</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6325</v>
+        <v>6331</v>
       </c>
       <c r="F17" t="s">
-        <v>6326</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3349</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13525" uniqueCount="6333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13533" uniqueCount="6336">
   <si>
     <t>名称</t>
   </si>
@@ -20465,6 +20465,15 @@
   </si>
   <si>
     <t>最早完成陆地和水上游乐设施的时间 I</t>
+  </si>
+  <si>
+    <t>LCR 065</t>
+  </si>
+  <si>
+    <t>同820题</t>
+  </si>
+  <si>
+    <t>寻找忠实客户</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22124,6 +22133,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22133,13 +22149,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23091,7 +23100,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3355"/>
+  <dimension ref="A1:N3365"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92722,6 +92731,9 @@
       <c r="B3349" t="s">
         <v>5943</v>
       </c>
+      <c r="C3349" s="2">
+        <v>46092</v>
+      </c>
       <c r="D3349" t="s">
         <v>138</v>
       </c>
@@ -92732,70 +92744,107 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="3352" spans="1:8">
-      <c r="A3352">
+    <row r="3350" spans="1:8">
+      <c r="A3350" t="s">
+        <v>5944</v>
+      </c>
+      <c r="B3350" t="s">
+        <v>4787</v>
+      </c>
+      <c r="C3350" s="2">
+        <v>46092</v>
+      </c>
+      <c r="D3350" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3350" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3350" s="1" t="s">
+        <v>5945</v>
+      </c>
+    </row>
+    <row r="3351" spans="1:8">
+      <c r="A3351">
+        <v>3657</v>
+      </c>
+      <c r="B3351" t="s">
+        <v>5946</v>
+      </c>
+      <c r="C3351" s="2">
+        <v>46092</v>
+      </c>
+      <c r="D3351" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3351" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3362" spans="1:7">
+      <c r="A3362">
         <v>3454</v>
       </c>
-      <c r="B3352" t="s">
-        <v>5944</v>
-      </c>
-      <c r="D3352" t="s">
+      <c r="B3362" t="s">
+        <v>5947</v>
+      </c>
+      <c r="D3362" t="s">
         <v>135</v>
       </c>
-      <c r="E3352" t="s">
+      <c r="E3362" t="s">
         <v>73</v>
       </c>
-      <c r="F3352">
+      <c r="F3362">
         <v>2671</v>
       </c>
-      <c r="G3352" s="1" t="s">
+      <c r="G3362" s="1" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="3353" spans="1:8">
-      <c r="A3353">
+    <row r="3363" spans="1:7">
+      <c r="A3363">
         <v>3562</v>
       </c>
-      <c r="B3353" t="s">
-        <v>5945</v>
-      </c>
-      <c r="D3353" t="s">
+      <c r="B3363" t="s">
+        <v>5948</v>
+      </c>
+      <c r="D3363" t="s">
         <v>135</v>
       </c>
-      <c r="F3353">
+      <c r="F3363">
         <v>2458</v>
       </c>
     </row>
-    <row r="3354" spans="1:8">
-      <c r="A3354" t="s">
-        <v>5946</v>
-      </c>
-      <c r="B3354" t="s">
-        <v>5947</v>
-      </c>
-      <c r="D3354" t="s">
+    <row r="3364" spans="1:7">
+      <c r="A3364" t="s">
+        <v>5949</v>
+      </c>
+      <c r="B3364" t="s">
+        <v>5950</v>
+      </c>
+      <c r="D3364" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3355" spans="1:8">
-      <c r="A3355">
+    <row r="3365" spans="1:7">
+      <c r="A3365">
         <v>3721</v>
       </c>
-      <c r="B3355" t="s">
-        <v>5948</v>
-      </c>
-      <c r="D3355" t="s">
+      <c r="B3365" t="s">
+        <v>5951</v>
+      </c>
+      <c r="D3365" t="s">
         <v>135</v>
       </c>
-      <c r="E3355" t="s">
+      <c r="E3365" t="s">
         <v>73</v>
       </c>
-      <c r="F3355">
+      <c r="F3365">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3347" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3349" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92842,10 +92891,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5949</v>
+        <v>5952</v>
       </c>
       <c r="D5" t="s">
-        <v>5950</v>
+        <v>5953</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92856,13 +92905,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5951</v>
+        <v>5954</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5952</v>
+        <v>5955</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92871,7 +92920,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5953</v>
+        <v>5956</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92886,16 +92935,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5954</v>
+        <v>5957</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5955</v>
+        <v>5958</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5956</v>
+        <v>5959</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92909,10 +92958,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5957</v>
+        <v>5960</v>
       </c>
       <c r="H14" t="s">
-        <v>5958</v>
+        <v>5961</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92927,16 +92976,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5959</v>
+        <v>5962</v>
       </c>
       <c r="W14" t="s">
-        <v>5960</v>
+        <v>5963</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92948,158 +92997,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5963</v>
+        <v>5966</v>
       </c>
       <c r="AL14" t="s">
-        <v>5964</v>
+        <v>5967</v>
       </c>
       <c r="AO14" t="s">
-        <v>5965</v>
+        <v>5968</v>
       </c>
       <c r="AR14" t="s">
-        <v>5966</v>
+        <v>5969</v>
       </c>
       <c r="AU14" t="s">
-        <v>5967</v>
+        <v>5970</v>
       </c>
       <c r="AX14" t="s">
-        <v>5968</v>
+        <v>5971</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5969</v>
+        <v>5972</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5970</v>
+        <v>5973</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5971</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="T15" t="s">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="W15" t="s">
-        <v>5975</v>
+        <v>5978</v>
       </c>
       <c r="Z15" t="s">
-        <v>5976</v>
+        <v>5979</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="AF15" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
       <c r="AI15" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="AL15" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5981</v>
+        <v>5984</v>
       </c>
       <c r="AU15" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
       <c r="AX15" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5984</v>
+        <v>5987</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5986</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="H16" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
       <c r="N16" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="T16" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="W16" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="Z16" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="AC16" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="AF16" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="AI16" t="s">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="AL16" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="AR16" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="AU16" t="s">
-        <v>5996</v>
+        <v>5999</v>
       </c>
       <c r="AX16" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>5998</v>
+        <v>6001</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93107,43 +93156,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="D17" t="s">
-        <v>6000</v>
+        <v>6003</v>
       </c>
       <c r="H17" t="s">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="N17" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="T17" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="W17" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="Z17" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="AC17" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
       <c r="AF17" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="AI17" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="AR17" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AU17" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="BA17" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93151,37 +93200,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="H18" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="N18" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="T18" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="W18" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="Z18" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="AC18" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="AF18" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="AI18" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="AU18" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="BA18" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93189,37 +93238,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="H19" t="s">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="N19" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="T19" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
       <c r="W19" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="Z19" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="AC19" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="AF19" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
       <c r="AI19" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="AU19" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="BA19" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93227,37 +93276,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="D20" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="H20" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="N20" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="T20" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="W20" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
       <c r="Z20" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="AC20" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AF20" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="AU20" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="BA20" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93265,37 +93314,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6041</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6042</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6043</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6044</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6045</v>
+      </c>
+      <c r="W21" t="s">
         <v>6038</v>
       </c>
-      <c r="D21" t="s">
-        <v>6039</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6040</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6041</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6042</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6035</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="AC21" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="AF21" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="AU21" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
       <c r="BA21" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93306,13 +93355,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93321,16 +93370,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AC22" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="AF22" t="s">
-        <v>6050</v>
+        <v>6053</v>
       </c>
       <c r="AU22" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93338,25 +93387,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="H23" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="T23" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="Z23" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="AC23" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="AF23" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="AU23" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93364,89 +93413,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="T24" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
       <c r="Z24" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="AC24" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="AF24" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="D25" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="T25" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="AC25" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="AF25" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
       <c r="AC26" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="AF26" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6071</v>
+        <v>6074</v>
       </c>
       <c r="AC27" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="AF27" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="AC28" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="AF28" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93456,22 +93505,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93481,7 +93530,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93489,7 +93538,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93504,7 +93553,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93522,227 +93571,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
       <c r="Q41" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="T41" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="W41" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
       <c r="AL41" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="AO41" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="AR41" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="Q42" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="T42" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="W42" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="AC42" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="AL42" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="AO42" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="AR42" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="K43" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="N43" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="Q43" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="T43" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="W43" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="Z43" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="AC43" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="AF43" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="AL43" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="AO43" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="AR43" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="F44" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="N44" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="Q44" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="W44" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
       <c r="Z44" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="AC44" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="AF44" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="AL44" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="AO44" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="AR44" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="F45" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="N45" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="Q45" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93751,103 +93800,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
       <c r="AF45" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="AO45" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="AR45" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="F46" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="N46" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="AC46" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="AF46" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
       <c r="AO46" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="AR46" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="F47" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="AC47" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="AF47" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AO47" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="AR47" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="F48" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93859,141 +93908,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="AF48" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="AO48" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="AR48" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="AF49" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="AR49" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="F50" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="AR50" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="F51" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="AR51" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="AR52" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="F53" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
       <c r="F54" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="F55" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94001,10 +94050,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
       <c r="F56" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94012,18 +94061,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="F57" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
       <c r="F58" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94031,42 +94080,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="F59" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="F60" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="F61" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
       <c r="F62" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="F63" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94074,181 +94123,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
       <c r="F64" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="F65" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
       <c r="F66" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
       <c r="F67" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="F68" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
       <c r="F69" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
     </row>
   </sheetData>
@@ -94275,10 +94324,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94287,13 +94336,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94301,13 +94350,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94319,13 +94368,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94336,19 +94385,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
       <c r="S10" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
       <c r="T10" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94362,15 +94411,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
       <c r="S11" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94379,18 +94428,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94399,7 +94448,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94410,13 +94459,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94427,7 +94476,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94436,10 +94485,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="T15" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94450,12 +94499,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94463,22 +94512,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94489,39 +94538,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="H32" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="K32" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
       <c r="N32" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="Q32" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="S32" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94530,13 +94579,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="K33" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
       <c r="N33" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94544,153 +94593,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
       <c r="K34" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="N34" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
       <c r="N35" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="N36" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="N37" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="N38" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94698,7 +94747,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94714,7 +94763,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94730,21 +94779,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
       <c r="J68" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94753,52 +94802,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5951</v>
+        <v>5954</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94860,7 +94909,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94868,10 +94917,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94879,7 +94928,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94892,15 +94941,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="F17" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3353</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13533" uniqueCount="6336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13553" uniqueCount="6343">
   <si>
     <t>名称</t>
   </si>
@@ -20474,6 +20474,27 @@
   </si>
   <si>
     <t>寻找忠实客户</t>
+  </si>
+  <si>
+    <t>覆盖网格的最少传感器数目</t>
+  </si>
+  <si>
+    <t>LCR 067</t>
+  </si>
+  <si>
+    <t>同421题</t>
+  </si>
+  <si>
+    <t>出现频率最低的数字</t>
+  </si>
+  <si>
+    <t>大于平均值的最小未出现正整数</t>
+  </si>
+  <si>
+    <t>LCR 068</t>
+  </si>
+  <si>
+    <t>同35题</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22133,17 +22154,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -92781,12 +92802,115 @@
         <v>2951</v>
       </c>
     </row>
+    <row r="3352" spans="1:8">
+      <c r="A3352">
+        <v>3648</v>
+      </c>
+      <c r="B3352" t="s">
+        <v>5947</v>
+      </c>
+      <c r="C3352" s="2">
+        <v>46093</v>
+      </c>
+      <c r="D3352" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3352" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3352">
+        <v>1395</v>
+      </c>
+      <c r="G3352" s="1" t="s">
+        <v>2972</v>
+      </c>
+    </row>
+    <row r="3353" spans="1:8">
+      <c r="A3353" t="s">
+        <v>5948</v>
+      </c>
+      <c r="B3353" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C3353" s="2">
+        <v>46093</v>
+      </c>
+      <c r="D3353" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3353" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3353" s="1" t="s">
+        <v>5949</v>
+      </c>
+    </row>
+    <row r="3354" spans="1:8">
+      <c r="A3354">
+        <v>3663</v>
+      </c>
+      <c r="B3354" t="s">
+        <v>5950</v>
+      </c>
+      <c r="C3354" s="2">
+        <v>46093</v>
+      </c>
+      <c r="D3354" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3354" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3354">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="3355" spans="1:8">
+      <c r="A3355">
+        <v>3678</v>
+      </c>
+      <c r="B3355" t="s">
+        <v>5951</v>
+      </c>
+      <c r="C3355" s="2">
+        <v>46094</v>
+      </c>
+      <c r="D3355" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3355" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3355">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="3356" spans="1:8">
+      <c r="A3356" t="s">
+        <v>5952</v>
+      </c>
+      <c r="B3356" t="s">
+        <v>663</v>
+      </c>
+      <c r="C3356" s="2">
+        <v>46094</v>
+      </c>
+      <c r="D3356" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3356" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3356" s="1" t="s">
+        <v>5953</v>
+      </c>
+    </row>
     <row r="3362" spans="1:7">
       <c r="A3362">
         <v>3454</v>
       </c>
       <c r="B3362" t="s">
-        <v>5947</v>
+        <v>5954</v>
       </c>
       <c r="D3362" t="s">
         <v>135</v>
@@ -92806,7 +92930,7 @@
         <v>3562</v>
       </c>
       <c r="B3363" t="s">
-        <v>5948</v>
+        <v>5955</v>
       </c>
       <c r="D3363" t="s">
         <v>135</v>
@@ -92817,10 +92941,10 @@
     </row>
     <row r="3364" spans="1:7">
       <c r="A3364" t="s">
-        <v>5949</v>
+        <v>5956</v>
       </c>
       <c r="B3364" t="s">
-        <v>5950</v>
+        <v>5957</v>
       </c>
       <c r="D3364" t="s">
         <v>135</v>
@@ -92831,7 +92955,7 @@
         <v>3721</v>
       </c>
       <c r="B3365" t="s">
-        <v>5951</v>
+        <v>5958</v>
       </c>
       <c r="D3365" t="s">
         <v>135</v>
@@ -92844,7 +92968,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3349" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3353" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -92891,10 +93015,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5952</v>
+        <v>5959</v>
       </c>
       <c r="D5" t="s">
-        <v>5953</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -92905,13 +93029,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5954</v>
+        <v>5961</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5955</v>
+        <v>5962</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -92920,7 +93044,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5956</v>
+        <v>5963</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -92935,16 +93059,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5957</v>
+        <v>5964</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5958</v>
+        <v>5965</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5959</v>
+        <v>5966</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -92958,10 +93082,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5960</v>
+        <v>5967</v>
       </c>
       <c r="H14" t="s">
-        <v>5961</v>
+        <v>5968</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -92976,16 +93100,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5962</v>
+        <v>5969</v>
       </c>
       <c r="W14" t="s">
-        <v>5963</v>
+        <v>5970</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5964</v>
+        <v>5971</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -92997,158 +93121,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5965</v>
+        <v>5972</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5966</v>
+        <v>5973</v>
       </c>
       <c r="AL14" t="s">
-        <v>5967</v>
+        <v>5974</v>
       </c>
       <c r="AO14" t="s">
-        <v>5968</v>
+        <v>5975</v>
       </c>
       <c r="AR14" t="s">
-        <v>5969</v>
+        <v>5976</v>
       </c>
       <c r="AU14" t="s">
-        <v>5970</v>
+        <v>5977</v>
       </c>
       <c r="AX14" t="s">
-        <v>5971</v>
+        <v>5978</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5972</v>
+        <v>5979</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5973</v>
+        <v>5980</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5974</v>
+        <v>5981</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5975</v>
+        <v>5982</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5976</v>
+        <v>5983</v>
       </c>
       <c r="T15" t="s">
-        <v>5977</v>
+        <v>5984</v>
       </c>
       <c r="W15" t="s">
-        <v>5978</v>
+        <v>5985</v>
       </c>
       <c r="Z15" t="s">
-        <v>5979</v>
+        <v>5986</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5980</v>
+        <v>5987</v>
       </c>
       <c r="AF15" t="s">
-        <v>5981</v>
+        <v>5988</v>
       </c>
       <c r="AI15" t="s">
-        <v>5982</v>
+        <v>5989</v>
       </c>
       <c r="AL15" t="s">
-        <v>5983</v>
+        <v>5990</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5984</v>
+        <v>5991</v>
       </c>
       <c r="AU15" t="s">
-        <v>5985</v>
+        <v>5992</v>
       </c>
       <c r="AX15" t="s">
-        <v>5986</v>
+        <v>5993</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5987</v>
+        <v>5994</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5988</v>
+        <v>5995</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5989</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
+        <v>5997</v>
+      </c>
+      <c r="H16" t="s">
+        <v>5998</v>
+      </c>
+      <c r="N16" t="s">
+        <v>5999</v>
+      </c>
+      <c r="T16" t="s">
+        <v>6000</v>
+      </c>
+      <c r="W16" t="s">
+        <v>6001</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>6002</v>
+      </c>
+      <c r="AC16" t="s">
         <v>5990</v>
       </c>
-      <c r="H16" t="s">
-        <v>5991</v>
-      </c>
-      <c r="N16" t="s">
-        <v>5992</v>
-      </c>
-      <c r="T16" t="s">
-        <v>5993</v>
-      </c>
-      <c r="W16" t="s">
-        <v>5994</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>5995</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>5983</v>
-      </c>
       <c r="AF16" t="s">
-        <v>5965</v>
+        <v>5972</v>
       </c>
       <c r="AI16" t="s">
-        <v>5996</v>
+        <v>6003</v>
       </c>
       <c r="AL16" t="s">
-        <v>5997</v>
+        <v>6004</v>
       </c>
       <c r="AR16" t="s">
-        <v>5998</v>
+        <v>6005</v>
       </c>
       <c r="AU16" t="s">
-        <v>5999</v>
+        <v>6006</v>
       </c>
       <c r="AX16" t="s">
-        <v>6000</v>
+        <v>6007</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6001</v>
+        <v>6008</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93156,43 +93280,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6002</v>
+        <v>6009</v>
       </c>
       <c r="D17" t="s">
-        <v>6003</v>
+        <v>6010</v>
       </c>
       <c r="H17" t="s">
-        <v>6004</v>
+        <v>6011</v>
       </c>
       <c r="N17" t="s">
-        <v>6005</v>
+        <v>6012</v>
       </c>
       <c r="T17" t="s">
-        <v>6006</v>
+        <v>6013</v>
       </c>
       <c r="W17" t="s">
-        <v>5965</v>
+        <v>5972</v>
       </c>
       <c r="Z17" t="s">
-        <v>5976</v>
+        <v>5983</v>
       </c>
       <c r="AC17" t="s">
-        <v>6007</v>
+        <v>6014</v>
       </c>
       <c r="AF17" t="s">
-        <v>6008</v>
+        <v>6015</v>
       </c>
       <c r="AI17" t="s">
-        <v>6009</v>
+        <v>6016</v>
       </c>
       <c r="AR17" t="s">
-        <v>6010</v>
+        <v>6017</v>
       </c>
       <c r="AU17" t="s">
-        <v>6011</v>
+        <v>6018</v>
       </c>
       <c r="BA17" t="s">
-        <v>6012</v>
+        <v>6019</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93200,37 +93324,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6013</v>
+        <v>6020</v>
       </c>
       <c r="H18" t="s">
-        <v>6014</v>
+        <v>6021</v>
       </c>
       <c r="N18" t="s">
-        <v>6015</v>
+        <v>6022</v>
       </c>
       <c r="T18" t="s">
-        <v>6016</v>
+        <v>6023</v>
       </c>
       <c r="W18" t="s">
-        <v>6017</v>
+        <v>6024</v>
       </c>
       <c r="Z18" t="s">
-        <v>5992</v>
+        <v>5999</v>
       </c>
       <c r="AC18" t="s">
-        <v>6018</v>
+        <v>6025</v>
       </c>
       <c r="AF18" t="s">
-        <v>6019</v>
+        <v>6026</v>
       </c>
       <c r="AI18" t="s">
-        <v>6020</v>
+        <v>6027</v>
       </c>
       <c r="AU18" t="s">
-        <v>6021</v>
+        <v>6028</v>
       </c>
       <c r="BA18" t="s">
-        <v>6022</v>
+        <v>6029</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93238,37 +93362,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6023</v>
+        <v>6030</v>
       </c>
       <c r="H19" t="s">
-        <v>6024</v>
+        <v>6031</v>
       </c>
       <c r="N19" t="s">
-        <v>6025</v>
+        <v>6032</v>
       </c>
       <c r="T19" t="s">
-        <v>6026</v>
+        <v>6033</v>
       </c>
       <c r="W19" t="s">
-        <v>6000</v>
+        <v>6007</v>
       </c>
       <c r="Z19" t="s">
-        <v>6005</v>
+        <v>6012</v>
       </c>
       <c r="AC19" t="s">
-        <v>6027</v>
+        <v>6034</v>
       </c>
       <c r="AF19" t="s">
-        <v>6028</v>
+        <v>6035</v>
       </c>
       <c r="AI19" t="s">
-        <v>6029</v>
+        <v>6036</v>
       </c>
       <c r="AU19" t="s">
-        <v>6030</v>
+        <v>6037</v>
       </c>
       <c r="BA19" t="s">
-        <v>6031</v>
+        <v>6038</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93276,37 +93400,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6032</v>
+        <v>6039</v>
       </c>
       <c r="D20" t="s">
-        <v>6033</v>
+        <v>6040</v>
       </c>
       <c r="H20" t="s">
-        <v>6034</v>
+        <v>6041</v>
       </c>
       <c r="N20" t="s">
+        <v>6042</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6043</v>
+      </c>
+      <c r="W20" t="s">
         <v>6035</v>
       </c>
-      <c r="T20" t="s">
-        <v>6036</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6028</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6015</v>
+        <v>6022</v>
       </c>
       <c r="AC20" t="s">
-        <v>6037</v>
+        <v>6044</v>
       </c>
       <c r="AF20" t="s">
-        <v>6038</v>
+        <v>6045</v>
       </c>
       <c r="AU20" t="s">
-        <v>6039</v>
+        <v>6046</v>
       </c>
       <c r="BA20" t="s">
-        <v>6040</v>
+        <v>6047</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93314,37 +93438,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6041</v>
+        <v>6048</v>
       </c>
       <c r="D21" t="s">
-        <v>6042</v>
+        <v>6049</v>
       </c>
       <c r="H21" t="s">
-        <v>6043</v>
+        <v>6050</v>
       </c>
       <c r="N21" t="s">
-        <v>6044</v>
+        <v>6051</v>
       </c>
       <c r="T21" t="s">
+        <v>6052</v>
+      </c>
+      <c r="W21" t="s">
         <v>6045</v>
       </c>
-      <c r="W21" t="s">
-        <v>6038</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6025</v>
+        <v>6032</v>
       </c>
       <c r="AC21" t="s">
-        <v>6046</v>
+        <v>6053</v>
       </c>
       <c r="AF21" t="s">
-        <v>6047</v>
+        <v>6054</v>
       </c>
       <c r="AU21" t="s">
-        <v>6048</v>
+        <v>6055</v>
       </c>
       <c r="BA21" t="s">
-        <v>6049</v>
+        <v>6056</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93355,13 +93479,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6050</v>
+        <v>6057</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6051</v>
+        <v>6058</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93370,16 +93494,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6035</v>
+        <v>6042</v>
       </c>
       <c r="AC22" t="s">
-        <v>6052</v>
+        <v>6059</v>
       </c>
       <c r="AF22" t="s">
-        <v>6053</v>
+        <v>6060</v>
       </c>
       <c r="AU22" t="s">
-        <v>6054</v>
+        <v>6061</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93387,25 +93511,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6055</v>
+        <v>6062</v>
       </c>
       <c r="H23" t="s">
-        <v>6056</v>
+        <v>6063</v>
       </c>
       <c r="T23" t="s">
-        <v>6057</v>
+        <v>6064</v>
       </c>
       <c r="Z23" t="s">
-        <v>6044</v>
+        <v>6051</v>
       </c>
       <c r="AC23" t="s">
-        <v>6058</v>
+        <v>6065</v>
       </c>
       <c r="AF23" t="s">
-        <v>6059</v>
+        <v>6066</v>
       </c>
       <c r="AU23" t="s">
-        <v>6060</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93413,89 +93537,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6061</v>
+        <v>6068</v>
       </c>
       <c r="T24" t="s">
-        <v>6062</v>
+        <v>6069</v>
       </c>
       <c r="Z24" t="s">
-        <v>6063</v>
+        <v>6070</v>
       </c>
       <c r="AC24" t="s">
-        <v>6064</v>
+        <v>6071</v>
       </c>
       <c r="AF24" t="s">
-        <v>6065</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6066</v>
+        <v>6073</v>
       </c>
       <c r="D25" t="s">
-        <v>6067</v>
+        <v>6074</v>
       </c>
       <c r="T25" t="s">
-        <v>6068</v>
+        <v>6075</v>
       </c>
       <c r="AC25" t="s">
-        <v>6069</v>
+        <v>6076</v>
       </c>
       <c r="AF25" t="s">
-        <v>6070</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6071</v>
+        <v>6078</v>
       </c>
       <c r="AC26" t="s">
-        <v>6072</v>
+        <v>6079</v>
       </c>
       <c r="AF26" t="s">
-        <v>6073</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6074</v>
+        <v>6081</v>
       </c>
       <c r="AC27" t="s">
-        <v>6075</v>
+        <v>6082</v>
       </c>
       <c r="AF27" t="s">
-        <v>6076</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6077</v>
+        <v>6084</v>
       </c>
       <c r="AC28" t="s">
-        <v>6078</v>
+        <v>6085</v>
       </c>
       <c r="AF28" t="s">
-        <v>6079</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6080</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6081</v>
+        <v>6088</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6082</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6083</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93505,22 +93629,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6084</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6085</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6086</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6087</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93530,7 +93654,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6088</v>
+        <v>6095</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93538,7 +93662,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6089</v>
+        <v>6096</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93553,7 +93677,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6090</v>
+        <v>6097</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93571,227 +93695,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6091</v>
+        <v>6098</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6092</v>
+        <v>6099</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6093</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6094</v>
+        <v>6101</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6095</v>
+        <v>6102</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6096</v>
+        <v>6103</v>
       </c>
       <c r="Q41" t="s">
-        <v>6084</v>
+        <v>6091</v>
       </c>
       <c r="T41" t="s">
-        <v>5980</v>
+        <v>5987</v>
       </c>
       <c r="W41" t="s">
-        <v>6097</v>
+        <v>6104</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6098</v>
+        <v>6105</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6099</v>
+        <v>6106</v>
       </c>
       <c r="AL41" t="s">
-        <v>6100</v>
+        <v>6107</v>
       </c>
       <c r="AO41" t="s">
-        <v>6101</v>
+        <v>6108</v>
       </c>
       <c r="AR41" t="s">
-        <v>6102</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6103</v>
+        <v>6110</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6104</v>
+        <v>6111</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6105</v>
+        <v>6112</v>
       </c>
       <c r="Q42" t="s">
-        <v>6085</v>
+        <v>6092</v>
       </c>
       <c r="T42" t="s">
-        <v>6106</v>
+        <v>6113</v>
       </c>
       <c r="W42" t="s">
-        <v>6107</v>
+        <v>6114</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6108</v>
+        <v>6115</v>
       </c>
       <c r="AC42" t="s">
-        <v>6109</v>
+        <v>6116</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6110</v>
+        <v>6117</v>
       </c>
       <c r="AL42" t="s">
-        <v>6111</v>
+        <v>6118</v>
       </c>
       <c r="AO42" t="s">
-        <v>6112</v>
+        <v>6119</v>
       </c>
       <c r="AR42" t="s">
-        <v>6113</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6114</v>
+        <v>6121</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6115</v>
+        <v>6122</v>
       </c>
       <c r="K43" t="s">
-        <v>6116</v>
+        <v>6123</v>
       </c>
       <c r="N43" t="s">
-        <v>6117</v>
+        <v>6124</v>
       </c>
       <c r="Q43" t="s">
-        <v>6086</v>
+        <v>6093</v>
       </c>
       <c r="T43" t="s">
-        <v>6118</v>
+        <v>6125</v>
       </c>
       <c r="W43" t="s">
-        <v>6119</v>
+        <v>6126</v>
       </c>
       <c r="Z43" t="s">
-        <v>6120</v>
+        <v>6127</v>
       </c>
       <c r="AC43" t="s">
-        <v>6121</v>
+        <v>6128</v>
       </c>
       <c r="AF43" t="s">
-        <v>6122</v>
+        <v>6129</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6123</v>
+        <v>6130</v>
       </c>
       <c r="AL43" t="s">
-        <v>6032</v>
+        <v>6039</v>
       </c>
       <c r="AO43" t="s">
-        <v>6124</v>
+        <v>6131</v>
       </c>
       <c r="AR43" t="s">
-        <v>6125</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6126</v>
+        <v>6133</v>
       </c>
       <c r="F44" t="s">
-        <v>6127</v>
+        <v>6134</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6128</v>
+        <v>6135</v>
       </c>
       <c r="N44" t="s">
-        <v>6129</v>
+        <v>6136</v>
       </c>
       <c r="Q44" t="s">
-        <v>6087</v>
+        <v>6094</v>
       </c>
       <c r="W44" t="s">
-        <v>6130</v>
+        <v>6137</v>
       </c>
       <c r="Z44" t="s">
-        <v>6131</v>
+        <v>6138</v>
       </c>
       <c r="AC44" t="s">
-        <v>6132</v>
+        <v>6139</v>
       </c>
       <c r="AF44" t="s">
-        <v>6069</v>
+        <v>6076</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6133</v>
+        <v>6140</v>
       </c>
       <c r="AL44" t="s">
-        <v>6134</v>
+        <v>6141</v>
       </c>
       <c r="AO44" t="s">
-        <v>6135</v>
+        <v>6142</v>
       </c>
       <c r="AR44" t="s">
-        <v>6136</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6137</v>
+        <v>6144</v>
       </c>
       <c r="F45" t="s">
-        <v>6138</v>
+        <v>6145</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6139</v>
+        <v>6146</v>
       </c>
       <c r="N45" t="s">
-        <v>6140</v>
+        <v>6147</v>
       </c>
       <c r="Q45" t="s">
-        <v>6141</v>
+        <v>6148</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93800,103 +93924,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6142</v>
+        <v>6149</v>
       </c>
       <c r="AF45" t="s">
-        <v>6143</v>
+        <v>6150</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6144</v>
+        <v>6151</v>
       </c>
       <c r="AO45" t="s">
-        <v>6145</v>
+        <v>6152</v>
       </c>
       <c r="AR45" t="s">
-        <v>6146</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6147</v>
+        <v>6154</v>
       </c>
       <c r="F46" t="s">
-        <v>6148</v>
+        <v>6155</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6149</v>
+        <v>6156</v>
       </c>
       <c r="N46" t="s">
-        <v>6150</v>
+        <v>6157</v>
       </c>
       <c r="AC46" t="s">
-        <v>6151</v>
+        <v>6158</v>
       </c>
       <c r="AF46" t="s">
-        <v>6152</v>
+        <v>6159</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6153</v>
+        <v>6160</v>
       </c>
       <c r="AO46" t="s">
-        <v>6154</v>
+        <v>6161</v>
       </c>
       <c r="AR46" t="s">
-        <v>6155</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6156</v>
+        <v>6163</v>
       </c>
       <c r="F47" t="s">
-        <v>6157</v>
+        <v>6164</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6158</v>
+        <v>6165</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6159</v>
+        <v>6166</v>
       </c>
       <c r="AC47" t="s">
-        <v>6160</v>
+        <v>6167</v>
       </c>
       <c r="AF47" t="s">
-        <v>6161</v>
+        <v>6168</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6162</v>
+        <v>6169</v>
       </c>
       <c r="AO47" t="s">
-        <v>6163</v>
+        <v>6170</v>
       </c>
       <c r="AR47" t="s">
-        <v>6164</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6165</v>
+        <v>6172</v>
       </c>
       <c r="F48" t="s">
-        <v>6166</v>
+        <v>6173</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -93908,141 +94032,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6167</v>
+        <v>6174</v>
       </c>
       <c r="AF48" t="s">
-        <v>6168</v>
+        <v>6175</v>
       </c>
       <c r="AO48" t="s">
-        <v>6169</v>
+        <v>6176</v>
       </c>
       <c r="AR48" t="s">
-        <v>6170</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6171</v>
+        <v>6178</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6172</v>
+        <v>6179</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6173</v>
+        <v>6180</v>
       </c>
       <c r="AF49" t="s">
-        <v>6174</v>
+        <v>6181</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6175</v>
+        <v>6182</v>
       </c>
       <c r="AR49" t="s">
-        <v>6176</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6177</v>
+        <v>6184</v>
       </c>
       <c r="F50" t="s">
-        <v>6178</v>
+        <v>6185</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6179</v>
+        <v>6186</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6180</v>
+        <v>6187</v>
       </c>
       <c r="AR50" t="s">
-        <v>6181</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6182</v>
+        <v>6189</v>
       </c>
       <c r="F51" t="s">
-        <v>6183</v>
+        <v>6190</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6184</v>
+        <v>6191</v>
       </c>
       <c r="AR51" t="s">
-        <v>6185</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6186</v>
+        <v>6193</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6187</v>
+        <v>6194</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6188</v>
+        <v>6195</v>
       </c>
       <c r="AR52" t="s">
-        <v>6189</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6190</v>
+        <v>6197</v>
       </c>
       <c r="F53" t="s">
-        <v>6191</v>
+        <v>6198</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6192</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6193</v>
+        <v>6200</v>
       </c>
       <c r="F54" t="s">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6195</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6196</v>
+        <v>6203</v>
       </c>
       <c r="F55" t="s">
-        <v>6197</v>
+        <v>6204</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94050,10 +94174,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6198</v>
+        <v>6205</v>
       </c>
       <c r="F56" t="s">
-        <v>6199</v>
+        <v>6206</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94061,18 +94185,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6200</v>
+        <v>6207</v>
       </c>
       <c r="F57" t="s">
-        <v>6201</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6202</v>
+        <v>6209</v>
       </c>
       <c r="F58" t="s">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94080,42 +94204,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6204</v>
+        <v>6211</v>
       </c>
       <c r="F59" t="s">
-        <v>6205</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6206</v>
+        <v>6213</v>
       </c>
       <c r="F60" t="s">
-        <v>6207</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6208</v>
+        <v>6215</v>
       </c>
       <c r="F61" t="s">
-        <v>6209</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6210</v>
+        <v>6217</v>
       </c>
       <c r="F62" t="s">
-        <v>6211</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6212</v>
+        <v>6219</v>
       </c>
       <c r="F63" t="s">
-        <v>6213</v>
+        <v>6220</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94123,181 +94247,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6214</v>
+        <v>6221</v>
       </c>
       <c r="F64" t="s">
-        <v>6215</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6177</v>
+        <v>6184</v>
       </c>
       <c r="F65" t="s">
-        <v>6168</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6216</v>
+        <v>6223</v>
       </c>
       <c r="F66" t="s">
-        <v>6217</v>
+        <v>6224</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6218</v>
+        <v>6225</v>
       </c>
       <c r="F67" t="s">
-        <v>6219</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6220</v>
+        <v>6227</v>
       </c>
       <c r="F68" t="s">
-        <v>6184</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6221</v>
+        <v>6228</v>
       </c>
       <c r="F69" t="s">
-        <v>6222</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6223</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6224</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6225</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6226</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6227</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6228</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6229</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6230</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6231</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6232</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6233</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6234</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6235</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6236</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6237</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6238</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6239</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6240</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6241</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6242</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5981</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6243</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6244</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6245</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6246</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6247</v>
+        <v>6254</v>
       </c>
     </row>
   </sheetData>
@@ -94324,10 +94448,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6248</v>
+        <v>6255</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6249</v>
+        <v>6256</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94336,13 +94460,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6250</v>
+        <v>6257</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6251</v>
+        <v>6258</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6252</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94350,13 +94474,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6253</v>
+        <v>6260</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6254</v>
+        <v>6261</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94368,13 +94492,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6255</v>
+        <v>6262</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6256</v>
+        <v>6263</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94385,19 +94509,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6257</v>
+        <v>6264</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6258</v>
+        <v>6265</v>
       </c>
       <c r="S10" t="s">
-        <v>6259</v>
+        <v>6266</v>
       </c>
       <c r="T10" t="s">
-        <v>6260</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94411,15 +94535,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6261</v>
+        <v>6268</v>
       </c>
       <c r="S11" t="s">
-        <v>5985</v>
+        <v>5992</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6262</v>
+        <v>6269</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94428,18 +94552,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6263</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6264</v>
+        <v>6271</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6265</v>
+        <v>6272</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94448,7 +94572,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6266</v>
+        <v>6273</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94459,13 +94583,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6267</v>
+        <v>6274</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6268</v>
+        <v>6275</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94476,7 +94600,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6269</v>
+        <v>6276</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94485,10 +94609,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6152</v>
+        <v>6159</v>
       </c>
       <c r="T15" t="s">
-        <v>6270</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94499,12 +94623,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6271</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6272</v>
+        <v>6279</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94512,22 +94636,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6273</v>
+        <v>6280</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6274</v>
+        <v>6281</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6275</v>
+        <v>6282</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6276</v>
+        <v>6283</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6277</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94538,39 +94662,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6278</v>
+        <v>6285</v>
       </c>
       <c r="H32" t="s">
-        <v>6279</v>
+        <v>6286</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6280</v>
+        <v>6287</v>
       </c>
       <c r="K32" t="s">
-        <v>6281</v>
+        <v>6288</v>
       </c>
       <c r="N32" t="s">
-        <v>6282</v>
+        <v>6289</v>
       </c>
       <c r="Q32" t="s">
-        <v>6283</v>
+        <v>6290</v>
       </c>
       <c r="S32" t="s">
-        <v>6009</v>
+        <v>6016</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6285</v>
+        <v>6292</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94579,13 +94703,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6286</v>
+        <v>6293</v>
       </c>
       <c r="K33" t="s">
-        <v>6287</v>
+        <v>6294</v>
       </c>
       <c r="N33" t="s">
-        <v>6288</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94593,153 +94717,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6289</v>
+        <v>6296</v>
       </c>
       <c r="K34" t="s">
-        <v>6290</v>
+        <v>6297</v>
       </c>
       <c r="N34" t="s">
-        <v>6291</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6292</v>
+        <v>6299</v>
       </c>
       <c r="N35" t="s">
-        <v>6293</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6294</v>
+        <v>6301</v>
       </c>
       <c r="N36" t="s">
-        <v>6295</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6296</v>
+        <v>6303</v>
       </c>
       <c r="N37" t="s">
-        <v>6297</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6298</v>
+        <v>6305</v>
       </c>
       <c r="N38" t="s">
-        <v>6299</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6022</v>
+        <v>6029</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6300</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6301</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6302</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6303</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6304</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6305</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6306</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6307</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6308</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6309</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6199</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6310</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6311</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6197</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6312</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6313</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6314</v>
+        <v>6321</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6315</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6316</v>
+        <v>6323</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6317</v>
+        <v>6324</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94747,7 +94871,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6318</v>
+        <v>6325</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94763,7 +94887,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6319</v>
+        <v>6326</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94779,21 +94903,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6320</v>
+        <v>6327</v>
       </c>
       <c r="J68" t="s">
-        <v>6321</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6322</v>
+        <v>6329</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6323</v>
+        <v>6330</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94802,52 +94926,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6097</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6324</v>
+        <v>6331</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5954</v>
+        <v>5961</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6107</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6130</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6325</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6326</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6119</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6327</v>
+        <v>6334</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6328</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -94909,7 +95033,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6329</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -94917,10 +95041,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6330</v>
+        <v>6337</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6331</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -94928,7 +95052,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6332</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -94941,15 +95065,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6333</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6334</v>
+        <v>6341</v>
       </c>
       <c r="F17" t="s">
-        <v>6335</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3353</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3356</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13553" uniqueCount="6343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13564" uniqueCount="6346">
   <si>
     <t>名称</t>
   </si>
@@ -20495,6 +20495,15 @@
   </si>
   <si>
     <t>同35题</t>
+  </si>
+  <si>
+    <t>使库存平衡的最少丢弃次数</t>
+  </si>
+  <si>
+    <t>寻找黄金时段客户</t>
+  </si>
+  <si>
+    <t>固定长度子数组中的最小逆序对数目</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22160,16 +22169,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -92905,12 +92914,75 @@
         <v>5953</v>
       </c>
     </row>
+    <row r="3357" spans="1:8">
+      <c r="A3357">
+        <v>3679</v>
+      </c>
+      <c r="B3357" t="s">
+        <v>5954</v>
+      </c>
+      <c r="C3357" s="2">
+        <v>46095</v>
+      </c>
+      <c r="D3357" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3357" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3357">
+        <v>1638</v>
+      </c>
+      <c r="G3357" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3358" spans="1:8">
+      <c r="A3358">
+        <v>3705</v>
+      </c>
+      <c r="B3358" t="s">
+        <v>5955</v>
+      </c>
+      <c r="C3358" s="2">
+        <v>46095</v>
+      </c>
+      <c r="D3358" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3358" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3359" spans="1:8">
+      <c r="A3359">
+        <v>3768</v>
+      </c>
+      <c r="B3359" t="s">
+        <v>5956</v>
+      </c>
+      <c r="C3359" s="2">
+        <v>46095</v>
+      </c>
+      <c r="D3359" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3359" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3359">
+        <v>2157</v>
+      </c>
+      <c r="G3359" s="1" t="s">
+        <v>3451</v>
+      </c>
+    </row>
     <row r="3362" spans="1:7">
       <c r="A3362">
         <v>3454</v>
       </c>
       <c r="B3362" t="s">
-        <v>5954</v>
+        <v>5957</v>
       </c>
       <c r="D3362" t="s">
         <v>135</v>
@@ -92930,7 +93002,7 @@
         <v>3562</v>
       </c>
       <c r="B3363" t="s">
-        <v>5955</v>
+        <v>5958</v>
       </c>
       <c r="D3363" t="s">
         <v>135</v>
@@ -92941,10 +93013,10 @@
     </row>
     <row r="3364" spans="1:7">
       <c r="A3364" t="s">
-        <v>5956</v>
+        <v>5959</v>
       </c>
       <c r="B3364" t="s">
-        <v>5957</v>
+        <v>5960</v>
       </c>
       <c r="D3364" t="s">
         <v>135</v>
@@ -92955,7 +93027,7 @@
         <v>3721</v>
       </c>
       <c r="B3365" t="s">
-        <v>5958</v>
+        <v>5961</v>
       </c>
       <c r="D3365" t="s">
         <v>135</v>
@@ -92968,7 +93040,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3353" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3356" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93015,10 +93087,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5959</v>
+        <v>5962</v>
       </c>
       <c r="D5" t="s">
-        <v>5960</v>
+        <v>5963</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93029,13 +93101,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93044,7 +93116,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5963</v>
+        <v>5966</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93059,16 +93131,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5964</v>
+        <v>5967</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5965</v>
+        <v>5968</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5966</v>
+        <v>5969</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93082,10 +93154,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5967</v>
+        <v>5970</v>
       </c>
       <c r="H14" t="s">
-        <v>5968</v>
+        <v>5971</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93100,16 +93172,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5969</v>
+        <v>5972</v>
       </c>
       <c r="W14" t="s">
-        <v>5970</v>
+        <v>5973</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5971</v>
+        <v>5974</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93121,158 +93193,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="AL14" t="s">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="AO14" t="s">
-        <v>5975</v>
+        <v>5978</v>
       </c>
       <c r="AR14" t="s">
-        <v>5976</v>
+        <v>5979</v>
       </c>
       <c r="AU14" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="AX14" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5981</v>
+        <v>5984</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="T15" t="s">
-        <v>5984</v>
+        <v>5987</v>
       </c>
       <c r="W15" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="Z15" t="s">
-        <v>5986</v>
+        <v>5989</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="AF15" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
       <c r="AI15" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="AL15" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="AU15" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="AX15" t="s">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5996</v>
+        <v>5999</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="H16" t="s">
-        <v>5998</v>
+        <v>6001</v>
       </c>
       <c r="N16" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="T16" t="s">
-        <v>6000</v>
+        <v>6003</v>
       </c>
       <c r="W16" t="s">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="Z16" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="AC16" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="AF16" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="AI16" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="AL16" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
       <c r="AR16" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="AU16" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="AX16" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93280,43 +93352,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="D17" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="H17" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="N17" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="T17" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="W17" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="Z17" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="AC17" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="AF17" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="AI17" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="AR17" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="AU17" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="BA17" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93324,37 +93396,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="H18" t="s">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="N18" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="T18" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
       <c r="W18" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="Z18" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="AC18" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
       <c r="AF18" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="AI18" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="AU18" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="BA18" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93362,37 +93434,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="H19" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="N19" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="T19" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="W19" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="Z19" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="AC19" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AF19" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="AI19" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="AU19" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="BA19" t="s">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93400,37 +93472,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="D20" t="s">
-        <v>6040</v>
+        <v>6043</v>
       </c>
       <c r="H20" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="N20" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="T20" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="W20" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="Z20" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="AC20" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="AF20" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
       <c r="AU20" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="BA20" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93438,37 +93510,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6051</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6052</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6053</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6054</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6055</v>
+      </c>
+      <c r="W21" t="s">
         <v>6048</v>
       </c>
-      <c r="D21" t="s">
-        <v>6049</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6050</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6051</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6052</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6045</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AC21" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="AF21" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="AU21" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="BA21" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93479,13 +93551,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93494,16 +93566,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="AC22" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
       <c r="AF22" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="AU22" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93511,25 +93583,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
       <c r="H23" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="T23" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="Z23" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="AC23" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="AF23" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="AU23" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93537,89 +93609,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
       <c r="T24" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="Z24" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="AC24" t="s">
-        <v>6071</v>
+        <v>6074</v>
       </c>
       <c r="AF24" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="D25" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="T25" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="AC25" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="AF25" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="AC26" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
       <c r="AF26" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="AC27" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="AF27" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="AC28" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="AF28" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93629,22 +93701,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93654,7 +93726,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93662,7 +93734,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93677,7 +93749,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93695,227 +93767,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="Q41" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="T41" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="W41" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="AL41" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="AO41" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="AR41" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="Q42" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="T42" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="W42" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="AC42" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="AL42" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="AO42" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
       <c r="AR42" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="K43" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="N43" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="Q43" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
       <c r="T43" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="W43" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="Z43" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
       <c r="AC43" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="AF43" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="AL43" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="AO43" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="AR43" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
       <c r="F44" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="N44" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="Q44" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
       <c r="W44" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="Z44" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="AC44" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
       <c r="AF44" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="AL44" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="AO44" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="AR44" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="F45" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="N45" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="Q45" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93924,103 +93996,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AF45" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="AO45" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="AR45" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="F46" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="N46" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="AC46" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="AF46" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="AO46" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
       <c r="AR46" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="F47" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="AC47" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="AF47" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="AO47" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="AR47" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="F48" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94032,141 +94104,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="AF48" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
       <c r="AO48" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="AR48" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="AF49" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="AR49" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="F50" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="AR50" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
       <c r="F51" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="AR51" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
       <c r="AR52" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="F53" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="F54" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="F55" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94174,10 +94246,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="F56" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94185,18 +94257,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
       <c r="F57" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="F58" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94204,42 +94276,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
       <c r="F59" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
       <c r="F60" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
       <c r="F61" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="F62" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
       <c r="F63" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94247,181 +94319,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
       <c r="F64" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="F65" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
       <c r="F66" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
       <c r="F67" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
       <c r="F68" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="F69" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
     </row>
   </sheetData>
@@ -94448,10 +94520,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94460,13 +94532,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94474,13 +94546,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94492,13 +94564,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94509,19 +94581,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="S10" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
       <c r="T10" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94535,15 +94607,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="S11" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94552,18 +94624,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94572,7 +94644,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94583,13 +94655,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94600,7 +94672,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94609,10 +94681,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="T15" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94623,12 +94695,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94636,22 +94708,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94662,39 +94734,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
       <c r="H32" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="K32" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
       <c r="N32" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
       <c r="Q32" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="S32" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94703,13 +94775,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="K33" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
       <c r="N33" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94717,153 +94789,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
       <c r="K34" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="N34" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="N35" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="N36" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
       <c r="N37" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="N38" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94871,7 +94943,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94887,7 +94959,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94903,21 +94975,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
       <c r="J68" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94926,52 +94998,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95033,7 +95105,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95041,10 +95113,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95052,7 +95124,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95065,15 +95137,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="F17" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3363</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13564" uniqueCount="6346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13579" uniqueCount="6350">
   <si>
     <t>名称</t>
   </si>
@@ -20504,6 +20504,18 @@
   </si>
   <si>
     <t>固定长度子数组中的最小逆序对数目</t>
+  </si>
+  <si>
+    <t>统计范围内的逗号</t>
+  </si>
+  <si>
+    <t>统计范围内的逗号II</t>
+  </si>
+  <si>
+    <t>替换最多一个元素后的最长等差子数组</t>
+  </si>
+  <si>
+    <t>添加一个点后可激活的最大点数</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22169,16 +22181,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23130,7 +23142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3365"/>
+  <dimension ref="A1:N3375"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -92977,70 +92989,165 @@
         <v>3451</v>
       </c>
     </row>
+    <row r="3360" spans="1:8">
+      <c r="A3360">
+        <v>3870</v>
+      </c>
+      <c r="B3360" t="s">
+        <v>5957</v>
+      </c>
+      <c r="C3360" s="2">
+        <v>46096</v>
+      </c>
+      <c r="D3360" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3360" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3361" spans="1:7">
+      <c r="A3361">
+        <v>3871</v>
+      </c>
+      <c r="B3361" t="s">
+        <v>5958</v>
+      </c>
+      <c r="C3361" s="2">
+        <v>46096</v>
+      </c>
+      <c r="D3361" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3361" t="s">
+        <v>223</v>
+      </c>
+      <c r="G3361" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
     <row r="3362" spans="1:7">
       <c r="A3362">
-        <v>3454</v>
+        <v>3872</v>
       </c>
       <c r="B3362" t="s">
-        <v>5957</v>
+        <v>5959</v>
+      </c>
+      <c r="C3362" s="2">
+        <v>46096</v>
       </c>
       <c r="D3362" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E3362" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3362">
-        <v>2671</v>
+        <v>34</v>
       </c>
       <c r="G3362" s="1" t="s">
-        <v>927</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="3363" spans="1:7">
       <c r="A3363">
-        <v>3562</v>
+        <v>3873</v>
       </c>
       <c r="B3363" t="s">
-        <v>5958</v>
+        <v>5960</v>
+      </c>
+      <c r="C3363" s="2">
+        <v>46096</v>
       </c>
       <c r="D3363" t="s">
         <v>135</v>
       </c>
-      <c r="F3363">
+      <c r="E3363" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3363" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3364" spans="1:7">
+      <c r="C3364" s="2"/>
+    </row>
+    <row r="3365" spans="1:7">
+      <c r="C3365" s="2"/>
+    </row>
+    <row r="3366" spans="1:7">
+      <c r="C3366" s="2"/>
+    </row>
+    <row r="3367" spans="1:7">
+      <c r="C3367" s="2"/>
+    </row>
+    <row r="3368" spans="1:7">
+      <c r="C3368" s="2"/>
+    </row>
+    <row r="3369" spans="1:7">
+      <c r="C3369" s="2"/>
+    </row>
+    <row r="3372" spans="1:7">
+      <c r="A3372">
+        <v>3454</v>
+      </c>
+      <c r="B3372" t="s">
+        <v>5961</v>
+      </c>
+      <c r="D3372" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3372" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3372">
+        <v>2671</v>
+      </c>
+      <c r="G3372" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="3373" spans="1:7">
+      <c r="A3373">
+        <v>3562</v>
+      </c>
+      <c r="B3373" t="s">
+        <v>5962</v>
+      </c>
+      <c r="D3373" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3373">
         <v>2458</v>
       </c>
     </row>
-    <row r="3364" spans="1:7">
-      <c r="A3364" t="s">
-        <v>5959</v>
-      </c>
-      <c r="B3364" t="s">
-        <v>5960</v>
-      </c>
-      <c r="D3364" t="s">
+    <row r="3374" spans="1:7">
+      <c r="A3374" t="s">
+        <v>5963</v>
+      </c>
+      <c r="B3374" t="s">
+        <v>5964</v>
+      </c>
+      <c r="D3374" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3365" spans="1:7">
-      <c r="A3365">
+    <row r="3375" spans="1:7">
+      <c r="A3375">
         <v>3721</v>
       </c>
-      <c r="B3365" t="s">
-        <v>5961</v>
-      </c>
-      <c r="D3365" t="s">
+      <c r="B3375" t="s">
+        <v>5965</v>
+      </c>
+      <c r="D3375" t="s">
         <v>135</v>
       </c>
-      <c r="E3365" t="s">
+      <c r="E3375" t="s">
         <v>73</v>
       </c>
-      <c r="F3365">
+      <c r="F3375">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3356" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3363" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93087,10 +93194,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5962</v>
+        <v>5966</v>
       </c>
       <c r="D5" t="s">
-        <v>5963</v>
+        <v>5967</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93101,13 +93208,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93116,7 +93223,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93131,16 +93238,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93154,10 +93261,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
       <c r="H14" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93172,16 +93279,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="W14" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93193,158 +93300,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="AL14" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="AO14" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="AR14" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="AU14" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="AX14" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="T15" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="W15" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="Z15" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="AF15" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="AI15" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="AL15" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="AU15" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AX15" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="H16" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="N16" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="T16" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="W16" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="Z16" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="AC16" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="AF16" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AI16" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="AL16" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="AR16" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AU16" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="AX16" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93352,43 +93459,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="D17" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="H17" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="N17" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="T17" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="W17" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="Z17" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="AC17" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="AF17" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="AI17" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="AR17" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="AU17" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="BA17" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93396,37 +93503,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="H18" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="N18" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="T18" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="W18" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="Z18" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="AC18" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="AF18" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="AI18" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="AU18" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="BA18" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93434,37 +93541,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="H19" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="N19" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="T19" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="W19" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="Z19" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AC19" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="AF19" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AI19" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AU19" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="BA19" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93472,37 +93579,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6046</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6047</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6048</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6049</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6050</v>
+      </c>
+      <c r="W20" t="s">
         <v>6042</v>
       </c>
-      <c r="D20" t="s">
-        <v>6043</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6044</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6045</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6046</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6038</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AC20" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="AF20" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="AU20" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="BA20" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93510,37 +93617,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="D21" t="s">
+        <v>6056</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6057</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6058</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6059</v>
+      </c>
+      <c r="W21" t="s">
         <v>6052</v>
       </c>
-      <c r="H21" t="s">
-        <v>6053</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6054</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6055</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6048</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AC21" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AF21" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AU21" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="BA21" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93551,13 +93658,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93566,16 +93673,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AC22" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="AF22" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="AU22" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93583,25 +93690,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="H23" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="T23" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="Z23" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AC23" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AF23" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="AU23" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93609,89 +93716,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="T24" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="Z24" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AC24" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AF24" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="D25" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="T25" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="AC25" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AF25" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AC26" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AF26" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AC27" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AF27" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AC28" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AF28" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93701,22 +93808,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93726,7 +93833,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93734,7 +93841,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93749,7 +93856,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93767,227 +93874,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="Q41" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="T41" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="W41" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AL41" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AO41" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AR41" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="Q42" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="T42" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="W42" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AC42" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AL42" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AO42" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AR42" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="K43" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="N43" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="Q43" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="T43" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="W43" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="Z43" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AC43" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AF43" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AL43" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AO43" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AR43" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="F44" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="N44" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="Q44" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="W44" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="Z44" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AC44" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AF44" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AL44" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AO44" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AR44" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="F45" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="N45" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="Q45" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -93996,103 +94103,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AF45" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AO45" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AR45" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="F46" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="N46" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AC46" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AF46" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AO46" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AR46" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="F47" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AC47" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="AF47" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AO47" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="AR47" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="F48" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94104,141 +94211,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="AF48" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AO48" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="AR48" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="AF49" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AR49" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="F50" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AR50" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="F51" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="AR51" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AR52" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="F53" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="F54" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="F55" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94246,10 +94353,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="F56" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94257,18 +94364,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="F57" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="F58" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94276,42 +94383,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="F59" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="F60" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="F61" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="F62" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="F63" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94319,181 +94426,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="F64" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="F65" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="F66" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="F67" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="F68" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="F69" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
     </row>
   </sheetData>
@@ -94520,10 +94627,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94532,13 +94639,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94546,13 +94653,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94564,13 +94671,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94581,19 +94688,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="S10" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="T10" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94607,15 +94714,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="S11" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94624,18 +94731,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94644,7 +94751,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94655,13 +94762,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94672,7 +94779,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94681,10 +94788,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="T15" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94695,12 +94802,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94708,22 +94815,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94734,39 +94841,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="H32" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="K32" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="N32" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="Q32" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="S32" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94775,13 +94882,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="K33" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="N33" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94789,153 +94896,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="K34" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="N34" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="N35" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="N36" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="N37" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="N38" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -94943,7 +95050,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -94959,7 +95066,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -94975,21 +95082,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
       <c r="J68" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -94998,52 +95105,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95105,7 +95212,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95113,10 +95220,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95124,7 +95231,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95137,15 +95244,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
       <c r="F17" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13579" uniqueCount="6350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13590" uniqueCount="6353">
   <si>
     <t>名称</t>
   </si>
@@ -20516,6 +20516,15 @@
   </si>
   <si>
     <t>添加一个点后可激活的最大点数</t>
+  </si>
+  <si>
+    <t>寻找流失风险客户</t>
+  </si>
+  <si>
+    <t>删除子字符串后不同的终点</t>
+  </si>
+  <si>
+    <t>转换数组的最少操作次数</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22181,16 +22190,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93006,7 +93015,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3361" spans="1:7">
+    <row r="3361" spans="1:8">
       <c r="A3361">
         <v>3871</v>
       </c>
@@ -93026,7 +93035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3362" spans="1:7">
+    <row r="3362" spans="1:8">
       <c r="A3362">
         <v>3872</v>
       </c>
@@ -93046,7 +93055,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="3363" spans="1:7">
+    <row r="3363" spans="1:8">
       <c r="A3363">
         <v>3873</v>
       </c>
@@ -93066,30 +93075,84 @@
         <v>198</v>
       </c>
     </row>
-    <row r="3364" spans="1:7">
-      <c r="C3364" s="2"/>
-    </row>
-    <row r="3365" spans="1:7">
-      <c r="C3365" s="2"/>
-    </row>
-    <row r="3366" spans="1:7">
-      <c r="C3366" s="2"/>
-    </row>
-    <row r="3367" spans="1:7">
+    <row r="3364" spans="1:8">
+      <c r="A3364">
+        <v>3716</v>
+      </c>
+      <c r="B3364" t="s">
+        <v>5961</v>
+      </c>
+      <c r="C3364" s="2">
+        <v>46097</v>
+      </c>
+      <c r="D3364" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3364" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3365" spans="1:8">
+      <c r="A3365">
+        <v>3694</v>
+      </c>
+      <c r="B3365" t="s">
+        <v>5962</v>
+      </c>
+      <c r="C3365" s="2">
+        <v>46097</v>
+      </c>
+      <c r="D3365" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3365" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3365">
+        <v>1739</v>
+      </c>
+      <c r="G3365" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3366" spans="1:8">
+      <c r="A3366">
+        <v>3724</v>
+      </c>
+      <c r="B3366" t="s">
+        <v>5963</v>
+      </c>
+      <c r="C3366" s="2">
+        <v>46097</v>
+      </c>
+      <c r="D3366" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3366" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3366">
+        <v>1790</v>
+      </c>
+      <c r="G3366" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="3367" spans="1:8">
       <c r="C3367" s="2"/>
     </row>
-    <row r="3368" spans="1:7">
+    <row r="3368" spans="1:8">
       <c r="C3368" s="2"/>
     </row>
-    <row r="3369" spans="1:7">
+    <row r="3369" spans="1:8">
       <c r="C3369" s="2"/>
     </row>
-    <row r="3372" spans="1:7">
+    <row r="3372" spans="1:8">
       <c r="A3372">
         <v>3454</v>
       </c>
       <c r="B3372" t="s">
-        <v>5961</v>
+        <v>5964</v>
       </c>
       <c r="D3372" t="s">
         <v>135</v>
@@ -93104,12 +93167,12 @@
         <v>927</v>
       </c>
     </row>
-    <row r="3373" spans="1:7">
+    <row r="3373" spans="1:8">
       <c r="A3373">
         <v>3562</v>
       </c>
       <c r="B3373" t="s">
-        <v>5962</v>
+        <v>5965</v>
       </c>
       <c r="D3373" t="s">
         <v>135</v>
@@ -93118,23 +93181,23 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="3374" spans="1:7">
+    <row r="3374" spans="1:8">
       <c r="A3374" t="s">
-        <v>5963</v>
+        <v>5966</v>
       </c>
       <c r="B3374" t="s">
-        <v>5964</v>
+        <v>5967</v>
       </c>
       <c r="D3374" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3375" spans="1:7">
+    <row r="3375" spans="1:8">
       <c r="A3375">
         <v>3721</v>
       </c>
       <c r="B3375" t="s">
-        <v>5965</v>
+        <v>5968</v>
       </c>
       <c r="D3375" t="s">
         <v>135</v>
@@ -93194,10 +93257,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5966</v>
+        <v>5969</v>
       </c>
       <c r="D5" t="s">
-        <v>5967</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93208,13 +93271,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5968</v>
+        <v>5971</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5969</v>
+        <v>5972</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93223,7 +93286,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5970</v>
+        <v>5973</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93238,16 +93301,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5971</v>
+        <v>5974</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5972</v>
+        <v>5975</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93261,10 +93324,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="H14" t="s">
-        <v>5975</v>
+        <v>5978</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93279,16 +93342,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5976</v>
+        <v>5979</v>
       </c>
       <c r="W14" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93300,158 +93363,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="AL14" t="s">
-        <v>5981</v>
+        <v>5984</v>
       </c>
       <c r="AO14" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
       <c r="AR14" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="AU14" t="s">
-        <v>5984</v>
+        <v>5987</v>
       </c>
       <c r="AX14" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5986</v>
+        <v>5989</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="T15" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="W15" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="Z15" t="s">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="AF15" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="AI15" t="s">
-        <v>5996</v>
+        <v>5999</v>
       </c>
       <c r="AL15" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>5998</v>
+        <v>6001</v>
       </c>
       <c r="AU15" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="AX15" t="s">
-        <v>6000</v>
+        <v>6003</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
       <c r="H16" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="N16" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="T16" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="W16" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="Z16" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="AC16" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="AF16" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="AI16" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="AL16" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="AR16" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="AU16" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="AX16" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93459,43 +93522,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="D17" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="H17" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="N17" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="T17" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="W17" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
       <c r="Z17" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="AC17" t="s">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="AF17" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="AI17" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
       <c r="AR17" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="AU17" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
       <c r="BA17" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93503,37 +93566,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="H18" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="N18" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="T18" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="W18" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="Z18" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="AC18" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AF18" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="AI18" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AU18" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="BA18" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93541,37 +93604,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="H19" t="s">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="N19" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="T19" t="s">
-        <v>6040</v>
+        <v>6043</v>
       </c>
       <c r="W19" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="Z19" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="AC19" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="AF19" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="AI19" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="AU19" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="BA19" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93579,37 +93642,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="D20" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="H20" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="N20" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="T20" t="s">
-        <v>6050</v>
+        <v>6053</v>
       </c>
       <c r="W20" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="Z20" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="AC20" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="AF20" t="s">
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="AU20" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="BA20" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93617,37 +93680,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6058</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6059</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6060</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6061</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6062</v>
+      </c>
+      <c r="W21" t="s">
         <v>6055</v>
       </c>
-      <c r="D21" t="s">
-        <v>6056</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6057</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6058</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6059</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6052</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="AC21" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="AF21" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="AU21" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
       <c r="BA21" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93658,13 +93721,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93673,16 +93736,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="AC22" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="AF22" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
       <c r="AU22" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93690,25 +93753,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="H23" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="T23" t="s">
-        <v>6071</v>
+        <v>6074</v>
       </c>
       <c r="Z23" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="AC23" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="AF23" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="AU23" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93716,89 +93779,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="T24" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="Z24" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
       <c r="AC24" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="AF24" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
       <c r="D25" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="T25" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="AC25" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="AF25" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="AC26" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="AF26" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="AC27" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="AF27" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="AC28" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="AF28" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93808,22 +93871,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93833,7 +93896,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93841,7 +93904,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93856,7 +93919,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93874,227 +93937,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="Q41" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="T41" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="W41" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="AL41" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="AO41" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="AR41" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
       <c r="Q42" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="T42" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="W42" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="AC42" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="AL42" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="AO42" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="AR42" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="K43" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="N43" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="Q43" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="T43" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="W43" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
       <c r="Z43" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="AC43" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="AF43" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="AL43" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="AO43" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="AR43" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="F44" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="N44" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
       <c r="Q44" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="W44" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="Z44" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="AC44" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="AF44" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="AL44" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="AO44" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AR44" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="F45" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="N45" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="Q45" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94103,103 +94166,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="AF45" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="AO45" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AR45" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
       <c r="F46" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="N46" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="AC46" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="AF46" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="AO46" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="AR46" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="F47" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="AC47" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="AF47" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="AO47" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="AR47" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="F48" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94211,141 +94274,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="AF48" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="AO48" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="AR48" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="AF49" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
       <c r="AR49" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="F50" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="AR50" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
       <c r="F51" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="AR51" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
       <c r="AR52" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="F53" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
       <c r="F54" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
       <c r="F55" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94353,10 +94416,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
       <c r="F56" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94364,18 +94427,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="F57" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
       <c r="F58" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94383,42 +94446,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
       <c r="F59" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
       <c r="F60" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
       <c r="F61" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="F62" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
       <c r="F63" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94426,181 +94489,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="F64" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="F65" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
       <c r="F66" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
       <c r="F67" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
       <c r="F68" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="F69" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
     </row>
   </sheetData>
@@ -94627,10 +94690,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94639,13 +94702,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94653,13 +94716,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94671,13 +94734,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94688,19 +94751,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="S10" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
       <c r="T10" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94714,15 +94777,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="S11" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94731,18 +94794,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94751,7 +94814,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94762,13 +94825,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94779,7 +94842,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94788,10 +94851,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="T15" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94802,12 +94865,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94815,22 +94878,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94841,39 +94904,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="H32" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
       <c r="K32" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="N32" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
       <c r="Q32" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="S32" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94882,13 +94945,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
       <c r="K33" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="N33" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94896,153 +94959,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
       <c r="K34" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="N34" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
       <c r="N35" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
       <c r="N36" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="N37" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
       <c r="N38" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95050,7 +95113,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95066,7 +95129,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95082,21 +95145,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
       <c r="J68" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95105,52 +95168,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5968</v>
+        <v>5971</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95212,7 +95275,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95220,10 +95283,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95231,7 +95294,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95244,15 +95307,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="F17" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3366</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13590" uniqueCount="6353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13600" uniqueCount="6357">
   <si>
     <t>名称</t>
   </si>
@@ -20525,6 +20525,18 @@
   </si>
   <si>
     <t>转换数组的最少操作次数</t>
+  </si>
+  <si>
+    <t>查找高 tokens 使用量的用户</t>
+  </si>
+  <si>
+    <t>LCR 069</t>
+  </si>
+  <si>
+    <t>同852题</t>
+  </si>
+  <si>
+    <t>分割数组得到最小绝对差</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22184,18 +22196,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -93139,20 +93151,63 @@
       </c>
     </row>
     <row r="3367" spans="1:8">
-      <c r="C3367" s="2"/>
+      <c r="A3367">
+        <v>3793</v>
+      </c>
+      <c r="B3367" t="s">
+        <v>5964</v>
+      </c>
+      <c r="C3367" s="2">
+        <v>46098</v>
+      </c>
+      <c r="D3367" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3367" s="1" t="s">
+        <v>2951</v>
+      </c>
     </row>
     <row r="3368" spans="1:8">
-      <c r="C3368" s="2"/>
+      <c r="A3368" t="s">
+        <v>5965</v>
+      </c>
+      <c r="B3368" t="s">
+        <v>4076</v>
+      </c>
+      <c r="C3368" s="2">
+        <v>46098</v>
+      </c>
+      <c r="D3368" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3368" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3368" s="1" t="s">
+        <v>5966</v>
+      </c>
     </row>
     <row r="3369" spans="1:8">
+      <c r="A3369">
+        <v>3698</v>
+      </c>
+      <c r="B3369" t="s">
+        <v>5967</v>
+      </c>
       <c r="C3369" s="2"/>
+      <c r="D3369" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3369">
+        <v>1648</v>
+      </c>
     </row>
     <row r="3372" spans="1:8">
       <c r="A3372">
         <v>3454</v>
       </c>
       <c r="B3372" t="s">
-        <v>5964</v>
+        <v>5968</v>
       </c>
       <c r="D3372" t="s">
         <v>135</v>
@@ -93172,7 +93227,7 @@
         <v>3562</v>
       </c>
       <c r="B3373" t="s">
-        <v>5965</v>
+        <v>5969</v>
       </c>
       <c r="D3373" t="s">
         <v>135</v>
@@ -93183,10 +93238,10 @@
     </row>
     <row r="3374" spans="1:8">
       <c r="A3374" t="s">
-        <v>5966</v>
+        <v>5970</v>
       </c>
       <c r="B3374" t="s">
-        <v>5967</v>
+        <v>5971</v>
       </c>
       <c r="D3374" t="s">
         <v>135</v>
@@ -93197,7 +93252,7 @@
         <v>3721</v>
       </c>
       <c r="B3375" t="s">
-        <v>5968</v>
+        <v>5972</v>
       </c>
       <c r="D3375" t="s">
         <v>135</v>
@@ -93210,7 +93265,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3363" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3366" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93257,10 +93312,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5969</v>
+        <v>5973</v>
       </c>
       <c r="D5" t="s">
-        <v>5970</v>
+        <v>5974</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93271,13 +93326,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5972</v>
+        <v>5976</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93286,7 +93341,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5973</v>
+        <v>5977</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93301,16 +93356,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5974</v>
+        <v>5978</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5975</v>
+        <v>5979</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5976</v>
+        <v>5980</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93324,10 +93379,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5977</v>
+        <v>5981</v>
       </c>
       <c r="H14" t="s">
-        <v>5978</v>
+        <v>5982</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93342,16 +93397,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="W14" t="s">
-        <v>5980</v>
+        <v>5984</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5981</v>
+        <v>5985</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93363,158 +93418,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5983</v>
+        <v>5987</v>
       </c>
       <c r="AL14" t="s">
-        <v>5984</v>
+        <v>5988</v>
       </c>
       <c r="AO14" t="s">
-        <v>5985</v>
+        <v>5989</v>
       </c>
       <c r="AR14" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="AU14" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="AX14" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="T15" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="W15" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="Z15" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="AF15" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="AI15" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="AL15" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="AU15" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="AX15" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="H16" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="N16" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="T16" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="W16" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="Z16" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="AC16" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="AF16" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="AI16" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="AL16" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="AR16" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AU16" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="AX16" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93522,43 +93577,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="D17" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="H17" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="N17" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="T17" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="W17" t="s">
-        <v>5982</v>
+        <v>5986</v>
       </c>
       <c r="Z17" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="AC17" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="AF17" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AI17" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="AR17" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="AU17" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="BA17" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93566,37 +93621,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="H18" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="N18" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="T18" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="W18" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="Z18" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="AC18" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AF18" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="AI18" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="AU18" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="BA18" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93604,37 +93659,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="H19" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="N19" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="T19" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="W19" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="Z19" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AC19" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="AF19" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AI19" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="AU19" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="BA19" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93642,37 +93697,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6053</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6054</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6055</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6056</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6057</v>
+      </c>
+      <c r="W20" t="s">
         <v>6049</v>
       </c>
-      <c r="D20" t="s">
-        <v>6050</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6051</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6052</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6053</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6045</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="AC20" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AF20" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AU20" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="BA20" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93680,37 +93735,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="D21" t="s">
+        <v>6063</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6064</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6065</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6066</v>
+      </c>
+      <c r="W21" t="s">
         <v>6059</v>
       </c>
-      <c r="H21" t="s">
-        <v>6060</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6061</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6062</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6055</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AC21" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="AF21" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="AU21" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="BA21" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93721,13 +93776,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93736,16 +93791,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="AC22" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="AF22" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="AU22" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93753,25 +93808,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="H23" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="T23" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="Z23" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AC23" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AF23" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AU23" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93779,89 +93834,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="T24" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="Z24" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="AC24" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AF24" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="D25" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="T25" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AC25" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AF25" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AC26" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="AF26" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AC27" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AF27" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="AC28" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AF28" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93871,22 +93926,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93896,7 +93951,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93904,7 +93959,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93919,7 +93974,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93937,227 +93992,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="Q41" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="T41" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="W41" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AL41" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AO41" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AR41" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="Q42" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="T42" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="W42" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AC42" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AL42" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AO42" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AR42" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="K43" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="N43" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="Q43" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="T43" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="W43" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="Z43" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AC43" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AF43" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="AL43" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="AO43" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AR43" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="F44" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="N44" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="Q44" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="W44" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="Z44" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AC44" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AF44" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AL44" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AO44" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AR44" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="F45" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="N45" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="Q45" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94166,103 +94221,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AF45" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AO45" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AR45" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="F46" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="N46" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AC46" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AF46" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="AO46" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AR46" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="F47" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="AC47" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="AF47" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="AO47" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="AR47" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="F48" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94274,141 +94329,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AF48" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AO48" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="AR48" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AF49" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="AR49" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="F50" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="AR50" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="F51" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AR51" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="AR52" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="F53" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="F54" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="F55" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94416,10 +94471,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="F56" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94427,18 +94482,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="F57" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="F58" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94446,42 +94501,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="F59" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="F60" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="F61" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="F62" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="F63" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94489,181 +94544,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="F64" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="F65" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="F66" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="F67" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="F68" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="F69" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
   </sheetData>
@@ -94690,10 +94745,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94702,13 +94757,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94716,13 +94771,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94734,13 +94789,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94751,19 +94806,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="S10" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="T10" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94777,15 +94832,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="S11" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94794,18 +94849,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94814,7 +94869,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94825,13 +94880,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94842,7 +94897,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94851,10 +94906,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="T15" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94865,12 +94920,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94878,22 +94933,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94904,39 +94959,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="H32" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="K32" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="N32" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="Q32" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="S32" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -94945,13 +95000,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="K33" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="N33" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -94959,153 +95014,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="K34" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="N34" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="N35" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="N36" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="N37" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
       <c r="N38" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95113,7 +95168,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95129,7 +95184,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95145,21 +95200,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="J68" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95168,52 +95223,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5971</v>
+        <v>5975</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95275,7 +95330,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95283,10 +95338,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95294,7 +95349,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95307,15 +95362,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
       <c r="F17" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3366</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3369</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13600" uniqueCount="6357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13617" uniqueCount="6362">
   <si>
     <t>名称</t>
   </si>
@@ -20537,6 +20537,21 @@
   </si>
   <si>
     <t>分割数组得到最小绝对差</t>
+  </si>
+  <si>
+    <t>最常见的课程组合</t>
+  </si>
+  <si>
+    <t>LCR 070</t>
+  </si>
+  <si>
+    <t>同540题</t>
+  </si>
+  <si>
+    <t>设计考试分数记录器</t>
+  </si>
+  <si>
+    <t>寻找情绪一致的用户</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22196,18 +22211,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -23163,7 +23178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3375"/>
+  <dimension ref="A1:N3385"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -93194,78 +93209,179 @@
       <c r="B3369" t="s">
         <v>5967</v>
       </c>
-      <c r="C3369" s="2"/>
+      <c r="C3369" s="2">
+        <v>46098</v>
+      </c>
       <c r="D3369" t="s">
         <v>145</v>
+      </c>
+      <c r="E3369" t="s">
+        <v>34</v>
       </c>
       <c r="F3369">
         <v>1648</v>
       </c>
+      <c r="G3369" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3370" spans="1:8">
+      <c r="A3370">
+        <v>3764</v>
+      </c>
+      <c r="B3370" t="s">
+        <v>5968</v>
+      </c>
+      <c r="C3370" s="2">
+        <v>46099</v>
+      </c>
+      <c r="D3370" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3370" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3371" spans="1:8">
+      <c r="A3371" t="s">
+        <v>5969</v>
+      </c>
+      <c r="B3371" t="s">
+        <v>702</v>
+      </c>
+      <c r="C3371" s="2">
+        <v>46099</v>
+      </c>
+      <c r="D3371" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3371" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3371" s="1" t="s">
+        <v>5970</v>
+      </c>
     </row>
     <row r="3372" spans="1:8">
       <c r="A3372">
-        <v>3454</v>
+        <v>3709</v>
       </c>
       <c r="B3372" t="s">
-        <v>5968</v>
+        <v>5971</v>
+      </c>
+      <c r="C3372" s="2">
+        <v>46099</v>
       </c>
       <c r="D3372" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E3372" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F3372">
-        <v>2671</v>
+        <v>1647</v>
       </c>
       <c r="G3372" s="1" t="s">
-        <v>927</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="3373" spans="1:8">
       <c r="A3373">
+        <v>3808</v>
+      </c>
+      <c r="B3373" t="s">
+        <v>5972</v>
+      </c>
+      <c r="C3373" s="2"/>
+      <c r="D3373" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3373" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3374" spans="1:8">
+      <c r="C3374" s="2"/>
+    </row>
+    <row r="3375" spans="1:8">
+      <c r="C3375" s="2"/>
+    </row>
+    <row r="3376" spans="1:8">
+      <c r="C3376" s="2"/>
+    </row>
+    <row r="3377" spans="1:7">
+      <c r="C3377" s="2"/>
+    </row>
+    <row r="3378" spans="1:7">
+      <c r="C3378" s="2"/>
+    </row>
+    <row r="3379" spans="1:7">
+      <c r="C3379" s="2"/>
+    </row>
+    <row r="3382" spans="1:7">
+      <c r="A3382">
+        <v>3454</v>
+      </c>
+      <c r="B3382" t="s">
+        <v>5973</v>
+      </c>
+      <c r="D3382" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3382" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3382">
+        <v>2671</v>
+      </c>
+      <c r="G3382" s="1" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="3383" spans="1:7">
+      <c r="A3383">
         <v>3562</v>
       </c>
-      <c r="B3373" t="s">
-        <v>5969</v>
-      </c>
-      <c r="D3373" t="s">
+      <c r="B3383" t="s">
+        <v>5974</v>
+      </c>
+      <c r="D3383" t="s">
         <v>135</v>
       </c>
-      <c r="F3373">
+      <c r="F3383">
         <v>2458</v>
       </c>
     </row>
-    <row r="3374" spans="1:8">
-      <c r="A3374" t="s">
-        <v>5970</v>
-      </c>
-      <c r="B3374" t="s">
-        <v>5971</v>
-      </c>
-      <c r="D3374" t="s">
+    <row r="3384" spans="1:7">
+      <c r="A3384" t="s">
+        <v>5975</v>
+      </c>
+      <c r="B3384" t="s">
+        <v>5976</v>
+      </c>
+      <c r="D3384" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3375" spans="1:8">
-      <c r="A3375">
+    <row r="3385" spans="1:7">
+      <c r="A3385">
         <v>3721</v>
       </c>
-      <c r="B3375" t="s">
-        <v>5972</v>
-      </c>
-      <c r="D3375" t="s">
+      <c r="B3385" t="s">
+        <v>5977</v>
+      </c>
+      <c r="D3385" t="s">
         <v>135</v>
       </c>
-      <c r="E3375" t="s">
+      <c r="E3385" t="s">
         <v>73</v>
       </c>
-      <c r="F3375">
+      <c r="F3385">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3366" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3369" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93312,10 +93428,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5973</v>
+        <v>5978</v>
       </c>
       <c r="D5" t="s">
-        <v>5974</v>
+        <v>5979</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93326,13 +93442,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5975</v>
+        <v>5980</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5976</v>
+        <v>5981</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93341,7 +93457,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5977</v>
+        <v>5982</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93356,16 +93472,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5978</v>
+        <v>5983</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5979</v>
+        <v>5984</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5980</v>
+        <v>5985</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93379,10 +93495,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5981</v>
+        <v>5986</v>
       </c>
       <c r="H14" t="s">
-        <v>5982</v>
+        <v>5987</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93397,16 +93513,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5983</v>
+        <v>5988</v>
       </c>
       <c r="W14" t="s">
-        <v>5984</v>
+        <v>5989</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5985</v>
+        <v>5990</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93418,158 +93534,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5986</v>
+        <v>5991</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5987</v>
+        <v>5992</v>
       </c>
       <c r="AL14" t="s">
-        <v>5988</v>
+        <v>5993</v>
       </c>
       <c r="AO14" t="s">
-        <v>5989</v>
+        <v>5994</v>
       </c>
       <c r="AR14" t="s">
-        <v>5990</v>
+        <v>5995</v>
       </c>
       <c r="AU14" t="s">
-        <v>5991</v>
+        <v>5996</v>
       </c>
       <c r="AX14" t="s">
-        <v>5992</v>
+        <v>5997</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5993</v>
+        <v>5998</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5994</v>
+        <v>5999</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>5995</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>5996</v>
+        <v>6001</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>5997</v>
+        <v>6002</v>
       </c>
       <c r="T15" t="s">
-        <v>5998</v>
+        <v>6003</v>
       </c>
       <c r="W15" t="s">
-        <v>5999</v>
+        <v>6004</v>
       </c>
       <c r="Z15" t="s">
-        <v>6000</v>
+        <v>6005</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6001</v>
+        <v>6006</v>
       </c>
       <c r="AF15" t="s">
-        <v>6002</v>
+        <v>6007</v>
       </c>
       <c r="AI15" t="s">
-        <v>6003</v>
+        <v>6008</v>
       </c>
       <c r="AL15" t="s">
-        <v>6004</v>
+        <v>6009</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6005</v>
+        <v>6010</v>
       </c>
       <c r="AU15" t="s">
-        <v>6006</v>
+        <v>6011</v>
       </c>
       <c r="AX15" t="s">
-        <v>6007</v>
+        <v>6012</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6008</v>
+        <v>6013</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6009</v>
+        <v>6014</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6010</v>
+        <v>6015</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6011</v>
+        <v>6016</v>
       </c>
       <c r="H16" t="s">
-        <v>6012</v>
+        <v>6017</v>
       </c>
       <c r="N16" t="s">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="T16" t="s">
-        <v>6014</v>
+        <v>6019</v>
       </c>
       <c r="W16" t="s">
-        <v>6015</v>
+        <v>6020</v>
       </c>
       <c r="Z16" t="s">
-        <v>6016</v>
+        <v>6021</v>
       </c>
       <c r="AC16" t="s">
-        <v>6004</v>
+        <v>6009</v>
       </c>
       <c r="AF16" t="s">
-        <v>5986</v>
+        <v>5991</v>
       </c>
       <c r="AI16" t="s">
-        <v>6017</v>
+        <v>6022</v>
       </c>
       <c r="AL16" t="s">
-        <v>6018</v>
+        <v>6023</v>
       </c>
       <c r="AR16" t="s">
-        <v>6019</v>
+        <v>6024</v>
       </c>
       <c r="AU16" t="s">
-        <v>6020</v>
+        <v>6025</v>
       </c>
       <c r="AX16" t="s">
-        <v>6021</v>
+        <v>6026</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6022</v>
+        <v>6027</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93577,43 +93693,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6023</v>
+        <v>6028</v>
       </c>
       <c r="D17" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="H17" t="s">
-        <v>6025</v>
+        <v>6030</v>
       </c>
       <c r="N17" t="s">
-        <v>6026</v>
+        <v>6031</v>
       </c>
       <c r="T17" t="s">
-        <v>6027</v>
+        <v>6032</v>
       </c>
       <c r="W17" t="s">
-        <v>5986</v>
+        <v>5991</v>
       </c>
       <c r="Z17" t="s">
-        <v>5997</v>
+        <v>6002</v>
       </c>
       <c r="AC17" t="s">
-        <v>6028</v>
+        <v>6033</v>
       </c>
       <c r="AF17" t="s">
-        <v>6029</v>
+        <v>6034</v>
       </c>
       <c r="AI17" t="s">
-        <v>6030</v>
+        <v>6035</v>
       </c>
       <c r="AR17" t="s">
-        <v>6031</v>
+        <v>6036</v>
       </c>
       <c r="AU17" t="s">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="BA17" t="s">
-        <v>6033</v>
+        <v>6038</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93621,37 +93737,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="H18" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="N18" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
       <c r="T18" t="s">
-        <v>6037</v>
+        <v>6042</v>
       </c>
       <c r="W18" t="s">
-        <v>6038</v>
+        <v>6043</v>
       </c>
       <c r="Z18" t="s">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="AC18" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="AF18" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="AI18" t="s">
-        <v>6041</v>
+        <v>6046</v>
       </c>
       <c r="AU18" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="BA18" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93659,37 +93775,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
       <c r="H19" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="N19" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="T19" t="s">
-        <v>6047</v>
+        <v>6052</v>
       </c>
       <c r="W19" t="s">
-        <v>6021</v>
+        <v>6026</v>
       </c>
       <c r="Z19" t="s">
-        <v>6026</v>
+        <v>6031</v>
       </c>
       <c r="AC19" t="s">
-        <v>6048</v>
+        <v>6053</v>
       </c>
       <c r="AF19" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="AI19" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="AU19" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
       <c r="BA19" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93697,37 +93813,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
       <c r="D20" t="s">
+        <v>6059</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6060</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6061</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6062</v>
+      </c>
+      <c r="W20" t="s">
         <v>6054</v>
       </c>
-      <c r="H20" t="s">
-        <v>6055</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6056</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6057</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6049</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
       <c r="AC20" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
       <c r="AF20" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="AU20" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="BA20" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93735,37 +93851,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="D21" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="H21" t="s">
+        <v>6069</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6070</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6071</v>
+      </c>
+      <c r="W21" t="s">
         <v>6064</v>
       </c>
-      <c r="N21" t="s">
-        <v>6065</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6066</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6059</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="AC21" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="AF21" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AU21" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="BA21" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93776,13 +93892,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93791,16 +93907,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
       <c r="AC22" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
       <c r="AF22" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="AU22" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93808,25 +93924,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="H23" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="T23" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="Z23" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="AC23" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="AF23" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="AU23" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93834,89 +93950,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="T24" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="Z24" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="AC24" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="AF24" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="D25" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="T25" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="AC25" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="AF25" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
       <c r="AC26" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="AF26" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="AC27" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="AF27" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="AC28" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="AF28" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -93926,22 +94042,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -93951,7 +94067,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -93959,7 +94075,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -93974,7 +94090,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -93992,227 +94108,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="Q41" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="T41" t="s">
-        <v>6001</v>
+        <v>6006</v>
       </c>
       <c r="W41" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="AL41" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="AO41" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AR41" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="Q42" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="T42" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="W42" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="AC42" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AL42" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="AO42" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="AR42" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="K43" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="N43" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="Q43" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="T43" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="W43" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="Z43" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="AC43" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="AF43" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AL43" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
       <c r="AO43" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
       <c r="AR43" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="F44" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="N44" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="Q44" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="W44" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="Z44" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
       <c r="AC44" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="AF44" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="AL44" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="AO44" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="AR44" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="F45" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="N45" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="Q45" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94221,103 +94337,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="AF45" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="AO45" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="AR45" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="F46" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="N46" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="AC46" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="AF46" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="AO46" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="AR46" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="F47" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="AC47" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="AF47" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="AO47" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="AR47" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="F48" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94329,141 +94445,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="AF48" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="AO48" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="AR48" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
       <c r="AF49" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="AR49" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="F50" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="AR50" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="F51" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="AR51" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
       <c r="AR52" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="F53" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
       <c r="F54" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="F55" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94471,10 +94587,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="F56" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94482,18 +94598,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="F57" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
       <c r="F58" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94501,42 +94617,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="F59" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="F60" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="F61" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="F62" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="F63" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94544,181 +94660,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="F64" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="F65" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="F66" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="F67" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="F68" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="F69" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6002</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
     </row>
   </sheetData>
@@ -94745,10 +94861,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94757,13 +94873,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94771,13 +94887,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94789,13 +94905,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94806,19 +94922,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="S10" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
       <c r="T10" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94832,15 +94948,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="S11" t="s">
-        <v>6006</v>
+        <v>6011</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94849,18 +94965,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94869,7 +94985,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94880,13 +94996,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -94897,7 +95013,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -94906,10 +95022,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="T15" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -94920,12 +95036,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -94933,22 +95049,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -94959,39 +95075,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
       <c r="H32" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="K32" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="N32" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
       <c r="Q32" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
       <c r="S32" t="s">
-        <v>6030</v>
+        <v>6035</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95000,13 +95116,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
       <c r="K33" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
       <c r="N33" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95014,153 +95130,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="K34" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
       <c r="N34" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
       <c r="N35" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
       <c r="N36" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="N37" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
       <c r="N38" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95168,7 +95284,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95184,7 +95300,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95200,21 +95316,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="J68" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95223,52 +95339,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5975</v>
+        <v>5980</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95330,7 +95446,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95338,10 +95454,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95349,7 +95465,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95362,15 +95478,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
       <c r="F17" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3369</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3373</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13617" uniqueCount="6362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13625" uniqueCount="6365">
   <si>
     <t>名称</t>
   </si>
@@ -20552,6 +20552,15 @@
   </si>
   <si>
     <t>寻找情绪一致的用户</t>
+  </si>
+  <si>
+    <t>众数频率字符</t>
+  </si>
+  <si>
+    <t>替换至多一个元素后最长非递减子数组</t>
+  </si>
+  <si>
+    <t>前缀缀分解</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22211,6 +22220,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22220,13 +22236,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93292,7 +93301,9 @@
       <c r="B3373" t="s">
         <v>5972</v>
       </c>
-      <c r="C3373" s="2"/>
+      <c r="C3373" s="2">
+        <v>46100</v>
+      </c>
       <c r="D3373" t="s">
         <v>145</v>
       </c>
@@ -93301,10 +93312,50 @@
       </c>
     </row>
     <row r="3374" spans="1:8">
-      <c r="C3374" s="2"/>
+      <c r="A3374">
+        <v>3692</v>
+      </c>
+      <c r="B3374" t="s">
+        <v>5973</v>
+      </c>
+      <c r="C3374" s="2">
+        <v>46100</v>
+      </c>
+      <c r="D3374" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3374" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3374">
+        <v>1384</v>
+      </c>
+      <c r="G3374" s="1" t="s">
+        <v>2414</v>
+      </c>
     </row>
     <row r="3375" spans="1:8">
-      <c r="C3375" s="2"/>
+      <c r="A3375">
+        <v>3738</v>
+      </c>
+      <c r="B3375" t="s">
+        <v>5974</v>
+      </c>
+      <c r="C3375" s="2">
+        <v>46100</v>
+      </c>
+      <c r="D3375" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3375" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3375">
+        <v>1811</v>
+      </c>
+      <c r="G3375" s="1" t="s">
+        <v>5975</v>
+      </c>
     </row>
     <row r="3376" spans="1:8">
       <c r="C3376" s="2"/>
@@ -93323,7 +93374,7 @@
         <v>3454</v>
       </c>
       <c r="B3382" t="s">
-        <v>5973</v>
+        <v>5976</v>
       </c>
       <c r="D3382" t="s">
         <v>135</v>
@@ -93343,7 +93394,7 @@
         <v>3562</v>
       </c>
       <c r="B3383" t="s">
-        <v>5974</v>
+        <v>5977</v>
       </c>
       <c r="D3383" t="s">
         <v>135</v>
@@ -93354,10 +93405,10 @@
     </row>
     <row r="3384" spans="1:7">
       <c r="A3384" t="s">
-        <v>5975</v>
+        <v>5978</v>
       </c>
       <c r="B3384" t="s">
-        <v>5976</v>
+        <v>5979</v>
       </c>
       <c r="D3384" t="s">
         <v>135</v>
@@ -93368,7 +93419,7 @@
         <v>3721</v>
       </c>
       <c r="B3385" t="s">
-        <v>5977</v>
+        <v>5980</v>
       </c>
       <c r="D3385" t="s">
         <v>135</v>
@@ -93381,7 +93432,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3369" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3373" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93428,10 +93479,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5978</v>
+        <v>5981</v>
       </c>
       <c r="D5" t="s">
-        <v>5979</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93442,13 +93493,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5981</v>
+        <v>5984</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93457,7 +93508,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5982</v>
+        <v>5985</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93472,16 +93523,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5983</v>
+        <v>5986</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5984</v>
+        <v>5987</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5985</v>
+        <v>5988</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93495,10 +93546,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5986</v>
+        <v>5989</v>
       </c>
       <c r="H14" t="s">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93513,16 +93564,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5988</v>
+        <v>5991</v>
       </c>
       <c r="W14" t="s">
-        <v>5989</v>
+        <v>5992</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5990</v>
+        <v>5993</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93534,158 +93585,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5992</v>
+        <v>5995</v>
       </c>
       <c r="AL14" t="s">
-        <v>5993</v>
+        <v>5996</v>
       </c>
       <c r="AO14" t="s">
-        <v>5994</v>
+        <v>5997</v>
       </c>
       <c r="AR14" t="s">
-        <v>5995</v>
+        <v>5998</v>
       </c>
       <c r="AU14" t="s">
-        <v>5996</v>
+        <v>5999</v>
       </c>
       <c r="AX14" t="s">
-        <v>5997</v>
+        <v>6000</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>5998</v>
+        <v>6001</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>5999</v>
+        <v>6002</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6000</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6001</v>
+        <v>6004</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="T15" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="W15" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
       <c r="Z15" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="AF15" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AI15" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="AL15" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="AU15" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="AX15" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="H16" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="N16" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="T16" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="W16" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="Z16" t="s">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="AC16" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="AF16" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="AI16" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="AL16" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
       <c r="AR16" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="AU16" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
       <c r="AX16" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93693,43 +93744,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="D17" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="H17" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="N17" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="T17" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="W17" t="s">
-        <v>5991</v>
+        <v>5994</v>
       </c>
       <c r="Z17" t="s">
-        <v>6002</v>
+        <v>6005</v>
       </c>
       <c r="AC17" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="AF17" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AI17" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="AR17" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="AU17" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="BA17" t="s">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93737,37 +93788,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="H18" t="s">
-        <v>6040</v>
+        <v>6043</v>
       </c>
       <c r="N18" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="T18" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="W18" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="Z18" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="AC18" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="AF18" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
       <c r="AI18" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="AU18" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="BA18" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93775,37 +93826,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="H19" t="s">
-        <v>6050</v>
+        <v>6053</v>
       </c>
       <c r="N19" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="T19" t="s">
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="W19" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="Z19" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="AC19" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="AF19" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="AI19" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="AU19" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="BA19" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93813,37 +93864,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="D20" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
       <c r="H20" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="N20" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="T20" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
       <c r="W20" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="Z20" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="AC20" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="AF20" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="AU20" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="BA20" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93851,37 +93902,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6070</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6071</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6072</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6073</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6074</v>
+      </c>
+      <c r="W21" t="s">
         <v>6067</v>
       </c>
-      <c r="D21" t="s">
-        <v>6068</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6069</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6070</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6071</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6064</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="AC21" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="AF21" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="AU21" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="BA21" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93892,13 +93943,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93907,16 +93958,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="AC22" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="AF22" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
       <c r="AU22" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93924,25 +93975,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="H23" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="T23" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="Z23" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="AC23" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="AF23" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="AU23" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -93950,89 +94001,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="T24" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="Z24" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="AC24" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
       <c r="AF24" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="D25" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
       <c r="T25" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
       <c r="AC25" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AF25" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="AC26" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="AF26" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="AC27" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="AF27" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="AC28" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="AF28" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94042,22 +94093,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94067,7 +94118,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -94075,7 +94126,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -94090,7 +94141,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -94108,227 +94159,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="Q41" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="T41" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="W41" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="AL41" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="AO41" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
       <c r="AR41" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="Q42" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="T42" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="W42" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="AC42" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="AL42" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="AO42" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="AR42" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="K43" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="N43" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
       <c r="Q43" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="T43" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="W43" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="Z43" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="AC43" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="AF43" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AL43" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="AO43" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
       <c r="AR43" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="F44" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="N44" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="Q44" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="W44" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="Z44" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="AC44" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="AF44" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AL44" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="AO44" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
       <c r="AR44" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="F45" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="N45" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="Q45" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94337,103 +94388,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="AF45" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="AO45" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="AR45" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="F46" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
       <c r="N46" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="AC46" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="AF46" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="AO46" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="AR46" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="F47" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="AC47" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="AF47" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="AO47" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
       <c r="AR47" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="F48" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94445,141 +94496,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="AF48" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="AO48" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
       <c r="AR48" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
       <c r="AF49" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="AR49" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="F50" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
       <c r="AR50" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
       <c r="F51" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
       <c r="AR51" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="AR52" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
       <c r="F53" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
       <c r="F54" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
       <c r="F55" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94587,10 +94638,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="F56" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94598,18 +94649,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
       <c r="F57" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="F58" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94617,42 +94668,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
       <c r="F59" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
       <c r="F60" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
       <c r="F61" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
       <c r="F62" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
       <c r="F63" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94660,181 +94711,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
       <c r="F64" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="F65" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
       <c r="F66" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
       <c r="F67" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
       <c r="F68" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="F69" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
     </row>
   </sheetData>
@@ -94861,10 +94912,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94873,13 +94924,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94887,13 +94938,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94905,13 +94956,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94922,19 +94973,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
       <c r="S10" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
       <c r="T10" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94948,15 +94999,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="S11" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -94965,18 +95016,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -94985,7 +95036,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -94996,13 +95047,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95013,7 +95064,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95022,10 +95073,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="T15" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95036,12 +95087,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95049,22 +95100,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95075,39 +95126,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="H32" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
       <c r="K32" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="N32" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
       <c r="Q32" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
       <c r="S32" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95116,13 +95167,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
       <c r="K33" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
       <c r="N33" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95130,153 +95181,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
       <c r="K34" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
       <c r="N34" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
       <c r="N35" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
       <c r="N36" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
       <c r="N37" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="N38" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95284,7 +95335,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95300,7 +95351,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95316,21 +95367,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="J68" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95339,52 +95390,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6350</v>
+        <v>6353</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5980</v>
+        <v>5983</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6351</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6352</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6353</v>
+        <v>6356</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6354</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95446,7 +95497,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6355</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95454,10 +95505,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6356</v>
+        <v>6359</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6357</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95465,7 +95516,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6358</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95478,15 +95529,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6359</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6360</v>
+        <v>6363</v>
       </c>
       <c r="F17" t="s">
-        <v>6361</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3379</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13625" uniqueCount="6365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13651" uniqueCount="6375">
   <si>
     <t>名称</t>
   </si>
@@ -20561,6 +20561,36 @@
   </si>
   <si>
     <t>前缀缀分解</t>
+  </si>
+  <si>
+    <t>计算十进制表示</t>
+  </si>
+  <si>
+    <t>LCR 074</t>
+  </si>
+  <si>
+    <t>同56题</t>
+  </si>
+  <si>
+    <t>字典序最小和为目标值且绝对值是排列的数组</t>
+  </si>
+  <si>
+    <t>查找具有持续行为模式的用户</t>
+  </si>
+  <si>
+    <t>统计每一行选择互质整数的方案数</t>
+  </si>
+  <si>
+    <t>位运算 + 记忆化搜索</t>
+  </si>
+  <si>
+    <t>105(3400题)</t>
+  </si>
+  <si>
+    <t>生成赛程</t>
+  </si>
+  <si>
+    <t>难度太大</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22220,8 +22250,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22233,9 +22264,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23187,7 +23217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3385"/>
+  <dimension ref="A1:N3395"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -93358,81 +93388,253 @@
       </c>
     </row>
     <row r="3376" spans="1:8">
-      <c r="C3376" s="2"/>
-    </row>
-    <row r="3377" spans="1:7">
-      <c r="C3377" s="2"/>
-    </row>
-    <row r="3378" spans="1:7">
-      <c r="C3378" s="2"/>
-    </row>
-    <row r="3379" spans="1:7">
-      <c r="C3379" s="2"/>
-    </row>
-    <row r="3382" spans="1:7">
-      <c r="A3382">
+      <c r="A3376">
+        <v>3697</v>
+      </c>
+      <c r="B3376" t="s">
+        <v>5976</v>
+      </c>
+      <c r="C3376" s="2">
+        <v>46101</v>
+      </c>
+      <c r="D3376" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3376" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3376">
+        <v>1250</v>
+      </c>
+      <c r="G3376" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="3377" spans="1:14">
+      <c r="A3377" t="s">
+        <v>5977</v>
+      </c>
+      <c r="B3377" t="s">
+        <v>410</v>
+      </c>
+      <c r="C3377" s="2">
+        <v>46101</v>
+      </c>
+      <c r="D3377" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3377" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3377" s="1" t="s">
+        <v>5978</v>
+      </c>
+    </row>
+    <row r="3378" spans="1:14">
+      <c r="A3378">
+        <v>3752</v>
+      </c>
+      <c r="B3378" t="s">
+        <v>5979</v>
+      </c>
+      <c r="C3378" s="2">
+        <v>46101</v>
+      </c>
+      <c r="D3378" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3378" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3378">
+        <v>1827</v>
+      </c>
+      <c r="G3378" s="1" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="3379" spans="1:14">
+      <c r="A3379">
+        <v>3832</v>
+      </c>
+      <c r="B3379" t="s">
+        <v>5980</v>
+      </c>
+      <c r="C3379" s="2">
+        <v>46102</v>
+      </c>
+      <c r="D3379" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3379" s="1" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="3380" spans="1:14">
+      <c r="A3380">
+        <v>3725</v>
+      </c>
+      <c r="B3380" t="s">
+        <v>5981</v>
+      </c>
+      <c r="C3380" s="2">
+        <v>46102</v>
+      </c>
+      <c r="D3380" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3380" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3380">
+        <v>1981</v>
+      </c>
+      <c r="G3380" s="1" t="s">
+        <v>5982</v>
+      </c>
+      <c r="J3380" t="s">
+        <v>5983</v>
+      </c>
+      <c r="K3380">
+        <v>2242</v>
+      </c>
+      <c r="L3380">
+        <v>5589</v>
+      </c>
+      <c r="M3380">
+        <v>2250</v>
+      </c>
+      <c r="N3380" s="17">
+        <v>0.0144</v>
+      </c>
+    </row>
+    <row r="3381" spans="1:14">
+      <c r="A3381">
+        <v>3680</v>
+      </c>
+      <c r="B3381" t="s">
+        <v>5984</v>
+      </c>
+      <c r="C3381" s="2">
+        <v>46102</v>
+      </c>
+      <c r="D3381" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3381" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3381">
+        <v>2377</v>
+      </c>
+      <c r="G3381" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="H3381" s="1" t="s">
+        <v>5985</v>
+      </c>
+      <c r="N3381" s="17"/>
+    </row>
+    <row r="3382" spans="1:14">
+      <c r="C3382" s="2"/>
+      <c r="N3382" s="17"/>
+    </row>
+    <row r="3383" spans="1:14">
+      <c r="C3383" s="2"/>
+      <c r="N3383" s="17"/>
+    </row>
+    <row r="3384" spans="1:14">
+      <c r="C3384" s="2"/>
+      <c r="N3384" s="17"/>
+    </row>
+    <row r="3385" spans="1:14">
+      <c r="C3385" s="2"/>
+      <c r="N3385" s="17"/>
+    </row>
+    <row r="3386" spans="1:14">
+      <c r="C3386" s="2"/>
+      <c r="N3386" s="17"/>
+    </row>
+    <row r="3387" spans="1:14">
+      <c r="C3387" s="2"/>
+      <c r="N3387" s="17"/>
+    </row>
+    <row r="3388" spans="1:14">
+      <c r="C3388" s="2"/>
+      <c r="N3388" s="17"/>
+    </row>
+    <row r="3389" spans="1:14">
+      <c r="C3389" s="2"/>
+      <c r="N3389" s="17"/>
+    </row>
+    <row r="3390" spans="1:14">
+      <c r="C3390" s="2"/>
+      <c r="N3390" s="17"/>
+    </row>
+    <row r="3392" spans="1:14">
+      <c r="A3392">
         <v>3454</v>
       </c>
-      <c r="B3382" t="s">
-        <v>5976</v>
-      </c>
-      <c r="D3382" t="s">
+      <c r="B3392" t="s">
+        <v>5986</v>
+      </c>
+      <c r="D3392" t="s">
         <v>135</v>
       </c>
-      <c r="E3382" t="s">
+      <c r="E3392" t="s">
         <v>73</v>
       </c>
-      <c r="F3382">
+      <c r="F3392">
         <v>2671</v>
       </c>
-      <c r="G3382" s="1" t="s">
+      <c r="G3392" s="1" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="3383" spans="1:7">
-      <c r="A3383">
+    <row r="3393" spans="1:6">
+      <c r="A3393">
         <v>3562</v>
       </c>
-      <c r="B3383" t="s">
-        <v>5977</v>
-      </c>
-      <c r="D3383" t="s">
+      <c r="B3393" t="s">
+        <v>5987</v>
+      </c>
+      <c r="D3393" t="s">
         <v>135</v>
       </c>
-      <c r="F3383">
+      <c r="F3393">
         <v>2458</v>
       </c>
     </row>
-    <row r="3384" spans="1:7">
-      <c r="A3384" t="s">
-        <v>5978</v>
-      </c>
-      <c r="B3384" t="s">
-        <v>5979</v>
-      </c>
-      <c r="D3384" t="s">
+    <row r="3394" spans="1:6">
+      <c r="A3394" t="s">
+        <v>5988</v>
+      </c>
+      <c r="B3394" t="s">
+        <v>5989</v>
+      </c>
+      <c r="D3394" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="3385" spans="1:7">
-      <c r="A3385">
+    <row r="3395" spans="1:6">
+      <c r="A3395">
         <v>3721</v>
       </c>
-      <c r="B3385" t="s">
-        <v>5980</v>
-      </c>
-      <c r="D3385" t="s">
+      <c r="B3395" t="s">
+        <v>5990</v>
+      </c>
+      <c r="D3395" t="s">
         <v>135</v>
       </c>
-      <c r="E3385" t="s">
+      <c r="E3395" t="s">
         <v>73</v>
       </c>
-      <c r="F3385">
+      <c r="F3395">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3373" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3379" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93479,10 +93681,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5981</v>
+        <v>5991</v>
       </c>
       <c r="D5" t="s">
-        <v>5982</v>
+        <v>5992</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93493,13 +93695,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5983</v>
+        <v>5993</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5984</v>
+        <v>5994</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93508,7 +93710,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5985</v>
+        <v>5995</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93523,16 +93725,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5986</v>
+        <v>5996</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5987</v>
+        <v>5997</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5988</v>
+        <v>5998</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93546,10 +93748,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5989</v>
+        <v>5999</v>
       </c>
       <c r="H14" t="s">
-        <v>5990</v>
+        <v>6000</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93564,16 +93766,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>5991</v>
+        <v>6001</v>
       </c>
       <c r="W14" t="s">
-        <v>5992</v>
+        <v>6002</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>5993</v>
+        <v>6003</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93585,158 +93787,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>5994</v>
+        <v>6004</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>5995</v>
+        <v>6005</v>
       </c>
       <c r="AL14" t="s">
-        <v>5996</v>
+        <v>6006</v>
       </c>
       <c r="AO14" t="s">
-        <v>5997</v>
+        <v>6007</v>
       </c>
       <c r="AR14" t="s">
-        <v>5998</v>
+        <v>6008</v>
       </c>
       <c r="AU14" t="s">
-        <v>5999</v>
+        <v>6009</v>
       </c>
       <c r="AX14" t="s">
-        <v>6000</v>
+        <v>6010</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6001</v>
+        <v>6011</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6002</v>
+        <v>6012</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6003</v>
+        <v>6013</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6004</v>
+        <v>6014</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>6005</v>
+        <v>6015</v>
       </c>
       <c r="T15" t="s">
-        <v>6006</v>
+        <v>6016</v>
       </c>
       <c r="W15" t="s">
-        <v>6007</v>
+        <v>6017</v>
       </c>
       <c r="Z15" t="s">
-        <v>6008</v>
+        <v>6018</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6009</v>
+        <v>6019</v>
       </c>
       <c r="AF15" t="s">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="AI15" t="s">
-        <v>6011</v>
+        <v>6021</v>
       </c>
       <c r="AL15" t="s">
-        <v>6012</v>
+        <v>6022</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6013</v>
+        <v>6023</v>
       </c>
       <c r="AU15" t="s">
-        <v>6014</v>
+        <v>6024</v>
       </c>
       <c r="AX15" t="s">
-        <v>6015</v>
+        <v>6025</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6016</v>
+        <v>6026</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6017</v>
+        <v>6027</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6018</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6019</v>
+        <v>6029</v>
       </c>
       <c r="H16" t="s">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="N16" t="s">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="T16" t="s">
+        <v>6032</v>
+      </c>
+      <c r="W16" t="s">
+        <v>6033</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>6034</v>
+      </c>
+      <c r="AC16" t="s">
         <v>6022</v>
       </c>
-      <c r="W16" t="s">
-        <v>6023</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>6024</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>6012</v>
-      </c>
       <c r="AF16" t="s">
-        <v>5994</v>
+        <v>6004</v>
       </c>
       <c r="AI16" t="s">
-        <v>6025</v>
+        <v>6035</v>
       </c>
       <c r="AL16" t="s">
-        <v>6026</v>
+        <v>6036</v>
       </c>
       <c r="AR16" t="s">
-        <v>6027</v>
+        <v>6037</v>
       </c>
       <c r="AU16" t="s">
-        <v>6028</v>
+        <v>6038</v>
       </c>
       <c r="AX16" t="s">
-        <v>6029</v>
+        <v>6039</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6030</v>
+        <v>6040</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93744,43 +93946,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6031</v>
+        <v>6041</v>
       </c>
       <c r="D17" t="s">
-        <v>6032</v>
+        <v>6042</v>
       </c>
       <c r="H17" t="s">
-        <v>6033</v>
+        <v>6043</v>
       </c>
       <c r="N17" t="s">
-        <v>6034</v>
+        <v>6044</v>
       </c>
       <c r="T17" t="s">
-        <v>6035</v>
+        <v>6045</v>
       </c>
       <c r="W17" t="s">
-        <v>5994</v>
+        <v>6004</v>
       </c>
       <c r="Z17" t="s">
-        <v>6005</v>
+        <v>6015</v>
       </c>
       <c r="AC17" t="s">
-        <v>6036</v>
+        <v>6046</v>
       </c>
       <c r="AF17" t="s">
-        <v>6037</v>
+        <v>6047</v>
       </c>
       <c r="AI17" t="s">
-        <v>6038</v>
+        <v>6048</v>
       </c>
       <c r="AR17" t="s">
-        <v>6039</v>
+        <v>6049</v>
       </c>
       <c r="AU17" t="s">
-        <v>6040</v>
+        <v>6050</v>
       </c>
       <c r="BA17" t="s">
-        <v>6041</v>
+        <v>6051</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93788,37 +93990,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6042</v>
+        <v>6052</v>
       </c>
       <c r="H18" t="s">
-        <v>6043</v>
+        <v>6053</v>
       </c>
       <c r="N18" t="s">
-        <v>6044</v>
+        <v>6054</v>
       </c>
       <c r="T18" t="s">
-        <v>6045</v>
+        <v>6055</v>
       </c>
       <c r="W18" t="s">
-        <v>6046</v>
+        <v>6056</v>
       </c>
       <c r="Z18" t="s">
-        <v>6021</v>
+        <v>6031</v>
       </c>
       <c r="AC18" t="s">
-        <v>6047</v>
+        <v>6057</v>
       </c>
       <c r="AF18" t="s">
-        <v>6048</v>
+        <v>6058</v>
       </c>
       <c r="AI18" t="s">
-        <v>6049</v>
+        <v>6059</v>
       </c>
       <c r="AU18" t="s">
-        <v>6050</v>
+        <v>6060</v>
       </c>
       <c r="BA18" t="s">
-        <v>6051</v>
+        <v>6061</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -93826,37 +94028,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6052</v>
+        <v>6062</v>
       </c>
       <c r="H19" t="s">
-        <v>6053</v>
+        <v>6063</v>
       </c>
       <c r="N19" t="s">
-        <v>6054</v>
+        <v>6064</v>
       </c>
       <c r="T19" t="s">
-        <v>6055</v>
+        <v>6065</v>
       </c>
       <c r="W19" t="s">
-        <v>6029</v>
+        <v>6039</v>
       </c>
       <c r="Z19" t="s">
-        <v>6034</v>
+        <v>6044</v>
       </c>
       <c r="AC19" t="s">
-        <v>6056</v>
+        <v>6066</v>
       </c>
       <c r="AF19" t="s">
-        <v>6057</v>
+        <v>6067</v>
       </c>
       <c r="AI19" t="s">
-        <v>6058</v>
+        <v>6068</v>
       </c>
       <c r="AU19" t="s">
-        <v>6059</v>
+        <v>6069</v>
       </c>
       <c r="BA19" t="s">
-        <v>6060</v>
+        <v>6070</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -93864,37 +94066,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6061</v>
+        <v>6071</v>
       </c>
       <c r="D20" t="s">
-        <v>6062</v>
+        <v>6072</v>
       </c>
       <c r="H20" t="s">
-        <v>6063</v>
+        <v>6073</v>
       </c>
       <c r="N20" t="s">
-        <v>6064</v>
+        <v>6074</v>
       </c>
       <c r="T20" t="s">
-        <v>6065</v>
+        <v>6075</v>
       </c>
       <c r="W20" t="s">
-        <v>6057</v>
+        <v>6067</v>
       </c>
       <c r="Z20" t="s">
-        <v>6044</v>
+        <v>6054</v>
       </c>
       <c r="AC20" t="s">
-        <v>6066</v>
+        <v>6076</v>
       </c>
       <c r="AF20" t="s">
-        <v>6067</v>
+        <v>6077</v>
       </c>
       <c r="AU20" t="s">
-        <v>6068</v>
+        <v>6078</v>
       </c>
       <c r="BA20" t="s">
-        <v>6069</v>
+        <v>6079</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -93902,37 +94104,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6070</v>
+        <v>6080</v>
       </c>
       <c r="D21" t="s">
-        <v>6071</v>
+        <v>6081</v>
       </c>
       <c r="H21" t="s">
-        <v>6072</v>
+        <v>6082</v>
       </c>
       <c r="N21" t="s">
-        <v>6073</v>
+        <v>6083</v>
       </c>
       <c r="T21" t="s">
-        <v>6074</v>
+        <v>6084</v>
       </c>
       <c r="W21" t="s">
-        <v>6067</v>
+        <v>6077</v>
       </c>
       <c r="Z21" t="s">
-        <v>6054</v>
+        <v>6064</v>
       </c>
       <c r="AC21" t="s">
-        <v>6075</v>
+        <v>6085</v>
       </c>
       <c r="AF21" t="s">
-        <v>6076</v>
+        <v>6086</v>
       </c>
       <c r="AU21" t="s">
-        <v>6077</v>
+        <v>6087</v>
       </c>
       <c r="BA21" t="s">
-        <v>6078</v>
+        <v>6088</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -93943,13 +94145,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6079</v>
+        <v>6089</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6080</v>
+        <v>6090</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -93958,16 +94160,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6064</v>
+        <v>6074</v>
       </c>
       <c r="AC22" t="s">
-        <v>6081</v>
+        <v>6091</v>
       </c>
       <c r="AF22" t="s">
-        <v>6082</v>
+        <v>6092</v>
       </c>
       <c r="AU22" t="s">
-        <v>6083</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -93975,25 +94177,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6084</v>
+        <v>6094</v>
       </c>
       <c r="H23" t="s">
-        <v>6085</v>
+        <v>6095</v>
       </c>
       <c r="T23" t="s">
-        <v>6086</v>
+        <v>6096</v>
       </c>
       <c r="Z23" t="s">
-        <v>6073</v>
+        <v>6083</v>
       </c>
       <c r="AC23" t="s">
-        <v>6087</v>
+        <v>6097</v>
       </c>
       <c r="AF23" t="s">
-        <v>6088</v>
+        <v>6098</v>
       </c>
       <c r="AU23" t="s">
-        <v>6089</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94001,89 +94203,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6090</v>
+        <v>6100</v>
       </c>
       <c r="T24" t="s">
-        <v>6091</v>
+        <v>6101</v>
       </c>
       <c r="Z24" t="s">
-        <v>6092</v>
+        <v>6102</v>
       </c>
       <c r="AC24" t="s">
-        <v>6093</v>
+        <v>6103</v>
       </c>
       <c r="AF24" t="s">
-        <v>6094</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6095</v>
+        <v>6105</v>
       </c>
       <c r="D25" t="s">
-        <v>6096</v>
+        <v>6106</v>
       </c>
       <c r="T25" t="s">
-        <v>6097</v>
+        <v>6107</v>
       </c>
       <c r="AC25" t="s">
-        <v>6098</v>
+        <v>6108</v>
       </c>
       <c r="AF25" t="s">
-        <v>6099</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6100</v>
+        <v>6110</v>
       </c>
       <c r="AC26" t="s">
-        <v>6101</v>
+        <v>6111</v>
       </c>
       <c r="AF26" t="s">
-        <v>6102</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6103</v>
+        <v>6113</v>
       </c>
       <c r="AC27" t="s">
-        <v>6104</v>
+        <v>6114</v>
       </c>
       <c r="AF27" t="s">
-        <v>6105</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6106</v>
+        <v>6116</v>
       </c>
       <c r="AC28" t="s">
-        <v>6107</v>
+        <v>6117</v>
       </c>
       <c r="AF28" t="s">
-        <v>6108</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6109</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6110</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6111</v>
+        <v>6121</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6112</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94093,22 +94295,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6113</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6114</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6115</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6116</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94118,7 +94320,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6117</v>
+        <v>6127</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -94126,7 +94328,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6118</v>
+        <v>6128</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -94141,7 +94343,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6119</v>
+        <v>6129</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -94159,227 +94361,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6120</v>
+        <v>6130</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6121</v>
+        <v>6131</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6122</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6123</v>
+        <v>6133</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6124</v>
+        <v>6134</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6125</v>
+        <v>6135</v>
       </c>
       <c r="Q41" t="s">
-        <v>6113</v>
+        <v>6123</v>
       </c>
       <c r="T41" t="s">
-        <v>6009</v>
+        <v>6019</v>
       </c>
       <c r="W41" t="s">
-        <v>6126</v>
+        <v>6136</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6127</v>
+        <v>6137</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6128</v>
+        <v>6138</v>
       </c>
       <c r="AL41" t="s">
-        <v>6129</v>
+        <v>6139</v>
       </c>
       <c r="AO41" t="s">
-        <v>6130</v>
+        <v>6140</v>
       </c>
       <c r="AR41" t="s">
-        <v>6131</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6132</v>
+        <v>6142</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6133</v>
+        <v>6143</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6134</v>
+        <v>6144</v>
       </c>
       <c r="Q42" t="s">
-        <v>6114</v>
+        <v>6124</v>
       </c>
       <c r="T42" t="s">
-        <v>6135</v>
+        <v>6145</v>
       </c>
       <c r="W42" t="s">
-        <v>6136</v>
+        <v>6146</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6137</v>
+        <v>6147</v>
       </c>
       <c r="AC42" t="s">
-        <v>6138</v>
+        <v>6148</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6139</v>
+        <v>6149</v>
       </c>
       <c r="AL42" t="s">
-        <v>6140</v>
+        <v>6150</v>
       </c>
       <c r="AO42" t="s">
-        <v>6141</v>
+        <v>6151</v>
       </c>
       <c r="AR42" t="s">
-        <v>6142</v>
+        <v>6152</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6143</v>
+        <v>6153</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6144</v>
+        <v>6154</v>
       </c>
       <c r="K43" t="s">
-        <v>6145</v>
+        <v>6155</v>
       </c>
       <c r="N43" t="s">
-        <v>6146</v>
+        <v>6156</v>
       </c>
       <c r="Q43" t="s">
-        <v>6115</v>
+        <v>6125</v>
       </c>
       <c r="T43" t="s">
-        <v>6147</v>
+        <v>6157</v>
       </c>
       <c r="W43" t="s">
-        <v>6148</v>
+        <v>6158</v>
       </c>
       <c r="Z43" t="s">
-        <v>6149</v>
+        <v>6159</v>
       </c>
       <c r="AC43" t="s">
-        <v>6150</v>
+        <v>6160</v>
       </c>
       <c r="AF43" t="s">
-        <v>6151</v>
+        <v>6161</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6152</v>
+        <v>6162</v>
       </c>
       <c r="AL43" t="s">
-        <v>6061</v>
+        <v>6071</v>
       </c>
       <c r="AO43" t="s">
-        <v>6153</v>
+        <v>6163</v>
       </c>
       <c r="AR43" t="s">
-        <v>6154</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6155</v>
+        <v>6165</v>
       </c>
       <c r="F44" t="s">
-        <v>6156</v>
+        <v>6166</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6157</v>
+        <v>6167</v>
       </c>
       <c r="N44" t="s">
-        <v>6158</v>
+        <v>6168</v>
       </c>
       <c r="Q44" t="s">
-        <v>6116</v>
+        <v>6126</v>
       </c>
       <c r="W44" t="s">
-        <v>6159</v>
+        <v>6169</v>
       </c>
       <c r="Z44" t="s">
-        <v>6160</v>
+        <v>6170</v>
       </c>
       <c r="AC44" t="s">
-        <v>6161</v>
+        <v>6171</v>
       </c>
       <c r="AF44" t="s">
-        <v>6098</v>
+        <v>6108</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6162</v>
+        <v>6172</v>
       </c>
       <c r="AL44" t="s">
-        <v>6163</v>
+        <v>6173</v>
       </c>
       <c r="AO44" t="s">
-        <v>6164</v>
+        <v>6174</v>
       </c>
       <c r="AR44" t="s">
-        <v>6165</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6166</v>
+        <v>6176</v>
       </c>
       <c r="F45" t="s">
-        <v>6167</v>
+        <v>6177</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6168</v>
+        <v>6178</v>
       </c>
       <c r="N45" t="s">
-        <v>6169</v>
+        <v>6179</v>
       </c>
       <c r="Q45" t="s">
-        <v>6170</v>
+        <v>6180</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94388,103 +94590,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6171</v>
+        <v>6181</v>
       </c>
       <c r="AF45" t="s">
-        <v>6172</v>
+        <v>6182</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6173</v>
+        <v>6183</v>
       </c>
       <c r="AO45" t="s">
-        <v>6174</v>
+        <v>6184</v>
       </c>
       <c r="AR45" t="s">
-        <v>6175</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6176</v>
+        <v>6186</v>
       </c>
       <c r="F46" t="s">
-        <v>6177</v>
+        <v>6187</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6178</v>
+        <v>6188</v>
       </c>
       <c r="N46" t="s">
-        <v>6179</v>
+        <v>6189</v>
       </c>
       <c r="AC46" t="s">
-        <v>6180</v>
+        <v>6190</v>
       </c>
       <c r="AF46" t="s">
-        <v>6181</v>
+        <v>6191</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6182</v>
+        <v>6192</v>
       </c>
       <c r="AO46" t="s">
-        <v>6183</v>
+        <v>6193</v>
       </c>
       <c r="AR46" t="s">
-        <v>6184</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6185</v>
+        <v>6195</v>
       </c>
       <c r="F47" t="s">
-        <v>6186</v>
+        <v>6196</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6187</v>
+        <v>6197</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6188</v>
+        <v>6198</v>
       </c>
       <c r="AC47" t="s">
-        <v>6189</v>
+        <v>6199</v>
       </c>
       <c r="AF47" t="s">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6191</v>
+        <v>6201</v>
       </c>
       <c r="AO47" t="s">
-        <v>6192</v>
+        <v>6202</v>
       </c>
       <c r="AR47" t="s">
-        <v>6193</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6194</v>
+        <v>6204</v>
       </c>
       <c r="F48" t="s">
-        <v>6195</v>
+        <v>6205</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94496,141 +94698,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6196</v>
+        <v>6206</v>
       </c>
       <c r="AF48" t="s">
-        <v>6197</v>
+        <v>6207</v>
       </c>
       <c r="AO48" t="s">
-        <v>6198</v>
+        <v>6208</v>
       </c>
       <c r="AR48" t="s">
-        <v>6199</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6200</v>
+        <v>6210</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6201</v>
+        <v>6211</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6202</v>
+        <v>6212</v>
       </c>
       <c r="AF49" t="s">
-        <v>6203</v>
+        <v>6213</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6204</v>
+        <v>6214</v>
       </c>
       <c r="AR49" t="s">
-        <v>6205</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6206</v>
+        <v>6216</v>
       </c>
       <c r="F50" t="s">
-        <v>6207</v>
+        <v>6217</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6208</v>
+        <v>6218</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6209</v>
+        <v>6219</v>
       </c>
       <c r="AR50" t="s">
-        <v>6210</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6211</v>
+        <v>6221</v>
       </c>
       <c r="F51" t="s">
-        <v>6212</v>
+        <v>6222</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6213</v>
+        <v>6223</v>
       </c>
       <c r="AR51" t="s">
-        <v>6214</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6215</v>
+        <v>6225</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6216</v>
+        <v>6226</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6217</v>
+        <v>6227</v>
       </c>
       <c r="AR52" t="s">
-        <v>6218</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6219</v>
+        <v>6229</v>
       </c>
       <c r="F53" t="s">
-        <v>6220</v>
+        <v>6230</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6221</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6222</v>
+        <v>6232</v>
       </c>
       <c r="F54" t="s">
-        <v>6223</v>
+        <v>6233</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6224</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6225</v>
+        <v>6235</v>
       </c>
       <c r="F55" t="s">
-        <v>6226</v>
+        <v>6236</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94638,10 +94840,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6227</v>
+        <v>6237</v>
       </c>
       <c r="F56" t="s">
-        <v>6228</v>
+        <v>6238</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94649,18 +94851,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6229</v>
+        <v>6239</v>
       </c>
       <c r="F57" t="s">
-        <v>6230</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6231</v>
+        <v>6241</v>
       </c>
       <c r="F58" t="s">
-        <v>6232</v>
+        <v>6242</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94668,42 +94870,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6233</v>
+        <v>6243</v>
       </c>
       <c r="F59" t="s">
-        <v>6234</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6235</v>
+        <v>6245</v>
       </c>
       <c r="F60" t="s">
-        <v>6236</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6237</v>
+        <v>6247</v>
       </c>
       <c r="F61" t="s">
-        <v>6238</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6239</v>
+        <v>6249</v>
       </c>
       <c r="F62" t="s">
-        <v>6240</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6241</v>
+        <v>6251</v>
       </c>
       <c r="F63" t="s">
-        <v>6242</v>
+        <v>6252</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94711,181 +94913,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6243</v>
+        <v>6253</v>
       </c>
       <c r="F64" t="s">
-        <v>6244</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6206</v>
+        <v>6216</v>
       </c>
       <c r="F65" t="s">
-        <v>6197</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6245</v>
+        <v>6255</v>
       </c>
       <c r="F66" t="s">
-        <v>6246</v>
+        <v>6256</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6247</v>
+        <v>6257</v>
       </c>
       <c r="F67" t="s">
-        <v>6248</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6249</v>
+        <v>6259</v>
       </c>
       <c r="F68" t="s">
-        <v>6213</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6250</v>
+        <v>6260</v>
       </c>
       <c r="F69" t="s">
-        <v>6251</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6252</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6253</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6254</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6255</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6256</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6257</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6258</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6259</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6260</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6261</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6262</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6263</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6264</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6265</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6266</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6267</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6268</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6269</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6270</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6271</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6010</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6272</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6273</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6274</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6275</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6276</v>
+        <v>6286</v>
       </c>
     </row>
   </sheetData>
@@ -94912,10 +95114,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6277</v>
+        <v>6287</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6278</v>
+        <v>6288</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -94924,13 +95126,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6279</v>
+        <v>6289</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6280</v>
+        <v>6290</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6281</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -94938,13 +95140,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6282</v>
+        <v>6292</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6283</v>
+        <v>6293</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -94956,13 +95158,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6284</v>
+        <v>6294</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6285</v>
+        <v>6295</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -94973,19 +95175,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6286</v>
+        <v>6296</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6287</v>
+        <v>6297</v>
       </c>
       <c r="S10" t="s">
-        <v>6288</v>
+        <v>6298</v>
       </c>
       <c r="T10" t="s">
-        <v>6289</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -94999,15 +95201,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6290</v>
+        <v>6300</v>
       </c>
       <c r="S11" t="s">
-        <v>6014</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6291</v>
+        <v>6301</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95016,18 +95218,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6292</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6293</v>
+        <v>6303</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6294</v>
+        <v>6304</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -95036,7 +95238,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6295</v>
+        <v>6305</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95047,13 +95249,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6296</v>
+        <v>6306</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6297</v>
+        <v>6307</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95064,7 +95266,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6298</v>
+        <v>6308</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95073,10 +95275,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6181</v>
+        <v>6191</v>
       </c>
       <c r="T15" t="s">
-        <v>6299</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95087,12 +95289,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6300</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6301</v>
+        <v>6311</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95100,22 +95302,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6302</v>
+        <v>6312</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6303</v>
+        <v>6313</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6304</v>
+        <v>6314</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6305</v>
+        <v>6315</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6306</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95126,39 +95328,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6307</v>
+        <v>6317</v>
       </c>
       <c r="H32" t="s">
-        <v>6308</v>
+        <v>6318</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6309</v>
+        <v>6319</v>
       </c>
       <c r="K32" t="s">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="N32" t="s">
-        <v>6311</v>
+        <v>6321</v>
       </c>
       <c r="Q32" t="s">
-        <v>6312</v>
+        <v>6322</v>
       </c>
       <c r="S32" t="s">
-        <v>6038</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6313</v>
+        <v>6323</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6314</v>
+        <v>6324</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95167,13 +95369,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6315</v>
+        <v>6325</v>
       </c>
       <c r="K33" t="s">
-        <v>6316</v>
+        <v>6326</v>
       </c>
       <c r="N33" t="s">
-        <v>6317</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95181,153 +95383,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6318</v>
+        <v>6328</v>
       </c>
       <c r="K34" t="s">
-        <v>6319</v>
+        <v>6329</v>
       </c>
       <c r="N34" t="s">
-        <v>6320</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6321</v>
+        <v>6331</v>
       </c>
       <c r="N35" t="s">
-        <v>6322</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6323</v>
+        <v>6333</v>
       </c>
       <c r="N36" t="s">
-        <v>6324</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6325</v>
+        <v>6335</v>
       </c>
       <c r="N37" t="s">
-        <v>6326</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6327</v>
+        <v>6337</v>
       </c>
       <c r="N38" t="s">
-        <v>6328</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6051</v>
+        <v>6061</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6329</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6330</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6331</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6332</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6333</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6334</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6335</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6336</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6337</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6338</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6228</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6339</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6340</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6226</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6341</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6342</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6343</v>
+        <v>6353</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6344</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6345</v>
+        <v>6355</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6346</v>
+        <v>6356</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95335,7 +95537,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6347</v>
+        <v>6357</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95351,7 +95553,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6348</v>
+        <v>6358</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95367,21 +95569,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6349</v>
+        <v>6359</v>
       </c>
       <c r="J68" t="s">
-        <v>6350</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6351</v>
+        <v>6361</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6352</v>
+        <v>6362</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95390,52 +95592,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6126</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6353</v>
+        <v>6363</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5983</v>
+        <v>5993</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6136</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6159</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6354</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6355</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6148</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6356</v>
+        <v>6366</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6357</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95497,7 +95699,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6358</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95505,10 +95707,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6359</v>
+        <v>6369</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6360</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95516,7 +95718,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6361</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95529,15 +95731,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6362</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6363</v>
+        <v>6373</v>
       </c>
       <c r="F17" t="s">
-        <v>6364</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3381</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13651" uniqueCount="6375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13664" uniqueCount="6379">
   <si>
     <t>名称</t>
   </si>
@@ -20591,6 +20591,18 @@
   </si>
   <si>
     <t>难度太大</t>
+  </si>
+  <si>
+    <t>统计好子数组</t>
+  </si>
+  <si>
+    <t>个人解法：贡献法+单调栈</t>
+  </si>
+  <si>
+    <t>二进制交换后的最大分数</t>
+  </si>
+  <si>
+    <t>相等子字符串分数</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22250,9 +22262,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22264,8 +22275,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93536,15 +93548,75 @@
       <c r="N3381" s="17"/>
     </row>
     <row r="3382" spans="1:14">
-      <c r="C3382" s="2"/>
+      <c r="A3382">
+        <v>3878</v>
+      </c>
+      <c r="B3382" t="s">
+        <v>5986</v>
+      </c>
+      <c r="C3382" s="2">
+        <v>46103</v>
+      </c>
+      <c r="D3382" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3382" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3382" s="1" t="s">
+        <v>3584</v>
+      </c>
+      <c r="H3382" s="1" t="s">
+        <v>5987</v>
+      </c>
       <c r="N3382" s="17"/>
     </row>
     <row r="3383" spans="1:14">
-      <c r="C3383" s="2"/>
+      <c r="A3383">
+        <v>3781</v>
+      </c>
+      <c r="B3383" t="s">
+        <v>5988</v>
+      </c>
+      <c r="C3383" s="2">
+        <v>46103</v>
+      </c>
+      <c r="D3383" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3383" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3383">
+        <v>1823</v>
+      </c>
+      <c r="G3383" s="1" t="s">
+        <v>1527</v>
+      </c>
       <c r="N3383" s="17"/>
     </row>
     <row r="3384" spans="1:14">
-      <c r="C3384" s="2"/>
+      <c r="A3384">
+        <v>3707</v>
+      </c>
+      <c r="B3384" t="s">
+        <v>5989</v>
+      </c>
+      <c r="C3384" s="2">
+        <v>46103</v>
+      </c>
+      <c r="D3384" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3384" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3384">
+        <v>1262</v>
+      </c>
+      <c r="G3384" s="1" t="s">
+        <v>685</v>
+      </c>
       <c r="N3384" s="17"/>
     </row>
     <row r="3385" spans="1:14">
@@ -93576,7 +93648,7 @@
         <v>3454</v>
       </c>
       <c r="B3392" t="s">
-        <v>5986</v>
+        <v>5990</v>
       </c>
       <c r="D3392" t="s">
         <v>135</v>
@@ -93596,7 +93668,7 @@
         <v>3562</v>
       </c>
       <c r="B3393" t="s">
-        <v>5987</v>
+        <v>5991</v>
       </c>
       <c r="D3393" t="s">
         <v>135</v>
@@ -93607,10 +93679,10 @@
     </row>
     <row r="3394" spans="1:6">
       <c r="A3394" t="s">
-        <v>5988</v>
+        <v>5992</v>
       </c>
       <c r="B3394" t="s">
-        <v>5989</v>
+        <v>5993</v>
       </c>
       <c r="D3394" t="s">
         <v>135</v>
@@ -93621,7 +93693,7 @@
         <v>3721</v>
       </c>
       <c r="B3395" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="D3395" t="s">
         <v>135</v>
@@ -93634,7 +93706,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3379" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3381" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93681,10 +93753,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="D5" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93695,13 +93767,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93710,7 +93782,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93725,16 +93797,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93748,10 +93820,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="H14" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93766,16 +93838,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="W14" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93787,158 +93859,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="AL14" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="AO14" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="AR14" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AU14" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="AX14" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="T15" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="W15" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
       <c r="Z15" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="AF15" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="AI15" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="AL15" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="AU15" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="AX15" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="H16" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="N16" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="T16" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="W16" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="Z16" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="AC16" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AF16" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="AI16" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AL16" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="AR16" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="AU16" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AX16" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -93946,43 +94018,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="D17" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="H17" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="N17" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="T17" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="W17" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="Z17" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="AC17" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="AF17" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="AI17" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="AR17" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="AU17" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="BA17" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -93990,37 +94062,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="H18" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="N18" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="T18" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="W18" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="Z18" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="AC18" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AF18" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AI18" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="AU18" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="BA18" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94028,37 +94100,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="H19" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="N19" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="T19" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="W19" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="Z19" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="AC19" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="AF19" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="AI19" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AU19" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="BA19" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94066,37 +94138,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6075</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6076</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6077</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6078</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6079</v>
+      </c>
+      <c r="W20" t="s">
         <v>6071</v>
       </c>
-      <c r="D20" t="s">
-        <v>6072</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6073</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6074</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6075</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6067</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AC20" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AF20" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="AU20" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="BA20" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94104,37 +94176,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="D21" t="s">
+        <v>6085</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6086</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6087</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6088</v>
+      </c>
+      <c r="W21" t="s">
         <v>6081</v>
       </c>
-      <c r="H21" t="s">
-        <v>6082</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6083</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6084</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6077</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="AC21" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AF21" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AU21" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="BA21" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94145,13 +94217,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94160,16 +94232,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AC22" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AF22" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AU22" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94177,25 +94249,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="H23" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="T23" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="Z23" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AC23" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AF23" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AU23" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94203,89 +94275,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="T24" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="Z24" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AC24" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="AF24" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="D25" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="T25" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AC25" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AF25" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AC26" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AF26" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="AC27" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AF27" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AC28" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AF28" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94295,22 +94367,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94320,7 +94392,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -94328,7 +94400,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -94343,7 +94415,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -94361,227 +94433,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="Q41" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="T41" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="W41" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AL41" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="AO41" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="AR41" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="Q42" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="T42" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="W42" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AC42" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AL42" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AO42" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AR42" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="K43" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="N43" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="Q43" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="T43" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="W43" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="Z43" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AC43" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AF43" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AL43" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AO43" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AR43" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="F44" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="N44" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="Q44" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="W44" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="Z44" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="AC44" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AF44" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AL44" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="AO44" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AR44" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="F45" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="N45" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="Q45" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94590,103 +94662,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="AF45" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="AO45" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AR45" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="F46" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="N46" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="AC46" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AF46" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="AO46" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="AR46" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="F47" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AC47" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="AF47" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AO47" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="AR47" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="F48" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94698,141 +94770,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="AF48" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="AO48" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="AR48" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="AF49" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="AR49" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="F50" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="AR50" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="F51" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="AR51" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AR52" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="F53" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="F54" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="F55" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94840,10 +94912,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="F56" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94851,18 +94923,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="F57" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="F58" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94870,42 +94942,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="F59" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="F60" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="F61" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="F62" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="F63" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94913,181 +94985,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="F64" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="F65" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="F66" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="F67" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="F68" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="F69" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
   </sheetData>
@@ -95114,10 +95186,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -95126,13 +95198,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95140,13 +95212,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95158,13 +95230,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -95175,19 +95247,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="S10" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="T10" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95201,15 +95273,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="S11" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95218,18 +95290,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -95238,7 +95310,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95249,13 +95321,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95266,7 +95338,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95275,10 +95347,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="T15" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95289,12 +95361,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95302,22 +95374,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95328,39 +95400,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="H32" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
       <c r="K32" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
       <c r="N32" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
       <c r="Q32" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="S32" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95369,13 +95441,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
       <c r="K33" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="N33" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95383,153 +95455,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="K34" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="N34" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
       <c r="N35" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="N36" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
       <c r="N37" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="N38" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95537,7 +95609,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95553,7 +95625,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95569,21 +95641,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="J68" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95592,52 +95664,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95699,7 +95771,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95707,10 +95779,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95718,7 +95790,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95731,15 +95803,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
       <c r="F17" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3381</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3384</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13664" uniqueCount="6379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13676" uniqueCount="6383">
   <si>
     <t>名称</t>
   </si>
@@ -20603,6 +20603,18 @@
   </si>
   <si>
     <t>相等子字符串分数</t>
+  </si>
+  <si>
+    <t>达到目标异或值的最少删除次数</t>
+  </si>
+  <si>
+    <t>这个思路还是有点难</t>
+  </si>
+  <si>
+    <t>最长斐波那契子数组</t>
+  </si>
+  <si>
+    <t>分块数组</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22262,13 +22274,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22278,6 +22283,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93620,15 +93632,69 @@
       <c r="N3384" s="17"/>
     </row>
     <row r="3385" spans="1:14">
-      <c r="C3385" s="2"/>
+      <c r="A3385">
+        <v>3877</v>
+      </c>
+      <c r="B3385" t="s">
+        <v>5990</v>
+      </c>
+      <c r="C3385" s="2">
+        <v>46104</v>
+      </c>
+      <c r="D3385" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3385" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3385" s="1" t="s">
+        <v>3384</v>
+      </c>
+      <c r="H3385" s="1" t="s">
+        <v>5991</v>
+      </c>
       <c r="N3385" s="17"/>
     </row>
     <row r="3386" spans="1:14">
-      <c r="C3386" s="2"/>
+      <c r="A3386">
+        <v>3708</v>
+      </c>
+      <c r="B3386" t="s">
+        <v>5992</v>
+      </c>
+      <c r="C3386" s="2">
+        <v>46104</v>
+      </c>
+      <c r="D3386" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3386" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3386">
+        <v>1380</v>
+      </c>
+      <c r="G3386" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="N3386" s="17"/>
     </row>
     <row r="3387" spans="1:14">
-      <c r="C3387" s="2"/>
+      <c r="A3387">
+        <v>2677</v>
+      </c>
+      <c r="B3387" t="s">
+        <v>5993</v>
+      </c>
+      <c r="C3387" s="2">
+        <v>46104</v>
+      </c>
+      <c r="D3387" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3387" s="1" t="s">
+        <v>5712</v>
+      </c>
       <c r="N3387" s="17"/>
     </row>
     <row r="3388" spans="1:14">
@@ -93648,7 +93714,7 @@
         <v>3454</v>
       </c>
       <c r="B3392" t="s">
-        <v>5990</v>
+        <v>5994</v>
       </c>
       <c r="D3392" t="s">
         <v>135</v>
@@ -93668,7 +93734,7 @@
         <v>3562</v>
       </c>
       <c r="B3393" t="s">
-        <v>5991</v>
+        <v>5995</v>
       </c>
       <c r="D3393" t="s">
         <v>135</v>
@@ -93679,10 +93745,10 @@
     </row>
     <row r="3394" spans="1:6">
       <c r="A3394" t="s">
-        <v>5992</v>
+        <v>5996</v>
       </c>
       <c r="B3394" t="s">
-        <v>5993</v>
+        <v>5997</v>
       </c>
       <c r="D3394" t="s">
         <v>135</v>
@@ -93693,7 +93759,7 @@
         <v>3721</v>
       </c>
       <c r="B3395" t="s">
-        <v>5994</v>
+        <v>5998</v>
       </c>
       <c r="D3395" t="s">
         <v>135</v>
@@ -93706,7 +93772,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3381" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3384" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93753,10 +93819,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>5995</v>
+        <v>5999</v>
       </c>
       <c r="D5" t="s">
-        <v>5996</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93767,13 +93833,13 @@
         <v>789</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1664</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5998</v>
+        <v>6002</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>122</v>
@@ -93782,7 +93848,7 @@
         <v>113</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>5999</v>
+        <v>6003</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>927</v>
@@ -93797,16 +93863,16 @@
         <v>765</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6000</v>
+        <v>6004</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6001</v>
+        <v>6005</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3545</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6002</v>
+        <v>6006</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2961</v>
@@ -93820,10 +93886,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="H14" t="s">
-        <v>6004</v>
+        <v>6008</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93838,16 +93904,16 @@
         <v>2180</v>
       </c>
       <c r="T14" t="s">
-        <v>6005</v>
+        <v>6009</v>
       </c>
       <c r="W14" t="s">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6007</v>
+        <v>6011</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -93859,158 +93925,158 @@
         <v>2101</v>
       </c>
       <c r="AF14" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6009</v>
+        <v>6013</v>
       </c>
       <c r="AL14" t="s">
-        <v>6010</v>
+        <v>6014</v>
       </c>
       <c r="AO14" t="s">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="AR14" t="s">
-        <v>6012</v>
+        <v>6016</v>
       </c>
       <c r="AU14" t="s">
-        <v>6013</v>
+        <v>6017</v>
       </c>
       <c r="AX14" t="s">
-        <v>6014</v>
+        <v>6018</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6015</v>
+        <v>6019</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6017</v>
+        <v>6021</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6018</v>
+        <v>6022</v>
       </c>
       <c r="H15" t="s">
         <v>1545</v>
       </c>
       <c r="N15" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="T15" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="W15" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="Z15" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="AF15" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="AI15" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="AL15" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="AO15" t="s">
         <v>2287</v>
       </c>
       <c r="AR15" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
       <c r="AU15" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="AX15" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="H16" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="N16" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="T16" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="W16" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="Z16" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AC16" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="AF16" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="AI16" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AL16" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="AR16" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AU16" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AX16" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94018,43 +94084,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="D17" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="H17" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="N17" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="T17" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="W17" t="s">
-        <v>6008</v>
+        <v>6012</v>
       </c>
       <c r="Z17" t="s">
-        <v>6019</v>
+        <v>6023</v>
       </c>
       <c r="AC17" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="AF17" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="AI17" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="AR17" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="AU17" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="BA17" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94062,37 +94128,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="H18" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="N18" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="T18" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="W18" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="Z18" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="AC18" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AF18" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="AI18" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="AU18" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="BA18" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94100,37 +94166,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="H19" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="N19" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="T19" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="W19" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="Z19" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="AC19" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="AF19" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AI19" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AU19" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="BA19" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94138,37 +94204,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6079</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6080</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6081</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6082</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6083</v>
+      </c>
+      <c r="W20" t="s">
         <v>6075</v>
       </c>
-      <c r="D20" t="s">
-        <v>6076</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6077</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6078</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6079</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6071</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AC20" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="AF20" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AU20" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="BA20" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94176,37 +94242,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="D21" t="s">
+        <v>6089</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6090</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6091</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6092</v>
+      </c>
+      <c r="W21" t="s">
         <v>6085</v>
       </c>
-      <c r="H21" t="s">
-        <v>6086</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6087</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6088</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6081</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AC21" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="AF21" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="AU21" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="BA21" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94217,13 +94283,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94232,16 +94298,16 @@
         <v>2152</v>
       </c>
       <c r="Z22" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="AC22" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AF22" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AU22" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94249,25 +94315,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="H23" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="T23" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="Z23" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AC23" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="AF23" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AU23" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94275,89 +94341,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="T24" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="Z24" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AC24" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AF24" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="D25" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="T25" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AC25" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AF25" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AC26" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AF26" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AC27" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AF27" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AC28" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AF28" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94367,22 +94433,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94392,7 +94458,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="T39" t="s">
         <v>2286</v>
@@ -94400,7 +94466,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>108</v>
@@ -94415,7 +94481,7 @@
         <v>1912</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>66</v>
@@ -94433,227 +94499,227 @@
         <v>3908</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="Q41" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="T41" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="W41" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AF41" t="s">
         <v>2231</v>
       </c>
       <c r="AI41" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AL41" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AO41" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AR41" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="Q42" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="T42" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="W42" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AC42" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AL42" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AO42" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AR42" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="K43" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="N43" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="Q43" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="T43" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="W43" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="Z43" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AC43" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AF43" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="AL43" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AO43" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AR43" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="F44" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="N44" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="Q44" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="W44" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="Z44" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AC44" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="AF44" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="AL44" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="AO44" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AR44" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="F45" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="N45" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="Q45" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94662,103 +94728,103 @@
         <v>2276</v>
       </c>
       <c r="AC45" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AF45" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="AO45" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="AR45" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="F46" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="N46" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="AC46" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="AF46" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="AO46" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="AR46" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="F47" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="AC47" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="AF47" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="AO47" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="AR47" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="F48" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94770,141 +94836,141 @@
         <v>2416</v>
       </c>
       <c r="AC48" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="AF48" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="AO48" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="AR48" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="AF49" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AR49" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="F50" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="AR50" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="F51" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AR51" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="AR52" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="F53" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="F54" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="F55" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -94912,10 +94978,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="F56" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -94923,18 +94989,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="F57" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="F58" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -94942,42 +95008,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="F59" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="F60" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="F61" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="F62" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="F63" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -94985,181 +95051,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="F64" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="F65" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="F66" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="F67" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="F68" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="F69" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
     </row>
   </sheetData>
@@ -95186,10 +95252,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>149</v>
@@ -95198,13 +95264,13 @@
         <v>1660</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95212,13 +95278,13 @@
         <v>1880</v>
       </c>
       <c r="H9" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95230,13 +95296,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="V9" t="s">
         <v>724</v>
@@ -95247,19 +95313,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="S10" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="T10" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95273,15 +95339,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="S11" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95290,18 +95356,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="H13" t="s">
         <v>541</v>
@@ -95310,7 +95376,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95321,13 +95387,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95338,7 +95404,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95347,10 +95413,10 @@
         <v>586</v>
       </c>
       <c r="S15" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="T15" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95361,12 +95427,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95374,22 +95440,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1277</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95400,39 +95466,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
       <c r="H32" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="K32" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="N32" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
       <c r="Q32" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="S32" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95441,13 +95507,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="K33" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
       <c r="N33" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95455,153 +95521,153 @@
         <v>2261</v>
       </c>
       <c r="J34" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="K34" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="N34" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
       <c r="N35" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="N36" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="N37" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
       <c r="N38" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="L39" t="s">
         <v>944</v>
       </c>
       <c r="N39" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3807</v>
       </c>
       <c r="N55" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95609,7 +95675,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95625,7 +95691,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95641,21 +95707,21 @@
         <v>1277</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="J68" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="H69" t="s">
         <v>198</v>
@@ -95664,52 +95730,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>5997</v>
+        <v>6001</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95771,7 +95837,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95779,10 +95845,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95790,7 +95856,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95803,15 +95869,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
       <c r="F17" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3391</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13689" uniqueCount="6387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13699" uniqueCount="6390">
   <si>
     <t>名称</t>
   </si>
@@ -20627,6 +20627,15 @@
   </si>
   <si>
     <t>包装数组</t>
+  </si>
+  <si>
+    <t>构造奇偶一致的数组 I</t>
+  </si>
+  <si>
+    <t>数位平方和的最大值</t>
+  </si>
+  <si>
+    <t>执行可取消的延迟函数</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22292,16 +22301,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23253,7 +23262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3396"/>
+  <dimension ref="A1:N3406"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -93786,70 +93795,158 @@
       </c>
       <c r="N3391" s="17"/>
     </row>
-    <row r="3393" spans="1:7">
+    <row r="3392" spans="1:14">
+      <c r="A3392">
+        <v>3875</v>
+      </c>
+      <c r="B3392" t="s">
+        <v>5998</v>
+      </c>
+      <c r="C3392" s="2">
+        <v>46106</v>
+      </c>
+      <c r="D3392" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3392" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3392" s="17"/>
+    </row>
+    <row r="3393" spans="1:14">
       <c r="A3393">
+        <v>3723</v>
+      </c>
+      <c r="B3393" t="s">
+        <v>5999</v>
+      </c>
+      <c r="C3393" s="2">
+        <v>46106</v>
+      </c>
+      <c r="D3393" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3393" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3393">
+        <v>1536</v>
+      </c>
+      <c r="G3393" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="N3393" s="17"/>
+    </row>
+    <row r="3394" spans="1:14">
+      <c r="A3394">
+        <v>2715</v>
+      </c>
+      <c r="B3394" t="s">
+        <v>6000</v>
+      </c>
+      <c r="C3394" s="2">
+        <v>46106</v>
+      </c>
+      <c r="D3394" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3394" s="1" t="s">
+        <v>5713</v>
+      </c>
+      <c r="N3394" s="17"/>
+    </row>
+    <row r="3395" spans="1:14">
+      <c r="C3395" s="2"/>
+      <c r="N3395" s="17"/>
+    </row>
+    <row r="3396" spans="1:14">
+      <c r="C3396" s="2"/>
+      <c r="N3396" s="17"/>
+    </row>
+    <row r="3397" spans="1:14">
+      <c r="C3397" s="2"/>
+      <c r="N3397" s="17"/>
+    </row>
+    <row r="3398" spans="1:14">
+      <c r="C3398" s="2"/>
+      <c r="N3398" s="17"/>
+    </row>
+    <row r="3399" spans="1:14">
+      <c r="C3399" s="2"/>
+      <c r="N3399" s="17"/>
+    </row>
+    <row r="3400" spans="1:14">
+      <c r="C3400" s="2"/>
+      <c r="N3400" s="17"/>
+    </row>
+    <row r="3401" spans="1:14">
+      <c r="C3401" s="2"/>
+      <c r="N3401" s="17"/>
+    </row>
+    <row r="3403" spans="1:14">
+      <c r="A3403">
         <v>3454</v>
       </c>
-      <c r="B3393" t="s">
-        <v>5998</v>
-      </c>
-      <c r="D3393" t="s">
+      <c r="B3403" t="s">
+        <v>6001</v>
+      </c>
+      <c r="D3403" t="s">
         <v>136</v>
       </c>
-      <c r="E3393" t="s">
+      <c r="E3403" t="s">
         <v>74</v>
       </c>
-      <c r="F3393">
+      <c r="F3403">
         <v>2671</v>
       </c>
-      <c r="G3393" s="1" t="s">
+      <c r="G3403" s="1" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="3394" spans="1:7">
-      <c r="A3394">
+    <row r="3404" spans="1:14">
+      <c r="A3404">
         <v>3562</v>
       </c>
-      <c r="B3394" t="s">
-        <v>5999</v>
-      </c>
-      <c r="D3394" t="s">
+      <c r="B3404" t="s">
+        <v>6002</v>
+      </c>
+      <c r="D3404" t="s">
         <v>136</v>
       </c>
-      <c r="F3394">
+      <c r="F3404">
         <v>2458</v>
       </c>
     </row>
-    <row r="3395" spans="1:7">
-      <c r="A3395" t="s">
-        <v>6000</v>
-      </c>
-      <c r="B3395" t="s">
-        <v>6001</v>
-      </c>
-      <c r="D3395" t="s">
+    <row r="3405" spans="1:14">
+      <c r="A3405" t="s">
+        <v>6003</v>
+      </c>
+      <c r="B3405" t="s">
+        <v>6004</v>
+      </c>
+      <c r="D3405" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="3396" spans="1:7">
-      <c r="A3396">
+    <row r="3406" spans="1:14">
+      <c r="A3406">
         <v>3721</v>
       </c>
-      <c r="B3396" t="s">
-        <v>6002</v>
-      </c>
-      <c r="D3396" t="s">
+      <c r="B3406" t="s">
+        <v>6005</v>
+      </c>
+      <c r="D3406" t="s">
         <v>136</v>
       </c>
-      <c r="E3396" t="s">
+      <c r="E3406" t="s">
         <v>74</v>
       </c>
-      <c r="F3396">
+      <c r="F3406">
         <v>2723</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3388" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3391" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -93896,10 +93993,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6003</v>
+        <v>6006</v>
       </c>
       <c r="D5" t="s">
-        <v>6004</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -93910,13 +94007,13 @@
         <v>790</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1665</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6006</v>
+        <v>6009</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>123</v>
@@ -93925,7 +94022,7 @@
         <v>114</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6007</v>
+        <v>6010</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>928</v>
@@ -93940,16 +94037,16 @@
         <v>766</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6008</v>
+        <v>6011</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2962</v>
@@ -93963,10 +94060,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="H14" t="s">
-        <v>6012</v>
+        <v>6015</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -93981,16 +94078,16 @@
         <v>2181</v>
       </c>
       <c r="T14" t="s">
-        <v>6013</v>
+        <v>6016</v>
       </c>
       <c r="W14" t="s">
-        <v>6014</v>
+        <v>6017</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6015</v>
+        <v>6018</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94002,158 +94099,158 @@
         <v>2102</v>
       </c>
       <c r="AF14" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6017</v>
+        <v>6020</v>
       </c>
       <c r="AL14" t="s">
-        <v>6018</v>
+        <v>6021</v>
       </c>
       <c r="AO14" t="s">
-        <v>6019</v>
+        <v>6022</v>
       </c>
       <c r="AR14" t="s">
-        <v>6020</v>
+        <v>6023</v>
       </c>
       <c r="AU14" t="s">
-        <v>6021</v>
+        <v>6024</v>
       </c>
       <c r="AX14" t="s">
-        <v>6022</v>
+        <v>6025</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6023</v>
+        <v>6026</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6024</v>
+        <v>6027</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6025</v>
+        <v>6028</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6026</v>
+        <v>6029</v>
       </c>
       <c r="H15" t="s">
         <v>1546</v>
       </c>
       <c r="N15" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="T15" t="s">
-        <v>6028</v>
+        <v>6031</v>
       </c>
       <c r="W15" t="s">
-        <v>6029</v>
+        <v>6032</v>
       </c>
       <c r="Z15" t="s">
-        <v>6030</v>
+        <v>6033</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="AF15" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
       <c r="AI15" t="s">
-        <v>6033</v>
+        <v>6036</v>
       </c>
       <c r="AL15" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AO15" t="s">
         <v>2288</v>
       </c>
       <c r="AR15" t="s">
-        <v>6035</v>
+        <v>6038</v>
       </c>
       <c r="AU15" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
       <c r="AX15" t="s">
-        <v>6037</v>
+        <v>6040</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6038</v>
+        <v>6041</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6039</v>
+        <v>6042</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6040</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6041</v>
+        <v>6044</v>
       </c>
       <c r="H16" t="s">
-        <v>6042</v>
+        <v>6045</v>
       </c>
       <c r="N16" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="T16" t="s">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="W16" t="s">
-        <v>6045</v>
+        <v>6048</v>
       </c>
       <c r="Z16" t="s">
-        <v>6046</v>
+        <v>6049</v>
       </c>
       <c r="AC16" t="s">
-        <v>6034</v>
+        <v>6037</v>
       </c>
       <c r="AF16" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="AI16" t="s">
-        <v>6047</v>
+        <v>6050</v>
       </c>
       <c r="AL16" t="s">
-        <v>6048</v>
+        <v>6051</v>
       </c>
       <c r="AR16" t="s">
-        <v>6049</v>
+        <v>6052</v>
       </c>
       <c r="AU16" t="s">
-        <v>6050</v>
+        <v>6053</v>
       </c>
       <c r="AX16" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6052</v>
+        <v>6055</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94161,43 +94258,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="D17" t="s">
-        <v>6054</v>
+        <v>6057</v>
       </c>
       <c r="H17" t="s">
-        <v>6055</v>
+        <v>6058</v>
       </c>
       <c r="N17" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="T17" t="s">
-        <v>6057</v>
+        <v>6060</v>
       </c>
       <c r="W17" t="s">
-        <v>6016</v>
+        <v>6019</v>
       </c>
       <c r="Z17" t="s">
-        <v>6027</v>
+        <v>6030</v>
       </c>
       <c r="AC17" t="s">
-        <v>6058</v>
+        <v>6061</v>
       </c>
       <c r="AF17" t="s">
-        <v>6059</v>
+        <v>6062</v>
       </c>
       <c r="AI17" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
       <c r="AR17" t="s">
-        <v>6061</v>
+        <v>6064</v>
       </c>
       <c r="AU17" t="s">
-        <v>6062</v>
+        <v>6065</v>
       </c>
       <c r="BA17" t="s">
-        <v>6063</v>
+        <v>6066</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94205,37 +94302,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6064</v>
+        <v>6067</v>
       </c>
       <c r="H18" t="s">
-        <v>6065</v>
+        <v>6068</v>
       </c>
       <c r="N18" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="T18" t="s">
-        <v>6067</v>
+        <v>6070</v>
       </c>
       <c r="W18" t="s">
-        <v>6068</v>
+        <v>6071</v>
       </c>
       <c r="Z18" t="s">
-        <v>6043</v>
+        <v>6046</v>
       </c>
       <c r="AC18" t="s">
-        <v>6069</v>
+        <v>6072</v>
       </c>
       <c r="AF18" t="s">
-        <v>6070</v>
+        <v>6073</v>
       </c>
       <c r="AI18" t="s">
-        <v>6071</v>
+        <v>6074</v>
       </c>
       <c r="AU18" t="s">
-        <v>6072</v>
+        <v>6075</v>
       </c>
       <c r="BA18" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94243,37 +94340,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6074</v>
+        <v>6077</v>
       </c>
       <c r="H19" t="s">
-        <v>6075</v>
+        <v>6078</v>
       </c>
       <c r="N19" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="T19" t="s">
-        <v>6077</v>
+        <v>6080</v>
       </c>
       <c r="W19" t="s">
-        <v>6051</v>
+        <v>6054</v>
       </c>
       <c r="Z19" t="s">
-        <v>6056</v>
+        <v>6059</v>
       </c>
       <c r="AC19" t="s">
-        <v>6078</v>
+        <v>6081</v>
       </c>
       <c r="AF19" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
       <c r="AI19" t="s">
-        <v>6080</v>
+        <v>6083</v>
       </c>
       <c r="AU19" t="s">
-        <v>6081</v>
+        <v>6084</v>
       </c>
       <c r="BA19" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94281,37 +94378,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="D20" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="H20" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="N20" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="T20" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="W20" t="s">
-        <v>6079</v>
+        <v>6082</v>
       </c>
       <c r="Z20" t="s">
-        <v>6066</v>
+        <v>6069</v>
       </c>
       <c r="AC20" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="AF20" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="AU20" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
       <c r="BA20" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94319,37 +94416,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6095</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6096</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6097</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6098</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6099</v>
+      </c>
+      <c r="W21" t="s">
         <v>6092</v>
       </c>
-      <c r="D21" t="s">
-        <v>6093</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6094</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6095</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6096</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6089</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6076</v>
+        <v>6079</v>
       </c>
       <c r="AC21" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="AF21" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="AU21" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="BA21" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94360,13 +94457,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94375,16 +94472,16 @@
         <v>2153</v>
       </c>
       <c r="Z22" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="AC22" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="AF22" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
       <c r="AU22" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94392,25 +94489,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="H23" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="T23" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="Z23" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AC23" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="AF23" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="AU23" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94418,89 +94515,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="T24" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="Z24" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="AC24" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="AF24" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="D25" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="T25" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
       <c r="AC25" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="AF25" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="AC26" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="AF26" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="AC27" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="AF27" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="AC28" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="AF28" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94510,22 +94607,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94535,7 +94632,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
       <c r="T39" t="s">
         <v>2287</v>
@@ -94543,7 +94640,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -94558,7 +94655,7 @@
         <v>1913</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -94576,227 +94673,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="Q41" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="T41" t="s">
-        <v>6031</v>
+        <v>6034</v>
       </c>
       <c r="W41" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AF41" t="s">
         <v>2232</v>
       </c>
       <c r="AI41" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
       <c r="AL41" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="AO41" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="AR41" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="Q42" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="T42" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="W42" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AC42" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
       <c r="AL42" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="AO42" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="AR42" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="K43" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="N43" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="Q43" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="T43" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="W43" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="Z43" t="s">
-        <v>6171</v>
+        <v>6174</v>
       </c>
       <c r="AC43" t="s">
-        <v>6172</v>
+        <v>6175</v>
       </c>
       <c r="AF43" t="s">
-        <v>6173</v>
+        <v>6176</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="AL43" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
       <c r="AO43" t="s">
-        <v>6175</v>
+        <v>6178</v>
       </c>
       <c r="AR43" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="F44" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="N44" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="Q44" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="W44" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="Z44" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="AC44" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="AF44" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
       <c r="AL44" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="AO44" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="AR44" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="F45" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
       <c r="N45" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="Q45" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94805,103 +94902,103 @@
         <v>2277</v>
       </c>
       <c r="AC45" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="AF45" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
       <c r="AO45" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
       <c r="AR45" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="F46" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
       <c r="N46" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="AC46" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
       <c r="AF46" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="AO46" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="AR46" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
       <c r="F47" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
       <c r="AC47" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
       <c r="AF47" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
       <c r="AO47" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="AR47" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
       <c r="F48" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -94913,141 +95010,141 @@
         <v>2417</v>
       </c>
       <c r="AC48" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
       <c r="AF48" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
       <c r="AO48" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
       <c r="AR48" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="AF49" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
       <c r="AR49" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="F50" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
       <c r="AR50" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
       <c r="F51" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="AR51" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
       <c r="AR52" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
       <c r="F53" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
       <c r="F54" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="F55" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95055,10 +95152,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
       <c r="F56" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95066,18 +95163,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
       <c r="F57" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
       <c r="F58" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95085,42 +95182,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
       <c r="F59" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
       <c r="F60" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
       <c r="F61" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="F62" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="F63" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95128,181 +95225,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="F64" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="F65" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="F66" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="F67" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="F68" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="F69" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6032</v>
+        <v>6035</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
     </row>
   </sheetData>
@@ -95329,10 +95426,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>150</v>
@@ -95341,13 +95438,13 @@
         <v>1661</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95355,13 +95452,13 @@
         <v>1881</v>
       </c>
       <c r="H9" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95373,13 +95470,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="V9" t="s">
         <v>725</v>
@@ -95390,19 +95487,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
       <c r="S10" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="T10" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95416,15 +95513,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
       <c r="S11" t="s">
-        <v>6036</v>
+        <v>6039</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95433,18 +95530,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
       <c r="H13" t="s">
         <v>542</v>
@@ -95453,7 +95550,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95464,13 +95561,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95481,7 +95578,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95490,10 +95587,10 @@
         <v>587</v>
       </c>
       <c r="S15" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
       <c r="T15" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95504,12 +95601,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95517,22 +95614,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1278</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95543,39 +95640,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
       <c r="H32" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
       <c r="K32" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="N32" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
       <c r="Q32" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
       <c r="S32" t="s">
-        <v>6060</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95584,13 +95681,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
       <c r="K33" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
       <c r="N33" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95598,153 +95695,153 @@
         <v>2262</v>
       </c>
       <c r="J34" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="K34" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
       <c r="N34" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="N35" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
       <c r="N36" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
       <c r="N37" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
       <c r="N38" t="s">
-        <v>6350</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6073</v>
+        <v>6076</v>
       </c>
       <c r="L39" t="s">
         <v>945</v>
       </c>
       <c r="N39" t="s">
-        <v>6351</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6352</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6353</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6354</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6355</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6356</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6357</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6358</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6359</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6360</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6361</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6362</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6363</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6364</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6365</v>
+        <v>6368</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6366</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6367</v>
+        <v>6370</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6368</v>
+        <v>6371</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95752,7 +95849,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6369</v>
+        <v>6372</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95768,7 +95865,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6370</v>
+        <v>6373</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95784,21 +95881,21 @@
         <v>1278</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6371</v>
+        <v>6374</v>
       </c>
       <c r="J68" t="s">
-        <v>6372</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6373</v>
+        <v>6376</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6374</v>
+        <v>6377</v>
       </c>
       <c r="H69" t="s">
         <v>199</v>
@@ -95807,52 +95904,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6375</v>
+        <v>6378</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6005</v>
+        <v>6008</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6376</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6377</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6378</v>
+        <v>6381</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6379</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -95914,7 +96011,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6380</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -95922,10 +96019,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6381</v>
+        <v>6384</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6382</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -95933,7 +96030,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -95946,15 +96043,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
       <c r="F17" t="s">
-        <v>6386</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3398</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13715" uniqueCount="6395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13726" uniqueCount="6400">
   <si>
     <t>名称</t>
   </si>
@@ -20651,6 +20651,21 @@
   </si>
   <si>
     <t>两个 Promise 对象相加</t>
+  </si>
+  <si>
+    <t>统计主要元素子数组数目 I</t>
+  </si>
+  <si>
+    <t>统计主要元素子数组数目 II</t>
+  </si>
+  <si>
+    <t>式子变形 + 树状数组</t>
+  </si>
+  <si>
+    <t>有序数组也可以</t>
+  </si>
+  <si>
+    <t>扁平化嵌套数组</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22310,17 +22325,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -93954,15 +93969,69 @@
       <c r="N3398" s="17"/>
     </row>
     <row r="3399" spans="1:14">
-      <c r="C3399" s="2"/>
+      <c r="A3399">
+        <v>3737</v>
+      </c>
+      <c r="B3399" t="s">
+        <v>6006</v>
+      </c>
+      <c r="C3399" s="2">
+        <v>46108</v>
+      </c>
+      <c r="D3399" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3399" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3399">
+        <v>1422</v>
+      </c>
       <c r="N3399" s="17"/>
     </row>
     <row r="3400" spans="1:14">
-      <c r="C3400" s="2"/>
+      <c r="A3400">
+        <v>3739</v>
+      </c>
+      <c r="B3400" t="s">
+        <v>6007</v>
+      </c>
+      <c r="C3400" s="2">
+        <v>46108</v>
+      </c>
+      <c r="D3400" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3400" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3400">
+        <v>2089</v>
+      </c>
+      <c r="G3400" s="1" t="s">
+        <v>6008</v>
+      </c>
+      <c r="H3400" s="1" t="s">
+        <v>6009</v>
+      </c>
       <c r="N3400" s="17"/>
     </row>
     <row r="3401" spans="1:14">
-      <c r="C3401" s="2"/>
+      <c r="A3401">
+        <v>2625</v>
+      </c>
+      <c r="B3401" t="s">
+        <v>6010</v>
+      </c>
+      <c r="C3401" s="2">
+        <v>46108</v>
+      </c>
+      <c r="D3401" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3401" s="1" t="s">
+        <v>5714</v>
+      </c>
       <c r="N3401" s="17"/>
     </row>
     <row r="3402" spans="1:14">
@@ -93974,7 +94043,7 @@
         <v>3454</v>
       </c>
       <c r="B3404" t="s">
-        <v>6006</v>
+        <v>6011</v>
       </c>
       <c r="D3404" t="s">
         <v>138</v>
@@ -93994,7 +94063,7 @@
         <v>3562</v>
       </c>
       <c r="B3405" t="s">
-        <v>6007</v>
+        <v>6012</v>
       </c>
       <c r="D3405" t="s">
         <v>138</v>
@@ -94005,10 +94074,10 @@
     </row>
     <row r="3406" spans="1:14">
       <c r="A3406" t="s">
-        <v>6008</v>
+        <v>6013</v>
       </c>
       <c r="B3406" t="s">
-        <v>6009</v>
+        <v>6014</v>
       </c>
       <c r="D3406" t="s">
         <v>138</v>
@@ -94019,7 +94088,7 @@
         <v>3721</v>
       </c>
       <c r="B3407" t="s">
-        <v>6010</v>
+        <v>6015</v>
       </c>
       <c r="D3407" t="s">
         <v>138</v>
@@ -94032,7 +94101,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3395" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3398" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94079,10 +94148,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6011</v>
+        <v>6016</v>
       </c>
       <c r="D5" t="s">
-        <v>6012</v>
+        <v>6017</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94093,13 +94162,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6014</v>
+        <v>6019</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94108,7 +94177,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6015</v>
+        <v>6020</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94123,16 +94192,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6016</v>
+        <v>6021</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6017</v>
+        <v>6022</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3547</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6018</v>
+        <v>6023</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94146,10 +94215,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6019</v>
+        <v>6024</v>
       </c>
       <c r="H14" t="s">
-        <v>6020</v>
+        <v>6025</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94164,16 +94233,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6021</v>
+        <v>6026</v>
       </c>
       <c r="W14" t="s">
-        <v>6022</v>
+        <v>6027</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6023</v>
+        <v>6028</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94185,158 +94254,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6025</v>
+        <v>6030</v>
       </c>
       <c r="AL14" t="s">
-        <v>6026</v>
+        <v>6031</v>
       </c>
       <c r="AO14" t="s">
-        <v>6027</v>
+        <v>6032</v>
       </c>
       <c r="AR14" t="s">
-        <v>6028</v>
+        <v>6033</v>
       </c>
       <c r="AU14" t="s">
-        <v>6029</v>
+        <v>6034</v>
       </c>
       <c r="AX14" t="s">
-        <v>6030</v>
+        <v>6035</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6031</v>
+        <v>6036</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6033</v>
+        <v>6038</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="T15" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
       <c r="W15" t="s">
-        <v>6037</v>
+        <v>6042</v>
       </c>
       <c r="Z15" t="s">
-        <v>6038</v>
+        <v>6043</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="AF15" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="AI15" t="s">
-        <v>6041</v>
+        <v>6046</v>
       </c>
       <c r="AL15" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
       <c r="AU15" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
       <c r="AX15" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6047</v>
+        <v>6052</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6048</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="H16" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="N16" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
       <c r="T16" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
       <c r="W16" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
       <c r="Z16" t="s">
-        <v>6054</v>
+        <v>6059</v>
       </c>
       <c r="AC16" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="AF16" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="AI16" t="s">
-        <v>6055</v>
+        <v>6060</v>
       </c>
       <c r="AL16" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
       <c r="AR16" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
       <c r="AU16" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
       <c r="AX16" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94344,43 +94413,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="D17" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="H17" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="N17" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
       <c r="T17" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="W17" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="Z17" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="AC17" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
       <c r="AF17" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="AI17" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AR17" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="AU17" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="BA17" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94388,37 +94457,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="H18" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
       <c r="N18" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="T18" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
       <c r="W18" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="Z18" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
       <c r="AC18" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="AF18" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="AI18" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="AU18" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="BA18" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94426,37 +94495,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="H19" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="N19" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="T19" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="W19" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="Z19" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
       <c r="AC19" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="AF19" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="AI19" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="AU19" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="BA19" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94464,37 +94533,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="D20" t="s">
+        <v>6097</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6098</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6099</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6100</v>
+      </c>
+      <c r="W20" t="s">
         <v>6092</v>
       </c>
-      <c r="H20" t="s">
-        <v>6093</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6094</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6095</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6087</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="AC20" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="AF20" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="AU20" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="BA20" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94502,37 +94571,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="D21" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="H21" t="s">
+        <v>6107</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6108</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6109</v>
+      </c>
+      <c r="W21" t="s">
         <v>6102</v>
       </c>
-      <c r="N21" t="s">
-        <v>6103</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6104</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6097</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="AC21" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="AF21" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="AU21" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="BA21" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94543,13 +94612,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94558,16 +94627,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AC22" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="AF22" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="AU22" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94575,25 +94644,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="H23" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="T23" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="Z23" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="AC23" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="AF23" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="AU23" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94601,89 +94670,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="T24" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="Z24" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AC24" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="AF24" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="D25" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="T25" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="AC25" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="AF25" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="AC26" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AF26" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="AC27" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="AF27" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="AC28" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="AF28" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94693,22 +94762,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94718,7 +94787,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -94726,7 +94795,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -94741,7 +94810,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -94759,227 +94828,227 @@
         <v>3910</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="Q41" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="T41" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="W41" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="AL41" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="AO41" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="AR41" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="Q42" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="T42" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="W42" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="AC42" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="AL42" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="AO42" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="AR42" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="K43" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="N43" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="Q43" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
       <c r="T43" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="W43" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
       <c r="Z43" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="AC43" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="AF43" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
       <c r="AL43" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="AO43" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="AR43" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="F44" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="N44" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="Q44" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="W44" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="Z44" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="AC44" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="AF44" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="AL44" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
       <c r="AO44" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
       <c r="AR44" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="F45" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="N45" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="Q45" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -94988,103 +95057,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="AF45" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="AO45" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="AR45" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="F46" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="N46" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
       <c r="AC46" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
       <c r="AF46" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="AO46" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="AR46" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
       <c r="F47" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="AC47" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="AF47" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="AO47" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="AR47" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="F48" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95096,141 +95165,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="AF48" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="AO48" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="AR48" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="AF49" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="AR49" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="F50" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="AR50" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="F51" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="AR51" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="AR52" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="F53" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="F54" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="F55" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95238,10 +95307,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
       <c r="F56" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95249,18 +95318,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="F57" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
       <c r="F58" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95268,42 +95337,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="F59" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="F60" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="F61" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="F62" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="F63" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95311,181 +95380,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="F64" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="F65" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
       <c r="F66" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="F67" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="F68" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
       <c r="F69" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
     </row>
   </sheetData>
@@ -95512,10 +95581,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -95524,13 +95593,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95538,13 +95607,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95556,13 +95625,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -95573,19 +95642,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="S10" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
       <c r="T10" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95599,15 +95668,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
       <c r="S11" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95616,18 +95685,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -95636,7 +95705,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95647,13 +95716,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95664,7 +95733,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95673,10 +95742,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="T15" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95687,12 +95756,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95700,22 +95769,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95726,39 +95795,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
       <c r="H32" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
       <c r="K32" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
       <c r="N32" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="Q32" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="S32" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95767,13 +95836,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
       <c r="K33" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
       <c r="N33" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95781,153 +95850,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
       <c r="K34" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
       <c r="N34" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="N35" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
       <c r="N36" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
       <c r="N37" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
       <c r="N38" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3809</v>
       </c>
       <c r="N55" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -95935,7 +96004,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -95951,7 +96020,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -95967,21 +96036,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
       <c r="J68" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -95990,52 +96059,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6013</v>
+        <v>6018</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96097,7 +96166,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96105,10 +96174,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96116,7 +96185,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96129,15 +96198,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
       <c r="F17" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3403</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13738" uniqueCount="6405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13754" uniqueCount="6410">
   <si>
     <t>名称</t>
   </si>
@@ -20678,6 +20678,21 @@
   </si>
   <si>
     <t>事件发射器</t>
+  </si>
+  <si>
+    <t>双端字符匹配</t>
+  </si>
+  <si>
+    <t>设计事件管理器</t>
+  </si>
+  <si>
+    <t>可排序整数求和</t>
+  </si>
+  <si>
+    <t>枚举 + 模拟</t>
+  </si>
+  <si>
+    <t>增量偶权环查询</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -94105,16 +94120,84 @@
       </c>
     </row>
     <row r="3404" spans="1:14">
-      <c r="C3404" s="2"/>
+      <c r="A3404">
+        <v>3884</v>
+      </c>
+      <c r="B3404" t="s">
+        <v>6015</v>
+      </c>
+      <c r="C3404" s="2">
+        <v>46110</v>
+      </c>
+      <c r="D3404" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3404" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3404" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3405" spans="1:14">
-      <c r="C3405" s="2"/>
+      <c r="A3405">
+        <v>3885</v>
+      </c>
+      <c r="B3405" t="s">
+        <v>6016</v>
+      </c>
+      <c r="C3405" s="2">
+        <v>46110</v>
+      </c>
+      <c r="D3405" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3405" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3405" s="1" t="s">
+        <v>1529</v>
+      </c>
     </row>
     <row r="3406" spans="1:14">
-      <c r="C3406" s="2"/>
+      <c r="A3406">
+        <v>3886</v>
+      </c>
+      <c r="B3406" t="s">
+        <v>6017</v>
+      </c>
+      <c r="C3406" s="2">
+        <v>46110</v>
+      </c>
+      <c r="D3406" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3406" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3406" s="1" t="s">
+        <v>6018</v>
+      </c>
     </row>
     <row r="3407" spans="1:14">
-      <c r="C3407" s="2"/>
+      <c r="A3407">
+        <v>3887</v>
+      </c>
+      <c r="B3407" t="s">
+        <v>6019</v>
+      </c>
+      <c r="C3407" s="2">
+        <v>46110</v>
+      </c>
+      <c r="D3407" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3407" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3407" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="3408" spans="1:14">
       <c r="C3408" s="2"/>
@@ -94133,7 +94216,7 @@
         <v>3454</v>
       </c>
       <c r="B3413" t="s">
-        <v>6015</v>
+        <v>6020</v>
       </c>
       <c r="D3413" t="s">
         <v>138</v>
@@ -94153,7 +94236,7 @@
         <v>3562</v>
       </c>
       <c r="B3414" t="s">
-        <v>6016</v>
+        <v>6021</v>
       </c>
       <c r="D3414" t="s">
         <v>138</v>
@@ -94164,10 +94247,10 @@
     </row>
     <row r="3415" spans="1:7">
       <c r="A3415" t="s">
-        <v>6017</v>
+        <v>6022</v>
       </c>
       <c r="B3415" t="s">
-        <v>6018</v>
+        <v>6023</v>
       </c>
       <c r="D3415" t="s">
         <v>138</v>
@@ -94178,7 +94261,7 @@
         <v>3721</v>
       </c>
       <c r="B3416" t="s">
-        <v>6019</v>
+        <v>6024</v>
       </c>
       <c r="D3416" t="s">
         <v>138</v>
@@ -94195,7 +94278,7 @@
         <v>3235</v>
       </c>
       <c r="B3417" t="s">
-        <v>6020</v>
+        <v>6025</v>
       </c>
       <c r="C3417" s="2"/>
       <c r="D3417" t="s">
@@ -94206,7 +94289,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3400" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3403" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94253,10 +94336,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6021</v>
+        <v>6026</v>
       </c>
       <c r="D5" t="s">
-        <v>6022</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94267,13 +94350,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6023</v>
+        <v>6028</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6024</v>
+        <v>6029</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94282,7 +94365,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6025</v>
+        <v>6030</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94297,16 +94380,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6026</v>
+        <v>6031</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6027</v>
+        <v>6032</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6028</v>
+        <v>6033</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94320,10 +94403,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6029</v>
+        <v>6034</v>
       </c>
       <c r="H14" t="s">
-        <v>6030</v>
+        <v>6035</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94338,16 +94421,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6031</v>
+        <v>6036</v>
       </c>
       <c r="W14" t="s">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6033</v>
+        <v>6038</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94359,158 +94442,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="AL14" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
       <c r="AO14" t="s">
-        <v>6037</v>
+        <v>6042</v>
       </c>
       <c r="AR14" t="s">
-        <v>6038</v>
+        <v>6043</v>
       </c>
       <c r="AU14" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="AX14" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6041</v>
+        <v>6046</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="T15" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="W15" t="s">
-        <v>6047</v>
+        <v>6052</v>
       </c>
       <c r="Z15" t="s">
-        <v>6048</v>
+        <v>6053</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="AF15" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="AI15" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
       <c r="AL15" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
       <c r="AU15" t="s">
-        <v>6054</v>
+        <v>6059</v>
       </c>
       <c r="AX15" t="s">
-        <v>6055</v>
+        <v>6060</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="H16" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="N16" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="T16" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="W16" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="Z16" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
       <c r="AC16" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
       <c r="AF16" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="AI16" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="AL16" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
       <c r="AR16" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="AU16" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AX16" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94518,43 +94601,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="D17" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="H17" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
       <c r="N17" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="T17" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
       <c r="W17" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="Z17" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="AC17" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="AF17" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="AI17" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="AR17" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="AU17" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="BA17" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94562,37 +94645,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="H18" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="N18" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="T18" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="W18" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="Z18" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="AC18" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="AF18" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="AI18" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="AU18" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="BA18" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94600,37 +94683,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
       <c r="H19" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="N19" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="T19" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="W19" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="Z19" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="AC19" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="AF19" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="AI19" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="AU19" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="BA19" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94638,37 +94721,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="D20" t="s">
+        <v>6107</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6108</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6109</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6110</v>
+      </c>
+      <c r="W20" t="s">
         <v>6102</v>
       </c>
-      <c r="H20" t="s">
-        <v>6103</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6104</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6105</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6097</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="AC20" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="AF20" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="AU20" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="BA20" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94676,37 +94759,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="D21" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="H21" t="s">
+        <v>6117</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6118</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6119</v>
+      </c>
+      <c r="W21" t="s">
         <v>6112</v>
       </c>
-      <c r="N21" t="s">
-        <v>6113</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6114</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6107</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AC21" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="AF21" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="AU21" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="BA21" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94717,13 +94800,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94732,16 +94815,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="AC22" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="AF22" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AU22" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94749,25 +94832,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="H23" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="T23" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="Z23" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="AC23" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="AF23" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="AU23" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94775,89 +94858,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="T24" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="Z24" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="AC24" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="AF24" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="D25" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="T25" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="AC25" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AF25" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="AC26" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="AF26" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="AC27" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AF27" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="AC28" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="AF28" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94867,22 +94950,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94892,7 +94975,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -94900,7 +94983,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -94915,7 +94998,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -94933,227 +95016,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="Q41" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="T41" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="W41" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="AL41" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="AO41" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="AR41" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="Q42" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="T42" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="W42" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="AC42" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="AL42" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="AO42" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="AR42" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="K43" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="N43" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="Q43" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="T43" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="W43" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="Z43" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="AC43" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="AF43" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="AL43" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="AO43" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
       <c r="AR43" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="F44" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="N44" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="Q44" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="W44" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="Z44" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="AC44" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="AF44" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="AL44" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="AO44" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="AR44" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="F45" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="N45" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
       <c r="Q45" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95162,103 +95245,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="AF45" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="AO45" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
       <c r="AR45" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="F46" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="N46" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="AC46" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="AF46" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="AO46" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
       <c r="AR46" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="F47" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="AC47" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="AF47" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="AO47" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="AR47" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="F48" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95270,141 +95353,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="AF48" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="AO48" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="AR48" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="AF49" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="AR49" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="F50" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="AR50" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="F51" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="AR51" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
       <c r="AR52" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="F53" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="F54" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="F55" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95412,10 +95495,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="F56" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95423,18 +95506,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="F57" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="F58" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95442,42 +95525,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="F59" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
       <c r="F60" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="F61" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="F62" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
       <c r="F63" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95485,181 +95568,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="F64" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="F65" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="F66" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="F67" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="F68" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
       <c r="F69" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
     </row>
   </sheetData>
@@ -95686,10 +95769,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -95698,13 +95781,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95712,13 +95795,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95730,13 +95813,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -95747,19 +95830,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
       <c r="S10" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
       <c r="T10" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95773,15 +95856,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
       <c r="S11" t="s">
-        <v>6054</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95790,18 +95873,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -95810,7 +95893,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95821,13 +95904,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95838,7 +95921,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95847,10 +95930,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="T15" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95861,12 +95944,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95874,22 +95957,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95900,39 +95983,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
       <c r="H32" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
       <c r="K32" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
       <c r="N32" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="Q32" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="S32" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -95941,13 +96024,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
       <c r="K33" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
       <c r="N33" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -95955,153 +96038,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
       <c r="K34" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
       <c r="N34" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
       <c r="N35" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
       <c r="N36" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
       <c r="N37" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
       <c r="N38" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96109,7 +96192,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96125,7 +96208,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96141,21 +96224,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
       <c r="J68" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96164,52 +96247,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6023</v>
+        <v>6028</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6395</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6396</v>
+        <v>6401</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6397</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96271,7 +96354,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6398</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96279,10 +96362,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6399</v>
+        <v>6404</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6400</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96290,7 +96373,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6401</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96303,15 +96386,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6402</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6403</v>
+        <v>6408</v>
       </c>
       <c r="F17" t="s">
-        <v>6404</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3403</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3407</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13754" uniqueCount="6410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13763" uniqueCount="6414">
   <si>
     <t>名称</t>
   </si>
@@ -20693,6 +20693,18 @@
   </si>
   <si>
     <t>增量偶权环查询</t>
+  </si>
+  <si>
+    <t>LCR 076</t>
+  </si>
+  <si>
+    <t>数组中的第 K 个最大元素</t>
+  </si>
+  <si>
+    <t>同215题</t>
+  </si>
+  <si>
+    <t>最小操作次数使数组元素相等 III</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22355,8 +22367,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22368,9 +22381,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -94200,10 +94212,47 @@
       </c>
     </row>
     <row r="3408" spans="1:14">
-      <c r="C3408" s="2"/>
+      <c r="A3408" t="s">
+        <v>6020</v>
+      </c>
+      <c r="B3408" t="s">
+        <v>6021</v>
+      </c>
+      <c r="C3408" s="2">
+        <v>46111</v>
+      </c>
+      <c r="D3408" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3408" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3408" s="1" t="s">
+        <v>6022</v>
+      </c>
     </row>
     <row r="3409" spans="1:7">
-      <c r="C3409" s="2"/>
+      <c r="A3409">
+        <v>3736</v>
+      </c>
+      <c r="B3409" t="s">
+        <v>6023</v>
+      </c>
+      <c r="C3409" s="2">
+        <v>46111</v>
+      </c>
+      <c r="D3409" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3409" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3409">
+        <v>1251</v>
+      </c>
+      <c r="G3409" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3410" spans="1:7">
       <c r="C3410" s="2"/>
@@ -94216,7 +94265,7 @@
         <v>3454</v>
       </c>
       <c r="B3413" t="s">
-        <v>6020</v>
+        <v>6024</v>
       </c>
       <c r="D3413" t="s">
         <v>138</v>
@@ -94236,7 +94285,7 @@
         <v>3562</v>
       </c>
       <c r="B3414" t="s">
-        <v>6021</v>
+        <v>6025</v>
       </c>
       <c r="D3414" t="s">
         <v>138</v>
@@ -94247,10 +94296,10 @@
     </row>
     <row r="3415" spans="1:7">
       <c r="A3415" t="s">
-        <v>6022</v>
+        <v>6026</v>
       </c>
       <c r="B3415" t="s">
-        <v>6023</v>
+        <v>6027</v>
       </c>
       <c r="D3415" t="s">
         <v>138</v>
@@ -94261,7 +94310,7 @@
         <v>3721</v>
       </c>
       <c r="B3416" t="s">
-        <v>6024</v>
+        <v>6028</v>
       </c>
       <c r="D3416" t="s">
         <v>138</v>
@@ -94278,7 +94327,7 @@
         <v>3235</v>
       </c>
       <c r="B3417" t="s">
-        <v>6025</v>
+        <v>6029</v>
       </c>
       <c r="C3417" s="2"/>
       <c r="D3417" t="s">
@@ -94289,7 +94338,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3403" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3407" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94336,10 +94385,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6026</v>
+        <v>6030</v>
       </c>
       <c r="D5" t="s">
-        <v>6027</v>
+        <v>6031</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94350,13 +94399,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6029</v>
+        <v>6033</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94365,7 +94414,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6030</v>
+        <v>6034</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94380,16 +94429,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6031</v>
+        <v>6035</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6032</v>
+        <v>6036</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6033</v>
+        <v>6037</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94403,10 +94452,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6034</v>
+        <v>6038</v>
       </c>
       <c r="H14" t="s">
-        <v>6035</v>
+        <v>6039</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94421,16 +94470,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="W14" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94442,158 +94491,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="AL14" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="AO14" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="AR14" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
       <c r="AU14" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="AX14" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="T15" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="W15" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="Z15" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AF15" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AI15" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AL15" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AU15" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="AX15" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="H16" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="N16" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="T16" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="W16" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="Z16" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="AC16" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AF16" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="AI16" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="AL16" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AR16" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AU16" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AX16" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94601,43 +94650,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="D17" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="H17" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="N17" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="T17" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="W17" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="Z17" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="AC17" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AF17" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AI17" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AR17" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AU17" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="BA17" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94645,37 +94694,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="H18" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="N18" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="T18" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="W18" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="Z18" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="AC18" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AF18" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="AI18" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="AU18" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="BA18" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94683,37 +94732,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="H19" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="N19" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="T19" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="W19" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="Z19" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AC19" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="AF19" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AI19" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="AU19" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="BA19" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94721,37 +94770,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6111</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6112</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6113</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6114</v>
+      </c>
+      <c r="W20" t="s">
         <v>6106</v>
       </c>
-      <c r="D20" t="s">
-        <v>6107</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6108</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6109</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6110</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6102</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="AC20" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AF20" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AU20" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="BA20" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94759,37 +94808,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="D21" t="s">
+        <v>6120</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6121</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6122</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6123</v>
+      </c>
+      <c r="W21" t="s">
         <v>6116</v>
       </c>
-      <c r="H21" t="s">
-        <v>6117</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6118</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6119</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6112</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AC21" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AF21" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AU21" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="BA21" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94800,13 +94849,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94815,16 +94864,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AC22" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AF22" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AU22" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94832,25 +94881,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="H23" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="T23" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="Z23" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AC23" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AF23" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AU23" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94858,89 +94907,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="T24" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="Z24" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AC24" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AF24" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="D25" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="T25" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AC25" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AF25" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AC26" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AF26" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AC27" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AF27" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AC28" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AF28" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94950,22 +94999,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -94975,7 +95024,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -94983,7 +95032,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -94998,7 +95047,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95016,227 +95065,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="Q41" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="T41" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="W41" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="AL41" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AO41" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="AR41" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="Q42" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="T42" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="W42" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="AC42" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AL42" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AO42" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="AR42" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="K43" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="N43" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="Q43" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="T43" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="W43" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="Z43" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="AC43" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="AF43" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="AL43" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AO43" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AR43" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="F44" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="N44" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="Q44" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="W44" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="Z44" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="AC44" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="AF44" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="AL44" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="AO44" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="AR44" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="F45" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="N45" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="Q45" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95245,103 +95294,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="AF45" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AO45" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="AR45" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="F46" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="N46" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AC46" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="AF46" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AO46" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="AR46" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="F47" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="AC47" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="AF47" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="AO47" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="AR47" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="F48" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95353,141 +95402,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="AF48" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="AO48" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="AR48" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="AF49" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="AR49" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="F50" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="AR50" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="F51" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="AR51" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="AR52" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="F53" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="F54" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="F55" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95495,10 +95544,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="F56" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95506,18 +95555,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="F57" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="F58" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95525,42 +95574,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="F59" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="F60" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="F62" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="F63" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95568,181 +95617,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="F64" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="F65" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="F66" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="F67" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="F68" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="F69" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
   </sheetData>
@@ -95769,10 +95818,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -95781,13 +95830,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95795,13 +95844,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95813,13 +95862,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -95830,19 +95879,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="S10" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="T10" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95856,15 +95905,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
       <c r="S11" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95873,18 +95922,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -95893,7 +95942,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95904,13 +95953,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95921,7 +95970,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95930,10 +95979,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="T15" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95944,12 +95993,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -95957,22 +96006,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -95983,39 +96032,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="H32" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
       <c r="K32" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
       <c r="N32" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
       <c r="Q32" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="S32" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96024,13 +96073,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
       <c r="K33" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
       <c r="N33" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96038,153 +96087,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="K34" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
       <c r="N34" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="N35" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
       <c r="N36" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
       <c r="N37" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
       <c r="N38" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96192,7 +96241,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96208,7 +96257,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96224,21 +96273,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
       <c r="J68" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96247,52 +96296,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6028</v>
+        <v>6032</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96354,7 +96403,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96362,10 +96411,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96373,7 +96422,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96386,15 +96435,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
       <c r="F17" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3407</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3412</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13763" uniqueCount="6414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13781" uniqueCount="6421">
   <si>
     <t>名称</t>
   </si>
@@ -20705,6 +20705,27 @@
   </si>
   <si>
     <t>最小操作次数使数组元素相等 III</t>
+  </si>
+  <si>
+    <t>范围内总波动值 I</t>
+  </si>
+  <si>
+    <t>LCR 077</t>
+  </si>
+  <si>
+    <t>同148题</t>
+  </si>
+  <si>
+    <t>将数字变成二进制回文数的最少操作</t>
+  </si>
+  <si>
+    <t>预处理 + 二分</t>
+  </si>
+  <si>
+    <t>完全质数</t>
+  </si>
+  <si>
+    <t>要看清题目</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22367,14 +22388,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22383,6 +22396,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23334,7 +23355,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3417"/>
+  <dimension ref="A1:N3427"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -94231,7 +94252,7 @@
         <v>6022</v>
       </c>
     </row>
-    <row r="3409" spans="1:7">
+    <row r="3409" spans="1:8">
       <c r="A3409">
         <v>3736</v>
       </c>
@@ -94254,91 +94275,201 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3410" spans="1:7">
-      <c r="C3410" s="2"/>
-    </row>
-    <row r="3411" spans="1:7">
-      <c r="C3411" s="2"/>
-    </row>
-    <row r="3413" spans="1:7">
+    <row r="3410" spans="1:8">
+      <c r="A3410">
+        <v>3751</v>
+      </c>
+      <c r="B3410" t="s">
+        <v>6024</v>
+      </c>
+      <c r="C3410" s="2">
+        <v>46111</v>
+      </c>
+      <c r="D3410" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3410" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3410">
+        <v>1404</v>
+      </c>
+      <c r="G3410" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="3411" spans="1:8">
+      <c r="A3411" t="s">
+        <v>6025</v>
+      </c>
+      <c r="B3411" t="s">
+        <v>421</v>
+      </c>
+      <c r="C3411" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D3411" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3411" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3411" s="1" t="s">
+        <v>6026</v>
+      </c>
+    </row>
+    <row r="3412" spans="1:8">
+      <c r="A3412">
+        <v>3766</v>
+      </c>
+      <c r="B3412" t="s">
+        <v>6027</v>
+      </c>
+      <c r="C3412" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D3412" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3412" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3412">
+        <v>1656</v>
+      </c>
+      <c r="G3412" s="1" t="s">
+        <v>6028</v>
+      </c>
+    </row>
+    <row r="3413" spans="1:8">
       <c r="A3413">
+        <v>3765</v>
+      </c>
+      <c r="B3413" t="s">
+        <v>6029</v>
+      </c>
+      <c r="C3413" s="2">
+        <v>46112</v>
+      </c>
+      <c r="D3413" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3413" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3413">
+        <v>1378</v>
+      </c>
+      <c r="G3413" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H3413" s="1" t="s">
+        <v>6030</v>
+      </c>
+    </row>
+    <row r="3414" spans="1:8">
+      <c r="C3414" s="2"/>
+    </row>
+    <row r="3415" spans="1:8">
+      <c r="C3415" s="2"/>
+    </row>
+    <row r="3416" spans="1:8">
+      <c r="C3416" s="2"/>
+    </row>
+    <row r="3417" spans="1:8">
+      <c r="C3417" s="2"/>
+    </row>
+    <row r="3418" spans="1:8">
+      <c r="C3418" s="2"/>
+    </row>
+    <row r="3419" spans="1:8">
+      <c r="C3419" s="2"/>
+    </row>
+    <row r="3420" spans="1:8">
+      <c r="C3420" s="2"/>
+    </row>
+    <row r="3421" spans="1:8">
+      <c r="C3421" s="2"/>
+    </row>
+    <row r="3423" spans="1:8">
+      <c r="A3423">
         <v>3454</v>
       </c>
-      <c r="B3413" t="s">
-        <v>6024</v>
-      </c>
-      <c r="D3413" t="s">
+      <c r="B3423" t="s">
+        <v>6031</v>
+      </c>
+      <c r="D3423" t="s">
         <v>138</v>
       </c>
-      <c r="E3413" t="s">
+      <c r="E3423" t="s">
         <v>74</v>
       </c>
-      <c r="F3413">
+      <c r="F3423">
         <v>2671</v>
       </c>
-      <c r="G3413" s="1" t="s">
+      <c r="G3423" s="1" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="3414" spans="1:7">
-      <c r="A3414">
+    <row r="3424" spans="1:8">
+      <c r="A3424">
         <v>3562</v>
       </c>
-      <c r="B3414" t="s">
-        <v>6025</v>
-      </c>
-      <c r="D3414" t="s">
+      <c r="B3424" t="s">
+        <v>6032</v>
+      </c>
+      <c r="D3424" t="s">
         <v>138</v>
       </c>
-      <c r="F3414">
+      <c r="F3424">
         <v>2458</v>
       </c>
     </row>
-    <row r="3415" spans="1:7">
-      <c r="A3415" t="s">
-        <v>6026</v>
-      </c>
-      <c r="B3415" t="s">
-        <v>6027</v>
-      </c>
-      <c r="D3415" t="s">
+    <row r="3425" spans="1:6">
+      <c r="A3425" t="s">
+        <v>6033</v>
+      </c>
+      <c r="B3425" t="s">
+        <v>6034</v>
+      </c>
+      <c r="D3425" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3416" spans="1:7">
-      <c r="A3416">
+    <row r="3426" spans="1:6">
+      <c r="A3426">
         <v>3721</v>
       </c>
-      <c r="B3416" t="s">
-        <v>6028</v>
-      </c>
-      <c r="D3416" t="s">
+      <c r="B3426" t="s">
+        <v>6035</v>
+      </c>
+      <c r="D3426" t="s">
         <v>138</v>
       </c>
-      <c r="E3416" t="s">
+      <c r="E3426" t="s">
         <v>74</v>
       </c>
-      <c r="F3416">
+      <c r="F3426">
         <v>2723</v>
       </c>
     </row>
-    <row r="3417" spans="1:7">
-      <c r="A3417">
+    <row r="3427" spans="1:6">
+      <c r="A3427">
         <v>3235</v>
       </c>
-      <c r="B3417" t="s">
-        <v>6029</v>
-      </c>
-      <c r="C3417" s="2"/>
-      <c r="D3417" t="s">
+      <c r="B3427" t="s">
+        <v>6036</v>
+      </c>
+      <c r="C3427" s="2"/>
+      <c r="D3427" t="s">
         <v>138</v>
       </c>
-      <c r="F3417">
+      <c r="F3427">
         <v>3773</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3407" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3412" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94385,10 +94516,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6030</v>
+        <v>6037</v>
       </c>
       <c r="D5" t="s">
-        <v>6031</v>
+        <v>6038</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94399,13 +94530,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6032</v>
+        <v>6039</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6033</v>
+        <v>6040</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94414,7 +94545,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6034</v>
+        <v>6041</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94429,16 +94560,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6035</v>
+        <v>6042</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6036</v>
+        <v>6043</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6037</v>
+        <v>6044</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94452,10 +94583,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6038</v>
+        <v>6045</v>
       </c>
       <c r="H14" t="s">
-        <v>6039</v>
+        <v>6046</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94470,16 +94601,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6040</v>
+        <v>6047</v>
       </c>
       <c r="W14" t="s">
-        <v>6041</v>
+        <v>6048</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6042</v>
+        <v>6049</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94491,158 +94622,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6043</v>
+        <v>6050</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6044</v>
+        <v>6051</v>
       </c>
       <c r="AL14" t="s">
-        <v>6045</v>
+        <v>6052</v>
       </c>
       <c r="AO14" t="s">
-        <v>6046</v>
+        <v>6053</v>
       </c>
       <c r="AR14" t="s">
-        <v>6047</v>
+        <v>6054</v>
       </c>
       <c r="AU14" t="s">
-        <v>6048</v>
+        <v>6055</v>
       </c>
       <c r="AX14" t="s">
-        <v>6049</v>
+        <v>6056</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6050</v>
+        <v>6057</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6051</v>
+        <v>6058</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6052</v>
+        <v>6059</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6053</v>
+        <v>6060</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6054</v>
+        <v>6061</v>
       </c>
       <c r="T15" t="s">
-        <v>6055</v>
+        <v>6062</v>
       </c>
       <c r="W15" t="s">
-        <v>6056</v>
+        <v>6063</v>
       </c>
       <c r="Z15" t="s">
-        <v>6057</v>
+        <v>6064</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6058</v>
+        <v>6065</v>
       </c>
       <c r="AF15" t="s">
-        <v>6059</v>
+        <v>6066</v>
       </c>
       <c r="AI15" t="s">
-        <v>6060</v>
+        <v>6067</v>
       </c>
       <c r="AL15" t="s">
-        <v>6061</v>
+        <v>6068</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6062</v>
+        <v>6069</v>
       </c>
       <c r="AU15" t="s">
-        <v>6063</v>
+        <v>6070</v>
       </c>
       <c r="AX15" t="s">
-        <v>6064</v>
+        <v>6071</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6065</v>
+        <v>6072</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6066</v>
+        <v>6073</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6067</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
+        <v>6075</v>
+      </c>
+      <c r="H16" t="s">
+        <v>6076</v>
+      </c>
+      <c r="N16" t="s">
+        <v>6077</v>
+      </c>
+      <c r="T16" t="s">
+        <v>6078</v>
+      </c>
+      <c r="W16" t="s">
+        <v>6079</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>6080</v>
+      </c>
+      <c r="AC16" t="s">
         <v>6068</v>
       </c>
-      <c r="H16" t="s">
-        <v>6069</v>
-      </c>
-      <c r="N16" t="s">
-        <v>6070</v>
-      </c>
-      <c r="T16" t="s">
-        <v>6071</v>
-      </c>
-      <c r="W16" t="s">
-        <v>6072</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>6073</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>6061</v>
-      </c>
       <c r="AF16" t="s">
-        <v>6043</v>
+        <v>6050</v>
       </c>
       <c r="AI16" t="s">
-        <v>6074</v>
+        <v>6081</v>
       </c>
       <c r="AL16" t="s">
-        <v>6075</v>
+        <v>6082</v>
       </c>
       <c r="AR16" t="s">
-        <v>6076</v>
+        <v>6083</v>
       </c>
       <c r="AU16" t="s">
-        <v>6077</v>
+        <v>6084</v>
       </c>
       <c r="AX16" t="s">
-        <v>6078</v>
+        <v>6085</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6079</v>
+        <v>6086</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94650,43 +94781,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6080</v>
+        <v>6087</v>
       </c>
       <c r="D17" t="s">
-        <v>6081</v>
+        <v>6088</v>
       </c>
       <c r="H17" t="s">
-        <v>6082</v>
+        <v>6089</v>
       </c>
       <c r="N17" t="s">
-        <v>6083</v>
+        <v>6090</v>
       </c>
       <c r="T17" t="s">
-        <v>6084</v>
+        <v>6091</v>
       </c>
       <c r="W17" t="s">
-        <v>6043</v>
+        <v>6050</v>
       </c>
       <c r="Z17" t="s">
-        <v>6054</v>
+        <v>6061</v>
       </c>
       <c r="AC17" t="s">
-        <v>6085</v>
+        <v>6092</v>
       </c>
       <c r="AF17" t="s">
-        <v>6086</v>
+        <v>6093</v>
       </c>
       <c r="AI17" t="s">
-        <v>6087</v>
+        <v>6094</v>
       </c>
       <c r="AR17" t="s">
-        <v>6088</v>
+        <v>6095</v>
       </c>
       <c r="AU17" t="s">
-        <v>6089</v>
+        <v>6096</v>
       </c>
       <c r="BA17" t="s">
-        <v>6090</v>
+        <v>6097</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94694,37 +94825,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6091</v>
+        <v>6098</v>
       </c>
       <c r="H18" t="s">
-        <v>6092</v>
+        <v>6099</v>
       </c>
       <c r="N18" t="s">
-        <v>6093</v>
+        <v>6100</v>
       </c>
       <c r="T18" t="s">
-        <v>6094</v>
+        <v>6101</v>
       </c>
       <c r="W18" t="s">
-        <v>6095</v>
+        <v>6102</v>
       </c>
       <c r="Z18" t="s">
-        <v>6070</v>
+        <v>6077</v>
       </c>
       <c r="AC18" t="s">
-        <v>6096</v>
+        <v>6103</v>
       </c>
       <c r="AF18" t="s">
-        <v>6097</v>
+        <v>6104</v>
       </c>
       <c r="AI18" t="s">
-        <v>6098</v>
+        <v>6105</v>
       </c>
       <c r="AU18" t="s">
-        <v>6099</v>
+        <v>6106</v>
       </c>
       <c r="BA18" t="s">
-        <v>6100</v>
+        <v>6107</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94732,37 +94863,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6101</v>
+        <v>6108</v>
       </c>
       <c r="H19" t="s">
-        <v>6102</v>
+        <v>6109</v>
       </c>
       <c r="N19" t="s">
-        <v>6103</v>
+        <v>6110</v>
       </c>
       <c r="T19" t="s">
-        <v>6104</v>
+        <v>6111</v>
       </c>
       <c r="W19" t="s">
-        <v>6078</v>
+        <v>6085</v>
       </c>
       <c r="Z19" t="s">
-        <v>6083</v>
+        <v>6090</v>
       </c>
       <c r="AC19" t="s">
-        <v>6105</v>
+        <v>6112</v>
       </c>
       <c r="AF19" t="s">
-        <v>6106</v>
+        <v>6113</v>
       </c>
       <c r="AI19" t="s">
-        <v>6107</v>
+        <v>6114</v>
       </c>
       <c r="AU19" t="s">
-        <v>6108</v>
+        <v>6115</v>
       </c>
       <c r="BA19" t="s">
-        <v>6109</v>
+        <v>6116</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94770,37 +94901,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6110</v>
+        <v>6117</v>
       </c>
       <c r="D20" t="s">
-        <v>6111</v>
+        <v>6118</v>
       </c>
       <c r="H20" t="s">
-        <v>6112</v>
+        <v>6119</v>
       </c>
       <c r="N20" t="s">
+        <v>6120</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6121</v>
+      </c>
+      <c r="W20" t="s">
         <v>6113</v>
       </c>
-      <c r="T20" t="s">
-        <v>6114</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6106</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6093</v>
+        <v>6100</v>
       </c>
       <c r="AC20" t="s">
-        <v>6115</v>
+        <v>6122</v>
       </c>
       <c r="AF20" t="s">
-        <v>6116</v>
+        <v>6123</v>
       </c>
       <c r="AU20" t="s">
-        <v>6117</v>
+        <v>6124</v>
       </c>
       <c r="BA20" t="s">
-        <v>6118</v>
+        <v>6125</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94808,37 +94939,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6119</v>
+        <v>6126</v>
       </c>
       <c r="D21" t="s">
-        <v>6120</v>
+        <v>6127</v>
       </c>
       <c r="H21" t="s">
-        <v>6121</v>
+        <v>6128</v>
       </c>
       <c r="N21" t="s">
-        <v>6122</v>
+        <v>6129</v>
       </c>
       <c r="T21" t="s">
+        <v>6130</v>
+      </c>
+      <c r="W21" t="s">
         <v>6123</v>
       </c>
-      <c r="W21" t="s">
-        <v>6116</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6103</v>
+        <v>6110</v>
       </c>
       <c r="AC21" t="s">
-        <v>6124</v>
+        <v>6131</v>
       </c>
       <c r="AF21" t="s">
-        <v>6125</v>
+        <v>6132</v>
       </c>
       <c r="AU21" t="s">
-        <v>6126</v>
+        <v>6133</v>
       </c>
       <c r="BA21" t="s">
-        <v>6127</v>
+        <v>6134</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94849,13 +94980,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6128</v>
+        <v>6135</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6129</v>
+        <v>6136</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94864,16 +94995,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6113</v>
+        <v>6120</v>
       </c>
       <c r="AC22" t="s">
-        <v>6130</v>
+        <v>6137</v>
       </c>
       <c r="AF22" t="s">
-        <v>6131</v>
+        <v>6138</v>
       </c>
       <c r="AU22" t="s">
-        <v>6132</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -94881,25 +95012,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6133</v>
+        <v>6140</v>
       </c>
       <c r="H23" t="s">
-        <v>6134</v>
+        <v>6141</v>
       </c>
       <c r="T23" t="s">
-        <v>6135</v>
+        <v>6142</v>
       </c>
       <c r="Z23" t="s">
-        <v>6122</v>
+        <v>6129</v>
       </c>
       <c r="AC23" t="s">
-        <v>6136</v>
+        <v>6143</v>
       </c>
       <c r="AF23" t="s">
-        <v>6137</v>
+        <v>6144</v>
       </c>
       <c r="AU23" t="s">
-        <v>6138</v>
+        <v>6145</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -94907,89 +95038,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6139</v>
+        <v>6146</v>
       </c>
       <c r="T24" t="s">
-        <v>6140</v>
+        <v>6147</v>
       </c>
       <c r="Z24" t="s">
-        <v>6141</v>
+        <v>6148</v>
       </c>
       <c r="AC24" t="s">
-        <v>6142</v>
+        <v>6149</v>
       </c>
       <c r="AF24" t="s">
-        <v>6143</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6144</v>
+        <v>6151</v>
       </c>
       <c r="D25" t="s">
-        <v>6145</v>
+        <v>6152</v>
       </c>
       <c r="T25" t="s">
-        <v>6146</v>
+        <v>6153</v>
       </c>
       <c r="AC25" t="s">
-        <v>6147</v>
+        <v>6154</v>
       </c>
       <c r="AF25" t="s">
-        <v>6148</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6149</v>
+        <v>6156</v>
       </c>
       <c r="AC26" t="s">
-        <v>6150</v>
+        <v>6157</v>
       </c>
       <c r="AF26" t="s">
-        <v>6151</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6152</v>
+        <v>6159</v>
       </c>
       <c r="AC27" t="s">
-        <v>6153</v>
+        <v>6160</v>
       </c>
       <c r="AF27" t="s">
-        <v>6154</v>
+        <v>6161</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6155</v>
+        <v>6162</v>
       </c>
       <c r="AC28" t="s">
-        <v>6156</v>
+        <v>6163</v>
       </c>
       <c r="AF28" t="s">
-        <v>6157</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6158</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6159</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6160</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6161</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -94999,22 +95130,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6162</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6163</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6164</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6165</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95024,7 +95155,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6166</v>
+        <v>6173</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95032,7 +95163,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6167</v>
+        <v>6174</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95047,7 +95178,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6168</v>
+        <v>6175</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95065,227 +95196,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6169</v>
+        <v>6176</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6170</v>
+        <v>6177</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6171</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6172</v>
+        <v>6179</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6173</v>
+        <v>6180</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6174</v>
+        <v>6181</v>
       </c>
       <c r="Q41" t="s">
-        <v>6162</v>
+        <v>6169</v>
       </c>
       <c r="T41" t="s">
-        <v>6058</v>
+        <v>6065</v>
       </c>
       <c r="W41" t="s">
-        <v>6175</v>
+        <v>6182</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6176</v>
+        <v>6183</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6177</v>
+        <v>6184</v>
       </c>
       <c r="AL41" t="s">
-        <v>6178</v>
+        <v>6185</v>
       </c>
       <c r="AO41" t="s">
-        <v>6179</v>
+        <v>6186</v>
       </c>
       <c r="AR41" t="s">
-        <v>6180</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6181</v>
+        <v>6188</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6182</v>
+        <v>6189</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6183</v>
+        <v>6190</v>
       </c>
       <c r="Q42" t="s">
-        <v>6163</v>
+        <v>6170</v>
       </c>
       <c r="T42" t="s">
-        <v>6184</v>
+        <v>6191</v>
       </c>
       <c r="W42" t="s">
-        <v>6185</v>
+        <v>6192</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6186</v>
+        <v>6193</v>
       </c>
       <c r="AC42" t="s">
-        <v>6187</v>
+        <v>6194</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6188</v>
+        <v>6195</v>
       </c>
       <c r="AL42" t="s">
-        <v>6189</v>
+        <v>6196</v>
       </c>
       <c r="AO42" t="s">
-        <v>6190</v>
+        <v>6197</v>
       </c>
       <c r="AR42" t="s">
-        <v>6191</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6192</v>
+        <v>6199</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6193</v>
+        <v>6200</v>
       </c>
       <c r="K43" t="s">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="N43" t="s">
-        <v>6195</v>
+        <v>6202</v>
       </c>
       <c r="Q43" t="s">
-        <v>6164</v>
+        <v>6171</v>
       </c>
       <c r="T43" t="s">
-        <v>6196</v>
+        <v>6203</v>
       </c>
       <c r="W43" t="s">
-        <v>6197</v>
+        <v>6204</v>
       </c>
       <c r="Z43" t="s">
-        <v>6198</v>
+        <v>6205</v>
       </c>
       <c r="AC43" t="s">
-        <v>6199</v>
+        <v>6206</v>
       </c>
       <c r="AF43" t="s">
-        <v>6200</v>
+        <v>6207</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6201</v>
+        <v>6208</v>
       </c>
       <c r="AL43" t="s">
-        <v>6110</v>
+        <v>6117</v>
       </c>
       <c r="AO43" t="s">
-        <v>6202</v>
+        <v>6209</v>
       </c>
       <c r="AR43" t="s">
-        <v>6203</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6204</v>
+        <v>6211</v>
       </c>
       <c r="F44" t="s">
-        <v>6205</v>
+        <v>6212</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6206</v>
+        <v>6213</v>
       </c>
       <c r="N44" t="s">
-        <v>6207</v>
+        <v>6214</v>
       </c>
       <c r="Q44" t="s">
-        <v>6165</v>
+        <v>6172</v>
       </c>
       <c r="W44" t="s">
-        <v>6208</v>
+        <v>6215</v>
       </c>
       <c r="Z44" t="s">
-        <v>6209</v>
+        <v>6216</v>
       </c>
       <c r="AC44" t="s">
-        <v>6210</v>
+        <v>6217</v>
       </c>
       <c r="AF44" t="s">
-        <v>6147</v>
+        <v>6154</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6211</v>
+        <v>6218</v>
       </c>
       <c r="AL44" t="s">
-        <v>6212</v>
+        <v>6219</v>
       </c>
       <c r="AO44" t="s">
-        <v>6213</v>
+        <v>6220</v>
       </c>
       <c r="AR44" t="s">
-        <v>6214</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6215</v>
+        <v>6222</v>
       </c>
       <c r="F45" t="s">
-        <v>6216</v>
+        <v>6223</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6217</v>
+        <v>6224</v>
       </c>
       <c r="N45" t="s">
-        <v>6218</v>
+        <v>6225</v>
       </c>
       <c r="Q45" t="s">
-        <v>6219</v>
+        <v>6226</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95294,103 +95425,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6220</v>
+        <v>6227</v>
       </c>
       <c r="AF45" t="s">
-        <v>6221</v>
+        <v>6228</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6222</v>
+        <v>6229</v>
       </c>
       <c r="AO45" t="s">
-        <v>6223</v>
+        <v>6230</v>
       </c>
       <c r="AR45" t="s">
-        <v>6224</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6225</v>
+        <v>6232</v>
       </c>
       <c r="F46" t="s">
-        <v>6226</v>
+        <v>6233</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6227</v>
+        <v>6234</v>
       </c>
       <c r="N46" t="s">
-        <v>6228</v>
+        <v>6235</v>
       </c>
       <c r="AC46" t="s">
-        <v>6229</v>
+        <v>6236</v>
       </c>
       <c r="AF46" t="s">
-        <v>6230</v>
+        <v>6237</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6231</v>
+        <v>6238</v>
       </c>
       <c r="AO46" t="s">
-        <v>6232</v>
+        <v>6239</v>
       </c>
       <c r="AR46" t="s">
-        <v>6233</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6234</v>
+        <v>6241</v>
       </c>
       <c r="F47" t="s">
-        <v>6235</v>
+        <v>6242</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6236</v>
+        <v>6243</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6237</v>
+        <v>6244</v>
       </c>
       <c r="AC47" t="s">
-        <v>6238</v>
+        <v>6245</v>
       </c>
       <c r="AF47" t="s">
-        <v>6239</v>
+        <v>6246</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6240</v>
+        <v>6247</v>
       </c>
       <c r="AO47" t="s">
-        <v>6241</v>
+        <v>6248</v>
       </c>
       <c r="AR47" t="s">
-        <v>6242</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6243</v>
+        <v>6250</v>
       </c>
       <c r="F48" t="s">
-        <v>6244</v>
+        <v>6251</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95402,141 +95533,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6245</v>
+        <v>6252</v>
       </c>
       <c r="AF48" t="s">
-        <v>6246</v>
+        <v>6253</v>
       </c>
       <c r="AO48" t="s">
-        <v>6247</v>
+        <v>6254</v>
       </c>
       <c r="AR48" t="s">
-        <v>6248</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6249</v>
+        <v>6256</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6250</v>
+        <v>6257</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6251</v>
+        <v>6258</v>
       </c>
       <c r="AF49" t="s">
-        <v>6252</v>
+        <v>6259</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6253</v>
+        <v>6260</v>
       </c>
       <c r="AR49" t="s">
-        <v>6254</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6255</v>
+        <v>6262</v>
       </c>
       <c r="F50" t="s">
-        <v>6256</v>
+        <v>6263</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6257</v>
+        <v>6264</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6258</v>
+        <v>6265</v>
       </c>
       <c r="AR50" t="s">
-        <v>6259</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6260</v>
+        <v>6267</v>
       </c>
       <c r="F51" t="s">
-        <v>6261</v>
+        <v>6268</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6262</v>
+        <v>6269</v>
       </c>
       <c r="AR51" t="s">
-        <v>6263</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6264</v>
+        <v>6271</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6265</v>
+        <v>6272</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6266</v>
+        <v>6273</v>
       </c>
       <c r="AR52" t="s">
-        <v>6267</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6268</v>
+        <v>6275</v>
       </c>
       <c r="F53" t="s">
-        <v>6269</v>
+        <v>6276</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6270</v>
+        <v>6277</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6271</v>
+        <v>6278</v>
       </c>
       <c r="F54" t="s">
-        <v>6272</v>
+        <v>6279</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6273</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6274</v>
+        <v>6281</v>
       </c>
       <c r="F55" t="s">
-        <v>6275</v>
+        <v>6282</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95544,10 +95675,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6276</v>
+        <v>6283</v>
       </c>
       <c r="F56" t="s">
-        <v>6277</v>
+        <v>6284</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95555,18 +95686,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6278</v>
+        <v>6285</v>
       </c>
       <c r="F57" t="s">
-        <v>6279</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6280</v>
+        <v>6287</v>
       </c>
       <c r="F58" t="s">
-        <v>6281</v>
+        <v>6288</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95574,42 +95705,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6282</v>
+        <v>6289</v>
       </c>
       <c r="F59" t="s">
-        <v>6283</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="F60" t="s">
-        <v>6285</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6286</v>
+        <v>6293</v>
       </c>
       <c r="F61" t="s">
-        <v>6287</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6288</v>
+        <v>6295</v>
       </c>
       <c r="F62" t="s">
-        <v>6289</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6290</v>
+        <v>6297</v>
       </c>
       <c r="F63" t="s">
-        <v>6291</v>
+        <v>6298</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95617,181 +95748,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6292</v>
+        <v>6299</v>
       </c>
       <c r="F64" t="s">
-        <v>6293</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6255</v>
+        <v>6262</v>
       </c>
       <c r="F65" t="s">
-        <v>6246</v>
+        <v>6253</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6294</v>
+        <v>6301</v>
       </c>
       <c r="F66" t="s">
-        <v>6295</v>
+        <v>6302</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6296</v>
+        <v>6303</v>
       </c>
       <c r="F67" t="s">
-        <v>6297</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6298</v>
+        <v>6305</v>
       </c>
       <c r="F68" t="s">
-        <v>6262</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6299</v>
+        <v>6306</v>
       </c>
       <c r="F69" t="s">
-        <v>6300</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6301</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6302</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6303</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6304</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6305</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6306</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6307</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6308</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6309</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6310</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6311</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6312</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6313</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6314</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6315</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6316</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6317</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6318</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6319</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6320</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6059</v>
+        <v>6066</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6321</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6322</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6323</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6324</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6325</v>
+        <v>6332</v>
       </c>
     </row>
   </sheetData>
@@ -95818,10 +95949,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6326</v>
+        <v>6333</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6327</v>
+        <v>6334</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -95830,13 +95961,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6328</v>
+        <v>6335</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6329</v>
+        <v>6336</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6330</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95844,13 +95975,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6331</v>
+        <v>6338</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6332</v>
+        <v>6339</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95862,13 +95993,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6333</v>
+        <v>6340</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6334</v>
+        <v>6341</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -95879,19 +96010,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6335</v>
+        <v>6342</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6336</v>
+        <v>6343</v>
       </c>
       <c r="S10" t="s">
-        <v>6337</v>
+        <v>6344</v>
       </c>
       <c r="T10" t="s">
-        <v>6338</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -95905,15 +96036,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6339</v>
+        <v>6346</v>
       </c>
       <c r="S11" t="s">
-        <v>6063</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6340</v>
+        <v>6347</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -95922,18 +96053,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6341</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6342</v>
+        <v>6349</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6343</v>
+        <v>6350</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -95942,7 +96073,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6344</v>
+        <v>6351</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -95953,13 +96084,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6345</v>
+        <v>6352</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6346</v>
+        <v>6353</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -95970,7 +96101,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6347</v>
+        <v>6354</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -95979,10 +96110,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6230</v>
+        <v>6237</v>
       </c>
       <c r="T15" t="s">
-        <v>6348</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -95993,12 +96124,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6349</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6350</v>
+        <v>6357</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96006,22 +96137,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6351</v>
+        <v>6358</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6352</v>
+        <v>6359</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6353</v>
+        <v>6360</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6354</v>
+        <v>6361</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6355</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96032,39 +96163,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6356</v>
+        <v>6363</v>
       </c>
       <c r="H32" t="s">
-        <v>6357</v>
+        <v>6364</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6358</v>
+        <v>6365</v>
       </c>
       <c r="K32" t="s">
-        <v>6359</v>
+        <v>6366</v>
       </c>
       <c r="N32" t="s">
-        <v>6360</v>
+        <v>6367</v>
       </c>
       <c r="Q32" t="s">
-        <v>6361</v>
+        <v>6368</v>
       </c>
       <c r="S32" t="s">
-        <v>6087</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6362</v>
+        <v>6369</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6363</v>
+        <v>6370</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96073,13 +96204,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6364</v>
+        <v>6371</v>
       </c>
       <c r="K33" t="s">
-        <v>6365</v>
+        <v>6372</v>
       </c>
       <c r="N33" t="s">
-        <v>6366</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96087,153 +96218,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6367</v>
+        <v>6374</v>
       </c>
       <c r="K34" t="s">
-        <v>6368</v>
+        <v>6375</v>
       </c>
       <c r="N34" t="s">
-        <v>6369</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6370</v>
+        <v>6377</v>
       </c>
       <c r="N35" t="s">
-        <v>6371</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6372</v>
+        <v>6379</v>
       </c>
       <c r="N36" t="s">
-        <v>6373</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6374</v>
+        <v>6381</v>
       </c>
       <c r="N37" t="s">
-        <v>6375</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="N38" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6100</v>
+        <v>6107</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6379</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6380</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6381</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6382</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6383</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6384</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6385</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6386</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6387</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6277</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6388</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6389</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6275</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6390</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6391</v>
+        <v>6398</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6392</v>
+        <v>6399</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6393</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6394</v>
+        <v>6401</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6395</v>
+        <v>6402</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96241,7 +96372,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6396</v>
+        <v>6403</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96257,7 +96388,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6397</v>
+        <v>6404</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96273,21 +96404,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6398</v>
+        <v>6405</v>
       </c>
       <c r="J68" t="s">
-        <v>6399</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6400</v>
+        <v>6407</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6401</v>
+        <v>6408</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96296,52 +96427,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6175</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6402</v>
+        <v>6409</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6032</v>
+        <v>6039</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6185</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6208</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6403</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6404</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6197</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6405</v>
+        <v>6412</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6406</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96403,7 +96534,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6407</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96411,10 +96542,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6408</v>
+        <v>6415</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6409</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96422,7 +96553,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6410</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96435,15 +96566,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6411</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6412</v>
+        <v>6419</v>
       </c>
       <c r="F17" t="s">
-        <v>6413</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3412</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3413</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13781" uniqueCount="6421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13794" uniqueCount="6426">
   <si>
     <t>名称</t>
   </si>
@@ -20726,6 +20726,21 @@
   </si>
   <si>
     <t>要看清题目</t>
+  </si>
+  <si>
+    <t>LCR 098</t>
+  </si>
+  <si>
+    <t>同62题</t>
+  </si>
+  <si>
+    <t>得到互不相同元素的最少操作次数</t>
+  </si>
+  <si>
+    <t>逆序处理</t>
+  </si>
+  <si>
+    <t>间隔取消</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22394,16 +22409,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -94368,13 +94383,67 @@
       </c>
     </row>
     <row r="3414" spans="1:8">
-      <c r="C3414" s="2"/>
+      <c r="A3414" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B3414" t="s">
+        <v>544</v>
+      </c>
+      <c r="C3414" s="2">
+        <v>46113</v>
+      </c>
+      <c r="D3414" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3414" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3414" s="1" t="s">
+        <v>6032</v>
+      </c>
     </row>
     <row r="3415" spans="1:8">
-      <c r="C3415" s="2"/>
+      <c r="A3415">
+        <v>3779</v>
+      </c>
+      <c r="B3415" t="s">
+        <v>6033</v>
+      </c>
+      <c r="C3415" s="2">
+        <v>46113</v>
+      </c>
+      <c r="D3415" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3415" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3415">
+        <v>1444</v>
+      </c>
+      <c r="G3415" s="1" t="s">
+        <v>6034</v>
+      </c>
     </row>
     <row r="3416" spans="1:8">
-      <c r="C3416" s="2"/>
+      <c r="A3416">
+        <v>2725</v>
+      </c>
+      <c r="B3416" t="s">
+        <v>6035</v>
+      </c>
+      <c r="C3416" s="2">
+        <v>46113</v>
+      </c>
+      <c r="D3416" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3416" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3416" s="1" t="s">
+        <v>5713</v>
+      </c>
     </row>
     <row r="3417" spans="1:8">
       <c r="C3417" s="2"/>
@@ -94396,7 +94465,7 @@
         <v>3454</v>
       </c>
       <c r="B3423" t="s">
-        <v>6031</v>
+        <v>6036</v>
       </c>
       <c r="D3423" t="s">
         <v>138</v>
@@ -94416,7 +94485,7 @@
         <v>3562</v>
       </c>
       <c r="B3424" t="s">
-        <v>6032</v>
+        <v>6037</v>
       </c>
       <c r="D3424" t="s">
         <v>138</v>
@@ -94427,10 +94496,10 @@
     </row>
     <row r="3425" spans="1:6">
       <c r="A3425" t="s">
-        <v>6033</v>
+        <v>6038</v>
       </c>
       <c r="B3425" t="s">
-        <v>6034</v>
+        <v>6039</v>
       </c>
       <c r="D3425" t="s">
         <v>138</v>
@@ -94441,7 +94510,7 @@
         <v>3721</v>
       </c>
       <c r="B3426" t="s">
-        <v>6035</v>
+        <v>6040</v>
       </c>
       <c r="D3426" t="s">
         <v>138</v>
@@ -94458,7 +94527,7 @@
         <v>3235</v>
       </c>
       <c r="B3427" t="s">
-        <v>6036</v>
+        <v>6041</v>
       </c>
       <c r="C3427" s="2"/>
       <c r="D3427" t="s">
@@ -94469,7 +94538,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3412" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3413" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94516,10 +94585,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6037</v>
+        <v>6042</v>
       </c>
       <c r="D5" t="s">
-        <v>6038</v>
+        <v>6043</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94530,13 +94599,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6040</v>
+        <v>6045</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94545,7 +94614,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6041</v>
+        <v>6046</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94560,16 +94629,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6042</v>
+        <v>6047</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6043</v>
+        <v>6048</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6044</v>
+        <v>6049</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94583,10 +94652,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6045</v>
+        <v>6050</v>
       </c>
       <c r="H14" t="s">
-        <v>6046</v>
+        <v>6051</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94601,16 +94670,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6047</v>
+        <v>6052</v>
       </c>
       <c r="W14" t="s">
-        <v>6048</v>
+        <v>6053</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6049</v>
+        <v>6054</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94622,158 +94691,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6051</v>
+        <v>6056</v>
       </c>
       <c r="AL14" t="s">
-        <v>6052</v>
+        <v>6057</v>
       </c>
       <c r="AO14" t="s">
-        <v>6053</v>
+        <v>6058</v>
       </c>
       <c r="AR14" t="s">
-        <v>6054</v>
+        <v>6059</v>
       </c>
       <c r="AU14" t="s">
-        <v>6055</v>
+        <v>6060</v>
       </c>
       <c r="AX14" t="s">
-        <v>6056</v>
+        <v>6061</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="T15" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="W15" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="Z15" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="AF15" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
       <c r="AI15" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="AL15" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="AU15" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="AX15" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
       <c r="H16" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="N16" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="T16" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="W16" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="Z16" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="AC16" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AF16" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="AI16" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="AL16" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="AR16" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="AU16" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="AX16" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94781,43 +94850,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="D17" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="H17" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="N17" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="T17" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="W17" t="s">
-        <v>6050</v>
+        <v>6055</v>
       </c>
       <c r="Z17" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="AC17" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
       <c r="AF17" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="AI17" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AR17" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="AU17" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="BA17" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94825,37 +94894,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="H18" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="N18" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="T18" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="W18" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
       <c r="Z18" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="AC18" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="AF18" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="AI18" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="AU18" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="BA18" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94863,37 +94932,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="H19" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="N19" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="T19" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="W19" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="Z19" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="AC19" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="AF19" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="AI19" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="AU19" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="BA19" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94901,37 +94970,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="D20" t="s">
+        <v>6123</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6124</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6125</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6126</v>
+      </c>
+      <c r="W20" t="s">
         <v>6118</v>
       </c>
-      <c r="H20" t="s">
-        <v>6119</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6120</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6121</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6113</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="AC20" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AF20" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="AU20" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="BA20" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -94939,37 +95008,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="D21" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="H21" t="s">
+        <v>6133</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6134</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6135</v>
+      </c>
+      <c r="W21" t="s">
         <v>6128</v>
       </c>
-      <c r="N21" t="s">
-        <v>6129</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6130</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6123</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="AC21" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AF21" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="AU21" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="BA21" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -94980,13 +95049,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -94995,16 +95064,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="AC22" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="AF22" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AU22" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95012,25 +95081,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="H23" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="T23" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="Z23" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="AC23" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="AF23" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AU23" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95038,89 +95107,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="T24" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="Z24" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="AC24" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="AF24" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="D25" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
       <c r="T25" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="AC25" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="AF25" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="AC26" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="AF26" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="AC27" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="AF27" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="AC28" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="AF28" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95130,22 +95199,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95155,7 +95224,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95163,7 +95232,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95178,7 +95247,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95196,227 +95265,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="Q41" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="T41" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="W41" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="AL41" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="AO41" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="AR41" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="Q42" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="T42" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="W42" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
       <c r="AC42" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="AL42" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="AO42" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="AR42" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="K43" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="N43" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="Q43" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="T43" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="W43" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
       <c r="Z43" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="AC43" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="AF43" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="AL43" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="AO43" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
       <c r="AR43" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="F44" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="N44" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
       <c r="Q44" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="W44" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
       <c r="Z44" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="AC44" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="AF44" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="AL44" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="AO44" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="AR44" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="F45" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="N45" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="Q45" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95425,103 +95494,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="AF45" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="AO45" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="AR45" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="F46" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="N46" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="AC46" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="AF46" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="AO46" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="AR46" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="F47" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="AC47" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="AF47" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="AO47" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
       <c r="AR47" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="F48" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95533,141 +95602,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="AF48" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="AO48" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="AR48" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="AF49" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="AR49" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="F50" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="AR50" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="F51" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="AR51" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="AR52" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
       <c r="F53" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
       <c r="F54" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
       <c r="F55" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95675,10 +95744,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="F56" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95686,18 +95755,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="F57" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="F58" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95705,42 +95774,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="F59" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="F60" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="F61" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="F62" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
       <c r="F63" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95748,181 +95817,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
       <c r="F64" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="F65" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="F66" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
       <c r="F67" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="F68" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
       <c r="F69" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
     </row>
   </sheetData>
@@ -95949,10 +96018,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -95961,13 +96030,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -95975,13 +96044,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -95993,13 +96062,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96010,19 +96079,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="S10" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="T10" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96036,15 +96105,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
       <c r="S11" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96053,18 +96122,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96073,7 +96142,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96084,13 +96153,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96101,7 +96170,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96110,10 +96179,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="T15" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96124,12 +96193,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96137,22 +96206,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96163,39 +96232,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
       <c r="H32" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
       <c r="K32" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
       <c r="N32" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
       <c r="Q32" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
       <c r="S32" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96204,13 +96273,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="K33" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="N33" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96218,153 +96287,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
       <c r="K34" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
       <c r="N34" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
       <c r="N35" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
       <c r="N36" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
       <c r="N37" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
       <c r="N38" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6395</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6396</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6397</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6398</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6399</v>
+        <v>6404</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6400</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6401</v>
+        <v>6406</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6402</v>
+        <v>6407</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96372,7 +96441,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6403</v>
+        <v>6408</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96388,7 +96457,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6404</v>
+        <v>6409</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96404,21 +96473,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6405</v>
+        <v>6410</v>
       </c>
       <c r="J68" t="s">
-        <v>6406</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6407</v>
+        <v>6412</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6408</v>
+        <v>6413</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96427,52 +96496,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6409</v>
+        <v>6414</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6039</v>
+        <v>6044</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6410</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6411</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6412</v>
+        <v>6417</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6413</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96534,7 +96603,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6414</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96542,10 +96611,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6415</v>
+        <v>6420</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6416</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96553,7 +96622,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6417</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96566,15 +96635,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6418</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6419</v>
+        <v>6424</v>
       </c>
       <c r="F17" t="s">
-        <v>6420</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3413</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3416</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13794" uniqueCount="6426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13805" uniqueCount="6430">
   <si>
     <t>名称</t>
   </si>
@@ -20741,6 +20741,18 @@
   </si>
   <si>
     <t>间隔取消</t>
+  </si>
+  <si>
+    <t>LCR 113</t>
+  </si>
+  <si>
+    <t>同210题</t>
+  </si>
+  <si>
+    <t>能被 3 整除的三元组最大和</t>
+  </si>
+  <si>
+    <t>判断对象是否为空</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22409,16 +22421,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -94438,21 +94450,70 @@
       <c r="D3416" t="s">
         <v>141</v>
       </c>
-      <c r="E3416" t="s">
-        <v>78</v>
-      </c>
+      <c r="E3416"/>
       <c r="H3416" s="1" t="s">
         <v>5713</v>
       </c>
     </row>
     <row r="3417" spans="1:8">
-      <c r="C3417" s="2"/>
+      <c r="A3417" t="s">
+        <v>6036</v>
+      </c>
+      <c r="B3417" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C3417" s="2">
+        <v>46114</v>
+      </c>
+      <c r="D3417" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3417" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3417" s="1" t="s">
+        <v>6037</v>
+      </c>
     </row>
     <row r="3418" spans="1:8">
-      <c r="C3418" s="2"/>
+      <c r="A3418">
+        <v>3780</v>
+      </c>
+      <c r="B3418" t="s">
+        <v>6038</v>
+      </c>
+      <c r="C3418" s="2">
+        <v>46114</v>
+      </c>
+      <c r="D3418" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3418" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3418">
+        <v>1584</v>
+      </c>
+      <c r="G3418" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3419" spans="1:8">
-      <c r="C3419" s="2"/>
+      <c r="A3419">
+        <v>2727</v>
+      </c>
+      <c r="B3419" t="s">
+        <v>6039</v>
+      </c>
+      <c r="C3419" s="2">
+        <v>46114</v>
+      </c>
+      <c r="D3419" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3419" s="1" t="s">
+        <v>5713</v>
+      </c>
     </row>
     <row r="3420" spans="1:8">
       <c r="C3420" s="2"/>
@@ -94465,7 +94526,7 @@
         <v>3454</v>
       </c>
       <c r="B3423" t="s">
-        <v>6036</v>
+        <v>6040</v>
       </c>
       <c r="D3423" t="s">
         <v>138</v>
@@ -94485,7 +94546,7 @@
         <v>3562</v>
       </c>
       <c r="B3424" t="s">
-        <v>6037</v>
+        <v>6041</v>
       </c>
       <c r="D3424" t="s">
         <v>138</v>
@@ -94496,10 +94557,10 @@
     </row>
     <row r="3425" spans="1:6">
       <c r="A3425" t="s">
-        <v>6038</v>
+        <v>6042</v>
       </c>
       <c r="B3425" t="s">
-        <v>6039</v>
+        <v>6043</v>
       </c>
       <c r="D3425" t="s">
         <v>138</v>
@@ -94510,7 +94571,7 @@
         <v>3721</v>
       </c>
       <c r="B3426" t="s">
-        <v>6040</v>
+        <v>6044</v>
       </c>
       <c r="D3426" t="s">
         <v>138</v>
@@ -94527,7 +94588,7 @@
         <v>3235</v>
       </c>
       <c r="B3427" t="s">
-        <v>6041</v>
+        <v>6045</v>
       </c>
       <c r="C3427" s="2"/>
       <c r="D3427" t="s">
@@ -94538,7 +94599,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3413" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3416" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94585,10 +94646,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6042</v>
+        <v>6046</v>
       </c>
       <c r="D5" t="s">
-        <v>6043</v>
+        <v>6047</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94599,13 +94660,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6045</v>
+        <v>6049</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94614,7 +94675,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94629,16 +94690,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94652,10 +94713,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="H14" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94670,16 +94731,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="W14" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94691,158 +94752,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AL14" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AO14" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AR14" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="AU14" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="AX14" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="T15" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="W15" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="Z15" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="AF15" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AI15" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AL15" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AU15" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="AX15" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="H16" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="N16" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="T16" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="W16" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="Z16" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AC16" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AF16" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="AI16" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AL16" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AR16" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="AU16" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="AX16" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94850,43 +94911,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="D17" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="H17" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="N17" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="T17" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="W17" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="Z17" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="AC17" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AF17" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AI17" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AR17" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="AU17" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="BA17" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94894,37 +94955,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="H18" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="N18" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="T18" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="W18" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="Z18" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AC18" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AF18" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AI18" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AU18" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="BA18" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94932,37 +94993,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="H19" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="N19" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="T19" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="W19" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="Z19" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AC19" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AF19" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AI19" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AU19" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="BA19" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -94970,37 +95031,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6127</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6128</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6129</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6130</v>
+      </c>
+      <c r="W20" t="s">
         <v>6122</v>
       </c>
-      <c r="D20" t="s">
-        <v>6123</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6124</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6125</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6126</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6118</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AC20" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AF20" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AU20" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="BA20" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95008,37 +95069,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="D21" t="s">
+        <v>6136</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6137</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6138</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6139</v>
+      </c>
+      <c r="W21" t="s">
         <v>6132</v>
       </c>
-      <c r="H21" t="s">
-        <v>6133</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6134</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6135</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6128</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AC21" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AF21" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AU21" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="BA21" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95049,13 +95110,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95064,16 +95125,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AC22" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="AF22" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AU22" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95081,25 +95142,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="H23" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="T23" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="Z23" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AC23" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AF23" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AU23" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95107,89 +95168,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="T24" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="Z24" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AC24" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AF24" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="D25" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="T25" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AC25" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AF25" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AC26" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AF26" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AC27" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="AF27" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AC28" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AF28" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95199,22 +95260,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95224,7 +95285,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95232,7 +95293,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95247,7 +95308,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95265,227 +95326,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="Q41" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="T41" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="W41" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="AL41" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AO41" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AR41" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="Q42" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="T42" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="W42" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AC42" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="AL42" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AO42" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="AR42" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="K43" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="N43" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="Q43" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="T43" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="W43" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="Z43" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="AC43" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="AF43" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="AL43" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AO43" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="AR43" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="F44" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="N44" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="Q44" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="W44" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="Z44" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="AC44" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="AF44" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="AL44" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AO44" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="AR44" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="F45" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="N45" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="Q45" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95494,103 +95555,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="AF45" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="AO45" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="AR45" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="F46" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="N46" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="AC46" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="AF46" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="AO46" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="AR46" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="F47" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="AC47" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="AF47" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="AO47" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="AR47" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="F48" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95602,141 +95663,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="AF48" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="AO48" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="AR48" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="AF49" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="AR49" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="F50" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="AR50" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="F51" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="AR51" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="AR52" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="F53" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="F54" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="F55" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95744,10 +95805,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="F56" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95755,18 +95816,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="F57" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="F58" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95774,42 +95835,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="F59" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="F60" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="F61" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="F62" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="F63" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95817,181 +95878,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="F64" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="F65" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="F66" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="F67" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="F68" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="F69" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
     </row>
   </sheetData>
@@ -96018,10 +96079,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96030,13 +96091,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96044,13 +96105,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96062,13 +96123,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96079,19 +96140,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
       <c r="S10" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
       <c r="T10" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96105,15 +96166,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
       <c r="S11" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96122,18 +96183,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96142,7 +96203,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96153,13 +96214,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96170,7 +96231,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96179,10 +96240,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="T15" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96193,12 +96254,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96206,22 +96267,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96232,39 +96293,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
       <c r="H32" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
       <c r="K32" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
       <c r="N32" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
       <c r="Q32" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
       <c r="S32" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96273,13 +96334,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
       <c r="K33" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
       <c r="N33" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96287,153 +96348,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
       <c r="K34" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
       <c r="N34" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
       <c r="N35" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
       <c r="N36" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="N37" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
       <c r="N38" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96441,7 +96502,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96457,7 +96518,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96473,21 +96534,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6410</v>
+        <v>6414</v>
       </c>
       <c r="J68" t="s">
-        <v>6411</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6412</v>
+        <v>6416</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6413</v>
+        <v>6417</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96496,52 +96557,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6414</v>
+        <v>6418</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6044</v>
+        <v>6048</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6415</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6416</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6417</v>
+        <v>6421</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6418</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96603,7 +96664,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96611,10 +96672,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6421</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96622,7 +96683,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6422</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96635,15 +96696,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6423</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6424</v>
+        <v>6428</v>
       </c>
       <c r="F17" t="s">
-        <v>6425</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3416</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3419</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13805" uniqueCount="6430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13818" uniqueCount="6436">
   <si>
     <t>名称</t>
   </si>
@@ -20753,6 +20753,24 @@
   </si>
   <si>
     <t>判断对象是否为空</t>
+  </si>
+  <si>
+    <t>使二进制字符串相等的最小成本</t>
+  </si>
+  <si>
+    <t>贪心+分类讨论</t>
+  </si>
+  <si>
+    <t>最小全 1 倍数</t>
+  </si>
+  <si>
+    <t>数论+模拟</t>
+  </si>
+  <si>
+    <t>有点不容易想到</t>
+  </si>
+  <si>
+    <t>非负元素轮替</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -23382,7 +23400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3427"/>
+  <dimension ref="A1:N3437"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -94450,7 +94468,6 @@
       <c r="D3416" t="s">
         <v>141</v>
       </c>
-      <c r="E3416"/>
       <c r="H3416" s="1" t="s">
         <v>5713</v>
       </c>
@@ -94516,90 +94533,183 @@
       </c>
     </row>
     <row r="3420" spans="1:8">
-      <c r="C3420" s="2"/>
+      <c r="A3420">
+        <v>3800</v>
+      </c>
+      <c r="B3420" t="s">
+        <v>6040</v>
+      </c>
+      <c r="C3420" s="2">
+        <v>46115</v>
+      </c>
+      <c r="D3420" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3420" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3420">
+        <v>1840</v>
+      </c>
+      <c r="G3420" s="1" t="s">
+        <v>6041</v>
+      </c>
     </row>
     <row r="3421" spans="1:8">
-      <c r="C3421" s="2"/>
+      <c r="A3421">
+        <v>3790</v>
+      </c>
+      <c r="B3421" t="s">
+        <v>6042</v>
+      </c>
+      <c r="C3421" s="2">
+        <v>46115</v>
+      </c>
+      <c r="D3421" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3421" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3421">
+        <v>1593</v>
+      </c>
+      <c r="G3421" s="1" t="s">
+        <v>6043</v>
+      </c>
+      <c r="H3421" s="1" t="s">
+        <v>6044</v>
+      </c>
+    </row>
+    <row r="3422" spans="1:8">
+      <c r="A3422">
+        <v>3819</v>
+      </c>
+      <c r="B3422" t="s">
+        <v>6045</v>
+      </c>
+      <c r="C3422" s="2">
+        <v>46115</v>
+      </c>
+      <c r="D3422" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3422" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3422">
+        <v>1381</v>
+      </c>
+      <c r="G3422" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3423" spans="1:8">
-      <c r="A3423">
+      <c r="C3423" s="2"/>
+    </row>
+    <row r="3424" spans="1:8">
+      <c r="C3424" s="2"/>
+    </row>
+    <row r="3425" spans="1:7">
+      <c r="C3425" s="2"/>
+    </row>
+    <row r="3426" spans="1:7">
+      <c r="C3426" s="2"/>
+    </row>
+    <row r="3427" spans="1:7">
+      <c r="C3427" s="2"/>
+    </row>
+    <row r="3428" spans="1:7">
+      <c r="C3428" s="2"/>
+    </row>
+    <row r="3429" spans="1:7">
+      <c r="C3429" s="2"/>
+    </row>
+    <row r="3430" spans="1:7">
+      <c r="C3430" s="2"/>
+    </row>
+    <row r="3431" spans="1:7">
+      <c r="C3431" s="2"/>
+    </row>
+    <row r="3433" spans="1:7">
+      <c r="A3433">
         <v>3454</v>
       </c>
-      <c r="B3423" t="s">
-        <v>6040</v>
-      </c>
-      <c r="D3423" t="s">
+      <c r="B3433" t="s">
+        <v>6046</v>
+      </c>
+      <c r="D3433" t="s">
         <v>138</v>
       </c>
-      <c r="E3423" t="s">
+      <c r="E3433" t="s">
         <v>74</v>
       </c>
-      <c r="F3423">
+      <c r="F3433">
         <v>2671</v>
       </c>
-      <c r="G3423" s="1" t="s">
+      <c r="G3433" s="1" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="3424" spans="1:8">
-      <c r="A3424">
+    <row r="3434" spans="1:7">
+      <c r="A3434">
         <v>3562</v>
       </c>
-      <c r="B3424" t="s">
-        <v>6041</v>
-      </c>
-      <c r="D3424" t="s">
+      <c r="B3434" t="s">
+        <v>6047</v>
+      </c>
+      <c r="D3434" t="s">
         <v>138</v>
       </c>
-      <c r="F3424">
+      <c r="F3434">
         <v>2458</v>
       </c>
     </row>
-    <row r="3425" spans="1:6">
-      <c r="A3425" t="s">
-        <v>6042</v>
-      </c>
-      <c r="B3425" t="s">
-        <v>6043</v>
-      </c>
-      <c r="D3425" t="s">
+    <row r="3435" spans="1:7">
+      <c r="A3435" t="s">
+        <v>6048</v>
+      </c>
+      <c r="B3435" t="s">
+        <v>6049</v>
+      </c>
+      <c r="D3435" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3426" spans="1:6">
-      <c r="A3426">
+    <row r="3436" spans="1:7">
+      <c r="A3436">
         <v>3721</v>
       </c>
-      <c r="B3426" t="s">
-        <v>6044</v>
-      </c>
-      <c r="D3426" t="s">
+      <c r="B3436" t="s">
+        <v>6050</v>
+      </c>
+      <c r="D3436" t="s">
         <v>138</v>
       </c>
-      <c r="E3426" t="s">
+      <c r="E3436" t="s">
         <v>74</v>
       </c>
-      <c r="F3426">
+      <c r="F3436">
         <v>2723</v>
       </c>
     </row>
-    <row r="3427" spans="1:6">
-      <c r="A3427">
+    <row r="3437" spans="1:7">
+      <c r="A3437">
         <v>3235</v>
       </c>
-      <c r="B3427" t="s">
-        <v>6045</v>
-      </c>
-      <c r="C3427" s="2"/>
-      <c r="D3427" t="s">
+      <c r="B3437" t="s">
+        <v>6051</v>
+      </c>
+      <c r="C3437" s="2"/>
+      <c r="D3437" t="s">
         <v>138</v>
       </c>
-      <c r="F3427">
+      <c r="F3437">
         <v>3773</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3416" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3419" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94646,10 +94756,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6046</v>
+        <v>6052</v>
       </c>
       <c r="D5" t="s">
-        <v>6047</v>
+        <v>6053</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94660,13 +94770,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6048</v>
+        <v>6054</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6049</v>
+        <v>6055</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94675,7 +94785,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6050</v>
+        <v>6056</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94690,16 +94800,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6051</v>
+        <v>6057</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6052</v>
+        <v>6058</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6053</v>
+        <v>6059</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94713,10 +94823,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6054</v>
+        <v>6060</v>
       </c>
       <c r="H14" t="s">
-        <v>6055</v>
+        <v>6061</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94731,16 +94841,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6056</v>
+        <v>6062</v>
       </c>
       <c r="W14" t="s">
-        <v>6057</v>
+        <v>6063</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6058</v>
+        <v>6064</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94752,158 +94862,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6059</v>
+        <v>6065</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6060</v>
+        <v>6066</v>
       </c>
       <c r="AL14" t="s">
-        <v>6061</v>
+        <v>6067</v>
       </c>
       <c r="AO14" t="s">
-        <v>6062</v>
+        <v>6068</v>
       </c>
       <c r="AR14" t="s">
-        <v>6063</v>
+        <v>6069</v>
       </c>
       <c r="AU14" t="s">
-        <v>6064</v>
+        <v>6070</v>
       </c>
       <c r="AX14" t="s">
-        <v>6065</v>
+        <v>6071</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6066</v>
+        <v>6072</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6067</v>
+        <v>6073</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6068</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6069</v>
+        <v>6075</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6070</v>
+        <v>6076</v>
       </c>
       <c r="T15" t="s">
-        <v>6071</v>
+        <v>6077</v>
       </c>
       <c r="W15" t="s">
-        <v>6072</v>
+        <v>6078</v>
       </c>
       <c r="Z15" t="s">
-        <v>6073</v>
+        <v>6079</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
       <c r="AF15" t="s">
-        <v>6075</v>
+        <v>6081</v>
       </c>
       <c r="AI15" t="s">
-        <v>6076</v>
+        <v>6082</v>
       </c>
       <c r="AL15" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6078</v>
+        <v>6084</v>
       </c>
       <c r="AU15" t="s">
-        <v>6079</v>
+        <v>6085</v>
       </c>
       <c r="AX15" t="s">
-        <v>6080</v>
+        <v>6086</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6081</v>
+        <v>6087</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6082</v>
+        <v>6088</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6083</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6084</v>
+        <v>6090</v>
       </c>
       <c r="H16" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="N16" t="s">
-        <v>6086</v>
+        <v>6092</v>
       </c>
       <c r="T16" t="s">
-        <v>6087</v>
+        <v>6093</v>
       </c>
       <c r="W16" t="s">
-        <v>6088</v>
+        <v>6094</v>
       </c>
       <c r="Z16" t="s">
-        <v>6089</v>
+        <v>6095</v>
       </c>
       <c r="AC16" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
       <c r="AF16" t="s">
-        <v>6059</v>
+        <v>6065</v>
       </c>
       <c r="AI16" t="s">
-        <v>6090</v>
+        <v>6096</v>
       </c>
       <c r="AL16" t="s">
-        <v>6091</v>
+        <v>6097</v>
       </c>
       <c r="AR16" t="s">
-        <v>6092</v>
+        <v>6098</v>
       </c>
       <c r="AU16" t="s">
-        <v>6093</v>
+        <v>6099</v>
       </c>
       <c r="AX16" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6095</v>
+        <v>6101</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -94911,43 +95021,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6096</v>
+        <v>6102</v>
       </c>
       <c r="D17" t="s">
-        <v>6097</v>
+        <v>6103</v>
       </c>
       <c r="H17" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="N17" t="s">
-        <v>6099</v>
+        <v>6105</v>
       </c>
       <c r="T17" t="s">
-        <v>6100</v>
+        <v>6106</v>
       </c>
       <c r="W17" t="s">
-        <v>6059</v>
+        <v>6065</v>
       </c>
       <c r="Z17" t="s">
-        <v>6070</v>
+        <v>6076</v>
       </c>
       <c r="AC17" t="s">
-        <v>6101</v>
+        <v>6107</v>
       </c>
       <c r="AF17" t="s">
-        <v>6102</v>
+        <v>6108</v>
       </c>
       <c r="AI17" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
       <c r="AR17" t="s">
-        <v>6104</v>
+        <v>6110</v>
       </c>
       <c r="AU17" t="s">
-        <v>6105</v>
+        <v>6111</v>
       </c>
       <c r="BA17" t="s">
-        <v>6106</v>
+        <v>6112</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -94955,37 +95065,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6107</v>
+        <v>6113</v>
       </c>
       <c r="H18" t="s">
-        <v>6108</v>
+        <v>6114</v>
       </c>
       <c r="N18" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
       <c r="T18" t="s">
-        <v>6110</v>
+        <v>6116</v>
       </c>
       <c r="W18" t="s">
-        <v>6111</v>
+        <v>6117</v>
       </c>
       <c r="Z18" t="s">
-        <v>6086</v>
+        <v>6092</v>
       </c>
       <c r="AC18" t="s">
-        <v>6112</v>
+        <v>6118</v>
       </c>
       <c r="AF18" t="s">
-        <v>6113</v>
+        <v>6119</v>
       </c>
       <c r="AI18" t="s">
-        <v>6114</v>
+        <v>6120</v>
       </c>
       <c r="AU18" t="s">
-        <v>6115</v>
+        <v>6121</v>
       </c>
       <c r="BA18" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -94993,37 +95103,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6117</v>
+        <v>6123</v>
       </c>
       <c r="H19" t="s">
-        <v>6118</v>
+        <v>6124</v>
       </c>
       <c r="N19" t="s">
-        <v>6119</v>
+        <v>6125</v>
       </c>
       <c r="T19" t="s">
-        <v>6120</v>
+        <v>6126</v>
       </c>
       <c r="W19" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
       <c r="Z19" t="s">
-        <v>6099</v>
+        <v>6105</v>
       </c>
       <c r="AC19" t="s">
-        <v>6121</v>
+        <v>6127</v>
       </c>
       <c r="AF19" t="s">
-        <v>6122</v>
+        <v>6128</v>
       </c>
       <c r="AI19" t="s">
-        <v>6123</v>
+        <v>6129</v>
       </c>
       <c r="AU19" t="s">
-        <v>6124</v>
+        <v>6130</v>
       </c>
       <c r="BA19" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95031,37 +95141,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6126</v>
+        <v>6132</v>
       </c>
       <c r="D20" t="s">
-        <v>6127</v>
+        <v>6133</v>
       </c>
       <c r="H20" t="s">
+        <v>6134</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6135</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6136</v>
+      </c>
+      <c r="W20" t="s">
         <v>6128</v>
       </c>
-      <c r="N20" t="s">
-        <v>6129</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6130</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6122</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
       <c r="AC20" t="s">
-        <v>6131</v>
+        <v>6137</v>
       </c>
       <c r="AF20" t="s">
-        <v>6132</v>
+        <v>6138</v>
       </c>
       <c r="AU20" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
       <c r="BA20" t="s">
-        <v>6134</v>
+        <v>6140</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95069,37 +95179,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="D21" t="s">
-        <v>6136</v>
+        <v>6142</v>
       </c>
       <c r="H21" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
       <c r="N21" t="s">
+        <v>6144</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6145</v>
+      </c>
+      <c r="W21" t="s">
         <v>6138</v>
       </c>
-      <c r="T21" t="s">
-        <v>6139</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6132</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6119</v>
+        <v>6125</v>
       </c>
       <c r="AC21" t="s">
-        <v>6140</v>
+        <v>6146</v>
       </c>
       <c r="AF21" t="s">
-        <v>6141</v>
+        <v>6147</v>
       </c>
       <c r="AU21" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="BA21" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95110,13 +95220,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6144</v>
+        <v>6150</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95125,16 +95235,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
       <c r="AC22" t="s">
-        <v>6146</v>
+        <v>6152</v>
       </c>
       <c r="AF22" t="s">
-        <v>6147</v>
+        <v>6153</v>
       </c>
       <c r="AU22" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95142,25 +95252,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6149</v>
+        <v>6155</v>
       </c>
       <c r="H23" t="s">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="T23" t="s">
-        <v>6151</v>
+        <v>6157</v>
       </c>
       <c r="Z23" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
       <c r="AC23" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
       <c r="AF23" t="s">
-        <v>6153</v>
+        <v>6159</v>
       </c>
       <c r="AU23" t="s">
-        <v>6154</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95168,89 +95278,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="T24" t="s">
-        <v>6156</v>
+        <v>6162</v>
       </c>
       <c r="Z24" t="s">
-        <v>6157</v>
+        <v>6163</v>
       </c>
       <c r="AC24" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
       <c r="AF24" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6160</v>
+        <v>6166</v>
       </c>
       <c r="D25" t="s">
-        <v>6161</v>
+        <v>6167</v>
       </c>
       <c r="T25" t="s">
-        <v>6162</v>
+        <v>6168</v>
       </c>
       <c r="AC25" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="AF25" t="s">
-        <v>6164</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6165</v>
+        <v>6171</v>
       </c>
       <c r="AC26" t="s">
-        <v>6166</v>
+        <v>6172</v>
       </c>
       <c r="AF26" t="s">
-        <v>6167</v>
+        <v>6173</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="AC27" t="s">
-        <v>6169</v>
+        <v>6175</v>
       </c>
       <c r="AF27" t="s">
-        <v>6170</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6171</v>
+        <v>6177</v>
       </c>
       <c r="AC28" t="s">
-        <v>6172</v>
+        <v>6178</v>
       </c>
       <c r="AF28" t="s">
-        <v>6173</v>
+        <v>6179</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6174</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6177</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95260,22 +95370,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6178</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95285,7 +95395,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6182</v>
+        <v>6188</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95293,7 +95403,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6183</v>
+        <v>6189</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95308,7 +95418,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6184</v>
+        <v>6190</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95326,227 +95436,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6185</v>
+        <v>6191</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6186</v>
+        <v>6192</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6187</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6188</v>
+        <v>6194</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6189</v>
+        <v>6195</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6190</v>
+        <v>6196</v>
       </c>
       <c r="Q41" t="s">
-        <v>6178</v>
+        <v>6184</v>
       </c>
       <c r="T41" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
       <c r="W41" t="s">
-        <v>6191</v>
+        <v>6197</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6192</v>
+        <v>6198</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6193</v>
+        <v>6199</v>
       </c>
       <c r="AL41" t="s">
-        <v>6194</v>
+        <v>6200</v>
       </c>
       <c r="AO41" t="s">
-        <v>6195</v>
+        <v>6201</v>
       </c>
       <c r="AR41" t="s">
-        <v>6196</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6197</v>
+        <v>6203</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6198</v>
+        <v>6204</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6199</v>
+        <v>6205</v>
       </c>
       <c r="Q42" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
       <c r="T42" t="s">
-        <v>6200</v>
+        <v>6206</v>
       </c>
       <c r="W42" t="s">
-        <v>6201</v>
+        <v>6207</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6202</v>
+        <v>6208</v>
       </c>
       <c r="AC42" t="s">
-        <v>6203</v>
+        <v>6209</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6204</v>
+        <v>6210</v>
       </c>
       <c r="AL42" t="s">
-        <v>6205</v>
+        <v>6211</v>
       </c>
       <c r="AO42" t="s">
-        <v>6206</v>
+        <v>6212</v>
       </c>
       <c r="AR42" t="s">
-        <v>6207</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6208</v>
+        <v>6214</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6209</v>
+        <v>6215</v>
       </c>
       <c r="K43" t="s">
-        <v>6210</v>
+        <v>6216</v>
       </c>
       <c r="N43" t="s">
-        <v>6211</v>
+        <v>6217</v>
       </c>
       <c r="Q43" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
       <c r="T43" t="s">
-        <v>6212</v>
+        <v>6218</v>
       </c>
       <c r="W43" t="s">
-        <v>6213</v>
+        <v>6219</v>
       </c>
       <c r="Z43" t="s">
-        <v>6214</v>
+        <v>6220</v>
       </c>
       <c r="AC43" t="s">
-        <v>6215</v>
+        <v>6221</v>
       </c>
       <c r="AF43" t="s">
-        <v>6216</v>
+        <v>6222</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
       <c r="AL43" t="s">
-        <v>6126</v>
+        <v>6132</v>
       </c>
       <c r="AO43" t="s">
-        <v>6218</v>
+        <v>6224</v>
       </c>
       <c r="AR43" t="s">
-        <v>6219</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6220</v>
+        <v>6226</v>
       </c>
       <c r="F44" t="s">
-        <v>6221</v>
+        <v>6227</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6222</v>
+        <v>6228</v>
       </c>
       <c r="N44" t="s">
-        <v>6223</v>
+        <v>6229</v>
       </c>
       <c r="Q44" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
       <c r="W44" t="s">
-        <v>6224</v>
+        <v>6230</v>
       </c>
       <c r="Z44" t="s">
-        <v>6225</v>
+        <v>6231</v>
       </c>
       <c r="AC44" t="s">
-        <v>6226</v>
+        <v>6232</v>
       </c>
       <c r="AF44" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
       <c r="AL44" t="s">
-        <v>6228</v>
+        <v>6234</v>
       </c>
       <c r="AO44" t="s">
-        <v>6229</v>
+        <v>6235</v>
       </c>
       <c r="AR44" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6231</v>
+        <v>6237</v>
       </c>
       <c r="F45" t="s">
-        <v>6232</v>
+        <v>6238</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6233</v>
+        <v>6239</v>
       </c>
       <c r="N45" t="s">
-        <v>6234</v>
+        <v>6240</v>
       </c>
       <c r="Q45" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95555,103 +95665,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="AF45" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
       <c r="AO45" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
       <c r="AR45" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6241</v>
+        <v>6247</v>
       </c>
       <c r="F46" t="s">
-        <v>6242</v>
+        <v>6248</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
       <c r="N46" t="s">
-        <v>6244</v>
+        <v>6250</v>
       </c>
       <c r="AC46" t="s">
-        <v>6245</v>
+        <v>6251</v>
       </c>
       <c r="AF46" t="s">
-        <v>6246</v>
+        <v>6252</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6247</v>
+        <v>6253</v>
       </c>
       <c r="AO46" t="s">
-        <v>6248</v>
+        <v>6254</v>
       </c>
       <c r="AR46" t="s">
-        <v>6249</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6250</v>
+        <v>6256</v>
       </c>
       <c r="F47" t="s">
-        <v>6251</v>
+        <v>6257</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6252</v>
+        <v>6258</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6253</v>
+        <v>6259</v>
       </c>
       <c r="AC47" t="s">
-        <v>6254</v>
+        <v>6260</v>
       </c>
       <c r="AF47" t="s">
-        <v>6255</v>
+        <v>6261</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6256</v>
+        <v>6262</v>
       </c>
       <c r="AO47" t="s">
-        <v>6257</v>
+        <v>6263</v>
       </c>
       <c r="AR47" t="s">
-        <v>6258</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6259</v>
+        <v>6265</v>
       </c>
       <c r="F48" t="s">
-        <v>6260</v>
+        <v>6266</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95663,141 +95773,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6261</v>
+        <v>6267</v>
       </c>
       <c r="AF48" t="s">
-        <v>6262</v>
+        <v>6268</v>
       </c>
       <c r="AO48" t="s">
-        <v>6263</v>
+        <v>6269</v>
       </c>
       <c r="AR48" t="s">
-        <v>6264</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6265</v>
+        <v>6271</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6266</v>
+        <v>6272</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6267</v>
+        <v>6273</v>
       </c>
       <c r="AF49" t="s">
-        <v>6268</v>
+        <v>6274</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6269</v>
+        <v>6275</v>
       </c>
       <c r="AR49" t="s">
-        <v>6270</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="F50" t="s">
-        <v>6272</v>
+        <v>6278</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6273</v>
+        <v>6279</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6274</v>
+        <v>6280</v>
       </c>
       <c r="AR50" t="s">
-        <v>6275</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6276</v>
+        <v>6282</v>
       </c>
       <c r="F51" t="s">
-        <v>6277</v>
+        <v>6283</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6278</v>
+        <v>6284</v>
       </c>
       <c r="AR51" t="s">
-        <v>6279</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6280</v>
+        <v>6286</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6281</v>
+        <v>6287</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6282</v>
+        <v>6288</v>
       </c>
       <c r="AR52" t="s">
-        <v>6283</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6284</v>
+        <v>6290</v>
       </c>
       <c r="F53" t="s">
-        <v>6285</v>
+        <v>6291</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6286</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6287</v>
+        <v>6293</v>
       </c>
       <c r="F54" t="s">
-        <v>6288</v>
+        <v>6294</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6289</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6290</v>
+        <v>6296</v>
       </c>
       <c r="F55" t="s">
-        <v>6291</v>
+        <v>6297</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95805,10 +95915,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6292</v>
+        <v>6298</v>
       </c>
       <c r="F56" t="s">
-        <v>6293</v>
+        <v>6299</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95816,18 +95926,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6294</v>
+        <v>6300</v>
       </c>
       <c r="F57" t="s">
-        <v>6295</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6296</v>
+        <v>6302</v>
       </c>
       <c r="F58" t="s">
-        <v>6297</v>
+        <v>6303</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95835,42 +95945,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6298</v>
+        <v>6304</v>
       </c>
       <c r="F59" t="s">
-        <v>6299</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6300</v>
+        <v>6306</v>
       </c>
       <c r="F60" t="s">
-        <v>6301</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6302</v>
+        <v>6308</v>
       </c>
       <c r="F61" t="s">
-        <v>6303</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6304</v>
+        <v>6310</v>
       </c>
       <c r="F62" t="s">
-        <v>6305</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6306</v>
+        <v>6312</v>
       </c>
       <c r="F63" t="s">
-        <v>6307</v>
+        <v>6313</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95878,181 +95988,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6308</v>
+        <v>6314</v>
       </c>
       <c r="F64" t="s">
-        <v>6309</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="F65" t="s">
-        <v>6262</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6310</v>
+        <v>6316</v>
       </c>
       <c r="F66" t="s">
-        <v>6311</v>
+        <v>6317</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6312</v>
+        <v>6318</v>
       </c>
       <c r="F67" t="s">
-        <v>6313</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6314</v>
+        <v>6320</v>
       </c>
       <c r="F68" t="s">
-        <v>6278</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6315</v>
+        <v>6321</v>
       </c>
       <c r="F69" t="s">
-        <v>6316</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6318</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6319</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6320</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6321</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6322</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6323</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6324</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6325</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6326</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6327</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6328</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6329</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6330</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6331</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6332</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6333</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6334</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6335</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6336</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6075</v>
+        <v>6081</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6337</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6338</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6339</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6340</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6341</v>
+        <v>6347</v>
       </c>
     </row>
   </sheetData>
@@ -96079,10 +96189,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6342</v>
+        <v>6348</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6343</v>
+        <v>6349</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96091,13 +96201,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6344</v>
+        <v>6350</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6345</v>
+        <v>6351</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6346</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96105,13 +96215,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6347</v>
+        <v>6353</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6348</v>
+        <v>6354</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96123,13 +96233,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6349</v>
+        <v>6355</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6350</v>
+        <v>6356</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96140,19 +96250,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6351</v>
+        <v>6357</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6352</v>
+        <v>6358</v>
       </c>
       <c r="S10" t="s">
-        <v>6353</v>
+        <v>6359</v>
       </c>
       <c r="T10" t="s">
-        <v>6354</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96166,15 +96276,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6355</v>
+        <v>6361</v>
       </c>
       <c r="S11" t="s">
-        <v>6079</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6356</v>
+        <v>6362</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96183,18 +96293,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6357</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96203,7 +96313,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96214,13 +96324,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6361</v>
+        <v>6367</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6362</v>
+        <v>6368</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96231,7 +96341,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6363</v>
+        <v>6369</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96240,10 +96350,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6246</v>
+        <v>6252</v>
       </c>
       <c r="T15" t="s">
-        <v>6364</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96254,12 +96364,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96267,22 +96377,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6368</v>
+        <v>6374</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6369</v>
+        <v>6375</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6370</v>
+        <v>6376</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6371</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96293,39 +96403,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6372</v>
+        <v>6378</v>
       </c>
       <c r="H32" t="s">
-        <v>6373</v>
+        <v>6379</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6374</v>
+        <v>6380</v>
       </c>
       <c r="K32" t="s">
-        <v>6375</v>
+        <v>6381</v>
       </c>
       <c r="N32" t="s">
-        <v>6376</v>
+        <v>6382</v>
       </c>
       <c r="Q32" t="s">
-        <v>6377</v>
+        <v>6383</v>
       </c>
       <c r="S32" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6378</v>
+        <v>6384</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6379</v>
+        <v>6385</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96334,13 +96444,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6380</v>
+        <v>6386</v>
       </c>
       <c r="K33" t="s">
-        <v>6381</v>
+        <v>6387</v>
       </c>
       <c r="N33" t="s">
-        <v>6382</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96348,153 +96458,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6383</v>
+        <v>6389</v>
       </c>
       <c r="K34" t="s">
-        <v>6384</v>
+        <v>6390</v>
       </c>
       <c r="N34" t="s">
-        <v>6385</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6386</v>
+        <v>6392</v>
       </c>
       <c r="N35" t="s">
-        <v>6387</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6388</v>
+        <v>6394</v>
       </c>
       <c r="N36" t="s">
-        <v>6389</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6390</v>
+        <v>6396</v>
       </c>
       <c r="N37" t="s">
-        <v>6391</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6392</v>
+        <v>6398</v>
       </c>
       <c r="N38" t="s">
-        <v>6393</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6394</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6395</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6396</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6397</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6398</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6399</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6400</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6401</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6402</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6403</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6293</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6404</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6405</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6291</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6406</v>
+        <v>6412</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6407</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6409</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6410</v>
+        <v>6416</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6411</v>
+        <v>6417</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96502,7 +96612,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6412</v>
+        <v>6418</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96518,7 +96628,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6413</v>
+        <v>6419</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96534,21 +96644,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6414</v>
+        <v>6420</v>
       </c>
       <c r="J68" t="s">
-        <v>6415</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6416</v>
+        <v>6422</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6417</v>
+        <v>6423</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96557,52 +96667,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6191</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6418</v>
+        <v>6424</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6048</v>
+        <v>6054</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6201</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6224</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6419</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6420</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6213</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6421</v>
+        <v>6427</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6422</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96664,7 +96774,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6423</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96672,10 +96782,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6424</v>
+        <v>6430</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6425</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96683,7 +96793,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6426</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96696,15 +96806,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6427</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6428</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="s">
-        <v>6429</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3419</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3422</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13818" uniqueCount="6436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13831" uniqueCount="6440">
   <si>
     <t>名称</t>
   </si>
@@ -20771,6 +20771,18 @@
   </si>
   <si>
     <t>非负元素轮替</t>
+  </si>
+  <si>
+    <t>找到带限制序列的最大值</t>
+  </si>
+  <si>
+    <t>从限高最小的点向周围传播约束</t>
+  </si>
+  <si>
+    <t>整数的镜像距离</t>
+  </si>
+  <si>
+    <t>不同元素和至少为 K 的最短子数组长度</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -94605,13 +94617,76 @@
       </c>
     </row>
     <row r="3423" spans="1:8">
-      <c r="C3423" s="2"/>
+      <c r="A3423">
+        <v>3796</v>
+      </c>
+      <c r="B3423" t="s">
+        <v>6046</v>
+      </c>
+      <c r="C3423" s="2">
+        <v>46116</v>
+      </c>
+      <c r="D3423" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3423" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3423">
+        <v>1832</v>
+      </c>
+      <c r="G3423" s="1" t="s">
+        <v>4465</v>
+      </c>
+      <c r="H3423" s="1" t="s">
+        <v>6047</v>
+      </c>
     </row>
     <row r="3424" spans="1:8">
-      <c r="C3424" s="2"/>
+      <c r="A3424">
+        <v>3783</v>
+      </c>
+      <c r="B3424" t="s">
+        <v>6048</v>
+      </c>
+      <c r="C3424" s="2">
+        <v>46116</v>
+      </c>
+      <c r="D3424" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3424" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3424">
+        <v>1170</v>
+      </c>
+      <c r="G3424" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3425" spans="1:7">
-      <c r="C3425" s="2"/>
+      <c r="A3425">
+        <v>3795</v>
+      </c>
+      <c r="B3425" t="s">
+        <v>6049</v>
+      </c>
+      <c r="C3425" s="2">
+        <v>46116</v>
+      </c>
+      <c r="D3425" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3425" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3425">
+        <v>1504</v>
+      </c>
+      <c r="G3425" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="3426" spans="1:7">
       <c r="C3426" s="2"/>
@@ -94636,7 +94711,7 @@
         <v>3454</v>
       </c>
       <c r="B3433" t="s">
-        <v>6046</v>
+        <v>6050</v>
       </c>
       <c r="D3433" t="s">
         <v>138</v>
@@ -94656,7 +94731,7 @@
         <v>3562</v>
       </c>
       <c r="B3434" t="s">
-        <v>6047</v>
+        <v>6051</v>
       </c>
       <c r="D3434" t="s">
         <v>138</v>
@@ -94667,10 +94742,10 @@
     </row>
     <row r="3435" spans="1:7">
       <c r="A3435" t="s">
-        <v>6048</v>
+        <v>6052</v>
       </c>
       <c r="B3435" t="s">
-        <v>6049</v>
+        <v>6053</v>
       </c>
       <c r="D3435" t="s">
         <v>138</v>
@@ -94681,7 +94756,7 @@
         <v>3721</v>
       </c>
       <c r="B3436" t="s">
-        <v>6050</v>
+        <v>6054</v>
       </c>
       <c r="D3436" t="s">
         <v>138</v>
@@ -94698,7 +94773,7 @@
         <v>3235</v>
       </c>
       <c r="B3437" t="s">
-        <v>6051</v>
+        <v>6055</v>
       </c>
       <c r="C3437" s="2"/>
       <c r="D3437" t="s">
@@ -94709,7 +94784,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3419" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3422" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94756,10 +94831,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6052</v>
+        <v>6056</v>
       </c>
       <c r="D5" t="s">
-        <v>6053</v>
+        <v>6057</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94770,13 +94845,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6055</v>
+        <v>6059</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94785,7 +94860,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6056</v>
+        <v>6060</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94800,16 +94875,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6057</v>
+        <v>6061</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6058</v>
+        <v>6062</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6059</v>
+        <v>6063</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94823,10 +94898,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6060</v>
+        <v>6064</v>
       </c>
       <c r="H14" t="s">
-        <v>6061</v>
+        <v>6065</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94841,16 +94916,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6062</v>
+        <v>6066</v>
       </c>
       <c r="W14" t="s">
-        <v>6063</v>
+        <v>6067</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6064</v>
+        <v>6068</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94862,158 +94937,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6066</v>
+        <v>6070</v>
       </c>
       <c r="AL14" t="s">
-        <v>6067</v>
+        <v>6071</v>
       </c>
       <c r="AO14" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="AR14" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
       <c r="AU14" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="AX14" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="T15" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="W15" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="Z15" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="AF15" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AI15" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AL15" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AU15" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AX15" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="H16" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="N16" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="T16" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="W16" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="Z16" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AC16" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AF16" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="AI16" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AL16" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AR16" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AU16" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AX16" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95021,43 +95096,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="D17" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="H17" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="N17" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="T17" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="W17" t="s">
-        <v>6065</v>
+        <v>6069</v>
       </c>
       <c r="Z17" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="AC17" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AF17" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AI17" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AR17" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AU17" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="BA17" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95065,37 +95140,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="H18" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="N18" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="T18" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="W18" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="Z18" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AC18" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AF18" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AI18" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AU18" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="BA18" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95103,37 +95178,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="H19" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="N19" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="T19" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="W19" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="Z19" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AC19" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="AF19" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AI19" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AU19" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="BA19" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95141,37 +95216,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6136</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6137</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6138</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6139</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6140</v>
+      </c>
+      <c r="W20" t="s">
         <v>6132</v>
       </c>
-      <c r="D20" t="s">
-        <v>6133</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6134</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6135</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6136</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6128</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AC20" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AF20" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AU20" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="BA20" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95179,37 +95254,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="D21" t="s">
+        <v>6146</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6147</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6148</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6149</v>
+      </c>
+      <c r="W21" t="s">
         <v>6142</v>
       </c>
-      <c r="H21" t="s">
-        <v>6143</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6144</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6145</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6138</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AC21" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AF21" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AU21" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="BA21" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95220,13 +95295,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95235,16 +95310,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AC22" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AF22" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AU22" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95252,25 +95327,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="H23" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="T23" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="Z23" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AC23" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AF23" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AU23" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95278,89 +95353,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="T24" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="Z24" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AC24" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AF24" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="D25" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="T25" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AC25" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AF25" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AC26" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AF26" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AC27" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="AF27" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="AC28" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AF28" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95370,22 +95445,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95395,7 +95470,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95403,7 +95478,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95418,7 +95493,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95436,227 +95511,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="Q41" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="T41" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="W41" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="AL41" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="AO41" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AR41" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="Q42" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="T42" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="W42" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="AC42" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="AL42" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="AO42" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="AR42" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="K43" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="N43" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="Q43" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="T43" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="W43" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="Z43" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="AC43" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="AF43" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="AL43" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AO43" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AR43" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="F44" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="N44" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="Q44" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="W44" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="Z44" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="AC44" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="AF44" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="AL44" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="AO44" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="AR44" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="F45" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="N45" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="Q45" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95665,103 +95740,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="AF45" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="AO45" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="AR45" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="F46" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="N46" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="AC46" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="AF46" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="AO46" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="AR46" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="F47" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="AC47" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="AF47" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
       <c r="AO47" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="AR47" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="F48" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95773,141 +95848,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="AF48" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="AO48" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="AR48" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="AF49" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="AR49" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="F50" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="AR50" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="F51" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="AR51" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="AR52" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="F53" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="F54" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="F55" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95915,10 +95990,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="F56" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -95926,18 +96001,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="F57" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="F58" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -95945,42 +96020,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="F59" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="F60" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="F61" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="F62" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="F63" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -95988,181 +96063,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="F64" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="F65" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
       <c r="F66" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
       <c r="F67" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
       <c r="F68" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
       <c r="F69" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
     </row>
   </sheetData>
@@ -96189,10 +96264,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96201,13 +96276,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96215,13 +96290,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96233,13 +96308,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96250,19 +96325,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
       <c r="S10" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="T10" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96276,15 +96351,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
       <c r="S11" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96293,18 +96368,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96313,7 +96388,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96324,13 +96399,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96341,7 +96416,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96350,10 +96425,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="T15" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96364,12 +96439,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96377,22 +96452,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96403,39 +96478,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
       <c r="H32" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
       <c r="K32" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
       <c r="N32" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
       <c r="Q32" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
       <c r="S32" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96444,13 +96519,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="K33" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="N33" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96458,153 +96533,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
       <c r="K34" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
       <c r="N34" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
       <c r="N35" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
       <c r="N36" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
       <c r="N37" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
       <c r="N38" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6410</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6411</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6412</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6413</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6414</v>
+        <v>6418</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6415</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6416</v>
+        <v>6420</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6417</v>
+        <v>6421</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96612,7 +96687,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6418</v>
+        <v>6422</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96628,7 +96703,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96644,21 +96719,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
       <c r="J68" t="s">
-        <v>6421</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6422</v>
+        <v>6426</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6423</v>
+        <v>6427</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96667,52 +96742,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6424</v>
+        <v>6428</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6054</v>
+        <v>6058</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6425</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6426</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6427</v>
+        <v>6431</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6428</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96774,7 +96849,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6429</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96782,10 +96857,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6430</v>
+        <v>6434</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6431</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96793,7 +96868,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6432</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96806,15 +96881,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6433</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6434</v>
+        <v>6438</v>
       </c>
       <c r="F17" t="s">
-        <v>6435</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3422</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3425</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13831" uniqueCount="6440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13845" uniqueCount="6447">
   <si>
     <t>名称</t>
   </si>
@@ -20783,6 +20783,27 @@
   </si>
   <si>
     <t>不同元素和至少为 K 的最短子数组长度</t>
+  </si>
+  <si>
+    <t>按位与结果非零的最长上升子序列</t>
+  </si>
+  <si>
+    <t>枚举 + LIS</t>
+  </si>
+  <si>
+    <t>这个按位枚举的思路还是很难想到的</t>
+  </si>
+  <si>
+    <t>使数组奇偶交替的最少操作</t>
+  </si>
+  <si>
+    <t>分类讨论 + 枚举</t>
+  </si>
+  <si>
+    <t>容易忽略变成奇偶奇和偶奇偶，数量相同的情况，需要都考虑</t>
+  </si>
+  <si>
+    <t>采购的最小花费</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -94665,7 +94686,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3425" spans="1:7">
+    <row r="3425" spans="1:8">
       <c r="A3425">
         <v>3795</v>
       </c>
@@ -94688,30 +94709,96 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3426" spans="1:7">
-      <c r="C3426" s="2"/>
-    </row>
-    <row r="3427" spans="1:7">
-      <c r="C3427" s="2"/>
-    </row>
-    <row r="3428" spans="1:7">
-      <c r="C3428" s="2"/>
-    </row>
-    <row r="3429" spans="1:7">
+    <row r="3426" spans="1:8">
+      <c r="A3426">
+        <v>3825</v>
+      </c>
+      <c r="B3426" t="s">
+        <v>6050</v>
+      </c>
+      <c r="C3426" s="2">
+        <v>46117</v>
+      </c>
+      <c r="D3426" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3426" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3426">
+        <v>1845</v>
+      </c>
+      <c r="G3426" s="1" t="s">
+        <v>6051</v>
+      </c>
+      <c r="H3426" s="1" t="s">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="3427" spans="1:8">
+      <c r="A3427">
+        <v>3854</v>
+      </c>
+      <c r="B3427" t="s">
+        <v>6053</v>
+      </c>
+      <c r="C3427" s="2">
+        <v>46117</v>
+      </c>
+      <c r="D3427" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3427" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3427">
+        <v>2095</v>
+      </c>
+      <c r="G3427" s="1" t="s">
+        <v>6054</v>
+      </c>
+      <c r="H3427" s="1" t="s">
+        <v>6055</v>
+      </c>
+    </row>
+    <row r="3428" spans="1:8">
+      <c r="A3428">
+        <v>3789</v>
+      </c>
+      <c r="B3428" t="s">
+        <v>6056</v>
+      </c>
+      <c r="C3428" s="2">
+        <v>46117</v>
+      </c>
+      <c r="D3428" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3428" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3428">
+        <v>1580</v>
+      </c>
+      <c r="G3428" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3429" spans="1:8">
       <c r="C3429" s="2"/>
     </row>
-    <row r="3430" spans="1:7">
+    <row r="3430" spans="1:8">
       <c r="C3430" s="2"/>
     </row>
-    <row r="3431" spans="1:7">
+    <row r="3431" spans="1:8">
       <c r="C3431" s="2"/>
     </row>
-    <row r="3433" spans="1:7">
+    <row r="3433" spans="1:8">
       <c r="A3433">
         <v>3454</v>
       </c>
       <c r="B3433" t="s">
-        <v>6050</v>
+        <v>6057</v>
       </c>
       <c r="D3433" t="s">
         <v>138</v>
@@ -94726,12 +94813,12 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3434" spans="1:7">
+    <row r="3434" spans="1:8">
       <c r="A3434">
         <v>3562</v>
       </c>
       <c r="B3434" t="s">
-        <v>6051</v>
+        <v>6058</v>
       </c>
       <c r="D3434" t="s">
         <v>138</v>
@@ -94740,23 +94827,23 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="3435" spans="1:7">
+    <row r="3435" spans="1:8">
       <c r="A3435" t="s">
-        <v>6052</v>
+        <v>6059</v>
       </c>
       <c r="B3435" t="s">
-        <v>6053</v>
+        <v>6060</v>
       </c>
       <c r="D3435" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3436" spans="1:7">
+    <row r="3436" spans="1:8">
       <c r="A3436">
         <v>3721</v>
       </c>
       <c r="B3436" t="s">
-        <v>6054</v>
+        <v>6061</v>
       </c>
       <c r="D3436" t="s">
         <v>138</v>
@@ -94768,12 +94855,12 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="3437" spans="1:7">
+    <row r="3437" spans="1:8">
       <c r="A3437">
         <v>3235</v>
       </c>
       <c r="B3437" t="s">
-        <v>6055</v>
+        <v>6062</v>
       </c>
       <c r="C3437" s="2"/>
       <c r="D3437" t="s">
@@ -94784,7 +94871,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3422" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3425" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94831,10 +94918,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6056</v>
+        <v>6063</v>
       </c>
       <c r="D5" t="s">
-        <v>6057</v>
+        <v>6064</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94845,13 +94932,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6058</v>
+        <v>6065</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6059</v>
+        <v>6066</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94860,7 +94947,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6060</v>
+        <v>6067</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94875,16 +94962,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6061</v>
+        <v>6068</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6062</v>
+        <v>6069</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6063</v>
+        <v>6070</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94898,10 +94985,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6064</v>
+        <v>6071</v>
       </c>
       <c r="H14" t="s">
-        <v>6065</v>
+        <v>6072</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -94916,16 +95003,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6066</v>
+        <v>6073</v>
       </c>
       <c r="W14" t="s">
-        <v>6067</v>
+        <v>6074</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6068</v>
+        <v>6075</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -94937,158 +95024,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6069</v>
+        <v>6076</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6070</v>
+        <v>6077</v>
       </c>
       <c r="AL14" t="s">
-        <v>6071</v>
+        <v>6078</v>
       </c>
       <c r="AO14" t="s">
-        <v>6072</v>
+        <v>6079</v>
       </c>
       <c r="AR14" t="s">
-        <v>6073</v>
+        <v>6080</v>
       </c>
       <c r="AU14" t="s">
-        <v>6074</v>
+        <v>6081</v>
       </c>
       <c r="AX14" t="s">
-        <v>6075</v>
+        <v>6082</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6076</v>
+        <v>6083</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6077</v>
+        <v>6084</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6078</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6079</v>
+        <v>6086</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6080</v>
+        <v>6087</v>
       </c>
       <c r="T15" t="s">
-        <v>6081</v>
+        <v>6088</v>
       </c>
       <c r="W15" t="s">
-        <v>6082</v>
+        <v>6089</v>
       </c>
       <c r="Z15" t="s">
-        <v>6083</v>
+        <v>6090</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6084</v>
+        <v>6091</v>
       </c>
       <c r="AF15" t="s">
-        <v>6085</v>
+        <v>6092</v>
       </c>
       <c r="AI15" t="s">
-        <v>6086</v>
+        <v>6093</v>
       </c>
       <c r="AL15" t="s">
-        <v>6087</v>
+        <v>6094</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6088</v>
+        <v>6095</v>
       </c>
       <c r="AU15" t="s">
-        <v>6089</v>
+        <v>6096</v>
       </c>
       <c r="AX15" t="s">
-        <v>6090</v>
+        <v>6097</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6091</v>
+        <v>6098</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6092</v>
+        <v>6099</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6093</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
+        <v>6101</v>
+      </c>
+      <c r="H16" t="s">
+        <v>6102</v>
+      </c>
+      <c r="N16" t="s">
+        <v>6103</v>
+      </c>
+      <c r="T16" t="s">
+        <v>6104</v>
+      </c>
+      <c r="W16" t="s">
+        <v>6105</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>6106</v>
+      </c>
+      <c r="AC16" t="s">
         <v>6094</v>
       </c>
-      <c r="H16" t="s">
-        <v>6095</v>
-      </c>
-      <c r="N16" t="s">
-        <v>6096</v>
-      </c>
-      <c r="T16" t="s">
-        <v>6097</v>
-      </c>
-      <c r="W16" t="s">
-        <v>6098</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>6099</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>6087</v>
-      </c>
       <c r="AF16" t="s">
-        <v>6069</v>
+        <v>6076</v>
       </c>
       <c r="AI16" t="s">
-        <v>6100</v>
+        <v>6107</v>
       </c>
       <c r="AL16" t="s">
-        <v>6101</v>
+        <v>6108</v>
       </c>
       <c r="AR16" t="s">
-        <v>6102</v>
+        <v>6109</v>
       </c>
       <c r="AU16" t="s">
-        <v>6103</v>
+        <v>6110</v>
       </c>
       <c r="AX16" t="s">
-        <v>6104</v>
+        <v>6111</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6105</v>
+        <v>6112</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95096,43 +95183,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6106</v>
+        <v>6113</v>
       </c>
       <c r="D17" t="s">
-        <v>6107</v>
+        <v>6114</v>
       </c>
       <c r="H17" t="s">
-        <v>6108</v>
+        <v>6115</v>
       </c>
       <c r="N17" t="s">
-        <v>6109</v>
+        <v>6116</v>
       </c>
       <c r="T17" t="s">
-        <v>6110</v>
+        <v>6117</v>
       </c>
       <c r="W17" t="s">
-        <v>6069</v>
+        <v>6076</v>
       </c>
       <c r="Z17" t="s">
-        <v>6080</v>
+        <v>6087</v>
       </c>
       <c r="AC17" t="s">
-        <v>6111</v>
+        <v>6118</v>
       </c>
       <c r="AF17" t="s">
-        <v>6112</v>
+        <v>6119</v>
       </c>
       <c r="AI17" t="s">
-        <v>6113</v>
+        <v>6120</v>
       </c>
       <c r="AR17" t="s">
-        <v>6114</v>
+        <v>6121</v>
       </c>
       <c r="AU17" t="s">
-        <v>6115</v>
+        <v>6122</v>
       </c>
       <c r="BA17" t="s">
-        <v>6116</v>
+        <v>6123</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95140,37 +95227,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6117</v>
+        <v>6124</v>
       </c>
       <c r="H18" t="s">
-        <v>6118</v>
+        <v>6125</v>
       </c>
       <c r="N18" t="s">
-        <v>6119</v>
+        <v>6126</v>
       </c>
       <c r="T18" t="s">
-        <v>6120</v>
+        <v>6127</v>
       </c>
       <c r="W18" t="s">
-        <v>6121</v>
+        <v>6128</v>
       </c>
       <c r="Z18" t="s">
-        <v>6096</v>
+        <v>6103</v>
       </c>
       <c r="AC18" t="s">
-        <v>6122</v>
+        <v>6129</v>
       </c>
       <c r="AF18" t="s">
-        <v>6123</v>
+        <v>6130</v>
       </c>
       <c r="AI18" t="s">
-        <v>6124</v>
+        <v>6131</v>
       </c>
       <c r="AU18" t="s">
-        <v>6125</v>
+        <v>6132</v>
       </c>
       <c r="BA18" t="s">
-        <v>6126</v>
+        <v>6133</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95178,37 +95265,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6127</v>
+        <v>6134</v>
       </c>
       <c r="H19" t="s">
-        <v>6128</v>
+        <v>6135</v>
       </c>
       <c r="N19" t="s">
-        <v>6129</v>
+        <v>6136</v>
       </c>
       <c r="T19" t="s">
-        <v>6130</v>
+        <v>6137</v>
       </c>
       <c r="W19" t="s">
-        <v>6104</v>
+        <v>6111</v>
       </c>
       <c r="Z19" t="s">
-        <v>6109</v>
+        <v>6116</v>
       </c>
       <c r="AC19" t="s">
-        <v>6131</v>
+        <v>6138</v>
       </c>
       <c r="AF19" t="s">
-        <v>6132</v>
+        <v>6139</v>
       </c>
       <c r="AI19" t="s">
-        <v>6133</v>
+        <v>6140</v>
       </c>
       <c r="AU19" t="s">
-        <v>6134</v>
+        <v>6141</v>
       </c>
       <c r="BA19" t="s">
-        <v>6135</v>
+        <v>6142</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95216,37 +95303,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6136</v>
+        <v>6143</v>
       </c>
       <c r="D20" t="s">
-        <v>6137</v>
+        <v>6144</v>
       </c>
       <c r="H20" t="s">
-        <v>6138</v>
+        <v>6145</v>
       </c>
       <c r="N20" t="s">
+        <v>6146</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6147</v>
+      </c>
+      <c r="W20" t="s">
         <v>6139</v>
       </c>
-      <c r="T20" t="s">
-        <v>6140</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6132</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6119</v>
+        <v>6126</v>
       </c>
       <c r="AC20" t="s">
-        <v>6141</v>
+        <v>6148</v>
       </c>
       <c r="AF20" t="s">
-        <v>6142</v>
+        <v>6149</v>
       </c>
       <c r="AU20" t="s">
-        <v>6143</v>
+        <v>6150</v>
       </c>
       <c r="BA20" t="s">
-        <v>6144</v>
+        <v>6151</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95254,37 +95341,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6145</v>
+        <v>6152</v>
       </c>
       <c r="D21" t="s">
-        <v>6146</v>
+        <v>6153</v>
       </c>
       <c r="H21" t="s">
-        <v>6147</v>
+        <v>6154</v>
       </c>
       <c r="N21" t="s">
-        <v>6148</v>
+        <v>6155</v>
       </c>
       <c r="T21" t="s">
+        <v>6156</v>
+      </c>
+      <c r="W21" t="s">
         <v>6149</v>
       </c>
-      <c r="W21" t="s">
-        <v>6142</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6129</v>
+        <v>6136</v>
       </c>
       <c r="AC21" t="s">
-        <v>6150</v>
+        <v>6157</v>
       </c>
       <c r="AF21" t="s">
-        <v>6151</v>
+        <v>6158</v>
       </c>
       <c r="AU21" t="s">
-        <v>6152</v>
+        <v>6159</v>
       </c>
       <c r="BA21" t="s">
-        <v>6153</v>
+        <v>6160</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95295,13 +95382,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6154</v>
+        <v>6161</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6155</v>
+        <v>6162</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95310,16 +95397,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6139</v>
+        <v>6146</v>
       </c>
       <c r="AC22" t="s">
-        <v>6156</v>
+        <v>6163</v>
       </c>
       <c r="AF22" t="s">
-        <v>6157</v>
+        <v>6164</v>
       </c>
       <c r="AU22" t="s">
-        <v>6158</v>
+        <v>6165</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95327,25 +95414,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6159</v>
+        <v>6166</v>
       </c>
       <c r="H23" t="s">
-        <v>6160</v>
+        <v>6167</v>
       </c>
       <c r="T23" t="s">
-        <v>6161</v>
+        <v>6168</v>
       </c>
       <c r="Z23" t="s">
-        <v>6148</v>
+        <v>6155</v>
       </c>
       <c r="AC23" t="s">
-        <v>6162</v>
+        <v>6169</v>
       </c>
       <c r="AF23" t="s">
-        <v>6163</v>
+        <v>6170</v>
       </c>
       <c r="AU23" t="s">
-        <v>6164</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95353,89 +95440,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6165</v>
+        <v>6172</v>
       </c>
       <c r="T24" t="s">
-        <v>6166</v>
+        <v>6173</v>
       </c>
       <c r="Z24" t="s">
-        <v>6167</v>
+        <v>6174</v>
       </c>
       <c r="AC24" t="s">
-        <v>6168</v>
+        <v>6175</v>
       </c>
       <c r="AF24" t="s">
-        <v>6169</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6170</v>
+        <v>6177</v>
       </c>
       <c r="D25" t="s">
-        <v>6171</v>
+        <v>6178</v>
       </c>
       <c r="T25" t="s">
-        <v>6172</v>
+        <v>6179</v>
       </c>
       <c r="AC25" t="s">
-        <v>6173</v>
+        <v>6180</v>
       </c>
       <c r="AF25" t="s">
-        <v>6174</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6175</v>
+        <v>6182</v>
       </c>
       <c r="AC26" t="s">
-        <v>6176</v>
+        <v>6183</v>
       </c>
       <c r="AF26" t="s">
-        <v>6177</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6178</v>
+        <v>6185</v>
       </c>
       <c r="AC27" t="s">
-        <v>6179</v>
+        <v>6186</v>
       </c>
       <c r="AF27" t="s">
-        <v>6180</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6181</v>
+        <v>6188</v>
       </c>
       <c r="AC28" t="s">
-        <v>6182</v>
+        <v>6189</v>
       </c>
       <c r="AF28" t="s">
-        <v>6183</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6184</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6185</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6186</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6187</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95445,22 +95532,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6188</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6189</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6190</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6191</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95470,7 +95557,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6192</v>
+        <v>6199</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95478,7 +95565,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6193</v>
+        <v>6200</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95493,7 +95580,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6194</v>
+        <v>6201</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95511,227 +95598,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6195</v>
+        <v>6202</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6196</v>
+        <v>6203</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6197</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6198</v>
+        <v>6205</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6199</v>
+        <v>6206</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6200</v>
+        <v>6207</v>
       </c>
       <c r="Q41" t="s">
-        <v>6188</v>
+        <v>6195</v>
       </c>
       <c r="T41" t="s">
-        <v>6084</v>
+        <v>6091</v>
       </c>
       <c r="W41" t="s">
-        <v>6201</v>
+        <v>6208</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6202</v>
+        <v>6209</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6203</v>
+        <v>6210</v>
       </c>
       <c r="AL41" t="s">
-        <v>6204</v>
+        <v>6211</v>
       </c>
       <c r="AO41" t="s">
-        <v>6205</v>
+        <v>6212</v>
       </c>
       <c r="AR41" t="s">
-        <v>6206</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6207</v>
+        <v>6214</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6208</v>
+        <v>6215</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6209</v>
+        <v>6216</v>
       </c>
       <c r="Q42" t="s">
-        <v>6189</v>
+        <v>6196</v>
       </c>
       <c r="T42" t="s">
-        <v>6210</v>
+        <v>6217</v>
       </c>
       <c r="W42" t="s">
-        <v>6211</v>
+        <v>6218</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6212</v>
+        <v>6219</v>
       </c>
       <c r="AC42" t="s">
-        <v>6213</v>
+        <v>6220</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6214</v>
+        <v>6221</v>
       </c>
       <c r="AL42" t="s">
-        <v>6215</v>
+        <v>6222</v>
       </c>
       <c r="AO42" t="s">
-        <v>6216</v>
+        <v>6223</v>
       </c>
       <c r="AR42" t="s">
-        <v>6217</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6218</v>
+        <v>6225</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6219</v>
+        <v>6226</v>
       </c>
       <c r="K43" t="s">
-        <v>6220</v>
+        <v>6227</v>
       </c>
       <c r="N43" t="s">
-        <v>6221</v>
+        <v>6228</v>
       </c>
       <c r="Q43" t="s">
-        <v>6190</v>
+        <v>6197</v>
       </c>
       <c r="T43" t="s">
-        <v>6222</v>
+        <v>6229</v>
       </c>
       <c r="W43" t="s">
-        <v>6223</v>
+        <v>6230</v>
       </c>
       <c r="Z43" t="s">
-        <v>6224</v>
+        <v>6231</v>
       </c>
       <c r="AC43" t="s">
-        <v>6225</v>
+        <v>6232</v>
       </c>
       <c r="AF43" t="s">
-        <v>6226</v>
+        <v>6233</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6227</v>
+        <v>6234</v>
       </c>
       <c r="AL43" t="s">
-        <v>6136</v>
+        <v>6143</v>
       </c>
       <c r="AO43" t="s">
-        <v>6228</v>
+        <v>6235</v>
       </c>
       <c r="AR43" t="s">
-        <v>6229</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6230</v>
+        <v>6237</v>
       </c>
       <c r="F44" t="s">
-        <v>6231</v>
+        <v>6238</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6232</v>
+        <v>6239</v>
       </c>
       <c r="N44" t="s">
-        <v>6233</v>
+        <v>6240</v>
       </c>
       <c r="Q44" t="s">
-        <v>6191</v>
+        <v>6198</v>
       </c>
       <c r="W44" t="s">
-        <v>6234</v>
+        <v>6241</v>
       </c>
       <c r="Z44" t="s">
-        <v>6235</v>
+        <v>6242</v>
       </c>
       <c r="AC44" t="s">
-        <v>6236</v>
+        <v>6243</v>
       </c>
       <c r="AF44" t="s">
-        <v>6173</v>
+        <v>6180</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6237</v>
+        <v>6244</v>
       </c>
       <c r="AL44" t="s">
-        <v>6238</v>
+        <v>6245</v>
       </c>
       <c r="AO44" t="s">
-        <v>6239</v>
+        <v>6246</v>
       </c>
       <c r="AR44" t="s">
-        <v>6240</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6241</v>
+        <v>6248</v>
       </c>
       <c r="F45" t="s">
-        <v>6242</v>
+        <v>6249</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6243</v>
+        <v>6250</v>
       </c>
       <c r="N45" t="s">
-        <v>6244</v>
+        <v>6251</v>
       </c>
       <c r="Q45" t="s">
-        <v>6245</v>
+        <v>6252</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95740,103 +95827,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6246</v>
+        <v>6253</v>
       </c>
       <c r="AF45" t="s">
-        <v>6247</v>
+        <v>6254</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6248</v>
+        <v>6255</v>
       </c>
       <c r="AO45" t="s">
-        <v>6249</v>
+        <v>6256</v>
       </c>
       <c r="AR45" t="s">
-        <v>6250</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6251</v>
+        <v>6258</v>
       </c>
       <c r="F46" t="s">
-        <v>6252</v>
+        <v>6259</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6253</v>
+        <v>6260</v>
       </c>
       <c r="N46" t="s">
-        <v>6254</v>
+        <v>6261</v>
       </c>
       <c r="AC46" t="s">
-        <v>6255</v>
+        <v>6262</v>
       </c>
       <c r="AF46" t="s">
-        <v>6256</v>
+        <v>6263</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6257</v>
+        <v>6264</v>
       </c>
       <c r="AO46" t="s">
-        <v>6258</v>
+        <v>6265</v>
       </c>
       <c r="AR46" t="s">
-        <v>6259</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6260</v>
+        <v>6267</v>
       </c>
       <c r="F47" t="s">
-        <v>6261</v>
+        <v>6268</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6262</v>
+        <v>6269</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6263</v>
+        <v>6270</v>
       </c>
       <c r="AC47" t="s">
-        <v>6264</v>
+        <v>6271</v>
       </c>
       <c r="AF47" t="s">
-        <v>6265</v>
+        <v>6272</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6266</v>
+        <v>6273</v>
       </c>
       <c r="AO47" t="s">
-        <v>6267</v>
+        <v>6274</v>
       </c>
       <c r="AR47" t="s">
-        <v>6268</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6269</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="s">
-        <v>6270</v>
+        <v>6277</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95848,141 +95935,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6271</v>
+        <v>6278</v>
       </c>
       <c r="AF48" t="s">
-        <v>6272</v>
+        <v>6279</v>
       </c>
       <c r="AO48" t="s">
-        <v>6273</v>
+        <v>6280</v>
       </c>
       <c r="AR48" t="s">
-        <v>6274</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6275</v>
+        <v>6282</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6276</v>
+        <v>6283</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6277</v>
+        <v>6284</v>
       </c>
       <c r="AF49" t="s">
-        <v>6278</v>
+        <v>6285</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6279</v>
+        <v>6286</v>
       </c>
       <c r="AR49" t="s">
-        <v>6280</v>
+        <v>6287</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6281</v>
+        <v>6288</v>
       </c>
       <c r="F50" t="s">
-        <v>6282</v>
+        <v>6289</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6283</v>
+        <v>6290</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6284</v>
+        <v>6291</v>
       </c>
       <c r="AR50" t="s">
-        <v>6285</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6286</v>
+        <v>6293</v>
       </c>
       <c r="F51" t="s">
-        <v>6287</v>
+        <v>6294</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6288</v>
+        <v>6295</v>
       </c>
       <c r="AR51" t="s">
-        <v>6289</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6290</v>
+        <v>6297</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6291</v>
+        <v>6298</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6292</v>
+        <v>6299</v>
       </c>
       <c r="AR52" t="s">
-        <v>6293</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6294</v>
+        <v>6301</v>
       </c>
       <c r="F53" t="s">
-        <v>6295</v>
+        <v>6302</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6296</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6297</v>
+        <v>6304</v>
       </c>
       <c r="F54" t="s">
-        <v>6298</v>
+        <v>6305</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6299</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6300</v>
+        <v>6307</v>
       </c>
       <c r="F55" t="s">
-        <v>6301</v>
+        <v>6308</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -95990,10 +96077,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6302</v>
+        <v>6309</v>
       </c>
       <c r="F56" t="s">
-        <v>6303</v>
+        <v>6310</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96001,18 +96088,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6304</v>
+        <v>6311</v>
       </c>
       <c r="F57" t="s">
-        <v>6305</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6306</v>
+        <v>6313</v>
       </c>
       <c r="F58" t="s">
-        <v>6307</v>
+        <v>6314</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96020,42 +96107,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6308</v>
+        <v>6315</v>
       </c>
       <c r="F59" t="s">
-        <v>6309</v>
+        <v>6316</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6310</v>
+        <v>6317</v>
       </c>
       <c r="F60" t="s">
-        <v>6311</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6312</v>
+        <v>6319</v>
       </c>
       <c r="F61" t="s">
-        <v>6313</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6314</v>
+        <v>6321</v>
       </c>
       <c r="F62" t="s">
-        <v>6315</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6316</v>
+        <v>6323</v>
       </c>
       <c r="F63" t="s">
-        <v>6317</v>
+        <v>6324</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96063,181 +96150,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6318</v>
+        <v>6325</v>
       </c>
       <c r="F64" t="s">
-        <v>6319</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6281</v>
+        <v>6288</v>
       </c>
       <c r="F65" t="s">
-        <v>6272</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6320</v>
+        <v>6327</v>
       </c>
       <c r="F66" t="s">
-        <v>6321</v>
+        <v>6328</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6322</v>
+        <v>6329</v>
       </c>
       <c r="F67" t="s">
-        <v>6323</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6324</v>
+        <v>6331</v>
       </c>
       <c r="F68" t="s">
-        <v>6288</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6325</v>
+        <v>6332</v>
       </c>
       <c r="F69" t="s">
-        <v>6326</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6327</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6328</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6329</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6330</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6331</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6332</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6333</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6334</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6335</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6336</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6337</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6338</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6339</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6340</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6341</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6342</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6343</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6344</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6345</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6346</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6085</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6347</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6348</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6349</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6350</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6351</v>
+        <v>6358</v>
       </c>
     </row>
   </sheetData>
@@ -96264,10 +96351,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6352</v>
+        <v>6359</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6353</v>
+        <v>6360</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96276,13 +96363,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6354</v>
+        <v>6361</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6355</v>
+        <v>6362</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6356</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96290,13 +96377,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6357</v>
+        <v>6364</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6358</v>
+        <v>6365</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96308,13 +96395,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6359</v>
+        <v>6366</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6360</v>
+        <v>6367</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96325,19 +96412,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6361</v>
+        <v>6368</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6362</v>
+        <v>6369</v>
       </c>
       <c r="S10" t="s">
-        <v>6363</v>
+        <v>6370</v>
       </c>
       <c r="T10" t="s">
-        <v>6364</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96351,15 +96438,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6365</v>
+        <v>6372</v>
       </c>
       <c r="S11" t="s">
-        <v>6089</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6366</v>
+        <v>6373</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96368,18 +96455,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6367</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6368</v>
+        <v>6375</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6369</v>
+        <v>6376</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96388,7 +96475,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6370</v>
+        <v>6377</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96399,13 +96486,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6371</v>
+        <v>6378</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6372</v>
+        <v>6379</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96416,7 +96503,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6373</v>
+        <v>6380</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96425,10 +96512,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6256</v>
+        <v>6263</v>
       </c>
       <c r="T15" t="s">
-        <v>6374</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96439,12 +96526,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6375</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96452,22 +96539,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6379</v>
+        <v>6386</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6380</v>
+        <v>6387</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6381</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96478,39 +96565,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6382</v>
+        <v>6389</v>
       </c>
       <c r="H32" t="s">
-        <v>6383</v>
+        <v>6390</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6384</v>
+        <v>6391</v>
       </c>
       <c r="K32" t="s">
-        <v>6385</v>
+        <v>6392</v>
       </c>
       <c r="N32" t="s">
-        <v>6386</v>
+        <v>6393</v>
       </c>
       <c r="Q32" t="s">
-        <v>6387</v>
+        <v>6394</v>
       </c>
       <c r="S32" t="s">
-        <v>6113</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6388</v>
+        <v>6395</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6389</v>
+        <v>6396</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96519,13 +96606,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6390</v>
+        <v>6397</v>
       </c>
       <c r="K33" t="s">
-        <v>6391</v>
+        <v>6398</v>
       </c>
       <c r="N33" t="s">
-        <v>6392</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96533,153 +96620,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6393</v>
+        <v>6400</v>
       </c>
       <c r="K34" t="s">
-        <v>6394</v>
+        <v>6401</v>
       </c>
       <c r="N34" t="s">
-        <v>6395</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6396</v>
+        <v>6403</v>
       </c>
       <c r="N35" t="s">
-        <v>6397</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6398</v>
+        <v>6405</v>
       </c>
       <c r="N36" t="s">
-        <v>6399</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6400</v>
+        <v>6407</v>
       </c>
       <c r="N37" t="s">
-        <v>6401</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6402</v>
+        <v>6409</v>
       </c>
       <c r="N38" t="s">
-        <v>6403</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6126</v>
+        <v>6133</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6404</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6405</v>
+        <v>6412</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6406</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6407</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6408</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6409</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6410</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6411</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6412</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6413</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6303</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6414</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6415</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6301</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6416</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6417</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6418</v>
+        <v>6425</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6419</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6420</v>
+        <v>6427</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6421</v>
+        <v>6428</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96687,7 +96774,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6422</v>
+        <v>6429</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96703,7 +96790,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6423</v>
+        <v>6430</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96719,21 +96806,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6424</v>
+        <v>6431</v>
       </c>
       <c r="J68" t="s">
-        <v>6425</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6426</v>
+        <v>6433</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6427</v>
+        <v>6434</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96742,52 +96829,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6201</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6428</v>
+        <v>6435</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6058</v>
+        <v>6065</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6211</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6234</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6429</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6430</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6223</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6431</v>
+        <v>6438</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6432</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96849,7 +96936,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6433</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96857,10 +96944,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6434</v>
+        <v>6441</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6435</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96868,7 +96955,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6436</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96881,15 +96968,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6437</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6438</v>
+        <v>6445</v>
       </c>
       <c r="F17" t="s">
-        <v>6439</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3425</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3430</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13845" uniqueCount="6447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13858" uniqueCount="6452">
   <si>
     <t>名称</t>
   </si>
@@ -20804,6 +20804,21 @@
   </si>
   <si>
     <t>采购的最小花费</t>
+  </si>
+  <si>
+    <t>避免禁用值的最小交换次数</t>
+  </si>
+  <si>
+    <t>统计在矩形格子里移动的路径数目</t>
+  </si>
+  <si>
+    <t>前缀和 + DP</t>
+  </si>
+  <si>
+    <t>树组的交互代价总和</t>
+  </si>
+  <si>
+    <t>考虑每条边的贡献值</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22466,6 +22481,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22474,14 +22497,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -94785,20 +94800,83 @@
       </c>
     </row>
     <row r="3429" spans="1:8">
-      <c r="C3429" s="2"/>
+      <c r="A3429">
+        <v>3785</v>
+      </c>
+      <c r="B3429" t="s">
+        <v>6057</v>
+      </c>
+      <c r="C3429" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D3429" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3429" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3429">
+        <v>2051</v>
+      </c>
+      <c r="G3429" s="1" t="s">
+        <v>4190</v>
+      </c>
     </row>
     <row r="3430" spans="1:8">
-      <c r="C3430" s="2"/>
+      <c r="A3430">
+        <v>3797</v>
+      </c>
+      <c r="B3430" t="s">
+        <v>6058</v>
+      </c>
+      <c r="C3430" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D3430" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3430" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3430">
+        <v>2375</v>
+      </c>
+      <c r="G3430" s="1" t="s">
+        <v>6059</v>
+      </c>
     </row>
     <row r="3431" spans="1:8">
-      <c r="C3431" s="2"/>
+      <c r="A3431">
+        <v>3786</v>
+      </c>
+      <c r="B3431" t="s">
+        <v>6060</v>
+      </c>
+      <c r="C3431" s="2">
+        <v>46118</v>
+      </c>
+      <c r="D3431" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3431" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3431">
+        <v>2139</v>
+      </c>
+      <c r="G3431" s="1" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H3431" s="1" t="s">
+        <v>6061</v>
+      </c>
     </row>
     <row r="3433" spans="1:8">
       <c r="A3433">
         <v>3454</v>
       </c>
       <c r="B3433" t="s">
-        <v>6057</v>
+        <v>6062</v>
       </c>
       <c r="D3433" t="s">
         <v>138</v>
@@ -94818,7 +94896,7 @@
         <v>3562</v>
       </c>
       <c r="B3434" t="s">
-        <v>6058</v>
+        <v>6063</v>
       </c>
       <c r="D3434" t="s">
         <v>138</v>
@@ -94829,10 +94907,10 @@
     </row>
     <row r="3435" spans="1:8">
       <c r="A3435" t="s">
-        <v>6059</v>
+        <v>6064</v>
       </c>
       <c r="B3435" t="s">
-        <v>6060</v>
+        <v>6065</v>
       </c>
       <c r="D3435" t="s">
         <v>138</v>
@@ -94843,7 +94921,7 @@
         <v>3721</v>
       </c>
       <c r="B3436" t="s">
-        <v>6061</v>
+        <v>6066</v>
       </c>
       <c r="D3436" t="s">
         <v>138</v>
@@ -94860,7 +94938,7 @@
         <v>3235</v>
       </c>
       <c r="B3437" t="s">
-        <v>6062</v>
+        <v>6067</v>
       </c>
       <c r="C3437" s="2"/>
       <c r="D3437" t="s">
@@ -94871,7 +94949,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3425" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3430" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94918,10 +94996,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6063</v>
+        <v>6068</v>
       </c>
       <c r="D5" t="s">
-        <v>6064</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -94932,13 +95010,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6066</v>
+        <v>6071</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -94947,7 +95025,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6067</v>
+        <v>6072</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -94962,16 +95040,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6068</v>
+        <v>6073</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6069</v>
+        <v>6074</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6070</v>
+        <v>6075</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -94985,10 +95063,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6071</v>
+        <v>6076</v>
       </c>
       <c r="H14" t="s">
-        <v>6072</v>
+        <v>6077</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95003,16 +95081,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6073</v>
+        <v>6078</v>
       </c>
       <c r="W14" t="s">
-        <v>6074</v>
+        <v>6079</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6075</v>
+        <v>6080</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95024,158 +95102,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6077</v>
+        <v>6082</v>
       </c>
       <c r="AL14" t="s">
-        <v>6078</v>
+        <v>6083</v>
       </c>
       <c r="AO14" t="s">
-        <v>6079</v>
+        <v>6084</v>
       </c>
       <c r="AR14" t="s">
-        <v>6080</v>
+        <v>6085</v>
       </c>
       <c r="AU14" t="s">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="AX14" t="s">
-        <v>6082</v>
+        <v>6087</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6083</v>
+        <v>6088</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6084</v>
+        <v>6089</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="T15" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="W15" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="Z15" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="AF15" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
       <c r="AI15" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="AL15" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="AU15" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="AX15" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="H16" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
       <c r="N16" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="T16" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="W16" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="Z16" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="AC16" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="AF16" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="AI16" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="AL16" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="AR16" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="AU16" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="AX16" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95183,43 +95261,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="D17" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="H17" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="N17" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="T17" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="W17" t="s">
-        <v>6076</v>
+        <v>6081</v>
       </c>
       <c r="Z17" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="AC17" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="AF17" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="AI17" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="AR17" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="AU17" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="BA17" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95227,37 +95305,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="H18" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="N18" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="T18" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="W18" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="Z18" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="AC18" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="AF18" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="AI18" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AU18" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="BA18" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95265,37 +95343,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="H19" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="N19" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="T19" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="W19" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="Z19" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="AC19" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AF19" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="AI19" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="AU19" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="BA19" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95303,37 +95381,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="D20" t="s">
+        <v>6149</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6150</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6151</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6152</v>
+      </c>
+      <c r="W20" t="s">
         <v>6144</v>
       </c>
-      <c r="H20" t="s">
-        <v>6145</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6146</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6147</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6139</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="AC20" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="AF20" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="AU20" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="BA20" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95341,37 +95419,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
       <c r="D21" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="H21" t="s">
+        <v>6159</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6160</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6161</v>
+      </c>
+      <c r="W21" t="s">
         <v>6154</v>
       </c>
-      <c r="N21" t="s">
-        <v>6155</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6156</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6149</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="AC21" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="AF21" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="AU21" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="BA21" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95382,13 +95460,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95397,16 +95475,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="AC22" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="AF22" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="AU22" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95414,25 +95492,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="H23" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="T23" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="Z23" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="AC23" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="AF23" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="AU23" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95440,89 +95518,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="T24" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="Z24" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="AC24" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="AF24" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="D25" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
       <c r="T25" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="AC25" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="AF25" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
       <c r="AC26" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="AF26" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="AC27" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="AF27" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="AC28" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="AF28" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95532,22 +95610,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95557,7 +95635,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95565,7 +95643,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95580,7 +95658,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95598,227 +95676,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="Q41" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="T41" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="W41" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
       <c r="AL41" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="AO41" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="AR41" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="Q42" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="T42" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="W42" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="AC42" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="AL42" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="AO42" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
       <c r="AR42" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="K43" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="N43" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="Q43" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="T43" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="W43" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="Z43" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="AC43" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="AF43" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="AL43" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="AO43" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="AR43" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="F44" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="N44" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
       <c r="Q44" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="W44" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="Z44" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="AC44" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="AF44" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="AL44" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="AO44" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="AR44" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
       <c r="F45" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="N45" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="Q45" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95827,103 +95905,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="AF45" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="AO45" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="AR45" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="F46" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="N46" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
       <c r="AC46" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="AF46" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
       <c r="AO46" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="AR46" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="F47" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
       <c r="AC47" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="AF47" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="AO47" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
       <c r="AR47" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="F48" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -95935,141 +96013,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
       <c r="AF48" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="AO48" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
       <c r="AR48" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
       <c r="AF49" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
       <c r="AR49" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="F50" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="AR50" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="F51" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="AR51" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
       <c r="AR52" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="F53" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
       <c r="F54" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
       <c r="F55" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96077,10 +96155,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
       <c r="F56" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96088,18 +96166,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
       <c r="F57" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
       <c r="F58" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96107,42 +96185,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
       <c r="F59" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="F60" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
       <c r="F61" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
       <c r="F62" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
       <c r="F63" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96150,181 +96228,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
       <c r="F64" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="F65" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
       <c r="F66" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
       <c r="F67" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
       <c r="F68" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
       <c r="F69" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
     </row>
   </sheetData>
@@ -96351,10 +96429,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96363,13 +96441,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96377,13 +96455,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96395,13 +96473,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96412,19 +96490,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
       <c r="S10" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
       <c r="T10" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96438,15 +96516,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="S11" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96455,18 +96533,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96475,7 +96553,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96486,13 +96564,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96503,7 +96581,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96512,10 +96590,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="T15" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96526,12 +96604,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96539,22 +96617,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96565,39 +96643,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
       <c r="H32" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
       <c r="K32" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
       <c r="N32" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
       <c r="Q32" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
       <c r="S32" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6395</v>
+        <v>6400</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6396</v>
+        <v>6401</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96606,13 +96684,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6397</v>
+        <v>6402</v>
       </c>
       <c r="K33" t="s">
-        <v>6398</v>
+        <v>6403</v>
       </c>
       <c r="N33" t="s">
-        <v>6399</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96620,153 +96698,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6400</v>
+        <v>6405</v>
       </c>
       <c r="K34" t="s">
-        <v>6401</v>
+        <v>6406</v>
       </c>
       <c r="N34" t="s">
-        <v>6402</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6403</v>
+        <v>6408</v>
       </c>
       <c r="N35" t="s">
-        <v>6404</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6405</v>
+        <v>6410</v>
       </c>
       <c r="N36" t="s">
-        <v>6406</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6407</v>
+        <v>6412</v>
       </c>
       <c r="N37" t="s">
-        <v>6408</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6409</v>
+        <v>6414</v>
       </c>
       <c r="N38" t="s">
-        <v>6410</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6411</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6412</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6413</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6414</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6415</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6416</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6417</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6418</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6419</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6420</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6421</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6422</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6423</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6424</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6425</v>
+        <v>6430</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6426</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6427</v>
+        <v>6432</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96774,7 +96852,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96790,7 +96868,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96806,21 +96884,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6431</v>
+        <v>6436</v>
       </c>
       <c r="J68" t="s">
-        <v>6432</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6433</v>
+        <v>6438</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6434</v>
+        <v>6439</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96829,52 +96907,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6435</v>
+        <v>6440</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6065</v>
+        <v>6070</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6436</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6437</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6438</v>
+        <v>6443</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6439</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -96936,7 +97014,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6440</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -96944,10 +97022,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6441</v>
+        <v>6446</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6442</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -96955,7 +97033,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6443</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -96968,15 +97046,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6444</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6445</v>
+        <v>6450</v>
       </c>
       <c r="F17" t="s">
-        <v>6446</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3431</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13858" uniqueCount="6452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13871" uniqueCount="6456">
   <si>
     <t>名称</t>
   </si>
@@ -20819,6 +20819,18 @@
   </si>
   <si>
     <t>考虑每条边的贡献值</t>
+  </si>
+  <si>
+    <t>LCR 116</t>
+  </si>
+  <si>
+    <t>同547题</t>
+  </si>
+  <si>
+    <t>使所有字符相等的最小删除代价</t>
+  </si>
+  <si>
+    <t>单词方块 II</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22481,9 +22493,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -22495,8 +22506,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23448,7 +23460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3437"/>
+  <dimension ref="A1:N3447"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -94871,85 +94883,172 @@
         <v>6061</v>
       </c>
     </row>
+    <row r="3432" spans="1:8">
+      <c r="A3432" t="s">
+        <v>6062</v>
+      </c>
+      <c r="B3432" t="s">
+        <v>3108</v>
+      </c>
+      <c r="C3432" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D3432" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3432" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3432" s="1" t="s">
+        <v>6063</v>
+      </c>
+    </row>
     <row r="3433" spans="1:8">
       <c r="A3433">
-        <v>3454</v>
+        <v>3784</v>
       </c>
       <c r="B3433" t="s">
-        <v>6062</v>
+        <v>6064</v>
+      </c>
+      <c r="C3433" s="2">
+        <v>46119</v>
       </c>
       <c r="D3433" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E3433" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F3433">
-        <v>2671</v>
+        <v>1387</v>
       </c>
       <c r="G3433" s="1" t="s">
-        <v>929</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3434" spans="1:8">
       <c r="A3434">
+        <v>3799</v>
+      </c>
+      <c r="B3434" t="s">
+        <v>6065</v>
+      </c>
+      <c r="C3434" s="2">
+        <v>46119</v>
+      </c>
+      <c r="D3434" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3434" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3434">
+        <v>1606</v>
+      </c>
+      <c r="G3434" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="3435" spans="1:8">
+      <c r="C3435" s="2"/>
+    </row>
+    <row r="3436" spans="1:8">
+      <c r="C3436" s="2"/>
+    </row>
+    <row r="3437" spans="1:8">
+      <c r="C3437" s="2"/>
+    </row>
+    <row r="3438" spans="1:8">
+      <c r="C3438" s="2"/>
+    </row>
+    <row r="3439" spans="1:8">
+      <c r="C3439" s="2"/>
+    </row>
+    <row r="3440" spans="1:8">
+      <c r="C3440" s="2"/>
+    </row>
+    <row r="3441" spans="1:7">
+      <c r="C3441" s="2"/>
+    </row>
+    <row r="3443" spans="1:7">
+      <c r="A3443">
+        <v>3454</v>
+      </c>
+      <c r="B3443" t="s">
+        <v>6066</v>
+      </c>
+      <c r="D3443" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3443" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3443">
+        <v>2671</v>
+      </c>
+      <c r="G3443" s="1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="3444" spans="1:7">
+      <c r="A3444">
         <v>3562</v>
       </c>
-      <c r="B3434" t="s">
-        <v>6063</v>
-      </c>
-      <c r="D3434" t="s">
+      <c r="B3444" t="s">
+        <v>6067</v>
+      </c>
+      <c r="D3444" t="s">
         <v>138</v>
       </c>
-      <c r="F3434">
+      <c r="F3444">
         <v>2458</v>
       </c>
     </row>
-    <row r="3435" spans="1:8">
-      <c r="A3435" t="s">
-        <v>6064</v>
-      </c>
-      <c r="B3435" t="s">
-        <v>6065</v>
-      </c>
-      <c r="D3435" t="s">
+    <row r="3445" spans="1:7">
+      <c r="A3445" t="s">
+        <v>6068</v>
+      </c>
+      <c r="B3445" t="s">
+        <v>6069</v>
+      </c>
+      <c r="D3445" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3436" spans="1:8">
-      <c r="A3436">
+    <row r="3446" spans="1:7">
+      <c r="A3446">
         <v>3721</v>
       </c>
-      <c r="B3436" t="s">
-        <v>6066</v>
-      </c>
-      <c r="D3436" t="s">
+      <c r="B3446" t="s">
+        <v>6070</v>
+      </c>
+      <c r="D3446" t="s">
         <v>138</v>
       </c>
-      <c r="E3436" t="s">
+      <c r="E3446" t="s">
         <v>74</v>
       </c>
-      <c r="F3436">
+      <c r="F3446">
         <v>2723</v>
       </c>
     </row>
-    <row r="3437" spans="1:8">
-      <c r="A3437">
+    <row r="3447" spans="1:7">
+      <c r="A3447">
         <v>3235</v>
       </c>
-      <c r="B3437" t="s">
-        <v>6067</v>
-      </c>
-      <c r="C3437" s="2"/>
-      <c r="D3437" t="s">
+      <c r="B3447" t="s">
+        <v>6071</v>
+      </c>
+      <c r="C3447" s="2"/>
+      <c r="D3447" t="s">
         <v>138</v>
       </c>
-      <c r="F3437">
+      <c r="F3447">
         <v>3773</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3430" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3431" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -94996,10 +95095,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6068</v>
+        <v>6072</v>
       </c>
       <c r="D5" t="s">
-        <v>6069</v>
+        <v>6073</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95010,13 +95109,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6071</v>
+        <v>6075</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95025,7 +95124,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95040,16 +95139,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95063,10 +95162,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="H14" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95081,16 +95180,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="W14" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95102,158 +95201,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AL14" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AO14" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AR14" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="AU14" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="AX14" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="T15" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="W15" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="Z15" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AF15" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AI15" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="AL15" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="AU15" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="AX15" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="H16" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="N16" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="T16" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="W16" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="Z16" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AC16" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="AF16" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="AI16" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AL16" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="AR16" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AU16" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AX16" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95261,43 +95360,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="D17" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="H17" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="N17" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="T17" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="W17" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="Z17" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AC17" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="AF17" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="AI17" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AR17" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AU17" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="BA17" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95305,37 +95404,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="H18" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="N18" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="T18" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="W18" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="Z18" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AC18" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AF18" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AI18" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AU18" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="BA18" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95343,37 +95442,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="H19" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="N19" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="T19" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="W19" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="Z19" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AC19" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="AF19" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AI19" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AU19" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="BA19" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95381,37 +95480,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6152</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6153</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6154</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6155</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6156</v>
+      </c>
+      <c r="W20" t="s">
         <v>6148</v>
       </c>
-      <c r="D20" t="s">
-        <v>6149</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6150</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6151</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6152</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6144</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AC20" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AF20" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AU20" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="BA20" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95419,37 +95518,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="D21" t="s">
+        <v>6162</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6163</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6164</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6165</v>
+      </c>
+      <c r="W21" t="s">
         <v>6158</v>
       </c>
-      <c r="H21" t="s">
-        <v>6159</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6160</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6161</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6154</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AC21" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AF21" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AU21" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="BA21" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95460,13 +95559,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95475,16 +95574,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AC22" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AF22" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AU22" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95492,25 +95591,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="H23" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="T23" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="Z23" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AC23" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AF23" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="AU23" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95518,89 +95617,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="T24" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="Z24" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="AC24" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="AF24" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="D25" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="T25" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AC25" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AF25" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="AC26" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="AF26" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AC27" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AF27" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="AC28" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="AF28" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95610,22 +95709,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95635,7 +95734,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95643,7 +95742,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95658,7 +95757,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95676,227 +95775,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="Q41" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="T41" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="W41" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="AL41" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="AO41" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="AR41" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="Q42" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="T42" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="W42" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AC42" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="AL42" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AO42" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
       <c r="AR42" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="K43" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="N43" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="Q43" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="T43" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="W43" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="Z43" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="AC43" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="AF43" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="AL43" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AO43" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="AR43" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="F44" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="N44" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="Q44" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="W44" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="Z44" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="AC44" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="AF44" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="AL44" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="AO44" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="AR44" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="F45" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="N45" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="Q45" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -95905,103 +96004,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="AF45" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="AO45" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="AR45" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="F46" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="N46" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="AC46" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="AF46" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="AO46" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="AR46" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="AC47" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="AF47" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="AO47" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="AR47" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="F48" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96013,141 +96112,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="AF48" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="AO48" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="AR48" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="AF49" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="AR49" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="F50" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="AR50" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="F51" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="AR51" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="AR52" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="F53" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="F54" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="F55" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96155,10 +96254,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="F56" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96166,18 +96265,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
       <c r="F57" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
       <c r="F58" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96185,42 +96284,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
       <c r="F59" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="F60" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="F61" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="F62" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="F63" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96228,181 +96327,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
       <c r="F64" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="F65" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="F66" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
       <c r="F67" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="F68" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="F69" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
     </row>
   </sheetData>
@@ -96429,10 +96528,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96441,13 +96540,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96455,13 +96554,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96473,13 +96572,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96490,19 +96589,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
       <c r="S10" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
       <c r="T10" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96516,15 +96615,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
       <c r="S11" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96533,18 +96632,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96553,7 +96652,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96564,13 +96663,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96581,7 +96680,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96590,10 +96689,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="T15" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96604,12 +96703,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96617,22 +96716,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96643,39 +96742,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
       <c r="H32" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
       <c r="K32" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
       <c r="N32" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
       <c r="Q32" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
       <c r="S32" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96684,13 +96783,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
       <c r="K33" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
       <c r="N33" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96698,153 +96797,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
       <c r="K34" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
       <c r="N34" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
       <c r="N35" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6410</v>
+        <v>6414</v>
       </c>
       <c r="N36" t="s">
-        <v>6411</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6412</v>
+        <v>6416</v>
       </c>
       <c r="N37" t="s">
-        <v>6413</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6414</v>
+        <v>6418</v>
       </c>
       <c r="N38" t="s">
-        <v>6415</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6416</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6417</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6418</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6421</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6422</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6423</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6424</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6425</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6426</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6427</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6428</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6429</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6430</v>
+        <v>6434</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6431</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6432</v>
+        <v>6436</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6433</v>
+        <v>6437</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96852,7 +96951,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6434</v>
+        <v>6438</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96868,7 +96967,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6435</v>
+        <v>6439</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96884,21 +96983,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6436</v>
+        <v>6440</v>
       </c>
       <c r="J68" t="s">
-        <v>6437</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6438</v>
+        <v>6442</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6439</v>
+        <v>6443</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -96907,52 +97006,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6440</v>
+        <v>6444</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6070</v>
+        <v>6074</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6441</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6442</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6443</v>
+        <v>6447</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6444</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97014,7 +97113,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6445</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97022,10 +97121,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6446</v>
+        <v>6450</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6447</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97033,7 +97132,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6448</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97046,15 +97145,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6449</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6450</v>
+        <v>6454</v>
       </c>
       <c r="F17" t="s">
-        <v>6451</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3434</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13871" uniqueCount="6456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13885" uniqueCount="6462">
   <si>
     <t>名称</t>
   </si>
@@ -20831,6 +20831,24 @@
   </si>
   <si>
     <t>单词方块 II</t>
+  </si>
+  <si>
+    <t>LCR 117</t>
+  </si>
+  <si>
+    <t>相似字符串组</t>
+  </si>
+  <si>
+    <t>同839题</t>
+  </si>
+  <si>
+    <t>分割的最大得分</t>
+  </si>
+  <si>
+    <t>树上的勾股距离节点</t>
+  </si>
+  <si>
+    <t>计算每点到xyz的距离</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22493,17 +22511,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -94950,13 +94968,73 @@
       </c>
     </row>
     <row r="3435" spans="1:8">
-      <c r="C3435" s="2"/>
+      <c r="A3435" t="s">
+        <v>6066</v>
+      </c>
+      <c r="B3435" t="s">
+        <v>6067</v>
+      </c>
+      <c r="C3435" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D3435" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3435" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3435" s="1" t="s">
+        <v>6068</v>
+      </c>
     </row>
     <row r="3436" spans="1:8">
-      <c r="C3436" s="2"/>
+      <c r="A3436">
+        <v>3788</v>
+      </c>
+      <c r="B3436" t="s">
+        <v>6069</v>
+      </c>
+      <c r="C3436" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D3436" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3436" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3436">
+        <v>1306</v>
+      </c>
+      <c r="G3436" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3437" spans="1:8">
-      <c r="C3437" s="2"/>
+      <c r="A3437">
+        <v>3820</v>
+      </c>
+      <c r="B3437" t="s">
+        <v>6070</v>
+      </c>
+      <c r="C3437" s="2">
+        <v>46120</v>
+      </c>
+      <c r="D3437" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3437" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3437">
+        <v>1725</v>
+      </c>
+      <c r="G3437" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3437" s="1" t="s">
+        <v>6071</v>
+      </c>
     </row>
     <row r="3438" spans="1:8">
       <c r="C3438" s="2"/>
@@ -94975,7 +95053,7 @@
         <v>3454</v>
       </c>
       <c r="B3443" t="s">
-        <v>6066</v>
+        <v>6072</v>
       </c>
       <c r="D3443" t="s">
         <v>138</v>
@@ -94995,7 +95073,7 @@
         <v>3562</v>
       </c>
       <c r="B3444" t="s">
-        <v>6067</v>
+        <v>6073</v>
       </c>
       <c r="D3444" t="s">
         <v>138</v>
@@ -95006,10 +95084,10 @@
     </row>
     <row r="3445" spans="1:7">
       <c r="A3445" t="s">
-        <v>6068</v>
+        <v>6074</v>
       </c>
       <c r="B3445" t="s">
-        <v>6069</v>
+        <v>6075</v>
       </c>
       <c r="D3445" t="s">
         <v>138</v>
@@ -95020,7 +95098,7 @@
         <v>3721</v>
       </c>
       <c r="B3446" t="s">
-        <v>6070</v>
+        <v>6076</v>
       </c>
       <c r="D3446" t="s">
         <v>138</v>
@@ -95037,7 +95115,7 @@
         <v>3235</v>
       </c>
       <c r="B3447" t="s">
-        <v>6071</v>
+        <v>6077</v>
       </c>
       <c r="C3447" s="2"/>
       <c r="D3447" t="s">
@@ -95048,7 +95126,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3431" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3434" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95095,10 +95173,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6072</v>
+        <v>6078</v>
       </c>
       <c r="D5" t="s">
-        <v>6073</v>
+        <v>6079</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95109,13 +95187,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6075</v>
+        <v>6081</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95124,7 +95202,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6076</v>
+        <v>6082</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95139,16 +95217,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6077</v>
+        <v>6083</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6078</v>
+        <v>6084</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6079</v>
+        <v>6085</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95162,10 +95240,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6080</v>
+        <v>6086</v>
       </c>
       <c r="H14" t="s">
-        <v>6081</v>
+        <v>6087</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95180,16 +95258,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6082</v>
+        <v>6088</v>
       </c>
       <c r="W14" t="s">
-        <v>6083</v>
+        <v>6089</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6084</v>
+        <v>6090</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95201,158 +95279,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6086</v>
+        <v>6092</v>
       </c>
       <c r="AL14" t="s">
-        <v>6087</v>
+        <v>6093</v>
       </c>
       <c r="AO14" t="s">
-        <v>6088</v>
+        <v>6094</v>
       </c>
       <c r="AR14" t="s">
-        <v>6089</v>
+        <v>6095</v>
       </c>
       <c r="AU14" t="s">
-        <v>6090</v>
+        <v>6096</v>
       </c>
       <c r="AX14" t="s">
-        <v>6091</v>
+        <v>6097</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6092</v>
+        <v>6098</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6093</v>
+        <v>6099</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6095</v>
+        <v>6101</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6096</v>
+        <v>6102</v>
       </c>
       <c r="T15" t="s">
-        <v>6097</v>
+        <v>6103</v>
       </c>
       <c r="W15" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="Z15" t="s">
-        <v>6099</v>
+        <v>6105</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6100</v>
+        <v>6106</v>
       </c>
       <c r="AF15" t="s">
-        <v>6101</v>
+        <v>6107</v>
       </c>
       <c r="AI15" t="s">
-        <v>6102</v>
+        <v>6108</v>
       </c>
       <c r="AL15" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6104</v>
+        <v>6110</v>
       </c>
       <c r="AU15" t="s">
-        <v>6105</v>
+        <v>6111</v>
       </c>
       <c r="AX15" t="s">
-        <v>6106</v>
+        <v>6112</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6107</v>
+        <v>6113</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6108</v>
+        <v>6114</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6110</v>
+        <v>6116</v>
       </c>
       <c r="H16" t="s">
-        <v>6111</v>
+        <v>6117</v>
       </c>
       <c r="N16" t="s">
-        <v>6112</v>
+        <v>6118</v>
       </c>
       <c r="T16" t="s">
-        <v>6113</v>
+        <v>6119</v>
       </c>
       <c r="W16" t="s">
-        <v>6114</v>
+        <v>6120</v>
       </c>
       <c r="Z16" t="s">
-        <v>6115</v>
+        <v>6121</v>
       </c>
       <c r="AC16" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
       <c r="AF16" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="AI16" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="AL16" t="s">
-        <v>6117</v>
+        <v>6123</v>
       </c>
       <c r="AR16" t="s">
-        <v>6118</v>
+        <v>6124</v>
       </c>
       <c r="AU16" t="s">
-        <v>6119</v>
+        <v>6125</v>
       </c>
       <c r="AX16" t="s">
-        <v>6120</v>
+        <v>6126</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6121</v>
+        <v>6127</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95360,43 +95438,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6122</v>
+        <v>6128</v>
       </c>
       <c r="D17" t="s">
-        <v>6123</v>
+        <v>6129</v>
       </c>
       <c r="H17" t="s">
-        <v>6124</v>
+        <v>6130</v>
       </c>
       <c r="N17" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="T17" t="s">
-        <v>6126</v>
+        <v>6132</v>
       </c>
       <c r="W17" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="Z17" t="s">
-        <v>6096</v>
+        <v>6102</v>
       </c>
       <c r="AC17" t="s">
-        <v>6127</v>
+        <v>6133</v>
       </c>
       <c r="AF17" t="s">
-        <v>6128</v>
+        <v>6134</v>
       </c>
       <c r="AI17" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
       <c r="AR17" t="s">
-        <v>6130</v>
+        <v>6136</v>
       </c>
       <c r="AU17" t="s">
-        <v>6131</v>
+        <v>6137</v>
       </c>
       <c r="BA17" t="s">
-        <v>6132</v>
+        <v>6138</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95404,37 +95482,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
       <c r="H18" t="s">
-        <v>6134</v>
+        <v>6140</v>
       </c>
       <c r="N18" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="T18" t="s">
-        <v>6136</v>
+        <v>6142</v>
       </c>
       <c r="W18" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
       <c r="Z18" t="s">
-        <v>6112</v>
+        <v>6118</v>
       </c>
       <c r="AC18" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
       <c r="AF18" t="s">
-        <v>6139</v>
+        <v>6145</v>
       </c>
       <c r="AI18" t="s">
-        <v>6140</v>
+        <v>6146</v>
       </c>
       <c r="AU18" t="s">
-        <v>6141</v>
+        <v>6147</v>
       </c>
       <c r="BA18" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95442,37 +95520,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
       <c r="H19" t="s">
-        <v>6144</v>
+        <v>6150</v>
       </c>
       <c r="N19" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="T19" t="s">
-        <v>6146</v>
+        <v>6152</v>
       </c>
       <c r="W19" t="s">
-        <v>6120</v>
+        <v>6126</v>
       </c>
       <c r="Z19" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="AC19" t="s">
-        <v>6147</v>
+        <v>6153</v>
       </c>
       <c r="AF19" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
       <c r="AI19" t="s">
-        <v>6149</v>
+        <v>6155</v>
       </c>
       <c r="AU19" t="s">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="BA19" t="s">
-        <v>6151</v>
+        <v>6157</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95480,37 +95558,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
       <c r="D20" t="s">
-        <v>6153</v>
+        <v>6159</v>
       </c>
       <c r="H20" t="s">
+        <v>6160</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6161</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6162</v>
+      </c>
+      <c r="W20" t="s">
         <v>6154</v>
       </c>
-      <c r="N20" t="s">
-        <v>6155</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6156</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6148</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="AC20" t="s">
-        <v>6157</v>
+        <v>6163</v>
       </c>
       <c r="AF20" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
       <c r="AU20" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
       <c r="BA20" t="s">
-        <v>6160</v>
+        <v>6166</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95518,37 +95596,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6161</v>
+        <v>6167</v>
       </c>
       <c r="D21" t="s">
-        <v>6162</v>
+        <v>6168</v>
       </c>
       <c r="H21" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="N21" t="s">
+        <v>6170</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6171</v>
+      </c>
+      <c r="W21" t="s">
         <v>6164</v>
       </c>
-      <c r="T21" t="s">
-        <v>6165</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6158</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="AC21" t="s">
-        <v>6166</v>
+        <v>6172</v>
       </c>
       <c r="AF21" t="s">
-        <v>6167</v>
+        <v>6173</v>
       </c>
       <c r="AU21" t="s">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="BA21" t="s">
-        <v>6169</v>
+        <v>6175</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95559,13 +95637,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6170</v>
+        <v>6176</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6171</v>
+        <v>6177</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95574,16 +95652,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="AC22" t="s">
-        <v>6172</v>
+        <v>6178</v>
       </c>
       <c r="AF22" t="s">
-        <v>6173</v>
+        <v>6179</v>
       </c>
       <c r="AU22" t="s">
-        <v>6174</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95591,25 +95669,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
       <c r="H23" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
       <c r="T23" t="s">
-        <v>6177</v>
+        <v>6183</v>
       </c>
       <c r="Z23" t="s">
-        <v>6164</v>
+        <v>6170</v>
       </c>
       <c r="AC23" t="s">
-        <v>6178</v>
+        <v>6184</v>
       </c>
       <c r="AF23" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
       <c r="AU23" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95617,89 +95695,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
       <c r="T24" t="s">
-        <v>6182</v>
+        <v>6188</v>
       </c>
       <c r="Z24" t="s">
-        <v>6183</v>
+        <v>6189</v>
       </c>
       <c r="AC24" t="s">
-        <v>6184</v>
+        <v>6190</v>
       </c>
       <c r="AF24" t="s">
-        <v>6185</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6186</v>
+        <v>6192</v>
       </c>
       <c r="D25" t="s">
-        <v>6187</v>
+        <v>6193</v>
       </c>
       <c r="T25" t="s">
-        <v>6188</v>
+        <v>6194</v>
       </c>
       <c r="AC25" t="s">
-        <v>6189</v>
+        <v>6195</v>
       </c>
       <c r="AF25" t="s">
-        <v>6190</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6191</v>
+        <v>6197</v>
       </c>
       <c r="AC26" t="s">
-        <v>6192</v>
+        <v>6198</v>
       </c>
       <c r="AF26" t="s">
-        <v>6193</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6194</v>
+        <v>6200</v>
       </c>
       <c r="AC27" t="s">
-        <v>6195</v>
+        <v>6201</v>
       </c>
       <c r="AF27" t="s">
-        <v>6196</v>
+        <v>6202</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6197</v>
+        <v>6203</v>
       </c>
       <c r="AC28" t="s">
-        <v>6198</v>
+        <v>6204</v>
       </c>
       <c r="AF28" t="s">
-        <v>6199</v>
+        <v>6205</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6200</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6201</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6202</v>
+        <v>6208</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6203</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95709,22 +95787,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6204</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6205</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6206</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6207</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95734,7 +95812,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6208</v>
+        <v>6214</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95742,7 +95820,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6209</v>
+        <v>6215</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95757,7 +95835,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6210</v>
+        <v>6216</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95775,227 +95853,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6211</v>
+        <v>6217</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6212</v>
+        <v>6218</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6213</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6214</v>
+        <v>6220</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6215</v>
+        <v>6221</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6216</v>
+        <v>6222</v>
       </c>
       <c r="Q41" t="s">
-        <v>6204</v>
+        <v>6210</v>
       </c>
       <c r="T41" t="s">
-        <v>6100</v>
+        <v>6106</v>
       </c>
       <c r="W41" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6218</v>
+        <v>6224</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6219</v>
+        <v>6225</v>
       </c>
       <c r="AL41" t="s">
-        <v>6220</v>
+        <v>6226</v>
       </c>
       <c r="AO41" t="s">
-        <v>6221</v>
+        <v>6227</v>
       </c>
       <c r="AR41" t="s">
-        <v>6222</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6223</v>
+        <v>6229</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6224</v>
+        <v>6230</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6225</v>
+        <v>6231</v>
       </c>
       <c r="Q42" t="s">
-        <v>6205</v>
+        <v>6211</v>
       </c>
       <c r="T42" t="s">
-        <v>6226</v>
+        <v>6232</v>
       </c>
       <c r="W42" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6228</v>
+        <v>6234</v>
       </c>
       <c r="AC42" t="s">
-        <v>6229</v>
+        <v>6235</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
       <c r="AL42" t="s">
-        <v>6231</v>
+        <v>6237</v>
       </c>
       <c r="AO42" t="s">
-        <v>6232</v>
+        <v>6238</v>
       </c>
       <c r="AR42" t="s">
-        <v>6233</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6234</v>
+        <v>6240</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
       <c r="K43" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="N43" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
       <c r="Q43" t="s">
-        <v>6206</v>
+        <v>6212</v>
       </c>
       <c r="T43" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
       <c r="W43" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
       <c r="Z43" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
       <c r="AC43" t="s">
-        <v>6241</v>
+        <v>6247</v>
       </c>
       <c r="AF43" t="s">
-        <v>6242</v>
+        <v>6248</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
       <c r="AL43" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
       <c r="AO43" t="s">
-        <v>6244</v>
+        <v>6250</v>
       </c>
       <c r="AR43" t="s">
-        <v>6245</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6246</v>
+        <v>6252</v>
       </c>
       <c r="F44" t="s">
-        <v>6247</v>
+        <v>6253</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6248</v>
+        <v>6254</v>
       </c>
       <c r="N44" t="s">
-        <v>6249</v>
+        <v>6255</v>
       </c>
       <c r="Q44" t="s">
-        <v>6207</v>
+        <v>6213</v>
       </c>
       <c r="W44" t="s">
-        <v>6250</v>
+        <v>6256</v>
       </c>
       <c r="Z44" t="s">
-        <v>6251</v>
+        <v>6257</v>
       </c>
       <c r="AC44" t="s">
-        <v>6252</v>
+        <v>6258</v>
       </c>
       <c r="AF44" t="s">
-        <v>6189</v>
+        <v>6195</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6253</v>
+        <v>6259</v>
       </c>
       <c r="AL44" t="s">
-        <v>6254</v>
+        <v>6260</v>
       </c>
       <c r="AO44" t="s">
-        <v>6255</v>
+        <v>6261</v>
       </c>
       <c r="AR44" t="s">
-        <v>6256</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6257</v>
+        <v>6263</v>
       </c>
       <c r="F45" t="s">
-        <v>6258</v>
+        <v>6264</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6259</v>
+        <v>6265</v>
       </c>
       <c r="N45" t="s">
-        <v>6260</v>
+        <v>6266</v>
       </c>
       <c r="Q45" t="s">
-        <v>6261</v>
+        <v>6267</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96004,103 +96082,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6262</v>
+        <v>6268</v>
       </c>
       <c r="AF45" t="s">
-        <v>6263</v>
+        <v>6269</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6264</v>
+        <v>6270</v>
       </c>
       <c r="AO45" t="s">
-        <v>6265</v>
+        <v>6271</v>
       </c>
       <c r="AR45" t="s">
-        <v>6266</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6267</v>
+        <v>6273</v>
       </c>
       <c r="F46" t="s">
-        <v>6268</v>
+        <v>6274</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6269</v>
+        <v>6275</v>
       </c>
       <c r="N46" t="s">
-        <v>6270</v>
+        <v>6276</v>
       </c>
       <c r="AC46" t="s">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="AF46" t="s">
-        <v>6272</v>
+        <v>6278</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6273</v>
+        <v>6279</v>
       </c>
       <c r="AO46" t="s">
-        <v>6274</v>
+        <v>6280</v>
       </c>
       <c r="AR46" t="s">
-        <v>6275</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6276</v>
+        <v>6282</v>
       </c>
       <c r="F47" t="s">
-        <v>6277</v>
+        <v>6283</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6278</v>
+        <v>6284</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6279</v>
+        <v>6285</v>
       </c>
       <c r="AC47" t="s">
-        <v>6280</v>
+        <v>6286</v>
       </c>
       <c r="AF47" t="s">
-        <v>6281</v>
+        <v>6287</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6282</v>
+        <v>6288</v>
       </c>
       <c r="AO47" t="s">
-        <v>6283</v>
+        <v>6289</v>
       </c>
       <c r="AR47" t="s">
-        <v>6284</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6285</v>
+        <v>6291</v>
       </c>
       <c r="F48" t="s">
-        <v>6286</v>
+        <v>6292</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96112,141 +96190,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6287</v>
+        <v>6293</v>
       </c>
       <c r="AF48" t="s">
-        <v>6288</v>
+        <v>6294</v>
       </c>
       <c r="AO48" t="s">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="AR48" t="s">
-        <v>6290</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6291</v>
+        <v>6297</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6292</v>
+        <v>6298</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6293</v>
+        <v>6299</v>
       </c>
       <c r="AF49" t="s">
-        <v>6294</v>
+        <v>6300</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6295</v>
+        <v>6301</v>
       </c>
       <c r="AR49" t="s">
-        <v>6296</v>
+        <v>6302</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6297</v>
+        <v>6303</v>
       </c>
       <c r="F50" t="s">
-        <v>6298</v>
+        <v>6304</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6299</v>
+        <v>6305</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6300</v>
+        <v>6306</v>
       </c>
       <c r="AR50" t="s">
-        <v>6301</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6302</v>
+        <v>6308</v>
       </c>
       <c r="F51" t="s">
-        <v>6303</v>
+        <v>6309</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6304</v>
+        <v>6310</v>
       </c>
       <c r="AR51" t="s">
-        <v>6305</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6306</v>
+        <v>6312</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6307</v>
+        <v>6313</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6308</v>
+        <v>6314</v>
       </c>
       <c r="AR52" t="s">
-        <v>6309</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6310</v>
+        <v>6316</v>
       </c>
       <c r="F53" t="s">
-        <v>6311</v>
+        <v>6317</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6312</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6313</v>
+        <v>6319</v>
       </c>
       <c r="F54" t="s">
-        <v>6314</v>
+        <v>6320</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6315</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6316</v>
+        <v>6322</v>
       </c>
       <c r="F55" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96254,10 +96332,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6318</v>
+        <v>6324</v>
       </c>
       <c r="F56" t="s">
-        <v>6319</v>
+        <v>6325</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96265,18 +96343,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6320</v>
+        <v>6326</v>
       </c>
       <c r="F57" t="s">
-        <v>6321</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6322</v>
+        <v>6328</v>
       </c>
       <c r="F58" t="s">
-        <v>6323</v>
+        <v>6329</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96284,42 +96362,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6324</v>
+        <v>6330</v>
       </c>
       <c r="F59" t="s">
-        <v>6325</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6326</v>
+        <v>6332</v>
       </c>
       <c r="F60" t="s">
-        <v>6327</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6328</v>
+        <v>6334</v>
       </c>
       <c r="F61" t="s">
-        <v>6329</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6330</v>
+        <v>6336</v>
       </c>
       <c r="F62" t="s">
-        <v>6331</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6332</v>
+        <v>6338</v>
       </c>
       <c r="F63" t="s">
-        <v>6333</v>
+        <v>6339</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96327,181 +96405,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6334</v>
+        <v>6340</v>
       </c>
       <c r="F64" t="s">
-        <v>6335</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6297</v>
+        <v>6303</v>
       </c>
       <c r="F65" t="s">
-        <v>6288</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6336</v>
+        <v>6342</v>
       </c>
       <c r="F66" t="s">
-        <v>6337</v>
+        <v>6343</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6338</v>
+        <v>6344</v>
       </c>
       <c r="F67" t="s">
-        <v>6339</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6340</v>
+        <v>6346</v>
       </c>
       <c r="F68" t="s">
-        <v>6304</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6341</v>
+        <v>6347</v>
       </c>
       <c r="F69" t="s">
-        <v>6342</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6343</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6344</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6345</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6346</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6347</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6348</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6349</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6350</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6351</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6352</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6353</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6354</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6355</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6356</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6357</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6361</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6362</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6101</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6363</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6364</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
   </sheetData>
@@ -96528,10 +96606,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6368</v>
+        <v>6374</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6369</v>
+        <v>6375</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96540,13 +96618,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6370</v>
+        <v>6376</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6371</v>
+        <v>6377</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6372</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96554,13 +96632,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6373</v>
+        <v>6379</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6374</v>
+        <v>6380</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96572,13 +96650,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6375</v>
+        <v>6381</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6376</v>
+        <v>6382</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96589,19 +96667,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6377</v>
+        <v>6383</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6378</v>
+        <v>6384</v>
       </c>
       <c r="S10" t="s">
-        <v>6379</v>
+        <v>6385</v>
       </c>
       <c r="T10" t="s">
-        <v>6380</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96615,15 +96693,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6381</v>
+        <v>6387</v>
       </c>
       <c r="S11" t="s">
-        <v>6105</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6382</v>
+        <v>6388</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96632,18 +96710,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6383</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6384</v>
+        <v>6390</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6385</v>
+        <v>6391</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96652,7 +96730,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6386</v>
+        <v>6392</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96663,13 +96741,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6387</v>
+        <v>6393</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6388</v>
+        <v>6394</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96680,7 +96758,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6389</v>
+        <v>6395</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96689,10 +96767,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6272</v>
+        <v>6278</v>
       </c>
       <c r="T15" t="s">
-        <v>6390</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96703,12 +96781,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6391</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6392</v>
+        <v>6398</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96716,22 +96794,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6393</v>
+        <v>6399</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6394</v>
+        <v>6400</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6395</v>
+        <v>6401</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6396</v>
+        <v>6402</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6397</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96742,39 +96820,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6398</v>
+        <v>6404</v>
       </c>
       <c r="H32" t="s">
-        <v>6399</v>
+        <v>6405</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6400</v>
+        <v>6406</v>
       </c>
       <c r="K32" t="s">
-        <v>6401</v>
+        <v>6407</v>
       </c>
       <c r="N32" t="s">
-        <v>6402</v>
+        <v>6408</v>
       </c>
       <c r="Q32" t="s">
-        <v>6403</v>
+        <v>6409</v>
       </c>
       <c r="S32" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6404</v>
+        <v>6410</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96783,13 +96861,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6406</v>
+        <v>6412</v>
       </c>
       <c r="K33" t="s">
-        <v>6407</v>
+        <v>6413</v>
       </c>
       <c r="N33" t="s">
-        <v>6408</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96797,153 +96875,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6409</v>
+        <v>6415</v>
       </c>
       <c r="K34" t="s">
-        <v>6410</v>
+        <v>6416</v>
       </c>
       <c r="N34" t="s">
-        <v>6411</v>
+        <v>6417</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6412</v>
+        <v>6418</v>
       </c>
       <c r="N35" t="s">
-        <v>6413</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6414</v>
+        <v>6420</v>
       </c>
       <c r="N36" t="s">
-        <v>6415</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6416</v>
+        <v>6422</v>
       </c>
       <c r="N37" t="s">
-        <v>6417</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6418</v>
+        <v>6424</v>
       </c>
       <c r="N38" t="s">
-        <v>6419</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6420</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6421</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6422</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6423</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6424</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6425</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6426</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6427</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6428</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6429</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6319</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6430</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6431</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6432</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6433</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6434</v>
+        <v>6440</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6435</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6436</v>
+        <v>6442</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6437</v>
+        <v>6443</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -96951,7 +97029,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6438</v>
+        <v>6444</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -96967,7 +97045,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6439</v>
+        <v>6445</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -96983,21 +97061,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="J68" t="s">
-        <v>6441</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6442</v>
+        <v>6448</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6443</v>
+        <v>6449</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97006,52 +97084,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6444</v>
+        <v>6450</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6074</v>
+        <v>6080</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6250</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6445</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6446</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6447</v>
+        <v>6453</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6448</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97113,7 +97191,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6449</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97121,10 +97199,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6450</v>
+        <v>6456</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6451</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97132,7 +97210,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6452</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97145,15 +97223,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6453</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6454</v>
+        <v>6460</v>
       </c>
       <c r="F17" t="s">
-        <v>6455</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3434</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3437</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13885" uniqueCount="6462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13897" uniqueCount="6466">
   <si>
     <t>名称</t>
   </si>
@@ -20849,6 +20849,18 @@
   </si>
   <si>
     <t>计算每点到xyz的距离</t>
+  </si>
+  <si>
+    <t>交替按位异或分割的数目</t>
+  </si>
+  <si>
+    <t>还挺不容易想到的，另外还有个坑，见代码注释</t>
+  </si>
+  <si>
+    <t>反转字符串前缀</t>
+  </si>
+  <si>
+    <t>最好可到达的塔</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22511,6 +22523,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22519,14 +22539,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -95037,13 +95049,73 @@
       </c>
     </row>
     <row r="3438" spans="1:8">
-      <c r="C3438" s="2"/>
+      <c r="A3438">
+        <v>3811</v>
+      </c>
+      <c r="B3438" t="s">
+        <v>6072</v>
+      </c>
+      <c r="C3438" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D3438" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3438" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3438">
+        <v>2005</v>
+      </c>
+      <c r="G3438" s="1" t="s">
+        <v>3528</v>
+      </c>
+      <c r="H3438" s="1" t="s">
+        <v>6073</v>
+      </c>
     </row>
     <row r="3439" spans="1:8">
-      <c r="C3439" s="2"/>
+      <c r="A3439">
+        <v>3794</v>
+      </c>
+      <c r="B3439" t="s">
+        <v>6074</v>
+      </c>
+      <c r="C3439" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D3439" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3439" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3439">
+        <v>1229</v>
+      </c>
     </row>
     <row r="3440" spans="1:8">
-      <c r="C3440" s="2"/>
+      <c r="A3440">
+        <v>3809</v>
+      </c>
+      <c r="B3440" t="s">
+        <v>6075</v>
+      </c>
+      <c r="C3440" s="2">
+        <v>46121</v>
+      </c>
+      <c r="D3440" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3440" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3440">
+        <v>1359</v>
+      </c>
+      <c r="G3440" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3441" spans="1:7">
       <c r="C3441" s="2"/>
@@ -95053,7 +95125,7 @@
         <v>3454</v>
       </c>
       <c r="B3443" t="s">
-        <v>6072</v>
+        <v>6076</v>
       </c>
       <c r="D3443" t="s">
         <v>138</v>
@@ -95073,7 +95145,7 @@
         <v>3562</v>
       </c>
       <c r="B3444" t="s">
-        <v>6073</v>
+        <v>6077</v>
       </c>
       <c r="D3444" t="s">
         <v>138</v>
@@ -95084,10 +95156,10 @@
     </row>
     <row r="3445" spans="1:7">
       <c r="A3445" t="s">
-        <v>6074</v>
+        <v>6078</v>
       </c>
       <c r="B3445" t="s">
-        <v>6075</v>
+        <v>6079</v>
       </c>
       <c r="D3445" t="s">
         <v>138</v>
@@ -95098,7 +95170,7 @@
         <v>3721</v>
       </c>
       <c r="B3446" t="s">
-        <v>6076</v>
+        <v>6080</v>
       </c>
       <c r="D3446" t="s">
         <v>138</v>
@@ -95115,7 +95187,7 @@
         <v>3235</v>
       </c>
       <c r="B3447" t="s">
-        <v>6077</v>
+        <v>6081</v>
       </c>
       <c r="C3447" s="2"/>
       <c r="D3447" t="s">
@@ -95126,7 +95198,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3434" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3437" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95173,10 +95245,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="D5" t="s">
-        <v>6079</v>
+        <v>6083</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95187,13 +95259,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95202,7 +95274,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6082</v>
+        <v>6086</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95217,16 +95289,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6083</v>
+        <v>6087</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6084</v>
+        <v>6088</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6085</v>
+        <v>6089</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95240,10 +95312,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6086</v>
+        <v>6090</v>
       </c>
       <c r="H14" t="s">
-        <v>6087</v>
+        <v>6091</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95258,16 +95330,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="W14" t="s">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6090</v>
+        <v>6094</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95279,158 +95351,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6092</v>
+        <v>6096</v>
       </c>
       <c r="AL14" t="s">
-        <v>6093</v>
+        <v>6097</v>
       </c>
       <c r="AO14" t="s">
-        <v>6094</v>
+        <v>6098</v>
       </c>
       <c r="AR14" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="AU14" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="AX14" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="T15" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="W15" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="Z15" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AF15" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AI15" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="AL15" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AU15" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AX15" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="H16" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="N16" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="T16" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="W16" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="Z16" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AC16" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AF16" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="AI16" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AL16" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="AR16" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="AU16" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AX16" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95438,43 +95510,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="D17" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="H17" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="N17" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="T17" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="W17" t="s">
-        <v>6091</v>
+        <v>6095</v>
       </c>
       <c r="Z17" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="AC17" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AF17" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AI17" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AR17" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AU17" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="BA17" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95482,37 +95554,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="H18" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="N18" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="T18" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="W18" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="Z18" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AC18" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AF18" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AI18" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AU18" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="BA18" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95520,37 +95592,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="H19" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="N19" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="T19" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="W19" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="Z19" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AC19" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AF19" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AI19" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="AU19" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="BA19" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95558,37 +95630,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6162</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6163</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6164</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6165</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6166</v>
+      </c>
+      <c r="W20" t="s">
         <v>6158</v>
       </c>
-      <c r="D20" t="s">
-        <v>6159</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6160</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6161</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6162</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6154</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AC20" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AF20" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AU20" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="BA20" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95596,37 +95668,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="D21" t="s">
+        <v>6172</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6173</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6174</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6175</v>
+      </c>
+      <c r="W21" t="s">
         <v>6168</v>
       </c>
-      <c r="H21" t="s">
-        <v>6169</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6170</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6171</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6164</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AC21" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AF21" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="AU21" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="BA21" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95637,13 +95709,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95652,16 +95724,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AC22" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AF22" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="AU22" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95669,25 +95741,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="H23" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="T23" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="Z23" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="AC23" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AF23" t="s">
-        <v>6185</v>
+        <v>6189</v>
       </c>
       <c r="AU23" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95695,89 +95767,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="T24" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="Z24" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="AC24" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AF24" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="D25" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="T25" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="AC25" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="AF25" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="AC26" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="AF26" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="AC27" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AF27" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="AC28" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="AF28" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95787,22 +95859,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95812,7 +95884,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95820,7 +95892,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95835,7 +95907,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95853,227 +95925,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
       <c r="Q41" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="T41" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="W41" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="AL41" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="AO41" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AR41" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
       <c r="Q42" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="T42" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
       <c r="W42" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="AC42" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="AL42" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="AO42" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="AR42" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="K43" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
       <c r="N43" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="Q43" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="T43" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="W43" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="Z43" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="AC43" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="AF43" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="AL43" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AO43" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="AR43" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="F44" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="N44" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="Q44" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="W44" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="Z44" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="AC44" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="AF44" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="AL44" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="AO44" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="AR44" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="F45" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="N45" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="Q45" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96082,103 +96154,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="AF45" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="AO45" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="AR45" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="F46" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="N46" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="AC46" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="AF46" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="AO46" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="AR46" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="F47" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
       <c r="AC47" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="AF47" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="AO47" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="AR47" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="F48" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96190,141 +96262,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="AF48" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="AO48" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
       <c r="AR48" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="AF49" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="AR49" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="F50" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="AR50" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="F51" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="AR51" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="AR52" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
       <c r="F53" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
       <c r="F54" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="F55" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96332,10 +96404,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="F56" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96343,18 +96415,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="F57" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="F58" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96362,42 +96434,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
       <c r="F59" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="F60" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
       <c r="F61" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="F62" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
       <c r="F63" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96405,181 +96477,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="F64" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="F65" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
       <c r="F66" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
       <c r="F67" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
       <c r="F68" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="F69" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
     </row>
   </sheetData>
@@ -96606,10 +96678,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96618,13 +96690,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96632,13 +96704,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96650,13 +96722,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96667,19 +96739,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
       <c r="S10" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
       <c r="T10" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96693,15 +96765,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="S11" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96710,18 +96782,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96730,7 +96802,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96741,13 +96813,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96758,7 +96830,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96767,10 +96839,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="T15" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96781,12 +96853,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96794,22 +96866,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96820,39 +96892,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
       <c r="H32" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
       <c r="K32" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
       <c r="N32" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
       <c r="Q32" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
       <c r="S32" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6410</v>
+        <v>6414</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6411</v>
+        <v>6415</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96861,13 +96933,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6412</v>
+        <v>6416</v>
       </c>
       <c r="K33" t="s">
-        <v>6413</v>
+        <v>6417</v>
       </c>
       <c r="N33" t="s">
-        <v>6414</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96875,153 +96947,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6415</v>
+        <v>6419</v>
       </c>
       <c r="K34" t="s">
-        <v>6416</v>
+        <v>6420</v>
       </c>
       <c r="N34" t="s">
-        <v>6417</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6418</v>
+        <v>6422</v>
       </c>
       <c r="N35" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
       <c r="N36" t="s">
-        <v>6421</v>
+        <v>6425</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6422</v>
+        <v>6426</v>
       </c>
       <c r="N37" t="s">
-        <v>6423</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6424</v>
+        <v>6428</v>
       </c>
       <c r="N38" t="s">
-        <v>6425</v>
+        <v>6429</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6426</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6427</v>
+        <v>6431</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6428</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6429</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6430</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6431</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6432</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6433</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6434</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6435</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6436</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6437</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6438</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6439</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6440</v>
+        <v>6444</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6441</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6442</v>
+        <v>6446</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6443</v>
+        <v>6447</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97029,7 +97101,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6444</v>
+        <v>6448</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97045,7 +97117,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6445</v>
+        <v>6449</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97061,21 +97133,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6446</v>
+        <v>6450</v>
       </c>
       <c r="J68" t="s">
-        <v>6447</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6448</v>
+        <v>6452</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6449</v>
+        <v>6453</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97084,52 +97156,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6450</v>
+        <v>6454</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6451</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6452</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6454</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97191,7 +97263,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6455</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97199,10 +97271,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6456</v>
+        <v>6460</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6457</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97210,7 +97282,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6458</v>
+        <v>6462</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97223,15 +97295,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6459</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6460</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="s">
-        <v>6461</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3440</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13897" uniqueCount="6466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13909" uniqueCount="6469">
   <si>
     <t>名称</t>
   </si>
@@ -20861,6 +20861,15 @@
   </si>
   <si>
     <t>最好可到达的塔</t>
+  </si>
+  <si>
+    <t>给定范围内平衡整数的数目</t>
+  </si>
+  <si>
+    <t>合并相邻且相等的元素</t>
+  </si>
+  <si>
+    <t>移除前缀使数组严格递增</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22523,14 +22532,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22539,6 +22540,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -23490,7 +23499,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3447"/>
+  <dimension ref="A1:N3457"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -95118,87 +95127,177 @@
       </c>
     </row>
     <row r="3441" spans="1:7">
-      <c r="C3441" s="2"/>
+      <c r="A3441">
+        <v>3791</v>
+      </c>
+      <c r="B3441" t="s">
+        <v>6076</v>
+      </c>
+      <c r="C3441" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D3441" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3441" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3441">
+        <v>2132</v>
+      </c>
+      <c r="G3441" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="3442" spans="1:7">
+      <c r="A3442">
+        <v>3834</v>
+      </c>
+      <c r="B3442" t="s">
+        <v>6077</v>
+      </c>
+      <c r="C3442" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D3442" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3442" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3442">
+        <v>1428</v>
+      </c>
+      <c r="G3442" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3443" spans="1:7">
       <c r="A3443">
+        <v>3818</v>
+      </c>
+      <c r="B3443" t="s">
+        <v>6078</v>
+      </c>
+      <c r="C3443" s="2">
+        <v>46122</v>
+      </c>
+      <c r="D3443" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3443" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3443">
+        <v>1206</v>
+      </c>
+      <c r="G3443" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="3444" spans="1:7">
+      <c r="C3444" s="2"/>
+    </row>
+    <row r="3445" spans="1:7">
+      <c r="C3445" s="2"/>
+    </row>
+    <row r="3446" spans="1:7">
+      <c r="C3446" s="2"/>
+    </row>
+    <row r="3447" spans="1:7">
+      <c r="C3447" s="2"/>
+    </row>
+    <row r="3448" spans="1:7">
+      <c r="C3448" s="2"/>
+    </row>
+    <row r="3449" spans="1:7">
+      <c r="C3449" s="2"/>
+    </row>
+    <row r="3450" spans="1:7">
+      <c r="C3450" s="2"/>
+    </row>
+    <row r="3451" spans="1:7">
+      <c r="C3451" s="2"/>
+    </row>
+    <row r="3453" spans="1:7">
+      <c r="A3453">
         <v>3454</v>
       </c>
-      <c r="B3443" t="s">
-        <v>6076</v>
-      </c>
-      <c r="D3443" t="s">
+      <c r="B3453" t="s">
+        <v>6079</v>
+      </c>
+      <c r="D3453" t="s">
         <v>138</v>
       </c>
-      <c r="E3443" t="s">
+      <c r="E3453" t="s">
         <v>74</v>
       </c>
-      <c r="F3443">
+      <c r="F3453">
         <v>2671</v>
       </c>
-      <c r="G3443" s="1" t="s">
+      <c r="G3453" s="1" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="3444" spans="1:7">
-      <c r="A3444">
+    <row r="3454" spans="1:7">
+      <c r="A3454">
         <v>3562</v>
       </c>
-      <c r="B3444" t="s">
-        <v>6077</v>
-      </c>
-      <c r="D3444" t="s">
+      <c r="B3454" t="s">
+        <v>6080</v>
+      </c>
+      <c r="D3454" t="s">
         <v>138</v>
       </c>
-      <c r="F3444">
+      <c r="F3454">
         <v>2458</v>
       </c>
     </row>
-    <row r="3445" spans="1:7">
-      <c r="A3445" t="s">
-        <v>6078</v>
-      </c>
-      <c r="B3445" t="s">
-        <v>6079</v>
-      </c>
-      <c r="D3445" t="s">
+    <row r="3455" spans="1:7">
+      <c r="A3455" t="s">
+        <v>6081</v>
+      </c>
+      <c r="B3455" t="s">
+        <v>6082</v>
+      </c>
+      <c r="D3455" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3446" spans="1:7">
-      <c r="A3446">
+    <row r="3456" spans="1:7">
+      <c r="A3456">
         <v>3721</v>
       </c>
-      <c r="B3446" t="s">
-        <v>6080</v>
-      </c>
-      <c r="D3446" t="s">
+      <c r="B3456" t="s">
+        <v>6083</v>
+      </c>
+      <c r="D3456" t="s">
         <v>138</v>
       </c>
-      <c r="E3446" t="s">
+      <c r="E3456" t="s">
         <v>74</v>
       </c>
-      <c r="F3446">
+      <c r="F3456">
         <v>2723</v>
       </c>
     </row>
-    <row r="3447" spans="1:7">
-      <c r="A3447">
+    <row r="3457" spans="1:6">
+      <c r="A3457">
         <v>3235</v>
       </c>
-      <c r="B3447" t="s">
-        <v>6081</v>
-      </c>
-      <c r="C3447" s="2"/>
-      <c r="D3447" t="s">
+      <c r="B3457" t="s">
+        <v>6084</v>
+      </c>
+      <c r="C3457" s="2"/>
+      <c r="D3457" t="s">
         <v>138</v>
       </c>
-      <c r="F3447">
+      <c r="F3457">
         <v>3773</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3437" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3440" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95245,10 +95344,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6082</v>
+        <v>6085</v>
       </c>
       <c r="D5" t="s">
-        <v>6083</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95259,13 +95358,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6085</v>
+        <v>6088</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95274,7 +95373,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6086</v>
+        <v>6089</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95289,16 +95388,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95312,10 +95411,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6090</v>
+        <v>6093</v>
       </c>
       <c r="H14" t="s">
-        <v>6091</v>
+        <v>6094</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95330,16 +95429,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6092</v>
+        <v>6095</v>
       </c>
       <c r="W14" t="s">
-        <v>6093</v>
+        <v>6096</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6094</v>
+        <v>6097</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95351,158 +95450,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6096</v>
+        <v>6099</v>
       </c>
       <c r="AL14" t="s">
-        <v>6097</v>
+        <v>6100</v>
       </c>
       <c r="AO14" t="s">
-        <v>6098</v>
+        <v>6101</v>
       </c>
       <c r="AR14" t="s">
-        <v>6099</v>
+        <v>6102</v>
       </c>
       <c r="AU14" t="s">
-        <v>6100</v>
+        <v>6103</v>
       </c>
       <c r="AX14" t="s">
-        <v>6101</v>
+        <v>6104</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6102</v>
+        <v>6105</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6104</v>
+        <v>6107</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6105</v>
+        <v>6108</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="T15" t="s">
-        <v>6107</v>
+        <v>6110</v>
       </c>
       <c r="W15" t="s">
-        <v>6108</v>
+        <v>6111</v>
       </c>
       <c r="Z15" t="s">
-        <v>6109</v>
+        <v>6112</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="AF15" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
       <c r="AI15" t="s">
-        <v>6112</v>
+        <v>6115</v>
       </c>
       <c r="AL15" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6114</v>
+        <v>6117</v>
       </c>
       <c r="AU15" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
       <c r="AX15" t="s">
-        <v>6116</v>
+        <v>6119</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6118</v>
+        <v>6121</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6119</v>
+        <v>6122</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6120</v>
+        <v>6123</v>
       </c>
       <c r="H16" t="s">
-        <v>6121</v>
+        <v>6124</v>
       </c>
       <c r="N16" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="T16" t="s">
-        <v>6123</v>
+        <v>6126</v>
       </c>
       <c r="W16" t="s">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="Z16" t="s">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="AC16" t="s">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="AF16" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="AI16" t="s">
-        <v>6126</v>
+        <v>6129</v>
       </c>
       <c r="AL16" t="s">
-        <v>6127</v>
+        <v>6130</v>
       </c>
       <c r="AR16" t="s">
-        <v>6128</v>
+        <v>6131</v>
       </c>
       <c r="AU16" t="s">
-        <v>6129</v>
+        <v>6132</v>
       </c>
       <c r="AX16" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6131</v>
+        <v>6134</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95510,43 +95609,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6132</v>
+        <v>6135</v>
       </c>
       <c r="D17" t="s">
-        <v>6133</v>
+        <v>6136</v>
       </c>
       <c r="H17" t="s">
-        <v>6134</v>
+        <v>6137</v>
       </c>
       <c r="N17" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="T17" t="s">
-        <v>6136</v>
+        <v>6139</v>
       </c>
       <c r="W17" t="s">
-        <v>6095</v>
+        <v>6098</v>
       </c>
       <c r="Z17" t="s">
-        <v>6106</v>
+        <v>6109</v>
       </c>
       <c r="AC17" t="s">
-        <v>6137</v>
+        <v>6140</v>
       </c>
       <c r="AF17" t="s">
-        <v>6138</v>
+        <v>6141</v>
       </c>
       <c r="AI17" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
       <c r="AR17" t="s">
-        <v>6140</v>
+        <v>6143</v>
       </c>
       <c r="AU17" t="s">
-        <v>6141</v>
+        <v>6144</v>
       </c>
       <c r="BA17" t="s">
-        <v>6142</v>
+        <v>6145</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95554,37 +95653,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6143</v>
+        <v>6146</v>
       </c>
       <c r="H18" t="s">
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="N18" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="T18" t="s">
-        <v>6146</v>
+        <v>6149</v>
       </c>
       <c r="W18" t="s">
-        <v>6147</v>
+        <v>6150</v>
       </c>
       <c r="Z18" t="s">
-        <v>6122</v>
+        <v>6125</v>
       </c>
       <c r="AC18" t="s">
-        <v>6148</v>
+        <v>6151</v>
       </c>
       <c r="AF18" t="s">
-        <v>6149</v>
+        <v>6152</v>
       </c>
       <c r="AI18" t="s">
-        <v>6150</v>
+        <v>6153</v>
       </c>
       <c r="AU18" t="s">
-        <v>6151</v>
+        <v>6154</v>
       </c>
       <c r="BA18" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95592,37 +95691,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6153</v>
+        <v>6156</v>
       </c>
       <c r="H19" t="s">
-        <v>6154</v>
+        <v>6157</v>
       </c>
       <c r="N19" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="T19" t="s">
-        <v>6156</v>
+        <v>6159</v>
       </c>
       <c r="W19" t="s">
-        <v>6130</v>
+        <v>6133</v>
       </c>
       <c r="Z19" t="s">
-        <v>6135</v>
+        <v>6138</v>
       </c>
       <c r="AC19" t="s">
-        <v>6157</v>
+        <v>6160</v>
       </c>
       <c r="AF19" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="AI19" t="s">
-        <v>6159</v>
+        <v>6162</v>
       </c>
       <c r="AU19" t="s">
-        <v>6160</v>
+        <v>6163</v>
       </c>
       <c r="BA19" t="s">
-        <v>6161</v>
+        <v>6164</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95630,37 +95729,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="D20" t="s">
-        <v>6163</v>
+        <v>6166</v>
       </c>
       <c r="H20" t="s">
-        <v>6164</v>
+        <v>6167</v>
       </c>
       <c r="N20" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="T20" t="s">
-        <v>6166</v>
+        <v>6169</v>
       </c>
       <c r="W20" t="s">
-        <v>6158</v>
+        <v>6161</v>
       </c>
       <c r="Z20" t="s">
-        <v>6145</v>
+        <v>6148</v>
       </c>
       <c r="AC20" t="s">
-        <v>6167</v>
+        <v>6170</v>
       </c>
       <c r="AF20" t="s">
-        <v>6168</v>
+        <v>6171</v>
       </c>
       <c r="AU20" t="s">
-        <v>6169</v>
+        <v>6172</v>
       </c>
       <c r="BA20" t="s">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95668,37 +95767,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
+        <v>6174</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6175</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6176</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6177</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6178</v>
+      </c>
+      <c r="W21" t="s">
         <v>6171</v>
       </c>
-      <c r="D21" t="s">
-        <v>6172</v>
-      </c>
-      <c r="H21" t="s">
-        <v>6173</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6174</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6175</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6168</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6155</v>
+        <v>6158</v>
       </c>
       <c r="AC21" t="s">
-        <v>6176</v>
+        <v>6179</v>
       </c>
       <c r="AF21" t="s">
-        <v>6177</v>
+        <v>6180</v>
       </c>
       <c r="AU21" t="s">
-        <v>6178</v>
+        <v>6181</v>
       </c>
       <c r="BA21" t="s">
-        <v>6179</v>
+        <v>6182</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95709,13 +95808,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6180</v>
+        <v>6183</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6181</v>
+        <v>6184</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95724,16 +95823,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6165</v>
+        <v>6168</v>
       </c>
       <c r="AC22" t="s">
-        <v>6182</v>
+        <v>6185</v>
       </c>
       <c r="AF22" t="s">
-        <v>6183</v>
+        <v>6186</v>
       </c>
       <c r="AU22" t="s">
-        <v>6184</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95741,25 +95840,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6185</v>
+        <v>6188</v>
       </c>
       <c r="H23" t="s">
-        <v>6186</v>
+        <v>6189</v>
       </c>
       <c r="T23" t="s">
-        <v>6187</v>
+        <v>6190</v>
       </c>
       <c r="Z23" t="s">
-        <v>6174</v>
+        <v>6177</v>
       </c>
       <c r="AC23" t="s">
-        <v>6188</v>
+        <v>6191</v>
       </c>
       <c r="AF23" t="s">
-        <v>6189</v>
+        <v>6192</v>
       </c>
       <c r="AU23" t="s">
-        <v>6190</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95767,89 +95866,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6191</v>
+        <v>6194</v>
       </c>
       <c r="T24" t="s">
-        <v>6192</v>
+        <v>6195</v>
       </c>
       <c r="Z24" t="s">
-        <v>6193</v>
+        <v>6196</v>
       </c>
       <c r="AC24" t="s">
-        <v>6194</v>
+        <v>6197</v>
       </c>
       <c r="AF24" t="s">
-        <v>6195</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6196</v>
+        <v>6199</v>
       </c>
       <c r="D25" t="s">
-        <v>6197</v>
+        <v>6200</v>
       </c>
       <c r="T25" t="s">
-        <v>6198</v>
+        <v>6201</v>
       </c>
       <c r="AC25" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
       <c r="AF25" t="s">
-        <v>6200</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6201</v>
+        <v>6204</v>
       </c>
       <c r="AC26" t="s">
-        <v>6202</v>
+        <v>6205</v>
       </c>
       <c r="AF26" t="s">
-        <v>6203</v>
+        <v>6206</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6204</v>
+        <v>6207</v>
       </c>
       <c r="AC27" t="s">
-        <v>6205</v>
+        <v>6208</v>
       </c>
       <c r="AF27" t="s">
-        <v>6206</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6207</v>
+        <v>6210</v>
       </c>
       <c r="AC28" t="s">
-        <v>6208</v>
+        <v>6211</v>
       </c>
       <c r="AF28" t="s">
-        <v>6209</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6210</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6211</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6212</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6213</v>
+        <v>6216</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95859,22 +95958,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95884,7 +95983,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6218</v>
+        <v>6221</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95892,7 +95991,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6219</v>
+        <v>6222</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -95907,7 +96006,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6220</v>
+        <v>6223</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -95925,227 +96024,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6221</v>
+        <v>6224</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6222</v>
+        <v>6225</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6223</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6224</v>
+        <v>6227</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6225</v>
+        <v>6228</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6226</v>
+        <v>6229</v>
       </c>
       <c r="Q41" t="s">
-        <v>6214</v>
+        <v>6217</v>
       </c>
       <c r="T41" t="s">
-        <v>6110</v>
+        <v>6113</v>
       </c>
       <c r="W41" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6228</v>
+        <v>6231</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6229</v>
+        <v>6232</v>
       </c>
       <c r="AL41" t="s">
-        <v>6230</v>
+        <v>6233</v>
       </c>
       <c r="AO41" t="s">
-        <v>6231</v>
+        <v>6234</v>
       </c>
       <c r="AR41" t="s">
-        <v>6232</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6233</v>
+        <v>6236</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6234</v>
+        <v>6237</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6235</v>
+        <v>6238</v>
       </c>
       <c r="Q42" t="s">
-        <v>6215</v>
+        <v>6218</v>
       </c>
       <c r="T42" t="s">
-        <v>6236</v>
+        <v>6239</v>
       </c>
       <c r="W42" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6238</v>
+        <v>6241</v>
       </c>
       <c r="AC42" t="s">
-        <v>6239</v>
+        <v>6242</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6240</v>
+        <v>6243</v>
       </c>
       <c r="AL42" t="s">
-        <v>6241</v>
+        <v>6244</v>
       </c>
       <c r="AO42" t="s">
-        <v>6242</v>
+        <v>6245</v>
       </c>
       <c r="AR42" t="s">
-        <v>6243</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6244</v>
+        <v>6247</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6245</v>
+        <v>6248</v>
       </c>
       <c r="K43" t="s">
-        <v>6246</v>
+        <v>6249</v>
       </c>
       <c r="N43" t="s">
-        <v>6247</v>
+        <v>6250</v>
       </c>
       <c r="Q43" t="s">
-        <v>6216</v>
+        <v>6219</v>
       </c>
       <c r="T43" t="s">
-        <v>6248</v>
+        <v>6251</v>
       </c>
       <c r="W43" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
       <c r="Z43" t="s">
-        <v>6250</v>
+        <v>6253</v>
       </c>
       <c r="AC43" t="s">
-        <v>6251</v>
+        <v>6254</v>
       </c>
       <c r="AF43" t="s">
-        <v>6252</v>
+        <v>6255</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6253</v>
+        <v>6256</v>
       </c>
       <c r="AL43" t="s">
-        <v>6162</v>
+        <v>6165</v>
       </c>
       <c r="AO43" t="s">
-        <v>6254</v>
+        <v>6257</v>
       </c>
       <c r="AR43" t="s">
-        <v>6255</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6256</v>
+        <v>6259</v>
       </c>
       <c r="F44" t="s">
-        <v>6257</v>
+        <v>6260</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6258</v>
+        <v>6261</v>
       </c>
       <c r="N44" t="s">
-        <v>6259</v>
+        <v>6262</v>
       </c>
       <c r="Q44" t="s">
-        <v>6217</v>
+        <v>6220</v>
       </c>
       <c r="W44" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
       <c r="Z44" t="s">
-        <v>6261</v>
+        <v>6264</v>
       </c>
       <c r="AC44" t="s">
-        <v>6262</v>
+        <v>6265</v>
       </c>
       <c r="AF44" t="s">
-        <v>6199</v>
+        <v>6202</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="AL44" t="s">
-        <v>6264</v>
+        <v>6267</v>
       </c>
       <c r="AO44" t="s">
-        <v>6265</v>
+        <v>6268</v>
       </c>
       <c r="AR44" t="s">
-        <v>6266</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6267</v>
+        <v>6270</v>
       </c>
       <c r="F45" t="s">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6269</v>
+        <v>6272</v>
       </c>
       <c r="N45" t="s">
-        <v>6270</v>
+        <v>6273</v>
       </c>
       <c r="Q45" t="s">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96154,103 +96253,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6272</v>
+        <v>6275</v>
       </c>
       <c r="AF45" t="s">
-        <v>6273</v>
+        <v>6276</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6274</v>
+        <v>6277</v>
       </c>
       <c r="AO45" t="s">
-        <v>6275</v>
+        <v>6278</v>
       </c>
       <c r="AR45" t="s">
-        <v>6276</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6277</v>
+        <v>6280</v>
       </c>
       <c r="F46" t="s">
-        <v>6278</v>
+        <v>6281</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="N46" t="s">
-        <v>6280</v>
+        <v>6283</v>
       </c>
       <c r="AC46" t="s">
-        <v>6281</v>
+        <v>6284</v>
       </c>
       <c r="AF46" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6283</v>
+        <v>6286</v>
       </c>
       <c r="AO46" t="s">
-        <v>6284</v>
+        <v>6287</v>
       </c>
       <c r="AR46" t="s">
-        <v>6285</v>
+        <v>6288</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6286</v>
+        <v>6289</v>
       </c>
       <c r="F47" t="s">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6288</v>
+        <v>6291</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6289</v>
+        <v>6292</v>
       </c>
       <c r="AC47" t="s">
-        <v>6290</v>
+        <v>6293</v>
       </c>
       <c r="AF47" t="s">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="AO47" t="s">
-        <v>6293</v>
+        <v>6296</v>
       </c>
       <c r="AR47" t="s">
-        <v>6294</v>
+        <v>6297</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="F48" t="s">
-        <v>6296</v>
+        <v>6299</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96262,141 +96361,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6297</v>
+        <v>6300</v>
       </c>
       <c r="AF48" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
       <c r="AO48" t="s">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="AR48" t="s">
-        <v>6300</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6301</v>
+        <v>6304</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6302</v>
+        <v>6305</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6303</v>
+        <v>6306</v>
       </c>
       <c r="AF49" t="s">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="AR49" t="s">
-        <v>6306</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="F50" t="s">
-        <v>6308</v>
+        <v>6311</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6309</v>
+        <v>6312</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6310</v>
+        <v>6313</v>
       </c>
       <c r="AR50" t="s">
-        <v>6311</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6312</v>
+        <v>6315</v>
       </c>
       <c r="F51" t="s">
-        <v>6313</v>
+        <v>6316</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
       <c r="AR51" t="s">
-        <v>6315</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6316</v>
+        <v>6319</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6317</v>
+        <v>6320</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6318</v>
+        <v>6321</v>
       </c>
       <c r="AR52" t="s">
-        <v>6319</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6320</v>
+        <v>6323</v>
       </c>
       <c r="F53" t="s">
-        <v>6321</v>
+        <v>6324</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6322</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6323</v>
+        <v>6326</v>
       </c>
       <c r="F54" t="s">
-        <v>6324</v>
+        <v>6327</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6325</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6326</v>
+        <v>6329</v>
       </c>
       <c r="F55" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96404,10 +96503,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6328</v>
+        <v>6331</v>
       </c>
       <c r="F56" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96415,18 +96514,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6330</v>
+        <v>6333</v>
       </c>
       <c r="F57" t="s">
-        <v>6331</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="F58" t="s">
-        <v>6333</v>
+        <v>6336</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96434,42 +96533,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6334</v>
+        <v>6337</v>
       </c>
       <c r="F59" t="s">
-        <v>6335</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6336</v>
+        <v>6339</v>
       </c>
       <c r="F60" t="s">
-        <v>6337</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6338</v>
+        <v>6341</v>
       </c>
       <c r="F61" t="s">
-        <v>6339</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6340</v>
+        <v>6343</v>
       </c>
       <c r="F62" t="s">
-        <v>6341</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6342</v>
+        <v>6345</v>
       </c>
       <c r="F63" t="s">
-        <v>6343</v>
+        <v>6346</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96477,181 +96576,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6344</v>
+        <v>6347</v>
       </c>
       <c r="F64" t="s">
-        <v>6345</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6307</v>
+        <v>6310</v>
       </c>
       <c r="F65" t="s">
-        <v>6298</v>
+        <v>6301</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6346</v>
+        <v>6349</v>
       </c>
       <c r="F66" t="s">
-        <v>6347</v>
+        <v>6350</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6348</v>
+        <v>6351</v>
       </c>
       <c r="F67" t="s">
-        <v>6349</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6350</v>
+        <v>6353</v>
       </c>
       <c r="F68" t="s">
-        <v>6314</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6351</v>
+        <v>6354</v>
       </c>
       <c r="F69" t="s">
-        <v>6352</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6353</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6354</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6355</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6356</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6357</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6358</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6359</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6360</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6361</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6362</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6363</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6364</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6365</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6366</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6367</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6368</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6369</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6370</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6371</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6372</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6111</v>
+        <v>6114</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6373</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6374</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6375</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6376</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6377</v>
+        <v>6380</v>
       </c>
     </row>
   </sheetData>
@@ -96678,10 +96777,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6378</v>
+        <v>6381</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6379</v>
+        <v>6382</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96690,13 +96789,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6380</v>
+        <v>6383</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6381</v>
+        <v>6384</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6382</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96704,13 +96803,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96722,13 +96821,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6386</v>
+        <v>6389</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96739,19 +96838,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6387</v>
+        <v>6390</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6388</v>
+        <v>6391</v>
       </c>
       <c r="S10" t="s">
-        <v>6389</v>
+        <v>6392</v>
       </c>
       <c r="T10" t="s">
-        <v>6390</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96765,15 +96864,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6391</v>
+        <v>6394</v>
       </c>
       <c r="S11" t="s">
-        <v>6115</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6392</v>
+        <v>6395</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96782,18 +96881,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6393</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6394</v>
+        <v>6397</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6395</v>
+        <v>6398</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96802,7 +96901,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6396</v>
+        <v>6399</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96813,13 +96912,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6397</v>
+        <v>6400</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6398</v>
+        <v>6401</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96830,7 +96929,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6399</v>
+        <v>6402</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96839,10 +96938,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6282</v>
+        <v>6285</v>
       </c>
       <c r="T15" t="s">
-        <v>6400</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96853,12 +96952,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6401</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6402</v>
+        <v>6405</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96866,22 +96965,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6403</v>
+        <v>6406</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6404</v>
+        <v>6407</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6405</v>
+        <v>6408</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6406</v>
+        <v>6409</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6407</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96892,39 +96991,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6408</v>
+        <v>6411</v>
       </c>
       <c r="H32" t="s">
-        <v>6409</v>
+        <v>6412</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6410</v>
+        <v>6413</v>
       </c>
       <c r="K32" t="s">
-        <v>6411</v>
+        <v>6414</v>
       </c>
       <c r="N32" t="s">
-        <v>6412</v>
+        <v>6415</v>
       </c>
       <c r="Q32" t="s">
-        <v>6413</v>
+        <v>6416</v>
       </c>
       <c r="S32" t="s">
-        <v>6139</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6414</v>
+        <v>6417</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6415</v>
+        <v>6418</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -96933,13 +97032,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6416</v>
+        <v>6419</v>
       </c>
       <c r="K33" t="s">
-        <v>6417</v>
+        <v>6420</v>
       </c>
       <c r="N33" t="s">
-        <v>6418</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -96947,153 +97046,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6419</v>
+        <v>6422</v>
       </c>
       <c r="K34" t="s">
-        <v>6420</v>
+        <v>6423</v>
       </c>
       <c r="N34" t="s">
-        <v>6421</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6422</v>
+        <v>6425</v>
       </c>
       <c r="N35" t="s">
-        <v>6423</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6424</v>
+        <v>6427</v>
       </c>
       <c r="N36" t="s">
-        <v>6425</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6426</v>
+        <v>6429</v>
       </c>
       <c r="N37" t="s">
-        <v>6427</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6428</v>
+        <v>6431</v>
       </c>
       <c r="N38" t="s">
-        <v>6429</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6152</v>
+        <v>6155</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6430</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6431</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6432</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6433</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6434</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6435</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6436</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6437</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6438</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6439</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6329</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6440</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6441</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6327</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6442</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6443</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6444</v>
+        <v>6447</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6445</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97101,7 +97200,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97117,7 +97216,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6449</v>
+        <v>6452</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97133,21 +97232,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="J68" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97156,52 +97255,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6227</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6454</v>
+        <v>6457</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6084</v>
+        <v>6087</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6237</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6260</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6455</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6456</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6249</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6457</v>
+        <v>6460</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6458</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97263,7 +97362,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6459</v>
+        <v>6462</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97271,10 +97370,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6460</v>
+        <v>6463</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6461</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97282,7 +97381,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6462</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97295,15 +97394,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6463</v>
+        <v>6466</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6464</v>
+        <v>6467</v>
       </c>
       <c r="F17" t="s">
-        <v>6465</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3440</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3444</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13909" uniqueCount="6469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13923" uniqueCount="6475">
   <si>
     <t>名称</t>
   </si>
@@ -20870,6 +20870,24 @@
   </si>
   <si>
     <t>移除前缀使数组严格递增</t>
+  </si>
+  <si>
+    <t>合并有序列表的最小成本</t>
+  </si>
+  <si>
+    <t>有效子序列的数量</t>
+  </si>
+  <si>
+    <t>容斥原理 + SOS DP</t>
+  </si>
+  <si>
+    <t>难度太多，还有点卡常</t>
+  </si>
+  <si>
+    <t>减小数组使其满足条件的最小 K 值</t>
+  </si>
+  <si>
+    <t>nonPositive(nums, k) &lt;= k2  左侧是单调下降，右侧是单调上升，可以二分</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22532,6 +22550,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22540,14 +22566,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -95126,7 +95144,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3441" spans="1:7">
+    <row r="3441" spans="1:8">
       <c r="A3441">
         <v>3791</v>
       </c>
@@ -95149,7 +95167,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="3442" spans="1:7">
+    <row r="3442" spans="1:8">
       <c r="A3442">
         <v>3834</v>
       </c>
@@ -95172,7 +95190,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3443" spans="1:7">
+    <row r="3443" spans="1:8">
       <c r="A3443">
         <v>3818</v>
       </c>
@@ -95195,36 +95213,102 @@
         <v>687</v>
       </c>
     </row>
-    <row r="3444" spans="1:7">
-      <c r="C3444" s="2"/>
-    </row>
-    <row r="3445" spans="1:7">
-      <c r="C3445" s="2"/>
-    </row>
-    <row r="3446" spans="1:7">
-      <c r="C3446" s="2"/>
-    </row>
-    <row r="3447" spans="1:7">
+    <row r="3444" spans="1:8">
+      <c r="A3444">
+        <v>3801</v>
+      </c>
+      <c r="B3444" t="s">
+        <v>6079</v>
+      </c>
+      <c r="C3444" s="2">
+        <v>46123</v>
+      </c>
+      <c r="D3444" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3444" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3444">
+        <v>2398</v>
+      </c>
+      <c r="G3444" s="1" t="s">
+        <v>4491</v>
+      </c>
+    </row>
+    <row r="3445" spans="1:8">
+      <c r="A3445">
+        <v>3757</v>
+      </c>
+      <c r="B3445" t="s">
+        <v>6080</v>
+      </c>
+      <c r="C3445" s="2">
+        <v>46123</v>
+      </c>
+      <c r="D3445" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3445" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3445">
+        <v>2519</v>
+      </c>
+      <c r="G3445" s="1" t="s">
+        <v>6081</v>
+      </c>
+      <c r="H3445" s="1" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="3446" spans="1:8">
+      <c r="A3446">
+        <v>3824</v>
+      </c>
+      <c r="B3446" t="s">
+        <v>6083</v>
+      </c>
+      <c r="C3446" s="2">
+        <v>46123</v>
+      </c>
+      <c r="D3446" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3446" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3446">
+        <v>1531</v>
+      </c>
+      <c r="G3446" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3446" s="1" t="s">
+        <v>6084</v>
+      </c>
+    </row>
+    <row r="3447" spans="1:8">
       <c r="C3447" s="2"/>
     </row>
-    <row r="3448" spans="1:7">
+    <row r="3448" spans="1:8">
       <c r="C3448" s="2"/>
     </row>
-    <row r="3449" spans="1:7">
+    <row r="3449" spans="1:8">
       <c r="C3449" s="2"/>
     </row>
-    <row r="3450" spans="1:7">
+    <row r="3450" spans="1:8">
       <c r="C3450" s="2"/>
     </row>
-    <row r="3451" spans="1:7">
+    <row r="3451" spans="1:8">
       <c r="C3451" s="2"/>
     </row>
-    <row r="3453" spans="1:7">
+    <row r="3453" spans="1:8">
       <c r="A3453">
         <v>3454</v>
       </c>
       <c r="B3453" t="s">
-        <v>6079</v>
+        <v>6085</v>
       </c>
       <c r="D3453" t="s">
         <v>138</v>
@@ -95239,12 +95323,12 @@
         <v>929</v>
       </c>
     </row>
-    <row r="3454" spans="1:7">
+    <row r="3454" spans="1:8">
       <c r="A3454">
         <v>3562</v>
       </c>
       <c r="B3454" t="s">
-        <v>6080</v>
+        <v>6086</v>
       </c>
       <c r="D3454" t="s">
         <v>138</v>
@@ -95253,23 +95337,23 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="3455" spans="1:7">
+    <row r="3455" spans="1:8">
       <c r="A3455" t="s">
-        <v>6081</v>
+        <v>6087</v>
       </c>
       <c r="B3455" t="s">
-        <v>6082</v>
+        <v>6088</v>
       </c>
       <c r="D3455" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3456" spans="1:7">
+    <row r="3456" spans="1:8">
       <c r="A3456">
         <v>3721</v>
       </c>
       <c r="B3456" t="s">
-        <v>6083</v>
+        <v>6089</v>
       </c>
       <c r="D3456" t="s">
         <v>138</v>
@@ -95286,7 +95370,7 @@
         <v>3235</v>
       </c>
       <c r="B3457" t="s">
-        <v>6084</v>
+        <v>6090</v>
       </c>
       <c r="C3457" s="2"/>
       <c r="D3457" t="s">
@@ -95297,7 +95381,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3440" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3444" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95344,10 +95428,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6085</v>
+        <v>6091</v>
       </c>
       <c r="D5" t="s">
-        <v>6086</v>
+        <v>6092</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95358,13 +95442,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6087</v>
+        <v>6093</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6088</v>
+        <v>6094</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95373,7 +95457,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6089</v>
+        <v>6095</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95388,16 +95472,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6090</v>
+        <v>6096</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6091</v>
+        <v>6097</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6092</v>
+        <v>6098</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95411,10 +95495,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6093</v>
+        <v>6099</v>
       </c>
       <c r="H14" t="s">
-        <v>6094</v>
+        <v>6100</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95429,16 +95513,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6095</v>
+        <v>6101</v>
       </c>
       <c r="W14" t="s">
-        <v>6096</v>
+        <v>6102</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6097</v>
+        <v>6103</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95450,158 +95534,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6099</v>
+        <v>6105</v>
       </c>
       <c r="AL14" t="s">
-        <v>6100</v>
+        <v>6106</v>
       </c>
       <c r="AO14" t="s">
-        <v>6101</v>
+        <v>6107</v>
       </c>
       <c r="AR14" t="s">
-        <v>6102</v>
+        <v>6108</v>
       </c>
       <c r="AU14" t="s">
-        <v>6103</v>
+        <v>6109</v>
       </c>
       <c r="AX14" t="s">
-        <v>6104</v>
+        <v>6110</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6105</v>
+        <v>6111</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6106</v>
+        <v>6112</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6107</v>
+        <v>6113</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6108</v>
+        <v>6114</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
       <c r="T15" t="s">
-        <v>6110</v>
+        <v>6116</v>
       </c>
       <c r="W15" t="s">
-        <v>6111</v>
+        <v>6117</v>
       </c>
       <c r="Z15" t="s">
-        <v>6112</v>
+        <v>6118</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6113</v>
+        <v>6119</v>
       </c>
       <c r="AF15" t="s">
-        <v>6114</v>
+        <v>6120</v>
       </c>
       <c r="AI15" t="s">
-        <v>6115</v>
+        <v>6121</v>
       </c>
       <c r="AL15" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6117</v>
+        <v>6123</v>
       </c>
       <c r="AU15" t="s">
-        <v>6118</v>
+        <v>6124</v>
       </c>
       <c r="AX15" t="s">
-        <v>6119</v>
+        <v>6125</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6120</v>
+        <v>6126</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6121</v>
+        <v>6127</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6122</v>
+        <v>6128</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6123</v>
+        <v>6129</v>
       </c>
       <c r="H16" t="s">
-        <v>6124</v>
+        <v>6130</v>
       </c>
       <c r="N16" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="T16" t="s">
-        <v>6126</v>
+        <v>6132</v>
       </c>
       <c r="W16" t="s">
-        <v>6127</v>
+        <v>6133</v>
       </c>
       <c r="Z16" t="s">
-        <v>6128</v>
+        <v>6134</v>
       </c>
       <c r="AC16" t="s">
-        <v>6116</v>
+        <v>6122</v>
       </c>
       <c r="AF16" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="AI16" t="s">
-        <v>6129</v>
+        <v>6135</v>
       </c>
       <c r="AL16" t="s">
-        <v>6130</v>
+        <v>6136</v>
       </c>
       <c r="AR16" t="s">
-        <v>6131</v>
+        <v>6137</v>
       </c>
       <c r="AU16" t="s">
-        <v>6132</v>
+        <v>6138</v>
       </c>
       <c r="AX16" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6134</v>
+        <v>6140</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95609,43 +95693,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6135</v>
+        <v>6141</v>
       </c>
       <c r="D17" t="s">
-        <v>6136</v>
+        <v>6142</v>
       </c>
       <c r="H17" t="s">
-        <v>6137</v>
+        <v>6143</v>
       </c>
       <c r="N17" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
       <c r="T17" t="s">
-        <v>6139</v>
+        <v>6145</v>
       </c>
       <c r="W17" t="s">
-        <v>6098</v>
+        <v>6104</v>
       </c>
       <c r="Z17" t="s">
-        <v>6109</v>
+        <v>6115</v>
       </c>
       <c r="AC17" t="s">
-        <v>6140</v>
+        <v>6146</v>
       </c>
       <c r="AF17" t="s">
-        <v>6141</v>
+        <v>6147</v>
       </c>
       <c r="AI17" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
       <c r="AR17" t="s">
-        <v>6143</v>
+        <v>6149</v>
       </c>
       <c r="AU17" t="s">
-        <v>6144</v>
+        <v>6150</v>
       </c>
       <c r="BA17" t="s">
-        <v>6145</v>
+        <v>6151</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95653,37 +95737,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6146</v>
+        <v>6152</v>
       </c>
       <c r="H18" t="s">
-        <v>6147</v>
+        <v>6153</v>
       </c>
       <c r="N18" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
       <c r="T18" t="s">
-        <v>6149</v>
+        <v>6155</v>
       </c>
       <c r="W18" t="s">
-        <v>6150</v>
+        <v>6156</v>
       </c>
       <c r="Z18" t="s">
-        <v>6125</v>
+        <v>6131</v>
       </c>
       <c r="AC18" t="s">
-        <v>6151</v>
+        <v>6157</v>
       </c>
       <c r="AF18" t="s">
-        <v>6152</v>
+        <v>6158</v>
       </c>
       <c r="AI18" t="s">
-        <v>6153</v>
+        <v>6159</v>
       </c>
       <c r="AU18" t="s">
-        <v>6154</v>
+        <v>6160</v>
       </c>
       <c r="BA18" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95691,37 +95775,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6156</v>
+        <v>6162</v>
       </c>
       <c r="H19" t="s">
-        <v>6157</v>
+        <v>6163</v>
       </c>
       <c r="N19" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
       <c r="T19" t="s">
-        <v>6159</v>
+        <v>6165</v>
       </c>
       <c r="W19" t="s">
-        <v>6133</v>
+        <v>6139</v>
       </c>
       <c r="Z19" t="s">
-        <v>6138</v>
+        <v>6144</v>
       </c>
       <c r="AC19" t="s">
-        <v>6160</v>
+        <v>6166</v>
       </c>
       <c r="AF19" t="s">
-        <v>6161</v>
+        <v>6167</v>
       </c>
       <c r="AI19" t="s">
-        <v>6162</v>
+        <v>6168</v>
       </c>
       <c r="AU19" t="s">
-        <v>6163</v>
+        <v>6169</v>
       </c>
       <c r="BA19" t="s">
-        <v>6164</v>
+        <v>6170</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95729,37 +95813,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6165</v>
+        <v>6171</v>
       </c>
       <c r="D20" t="s">
-        <v>6166</v>
+        <v>6172</v>
       </c>
       <c r="H20" t="s">
+        <v>6173</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6174</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6175</v>
+      </c>
+      <c r="W20" t="s">
         <v>6167</v>
       </c>
-      <c r="N20" t="s">
-        <v>6168</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6169</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6161</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6148</v>
+        <v>6154</v>
       </c>
       <c r="AC20" t="s">
-        <v>6170</v>
+        <v>6176</v>
       </c>
       <c r="AF20" t="s">
-        <v>6171</v>
+        <v>6177</v>
       </c>
       <c r="AU20" t="s">
-        <v>6172</v>
+        <v>6178</v>
       </c>
       <c r="BA20" t="s">
-        <v>6173</v>
+        <v>6179</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95767,37 +95851,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6174</v>
+        <v>6180</v>
       </c>
       <c r="D21" t="s">
-        <v>6175</v>
+        <v>6181</v>
       </c>
       <c r="H21" t="s">
-        <v>6176</v>
+        <v>6182</v>
       </c>
       <c r="N21" t="s">
+        <v>6183</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6184</v>
+      </c>
+      <c r="W21" t="s">
         <v>6177</v>
       </c>
-      <c r="T21" t="s">
-        <v>6178</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6171</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6158</v>
+        <v>6164</v>
       </c>
       <c r="AC21" t="s">
-        <v>6179</v>
+        <v>6185</v>
       </c>
       <c r="AF21" t="s">
-        <v>6180</v>
+        <v>6186</v>
       </c>
       <c r="AU21" t="s">
-        <v>6181</v>
+        <v>6187</v>
       </c>
       <c r="BA21" t="s">
-        <v>6182</v>
+        <v>6188</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95808,13 +95892,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6183</v>
+        <v>6189</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6184</v>
+        <v>6190</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95823,16 +95907,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="AC22" t="s">
-        <v>6185</v>
+        <v>6191</v>
       </c>
       <c r="AF22" t="s">
-        <v>6186</v>
+        <v>6192</v>
       </c>
       <c r="AU22" t="s">
-        <v>6187</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95840,25 +95924,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6188</v>
+        <v>6194</v>
       </c>
       <c r="H23" t="s">
-        <v>6189</v>
+        <v>6195</v>
       </c>
       <c r="T23" t="s">
-        <v>6190</v>
+        <v>6196</v>
       </c>
       <c r="Z23" t="s">
-        <v>6177</v>
+        <v>6183</v>
       </c>
       <c r="AC23" t="s">
-        <v>6191</v>
+        <v>6197</v>
       </c>
       <c r="AF23" t="s">
-        <v>6192</v>
+        <v>6198</v>
       </c>
       <c r="AU23" t="s">
-        <v>6193</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95866,89 +95950,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6194</v>
+        <v>6200</v>
       </c>
       <c r="T24" t="s">
-        <v>6195</v>
+        <v>6201</v>
       </c>
       <c r="Z24" t="s">
-        <v>6196</v>
+        <v>6202</v>
       </c>
       <c r="AC24" t="s">
-        <v>6197</v>
+        <v>6203</v>
       </c>
       <c r="AF24" t="s">
-        <v>6198</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6199</v>
+        <v>6205</v>
       </c>
       <c r="D25" t="s">
-        <v>6200</v>
+        <v>6206</v>
       </c>
       <c r="T25" t="s">
-        <v>6201</v>
+        <v>6207</v>
       </c>
       <c r="AC25" t="s">
-        <v>6202</v>
+        <v>6208</v>
       </c>
       <c r="AF25" t="s">
-        <v>6203</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6204</v>
+        <v>6210</v>
       </c>
       <c r="AC26" t="s">
-        <v>6205</v>
+        <v>6211</v>
       </c>
       <c r="AF26" t="s">
-        <v>6206</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6207</v>
+        <v>6213</v>
       </c>
       <c r="AC27" t="s">
-        <v>6208</v>
+        <v>6214</v>
       </c>
       <c r="AF27" t="s">
-        <v>6209</v>
+        <v>6215</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6210</v>
+        <v>6216</v>
       </c>
       <c r="AC28" t="s">
-        <v>6211</v>
+        <v>6217</v>
       </c>
       <c r="AF28" t="s">
-        <v>6212</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6213</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6214</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6215</v>
+        <v>6221</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6216</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -95958,22 +96042,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6218</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6219</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6220</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -95983,7 +96067,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6221</v>
+        <v>6227</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -95991,7 +96075,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6222</v>
+        <v>6228</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -96006,7 +96090,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6223</v>
+        <v>6229</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -96024,227 +96108,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6224</v>
+        <v>6230</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6225</v>
+        <v>6231</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6226</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6227</v>
+        <v>6233</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6228</v>
+        <v>6234</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6229</v>
+        <v>6235</v>
       </c>
       <c r="Q41" t="s">
-        <v>6217</v>
+        <v>6223</v>
       </c>
       <c r="T41" t="s">
-        <v>6113</v>
+        <v>6119</v>
       </c>
       <c r="W41" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6231</v>
+        <v>6237</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6232</v>
+        <v>6238</v>
       </c>
       <c r="AL41" t="s">
-        <v>6233</v>
+        <v>6239</v>
       </c>
       <c r="AO41" t="s">
-        <v>6234</v>
+        <v>6240</v>
       </c>
       <c r="AR41" t="s">
-        <v>6235</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6236</v>
+        <v>6242</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6237</v>
+        <v>6243</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6238</v>
+        <v>6244</v>
       </c>
       <c r="Q42" t="s">
-        <v>6218</v>
+        <v>6224</v>
       </c>
       <c r="T42" t="s">
-        <v>6239</v>
+        <v>6245</v>
       </c>
       <c r="W42" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6241</v>
+        <v>6247</v>
       </c>
       <c r="AC42" t="s">
-        <v>6242</v>
+        <v>6248</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6243</v>
+        <v>6249</v>
       </c>
       <c r="AL42" t="s">
-        <v>6244</v>
+        <v>6250</v>
       </c>
       <c r="AO42" t="s">
-        <v>6245</v>
+        <v>6251</v>
       </c>
       <c r="AR42" t="s">
-        <v>6246</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6247</v>
+        <v>6253</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6248</v>
+        <v>6254</v>
       </c>
       <c r="K43" t="s">
-        <v>6249</v>
+        <v>6255</v>
       </c>
       <c r="N43" t="s">
-        <v>6250</v>
+        <v>6256</v>
       </c>
       <c r="Q43" t="s">
-        <v>6219</v>
+        <v>6225</v>
       </c>
       <c r="T43" t="s">
-        <v>6251</v>
+        <v>6257</v>
       </c>
       <c r="W43" t="s">
-        <v>6252</v>
+        <v>6258</v>
       </c>
       <c r="Z43" t="s">
-        <v>6253</v>
+        <v>6259</v>
       </c>
       <c r="AC43" t="s">
-        <v>6254</v>
+        <v>6260</v>
       </c>
       <c r="AF43" t="s">
-        <v>6255</v>
+        <v>6261</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6256</v>
+        <v>6262</v>
       </c>
       <c r="AL43" t="s">
-        <v>6165</v>
+        <v>6171</v>
       </c>
       <c r="AO43" t="s">
-        <v>6257</v>
+        <v>6263</v>
       </c>
       <c r="AR43" t="s">
-        <v>6258</v>
+        <v>6264</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6259</v>
+        <v>6265</v>
       </c>
       <c r="F44" t="s">
-        <v>6260</v>
+        <v>6266</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6261</v>
+        <v>6267</v>
       </c>
       <c r="N44" t="s">
-        <v>6262</v>
+        <v>6268</v>
       </c>
       <c r="Q44" t="s">
-        <v>6220</v>
+        <v>6226</v>
       </c>
       <c r="W44" t="s">
-        <v>6263</v>
+        <v>6269</v>
       </c>
       <c r="Z44" t="s">
-        <v>6264</v>
+        <v>6270</v>
       </c>
       <c r="AC44" t="s">
-        <v>6265</v>
+        <v>6271</v>
       </c>
       <c r="AF44" t="s">
-        <v>6202</v>
+        <v>6208</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6266</v>
+        <v>6272</v>
       </c>
       <c r="AL44" t="s">
-        <v>6267</v>
+        <v>6273</v>
       </c>
       <c r="AO44" t="s">
-        <v>6268</v>
+        <v>6274</v>
       </c>
       <c r="AR44" t="s">
-        <v>6269</v>
+        <v>6275</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6270</v>
+        <v>6276</v>
       </c>
       <c r="F45" t="s">
-        <v>6271</v>
+        <v>6277</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6272</v>
+        <v>6278</v>
       </c>
       <c r="N45" t="s">
-        <v>6273</v>
+        <v>6279</v>
       </c>
       <c r="Q45" t="s">
-        <v>6274</v>
+        <v>6280</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96253,103 +96337,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6275</v>
+        <v>6281</v>
       </c>
       <c r="AF45" t="s">
-        <v>6276</v>
+        <v>6282</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6277</v>
+        <v>6283</v>
       </c>
       <c r="AO45" t="s">
-        <v>6278</v>
+        <v>6284</v>
       </c>
       <c r="AR45" t="s">
-        <v>6279</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6280</v>
+        <v>6286</v>
       </c>
       <c r="F46" t="s">
-        <v>6281</v>
+        <v>6287</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6282</v>
+        <v>6288</v>
       </c>
       <c r="N46" t="s">
-        <v>6283</v>
+        <v>6289</v>
       </c>
       <c r="AC46" t="s">
-        <v>6284</v>
+        <v>6290</v>
       </c>
       <c r="AF46" t="s">
-        <v>6285</v>
+        <v>6291</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6286</v>
+        <v>6292</v>
       </c>
       <c r="AO46" t="s">
-        <v>6287</v>
+        <v>6293</v>
       </c>
       <c r="AR46" t="s">
-        <v>6288</v>
+        <v>6294</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="F47" t="s">
-        <v>6290</v>
+        <v>6296</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6291</v>
+        <v>6297</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6292</v>
+        <v>6298</v>
       </c>
       <c r="AC47" t="s">
-        <v>6293</v>
+        <v>6299</v>
       </c>
       <c r="AF47" t="s">
-        <v>6294</v>
+        <v>6300</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6295</v>
+        <v>6301</v>
       </c>
       <c r="AO47" t="s">
-        <v>6296</v>
+        <v>6302</v>
       </c>
       <c r="AR47" t="s">
-        <v>6297</v>
+        <v>6303</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6298</v>
+        <v>6304</v>
       </c>
       <c r="F48" t="s">
-        <v>6299</v>
+        <v>6305</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96361,141 +96445,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6300</v>
+        <v>6306</v>
       </c>
       <c r="AF48" t="s">
-        <v>6301</v>
+        <v>6307</v>
       </c>
       <c r="AO48" t="s">
-        <v>6302</v>
+        <v>6308</v>
       </c>
       <c r="AR48" t="s">
-        <v>6303</v>
+        <v>6309</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6304</v>
+        <v>6310</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6305</v>
+        <v>6311</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6306</v>
+        <v>6312</v>
       </c>
       <c r="AF49" t="s">
-        <v>6307</v>
+        <v>6313</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6308</v>
+        <v>6314</v>
       </c>
       <c r="AR49" t="s">
-        <v>6309</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6310</v>
+        <v>6316</v>
       </c>
       <c r="F50" t="s">
-        <v>6311</v>
+        <v>6317</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6312</v>
+        <v>6318</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6313</v>
+        <v>6319</v>
       </c>
       <c r="AR50" t="s">
-        <v>6314</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6315</v>
+        <v>6321</v>
       </c>
       <c r="F51" t="s">
-        <v>6316</v>
+        <v>6322</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
       <c r="AR51" t="s">
-        <v>6318</v>
+        <v>6324</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6319</v>
+        <v>6325</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6320</v>
+        <v>6326</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6321</v>
+        <v>6327</v>
       </c>
       <c r="AR52" t="s">
-        <v>6322</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6323</v>
+        <v>6329</v>
       </c>
       <c r="F53" t="s">
-        <v>6324</v>
+        <v>6330</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6325</v>
+        <v>6331</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6326</v>
+        <v>6332</v>
       </c>
       <c r="F54" t="s">
-        <v>6327</v>
+        <v>6333</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6328</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6329</v>
+        <v>6335</v>
       </c>
       <c r="F55" t="s">
-        <v>6330</v>
+        <v>6336</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96503,10 +96587,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6331</v>
+        <v>6337</v>
       </c>
       <c r="F56" t="s">
-        <v>6332</v>
+        <v>6338</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96514,18 +96598,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6333</v>
+        <v>6339</v>
       </c>
       <c r="F57" t="s">
-        <v>6334</v>
+        <v>6340</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6335</v>
+        <v>6341</v>
       </c>
       <c r="F58" t="s">
-        <v>6336</v>
+        <v>6342</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96533,42 +96617,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6337</v>
+        <v>6343</v>
       </c>
       <c r="F59" t="s">
-        <v>6338</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6339</v>
+        <v>6345</v>
       </c>
       <c r="F60" t="s">
-        <v>6340</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6341</v>
+        <v>6347</v>
       </c>
       <c r="F61" t="s">
-        <v>6342</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6343</v>
+        <v>6349</v>
       </c>
       <c r="F62" t="s">
-        <v>6344</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6345</v>
+        <v>6351</v>
       </c>
       <c r="F63" t="s">
-        <v>6346</v>
+        <v>6352</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96576,181 +96660,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6347</v>
+        <v>6353</v>
       </c>
       <c r="F64" t="s">
-        <v>6348</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6310</v>
+        <v>6316</v>
       </c>
       <c r="F65" t="s">
-        <v>6301</v>
+        <v>6307</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6349</v>
+        <v>6355</v>
       </c>
       <c r="F66" t="s">
-        <v>6350</v>
+        <v>6356</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6351</v>
+        <v>6357</v>
       </c>
       <c r="F67" t="s">
-        <v>6352</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6353</v>
+        <v>6359</v>
       </c>
       <c r="F68" t="s">
-        <v>6317</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6354</v>
+        <v>6360</v>
       </c>
       <c r="F69" t="s">
-        <v>6355</v>
+        <v>6361</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6356</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6357</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6361</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6362</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6363</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6364</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6368</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6369</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6370</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6371</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6372</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6373</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6374</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6375</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6114</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6376</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6377</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6378</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6379</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6380</v>
+        <v>6386</v>
       </c>
     </row>
   </sheetData>
@@ -96777,10 +96861,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6381</v>
+        <v>6387</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6382</v>
+        <v>6388</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96789,13 +96873,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6383</v>
+        <v>6389</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6384</v>
+        <v>6390</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6385</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96803,13 +96887,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6386</v>
+        <v>6392</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6387</v>
+        <v>6393</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96821,13 +96905,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6388</v>
+        <v>6394</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6389</v>
+        <v>6395</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96838,19 +96922,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6390</v>
+        <v>6396</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6391</v>
+        <v>6397</v>
       </c>
       <c r="S10" t="s">
-        <v>6392</v>
+        <v>6398</v>
       </c>
       <c r="T10" t="s">
-        <v>6393</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96864,15 +96948,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6394</v>
+        <v>6400</v>
       </c>
       <c r="S11" t="s">
-        <v>6118</v>
+        <v>6124</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6395</v>
+        <v>6401</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96881,18 +96965,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6396</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6397</v>
+        <v>6403</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6398</v>
+        <v>6404</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96901,7 +96985,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6399</v>
+        <v>6405</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96912,13 +96996,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6400</v>
+        <v>6406</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6401</v>
+        <v>6407</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -96929,7 +97013,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6402</v>
+        <v>6408</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -96938,10 +97022,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6285</v>
+        <v>6291</v>
       </c>
       <c r="T15" t="s">
-        <v>6403</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -96952,12 +97036,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6404</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -96965,22 +97049,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6406</v>
+        <v>6412</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6407</v>
+        <v>6413</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6408</v>
+        <v>6414</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6409</v>
+        <v>6415</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6410</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -96991,39 +97075,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6411</v>
+        <v>6417</v>
       </c>
       <c r="H32" t="s">
-        <v>6412</v>
+        <v>6418</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6413</v>
+        <v>6419</v>
       </c>
       <c r="K32" t="s">
-        <v>6414</v>
+        <v>6420</v>
       </c>
       <c r="N32" t="s">
-        <v>6415</v>
+        <v>6421</v>
       </c>
       <c r="Q32" t="s">
-        <v>6416</v>
+        <v>6422</v>
       </c>
       <c r="S32" t="s">
-        <v>6142</v>
+        <v>6148</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6417</v>
+        <v>6423</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6418</v>
+        <v>6424</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -97032,13 +97116,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6419</v>
+        <v>6425</v>
       </c>
       <c r="K33" t="s">
-        <v>6420</v>
+        <v>6426</v>
       </c>
       <c r="N33" t="s">
-        <v>6421</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -97046,153 +97130,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6422</v>
+        <v>6428</v>
       </c>
       <c r="K34" t="s">
-        <v>6423</v>
+        <v>6429</v>
       </c>
       <c r="N34" t="s">
-        <v>6424</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6425</v>
+        <v>6431</v>
       </c>
       <c r="N35" t="s">
-        <v>6426</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6427</v>
+        <v>6433</v>
       </c>
       <c r="N36" t="s">
-        <v>6428</v>
+        <v>6434</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6429</v>
+        <v>6435</v>
       </c>
       <c r="N37" t="s">
-        <v>6430</v>
+        <v>6436</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6431</v>
+        <v>6437</v>
       </c>
       <c r="N38" t="s">
-        <v>6432</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6155</v>
+        <v>6161</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6433</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6434</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6435</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6436</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6437</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6438</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6439</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6440</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6441</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6442</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6332</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6443</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6444</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6330</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6445</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6446</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6447</v>
+        <v>6453</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6448</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6449</v>
+        <v>6455</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6450</v>
+        <v>6456</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97200,7 +97284,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6451</v>
+        <v>6457</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97216,7 +97300,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6452</v>
+        <v>6458</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97232,21 +97316,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6453</v>
+        <v>6459</v>
       </c>
       <c r="J68" t="s">
-        <v>6454</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6455</v>
+        <v>6461</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97255,52 +97339,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6230</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6087</v>
+        <v>6093</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6240</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6263</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6458</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6459</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6252</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6460</v>
+        <v>6466</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6461</v>
+        <v>6467</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97362,7 +97446,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6462</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97370,10 +97454,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6463</v>
+        <v>6469</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6464</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97381,7 +97465,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6465</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97394,15 +97478,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6466</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6467</v>
+        <v>6473</v>
       </c>
       <c r="F17" t="s">
-        <v>6468</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3444</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3446</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13923" uniqueCount="6475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13936" uniqueCount="6480">
   <si>
     <t>名称</t>
   </si>
@@ -20888,6 +20888,21 @@
   </si>
   <si>
     <t>nonPositive(nums, k) &lt;= k2  左侧是单调下降，右侧是单调上升，可以二分</t>
+  </si>
+  <si>
+    <t>统计每个顶点的度</t>
+  </si>
+  <si>
+    <t>三角形的内角度数</t>
+  </si>
+  <si>
+    <t>余弦定理</t>
+  </si>
+  <si>
+    <t>一次交换后的最长平衡子串0</t>
+  </si>
+  <si>
+    <t>差值前缀和</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22550,14 +22565,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -22566,6 +22573,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -95289,13 +95304,67 @@
       </c>
     </row>
     <row r="3447" spans="1:8">
-      <c r="C3447" s="2"/>
+      <c r="A3447">
+        <v>3898</v>
+      </c>
+      <c r="B3447" t="s">
+        <v>6085</v>
+      </c>
+      <c r="C3447" s="2">
+        <v>46124</v>
+      </c>
+      <c r="D3447" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3447" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="3448" spans="1:8">
-      <c r="C3448" s="2"/>
+      <c r="A3448">
+        <v>3899</v>
+      </c>
+      <c r="B3448" t="s">
+        <v>6086</v>
+      </c>
+      <c r="C3448" s="2">
+        <v>46124</v>
+      </c>
+      <c r="D3448" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3448" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3448" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="H3448" s="1" t="s">
+        <v>6087</v>
+      </c>
     </row>
     <row r="3449" spans="1:8">
-      <c r="C3449" s="2"/>
+      <c r="A3449">
+        <v>3900</v>
+      </c>
+      <c r="B3449" t="s">
+        <v>6088</v>
+      </c>
+      <c r="C3449" s="2">
+        <v>46124</v>
+      </c>
+      <c r="D3449" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3449" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3449" s="1" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H3449" s="1" t="s">
+        <v>6089</v>
+      </c>
     </row>
     <row r="3450" spans="1:8">
       <c r="C3450" s="2"/>
@@ -95308,7 +95377,7 @@
         <v>3454</v>
       </c>
       <c r="B3453" t="s">
-        <v>6085</v>
+        <v>6090</v>
       </c>
       <c r="D3453" t="s">
         <v>138</v>
@@ -95328,7 +95397,7 @@
         <v>3562</v>
       </c>
       <c r="B3454" t="s">
-        <v>6086</v>
+        <v>6091</v>
       </c>
       <c r="D3454" t="s">
         <v>138</v>
@@ -95339,10 +95408,10 @@
     </row>
     <row r="3455" spans="1:8">
       <c r="A3455" t="s">
-        <v>6087</v>
+        <v>6092</v>
       </c>
       <c r="B3455" t="s">
-        <v>6088</v>
+        <v>6093</v>
       </c>
       <c r="D3455" t="s">
         <v>138</v>
@@ -95353,7 +95422,7 @@
         <v>3721</v>
       </c>
       <c r="B3456" t="s">
-        <v>6089</v>
+        <v>6094</v>
       </c>
       <c r="D3456" t="s">
         <v>138</v>
@@ -95370,7 +95439,7 @@
         <v>3235</v>
       </c>
       <c r="B3457" t="s">
-        <v>6090</v>
+        <v>6095</v>
       </c>
       <c r="C3457" s="2"/>
       <c r="D3457" t="s">
@@ -95381,7 +95450,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3444" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3446" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95428,10 +95497,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6091</v>
+        <v>6096</v>
       </c>
       <c r="D5" t="s">
-        <v>6092</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95442,13 +95511,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6094</v>
+        <v>6099</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95457,7 +95526,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6095</v>
+        <v>6100</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95472,16 +95541,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95495,10 +95564,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="H14" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95513,16 +95582,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="W14" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95534,158 +95603,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="AL14" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="AO14" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="AR14" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="AU14" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="AX14" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="T15" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="W15" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="Z15" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="AF15" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="AI15" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="AL15" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="AU15" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="AX15" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="H16" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="N16" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="T16" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="W16" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
       <c r="Z16" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="AC16" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="AF16" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="AI16" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="AL16" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="AR16" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="AU16" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="AX16" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95693,43 +95762,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="D17" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="H17" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="N17" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="T17" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
       <c r="W17" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="Z17" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="AC17" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="AF17" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="AI17" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="AR17" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="AU17" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="BA17" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95737,37 +95806,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
       <c r="H18" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="N18" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="T18" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="W18" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="Z18" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="AC18" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="AF18" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="AI18" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="AU18" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="BA18" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95775,37 +95844,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="H19" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="N19" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="T19" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="W19" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="Z19" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AC19" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="AF19" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="AI19" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="AU19" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="BA19" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95813,37 +95882,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="D20" t="s">
+        <v>6177</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6178</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6179</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6180</v>
+      </c>
+      <c r="W20" t="s">
         <v>6172</v>
       </c>
-      <c r="H20" t="s">
-        <v>6173</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6174</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6175</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6167</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="AC20" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="AF20" t="s">
-        <v>6177</v>
+        <v>6182</v>
       </c>
       <c r="AU20" t="s">
-        <v>6178</v>
+        <v>6183</v>
       </c>
       <c r="BA20" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95851,37 +95920,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6180</v>
+        <v>6185</v>
       </c>
       <c r="D21" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="H21" t="s">
+        <v>6187</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6188</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6189</v>
+      </c>
+      <c r="W21" t="s">
         <v>6182</v>
       </c>
-      <c r="N21" t="s">
-        <v>6183</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6184</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6177</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="AC21" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="AF21" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="AU21" t="s">
-        <v>6187</v>
+        <v>6192</v>
       </c>
       <c r="BA21" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95892,13 +95961,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6189</v>
+        <v>6194</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95907,16 +95976,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="AC22" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="AF22" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="AU22" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95924,25 +95993,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
       <c r="H23" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="T23" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="Z23" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="AC23" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="AF23" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
       <c r="AU23" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -95950,89 +96019,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="T24" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="Z24" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="AC24" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="AF24" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="D25" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="T25" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="AC25" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="AF25" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
       <c r="AC26" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="AF26" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="AC27" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
       <c r="AF27" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="AC28" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
       <c r="AF28" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -96042,22 +96111,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -96067,7 +96136,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -96075,7 +96144,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -96090,7 +96159,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -96108,227 +96177,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="Q41" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
       <c r="T41" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="W41" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="AL41" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="AO41" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
       <c r="AR41" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="Q42" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
       <c r="T42" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="W42" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="AC42" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="AL42" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="AO42" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="AR42" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="K43" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="N43" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="Q43" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
       <c r="T43" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
       <c r="W43" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="Z43" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="AC43" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="AF43" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="AL43" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="AO43" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="AR43" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="F44" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="N44" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
       <c r="Q44" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
       <c r="W44" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
       <c r="Z44" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
       <c r="AC44" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="AF44" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="AL44" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="AO44" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
       <c r="AR44" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="F45" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
       <c r="N45" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="Q45" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96337,103 +96406,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
       <c r="AF45" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="AO45" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
       <c r="AR45" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
       <c r="F46" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="N46" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="AC46" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
       <c r="AF46" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
       <c r="AO46" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="AR46" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="F47" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
       <c r="AC47" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
       <c r="AF47" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="AO47" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="AR47" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
       <c r="F48" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96445,141 +96514,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
       <c r="AF48" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
       <c r="AO48" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
       <c r="AR48" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
       <c r="AF49" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
       <c r="AR49" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
       <c r="F50" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
       <c r="AR50" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
       <c r="F51" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
       <c r="AR51" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
       <c r="AR52" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
       <c r="F53" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
       <c r="F54" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="F55" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96587,10 +96656,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
       <c r="F56" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96598,18 +96667,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
       <c r="F57" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="F58" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96617,42 +96686,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="F59" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
       <c r="F60" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
       <c r="F61" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
       <c r="F62" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="F63" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96660,181 +96729,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
       <c r="F64" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
       <c r="F65" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
       <c r="F66" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
       <c r="F67" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
       <c r="F68" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
       <c r="F69" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
     </row>
   </sheetData>
@@ -96861,10 +96930,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96873,13 +96942,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96887,13 +96956,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96905,13 +96974,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6395</v>
+        <v>6400</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96922,19 +96991,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6396</v>
+        <v>6401</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6397</v>
+        <v>6402</v>
       </c>
       <c r="S10" t="s">
-        <v>6398</v>
+        <v>6403</v>
       </c>
       <c r="T10" t="s">
-        <v>6399</v>
+        <v>6404</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -96948,15 +97017,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6400</v>
+        <v>6405</v>
       </c>
       <c r="S11" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6401</v>
+        <v>6406</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -96965,18 +97034,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6402</v>
+        <v>6407</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6403</v>
+        <v>6408</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6404</v>
+        <v>6409</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -96985,7 +97054,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6405</v>
+        <v>6410</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -96996,13 +97065,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6406</v>
+        <v>6411</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6407</v>
+        <v>6412</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -97013,7 +97082,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6408</v>
+        <v>6413</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -97022,10 +97091,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="T15" t="s">
-        <v>6409</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -97036,12 +97105,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6410</v>
+        <v>6415</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6411</v>
+        <v>6416</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -97049,22 +97118,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6412</v>
+        <v>6417</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6413</v>
+        <v>6418</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6414</v>
+        <v>6419</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6415</v>
+        <v>6420</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6416</v>
+        <v>6421</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -97075,39 +97144,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="H32" t="s">
-        <v>6418</v>
+        <v>6423</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6419</v>
+        <v>6424</v>
       </c>
       <c r="K32" t="s">
-        <v>6420</v>
+        <v>6425</v>
       </c>
       <c r="N32" t="s">
-        <v>6421</v>
+        <v>6426</v>
       </c>
       <c r="Q32" t="s">
-        <v>6422</v>
+        <v>6427</v>
       </c>
       <c r="S32" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6423</v>
+        <v>6428</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6424</v>
+        <v>6429</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -97116,13 +97185,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6425</v>
+        <v>6430</v>
       </c>
       <c r="K33" t="s">
-        <v>6426</v>
+        <v>6431</v>
       </c>
       <c r="N33" t="s">
-        <v>6427</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -97130,153 +97199,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="K34" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="N34" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6431</v>
+        <v>6436</v>
       </c>
       <c r="N35" t="s">
-        <v>6432</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6433</v>
+        <v>6438</v>
       </c>
       <c r="N36" t="s">
-        <v>6434</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6435</v>
+        <v>6440</v>
       </c>
       <c r="N37" t="s">
-        <v>6436</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6437</v>
+        <v>6442</v>
       </c>
       <c r="N38" t="s">
-        <v>6438</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6439</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6440</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6441</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6442</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6443</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6444</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6445</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6446</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6447</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6448</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6449</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6450</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6451</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6452</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6454</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6455</v>
+        <v>6460</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97284,7 +97353,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97300,7 +97369,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97316,21 +97385,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6459</v>
+        <v>6464</v>
       </c>
       <c r="J68" t="s">
-        <v>6460</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6461</v>
+        <v>6466</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6462</v>
+        <v>6467</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97339,52 +97408,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6463</v>
+        <v>6468</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6093</v>
+        <v>6098</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6464</v>
+        <v>6469</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6465</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6466</v>
+        <v>6471</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6467</v>
+        <v>6472</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97446,7 +97515,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6468</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97454,10 +97523,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6469</v>
+        <v>6474</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6470</v>
+        <v>6475</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97465,7 +97534,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6471</v>
+        <v>6476</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97478,15 +97547,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6472</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6473</v>
+        <v>6478</v>
       </c>
       <c r="F17" t="s">
-        <v>6474</v>
+        <v>6479</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3449</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13936" uniqueCount="6480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13950" uniqueCount="6485">
   <si>
     <t>名称</t>
   </si>
@@ -20903,6 +20903,21 @@
   </si>
   <si>
     <t>差值前缀和</t>
+  </si>
+  <si>
+    <t>最大的偶数</t>
+  </si>
+  <si>
+    <t>开销小于等于 K 的子数组数目</t>
+  </si>
+  <si>
+    <t>个人解法，有序数组，性能较差</t>
+  </si>
+  <si>
+    <t>变成目标数组的最少操作次数</t>
+  </si>
+  <si>
+    <t>太难理解</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -23532,7 +23547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3457"/>
+  <dimension ref="A1:N3467"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.1111111111111" customWidth="1"/>
@@ -95367,90 +95382,186 @@
       </c>
     </row>
     <row r="3450" spans="1:8">
-      <c r="C3450" s="2"/>
+      <c r="A3450">
+        <v>3798</v>
+      </c>
+      <c r="B3450" t="s">
+        <v>6090</v>
+      </c>
+      <c r="C3450" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D3450" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3450" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3450">
+        <v>1365</v>
+      </c>
+      <c r="G3450" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3451" spans="1:8">
-      <c r="C3451" s="2"/>
+      <c r="A3451">
+        <v>3835</v>
+      </c>
+      <c r="B3451" t="s">
+        <v>6091</v>
+      </c>
+      <c r="C3451" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D3451" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3451" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3451">
+        <v>1759</v>
+      </c>
+      <c r="G3451" s="1" t="s">
+        <v>2637</v>
+      </c>
+      <c r="H3451" s="1" t="s">
+        <v>6092</v>
+      </c>
+    </row>
+    <row r="3452" spans="1:8">
+      <c r="A3452">
+        <v>3810</v>
+      </c>
+      <c r="B3452" t="s">
+        <v>6093</v>
+      </c>
+      <c r="C3452" s="2">
+        <v>46125</v>
+      </c>
+      <c r="D3452" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3452" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3452">
+        <v>1492</v>
+      </c>
+      <c r="G3452" s="1" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H3452" s="1" t="s">
+        <v>6094</v>
+      </c>
     </row>
     <row r="3453" spans="1:8">
-      <c r="A3453">
+      <c r="C3453" s="2"/>
+    </row>
+    <row r="3454" spans="1:8">
+      <c r="C3454" s="2"/>
+    </row>
+    <row r="3455" spans="1:8">
+      <c r="C3455" s="2"/>
+    </row>
+    <row r="3456" spans="1:8">
+      <c r="C3456" s="2"/>
+    </row>
+    <row r="3457" spans="1:7">
+      <c r="C3457" s="2"/>
+    </row>
+    <row r="3458" spans="1:7">
+      <c r="C3458" s="2"/>
+    </row>
+    <row r="3459" spans="1:7">
+      <c r="C3459" s="2"/>
+    </row>
+    <row r="3460" spans="1:7">
+      <c r="C3460" s="2"/>
+    </row>
+    <row r="3461" spans="1:7">
+      <c r="C3461" s="2"/>
+    </row>
+    <row r="3463" spans="1:7">
+      <c r="A3463">
         <v>3454</v>
       </c>
-      <c r="B3453" t="s">
-        <v>6090</v>
-      </c>
-      <c r="D3453" t="s">
+      <c r="B3463" t="s">
+        <v>6095</v>
+      </c>
+      <c r="D3463" t="s">
         <v>138</v>
       </c>
-      <c r="E3453" t="s">
+      <c r="E3463" t="s">
         <v>74</v>
       </c>
-      <c r="F3453">
+      <c r="F3463">
         <v>2671</v>
       </c>
-      <c r="G3453" s="1" t="s">
+      <c r="G3463" s="1" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="3454" spans="1:8">
-      <c r="A3454">
+    <row r="3464" spans="1:7">
+      <c r="A3464">
         <v>3562</v>
       </c>
-      <c r="B3454" t="s">
-        <v>6091</v>
-      </c>
-      <c r="D3454" t="s">
+      <c r="B3464" t="s">
+        <v>6096</v>
+      </c>
+      <c r="D3464" t="s">
         <v>138</v>
       </c>
-      <c r="F3454">
+      <c r="F3464">
         <v>2458</v>
       </c>
     </row>
-    <row r="3455" spans="1:8">
-      <c r="A3455" t="s">
-        <v>6092</v>
-      </c>
-      <c r="B3455" t="s">
-        <v>6093</v>
-      </c>
-      <c r="D3455" t="s">
+    <row r="3465" spans="1:7">
+      <c r="A3465" t="s">
+        <v>6097</v>
+      </c>
+      <c r="B3465" t="s">
+        <v>6098</v>
+      </c>
+      <c r="D3465" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3456" spans="1:8">
-      <c r="A3456">
+    <row r="3466" spans="1:7">
+      <c r="A3466">
         <v>3721</v>
       </c>
-      <c r="B3456" t="s">
-        <v>6094</v>
-      </c>
-      <c r="D3456" t="s">
+      <c r="B3466" t="s">
+        <v>6099</v>
+      </c>
+      <c r="D3466" t="s">
         <v>138</v>
       </c>
-      <c r="E3456" t="s">
+      <c r="E3466" t="s">
         <v>74</v>
       </c>
-      <c r="F3456">
+      <c r="F3466">
         <v>2723</v>
       </c>
     </row>
-    <row r="3457" spans="1:6">
-      <c r="A3457">
+    <row r="3467" spans="1:7">
+      <c r="A3467">
         <v>3235</v>
       </c>
-      <c r="B3457" t="s">
-        <v>6095</v>
-      </c>
-      <c r="C3457" s="2"/>
-      <c r="D3457" t="s">
+      <c r="B3467" t="s">
+        <v>6100</v>
+      </c>
+      <c r="C3467" s="2"/>
+      <c r="D3467" t="s">
         <v>138</v>
       </c>
-      <c r="F3457">
+      <c r="F3467">
         <v>3773</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3446" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3449" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95497,10 +95608,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6096</v>
+        <v>6101</v>
       </c>
       <c r="D5" t="s">
-        <v>6097</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95511,13 +95622,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6099</v>
+        <v>6104</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95526,7 +95637,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6100</v>
+        <v>6105</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95541,16 +95652,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6101</v>
+        <v>6106</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6102</v>
+        <v>6107</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6103</v>
+        <v>6108</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95564,10 +95675,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6104</v>
+        <v>6109</v>
       </c>
       <c r="H14" t="s">
-        <v>6105</v>
+        <v>6110</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95582,16 +95693,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6106</v>
+        <v>6111</v>
       </c>
       <c r="W14" t="s">
-        <v>6107</v>
+        <v>6112</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6108</v>
+        <v>6113</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95603,158 +95714,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6110</v>
+        <v>6115</v>
       </c>
       <c r="AL14" t="s">
-        <v>6111</v>
+        <v>6116</v>
       </c>
       <c r="AO14" t="s">
-        <v>6112</v>
+        <v>6117</v>
       </c>
       <c r="AR14" t="s">
-        <v>6113</v>
+        <v>6118</v>
       </c>
       <c r="AU14" t="s">
-        <v>6114</v>
+        <v>6119</v>
       </c>
       <c r="AX14" t="s">
-        <v>6115</v>
+        <v>6120</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6116</v>
+        <v>6121</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6117</v>
+        <v>6122</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6118</v>
+        <v>6123</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6119</v>
+        <v>6124</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="T15" t="s">
-        <v>6121</v>
+        <v>6126</v>
       </c>
       <c r="W15" t="s">
-        <v>6122</v>
+        <v>6127</v>
       </c>
       <c r="Z15" t="s">
-        <v>6123</v>
+        <v>6128</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="AF15" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
       <c r="AI15" t="s">
-        <v>6126</v>
+        <v>6131</v>
       </c>
       <c r="AL15" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6128</v>
+        <v>6133</v>
       </c>
       <c r="AU15" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
       <c r="AX15" t="s">
-        <v>6130</v>
+        <v>6135</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6131</v>
+        <v>6136</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6132</v>
+        <v>6137</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6133</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6134</v>
+        <v>6139</v>
       </c>
       <c r="H16" t="s">
-        <v>6135</v>
+        <v>6140</v>
       </c>
       <c r="N16" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="T16" t="s">
-        <v>6137</v>
+        <v>6142</v>
       </c>
       <c r="W16" t="s">
-        <v>6138</v>
+        <v>6143</v>
       </c>
       <c r="Z16" t="s">
-        <v>6139</v>
+        <v>6144</v>
       </c>
       <c r="AC16" t="s">
-        <v>6127</v>
+        <v>6132</v>
       </c>
       <c r="AF16" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="AI16" t="s">
-        <v>6140</v>
+        <v>6145</v>
       </c>
       <c r="AL16" t="s">
-        <v>6141</v>
+        <v>6146</v>
       </c>
       <c r="AR16" t="s">
-        <v>6142</v>
+        <v>6147</v>
       </c>
       <c r="AU16" t="s">
-        <v>6143</v>
+        <v>6148</v>
       </c>
       <c r="AX16" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6145</v>
+        <v>6150</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95762,43 +95873,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6146</v>
+        <v>6151</v>
       </c>
       <c r="D17" t="s">
-        <v>6147</v>
+        <v>6152</v>
       </c>
       <c r="H17" t="s">
-        <v>6148</v>
+        <v>6153</v>
       </c>
       <c r="N17" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="T17" t="s">
-        <v>6150</v>
+        <v>6155</v>
       </c>
       <c r="W17" t="s">
-        <v>6109</v>
+        <v>6114</v>
       </c>
       <c r="Z17" t="s">
-        <v>6120</v>
+        <v>6125</v>
       </c>
       <c r="AC17" t="s">
-        <v>6151</v>
+        <v>6156</v>
       </c>
       <c r="AF17" t="s">
-        <v>6152</v>
+        <v>6157</v>
       </c>
       <c r="AI17" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
       <c r="AR17" t="s">
-        <v>6154</v>
+        <v>6159</v>
       </c>
       <c r="AU17" t="s">
-        <v>6155</v>
+        <v>6160</v>
       </c>
       <c r="BA17" t="s">
-        <v>6156</v>
+        <v>6161</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95806,37 +95917,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6157</v>
+        <v>6162</v>
       </c>
       <c r="H18" t="s">
-        <v>6158</v>
+        <v>6163</v>
       </c>
       <c r="N18" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="T18" t="s">
-        <v>6160</v>
+        <v>6165</v>
       </c>
       <c r="W18" t="s">
-        <v>6161</v>
+        <v>6166</v>
       </c>
       <c r="Z18" t="s">
-        <v>6136</v>
+        <v>6141</v>
       </c>
       <c r="AC18" t="s">
-        <v>6162</v>
+        <v>6167</v>
       </c>
       <c r="AF18" t="s">
-        <v>6163</v>
+        <v>6168</v>
       </c>
       <c r="AI18" t="s">
-        <v>6164</v>
+        <v>6169</v>
       </c>
       <c r="AU18" t="s">
-        <v>6165</v>
+        <v>6170</v>
       </c>
       <c r="BA18" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95844,37 +95955,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6167</v>
+        <v>6172</v>
       </c>
       <c r="H19" t="s">
-        <v>6168</v>
+        <v>6173</v>
       </c>
       <c r="N19" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="T19" t="s">
-        <v>6170</v>
+        <v>6175</v>
       </c>
       <c r="W19" t="s">
-        <v>6144</v>
+        <v>6149</v>
       </c>
       <c r="Z19" t="s">
-        <v>6149</v>
+        <v>6154</v>
       </c>
       <c r="AC19" t="s">
-        <v>6171</v>
+        <v>6176</v>
       </c>
       <c r="AF19" t="s">
-        <v>6172</v>
+        <v>6177</v>
       </c>
       <c r="AI19" t="s">
-        <v>6173</v>
+        <v>6178</v>
       </c>
       <c r="AU19" t="s">
-        <v>6174</v>
+        <v>6179</v>
       </c>
       <c r="BA19" t="s">
-        <v>6175</v>
+        <v>6180</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95882,37 +95993,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="D20" t="s">
+        <v>6182</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6183</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6184</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6185</v>
+      </c>
+      <c r="W20" t="s">
         <v>6177</v>
       </c>
-      <c r="H20" t="s">
-        <v>6178</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6179</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6180</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6172</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6159</v>
+        <v>6164</v>
       </c>
       <c r="AC20" t="s">
-        <v>6181</v>
+        <v>6186</v>
       </c>
       <c r="AF20" t="s">
-        <v>6182</v>
+        <v>6187</v>
       </c>
       <c r="AU20" t="s">
-        <v>6183</v>
+        <v>6188</v>
       </c>
       <c r="BA20" t="s">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -95920,37 +96031,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6185</v>
+        <v>6190</v>
       </c>
       <c r="D21" t="s">
-        <v>6186</v>
+        <v>6191</v>
       </c>
       <c r="H21" t="s">
+        <v>6192</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6193</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6194</v>
+      </c>
+      <c r="W21" t="s">
         <v>6187</v>
       </c>
-      <c r="N21" t="s">
-        <v>6188</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6189</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6182</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6169</v>
+        <v>6174</v>
       </c>
       <c r="AC21" t="s">
-        <v>6190</v>
+        <v>6195</v>
       </c>
       <c r="AF21" t="s">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="AU21" t="s">
-        <v>6192</v>
+        <v>6197</v>
       </c>
       <c r="BA21" t="s">
-        <v>6193</v>
+        <v>6198</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -95961,13 +96072,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6194</v>
+        <v>6199</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6195</v>
+        <v>6200</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -95976,16 +96087,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6179</v>
+        <v>6184</v>
       </c>
       <c r="AC22" t="s">
-        <v>6196</v>
+        <v>6201</v>
       </c>
       <c r="AF22" t="s">
-        <v>6197</v>
+        <v>6202</v>
       </c>
       <c r="AU22" t="s">
-        <v>6198</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -95993,25 +96104,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6199</v>
+        <v>6204</v>
       </c>
       <c r="H23" t="s">
-        <v>6200</v>
+        <v>6205</v>
       </c>
       <c r="T23" t="s">
-        <v>6201</v>
+        <v>6206</v>
       </c>
       <c r="Z23" t="s">
-        <v>6188</v>
+        <v>6193</v>
       </c>
       <c r="AC23" t="s">
-        <v>6202</v>
+        <v>6207</v>
       </c>
       <c r="AF23" t="s">
-        <v>6203</v>
+        <v>6208</v>
       </c>
       <c r="AU23" t="s">
-        <v>6204</v>
+        <v>6209</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -96019,89 +96130,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6205</v>
+        <v>6210</v>
       </c>
       <c r="T24" t="s">
-        <v>6206</v>
+        <v>6211</v>
       </c>
       <c r="Z24" t="s">
-        <v>6207</v>
+        <v>6212</v>
       </c>
       <c r="AC24" t="s">
-        <v>6208</v>
+        <v>6213</v>
       </c>
       <c r="AF24" t="s">
-        <v>6209</v>
+        <v>6214</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6210</v>
+        <v>6215</v>
       </c>
       <c r="D25" t="s">
-        <v>6211</v>
+        <v>6216</v>
       </c>
       <c r="T25" t="s">
-        <v>6212</v>
+        <v>6217</v>
       </c>
       <c r="AC25" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="AF25" t="s">
-        <v>6214</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6215</v>
+        <v>6220</v>
       </c>
       <c r="AC26" t="s">
-        <v>6216</v>
+        <v>6221</v>
       </c>
       <c r="AF26" t="s">
-        <v>6217</v>
+        <v>6222</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6218</v>
+        <v>6223</v>
       </c>
       <c r="AC27" t="s">
-        <v>6219</v>
+        <v>6224</v>
       </c>
       <c r="AF27" t="s">
-        <v>6220</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6221</v>
+        <v>6226</v>
       </c>
       <c r="AC28" t="s">
-        <v>6222</v>
+        <v>6227</v>
       </c>
       <c r="AF28" t="s">
-        <v>6223</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6224</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6225</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6226</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6227</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -96111,22 +96222,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -96136,7 +96247,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6232</v>
+        <v>6237</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -96144,7 +96255,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -96159,7 +96270,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6234</v>
+        <v>6239</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -96177,227 +96288,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6235</v>
+        <v>6240</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6236</v>
+        <v>6241</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6237</v>
+        <v>6242</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6238</v>
+        <v>6243</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6239</v>
+        <v>6244</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6240</v>
+        <v>6245</v>
       </c>
       <c r="Q41" t="s">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="T41" t="s">
-        <v>6124</v>
+        <v>6129</v>
       </c>
       <c r="W41" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6242</v>
+        <v>6247</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6243</v>
+        <v>6248</v>
       </c>
       <c r="AL41" t="s">
-        <v>6244</v>
+        <v>6249</v>
       </c>
       <c r="AO41" t="s">
-        <v>6245</v>
+        <v>6250</v>
       </c>
       <c r="AR41" t="s">
-        <v>6246</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6247</v>
+        <v>6252</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6248</v>
+        <v>6253</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6249</v>
+        <v>6254</v>
       </c>
       <c r="Q42" t="s">
-        <v>6229</v>
+        <v>6234</v>
       </c>
       <c r="T42" t="s">
-        <v>6250</v>
+        <v>6255</v>
       </c>
       <c r="W42" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6252</v>
+        <v>6257</v>
       </c>
       <c r="AC42" t="s">
-        <v>6253</v>
+        <v>6258</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6254</v>
+        <v>6259</v>
       </c>
       <c r="AL42" t="s">
-        <v>6255</v>
+        <v>6260</v>
       </c>
       <c r="AO42" t="s">
-        <v>6256</v>
+        <v>6261</v>
       </c>
       <c r="AR42" t="s">
-        <v>6257</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6258</v>
+        <v>6263</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6259</v>
+        <v>6264</v>
       </c>
       <c r="K43" t="s">
-        <v>6260</v>
+        <v>6265</v>
       </c>
       <c r="N43" t="s">
-        <v>6261</v>
+        <v>6266</v>
       </c>
       <c r="Q43" t="s">
-        <v>6230</v>
+        <v>6235</v>
       </c>
       <c r="T43" t="s">
-        <v>6262</v>
+        <v>6267</v>
       </c>
       <c r="W43" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
       <c r="Z43" t="s">
-        <v>6264</v>
+        <v>6269</v>
       </c>
       <c r="AC43" t="s">
-        <v>6265</v>
+        <v>6270</v>
       </c>
       <c r="AF43" t="s">
-        <v>6266</v>
+        <v>6271</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6267</v>
+        <v>6272</v>
       </c>
       <c r="AL43" t="s">
-        <v>6176</v>
+        <v>6181</v>
       </c>
       <c r="AO43" t="s">
-        <v>6268</v>
+        <v>6273</v>
       </c>
       <c r="AR43" t="s">
-        <v>6269</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6270</v>
+        <v>6275</v>
       </c>
       <c r="F44" t="s">
-        <v>6271</v>
+        <v>6276</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6272</v>
+        <v>6277</v>
       </c>
       <c r="N44" t="s">
-        <v>6273</v>
+        <v>6278</v>
       </c>
       <c r="Q44" t="s">
-        <v>6231</v>
+        <v>6236</v>
       </c>
       <c r="W44" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
       <c r="Z44" t="s">
-        <v>6275</v>
+        <v>6280</v>
       </c>
       <c r="AC44" t="s">
-        <v>6276</v>
+        <v>6281</v>
       </c>
       <c r="AF44" t="s">
-        <v>6213</v>
+        <v>6218</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6277</v>
+        <v>6282</v>
       </c>
       <c r="AL44" t="s">
-        <v>6278</v>
+        <v>6283</v>
       </c>
       <c r="AO44" t="s">
-        <v>6279</v>
+        <v>6284</v>
       </c>
       <c r="AR44" t="s">
-        <v>6280</v>
+        <v>6285</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6281</v>
+        <v>6286</v>
       </c>
       <c r="F45" t="s">
-        <v>6282</v>
+        <v>6287</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6283</v>
+        <v>6288</v>
       </c>
       <c r="N45" t="s">
-        <v>6284</v>
+        <v>6289</v>
       </c>
       <c r="Q45" t="s">
-        <v>6285</v>
+        <v>6290</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96406,103 +96517,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6286</v>
+        <v>6291</v>
       </c>
       <c r="AF45" t="s">
-        <v>6287</v>
+        <v>6292</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6288</v>
+        <v>6293</v>
       </c>
       <c r="AO45" t="s">
-        <v>6289</v>
+        <v>6294</v>
       </c>
       <c r="AR45" t="s">
-        <v>6290</v>
+        <v>6295</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6291</v>
+        <v>6296</v>
       </c>
       <c r="F46" t="s">
-        <v>6292</v>
+        <v>6297</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6293</v>
+        <v>6298</v>
       </c>
       <c r="N46" t="s">
-        <v>6294</v>
+        <v>6299</v>
       </c>
       <c r="AC46" t="s">
-        <v>6295</v>
+        <v>6300</v>
       </c>
       <c r="AF46" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6297</v>
+        <v>6302</v>
       </c>
       <c r="AO46" t="s">
-        <v>6298</v>
+        <v>6303</v>
       </c>
       <c r="AR46" t="s">
-        <v>6299</v>
+        <v>6304</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6300</v>
+        <v>6305</v>
       </c>
       <c r="F47" t="s">
-        <v>6301</v>
+        <v>6306</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6302</v>
+        <v>6307</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6303</v>
+        <v>6308</v>
       </c>
       <c r="AC47" t="s">
-        <v>6304</v>
+        <v>6309</v>
       </c>
       <c r="AF47" t="s">
-        <v>6305</v>
+        <v>6310</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6306</v>
+        <v>6311</v>
       </c>
       <c r="AO47" t="s">
-        <v>6307</v>
+        <v>6312</v>
       </c>
       <c r="AR47" t="s">
-        <v>6308</v>
+        <v>6313</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6309</v>
+        <v>6314</v>
       </c>
       <c r="F48" t="s">
-        <v>6310</v>
+        <v>6315</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96514,141 +96625,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6311</v>
+        <v>6316</v>
       </c>
       <c r="AF48" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
       <c r="AO48" t="s">
-        <v>6313</v>
+        <v>6318</v>
       </c>
       <c r="AR48" t="s">
-        <v>6314</v>
+        <v>6319</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6315</v>
+        <v>6320</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6316</v>
+        <v>6321</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6317</v>
+        <v>6322</v>
       </c>
       <c r="AF49" t="s">
-        <v>6318</v>
+        <v>6323</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6319</v>
+        <v>6324</v>
       </c>
       <c r="AR49" t="s">
-        <v>6320</v>
+        <v>6325</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
       <c r="F50" t="s">
-        <v>6322</v>
+        <v>6327</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6323</v>
+        <v>6328</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6324</v>
+        <v>6329</v>
       </c>
       <c r="AR50" t="s">
-        <v>6325</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6326</v>
+        <v>6331</v>
       </c>
       <c r="F51" t="s">
-        <v>6327</v>
+        <v>6332</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
       <c r="AR51" t="s">
-        <v>6329</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6330</v>
+        <v>6335</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6331</v>
+        <v>6336</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6332</v>
+        <v>6337</v>
       </c>
       <c r="AR52" t="s">
-        <v>6333</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6334</v>
+        <v>6339</v>
       </c>
       <c r="F53" t="s">
-        <v>6335</v>
+        <v>6340</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6336</v>
+        <v>6341</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6337</v>
+        <v>6342</v>
       </c>
       <c r="F54" t="s">
-        <v>6338</v>
+        <v>6343</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6339</v>
+        <v>6344</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6340</v>
+        <v>6345</v>
       </c>
       <c r="F55" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96656,10 +96767,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6342</v>
+        <v>6347</v>
       </c>
       <c r="F56" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96667,18 +96778,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6344</v>
+        <v>6349</v>
       </c>
       <c r="F57" t="s">
-        <v>6345</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
       <c r="F58" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96686,42 +96797,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
       <c r="F59" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
       <c r="F60" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="F61" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6354</v>
+        <v>6359</v>
       </c>
       <c r="F62" t="s">
-        <v>6355</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6356</v>
+        <v>6361</v>
       </c>
       <c r="F63" t="s">
-        <v>6357</v>
+        <v>6362</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96729,181 +96840,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6358</v>
+        <v>6363</v>
       </c>
       <c r="F64" t="s">
-        <v>6359</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6321</v>
+        <v>6326</v>
       </c>
       <c r="F65" t="s">
-        <v>6312</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6360</v>
+        <v>6365</v>
       </c>
       <c r="F66" t="s">
-        <v>6361</v>
+        <v>6366</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6362</v>
+        <v>6367</v>
       </c>
       <c r="F67" t="s">
-        <v>6363</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6364</v>
+        <v>6369</v>
       </c>
       <c r="F68" t="s">
-        <v>6328</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6365</v>
+        <v>6370</v>
       </c>
       <c r="F69" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6374</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6375</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6376</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6377</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6378</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6379</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6380</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6381</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6382</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6383</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6384</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6385</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6386</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6125</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6387</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6388</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6389</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6390</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6391</v>
+        <v>6396</v>
       </c>
     </row>
   </sheetData>
@@ -96930,10 +97041,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6392</v>
+        <v>6397</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6393</v>
+        <v>6398</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -96942,13 +97053,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6394</v>
+        <v>6399</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6395</v>
+        <v>6400</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6396</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -96956,13 +97067,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6397</v>
+        <v>6402</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6398</v>
+        <v>6403</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -96974,13 +97085,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6399</v>
+        <v>6404</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6400</v>
+        <v>6405</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -96991,19 +97102,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6401</v>
+        <v>6406</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6402</v>
+        <v>6407</v>
       </c>
       <c r="S10" t="s">
-        <v>6403</v>
+        <v>6408</v>
       </c>
       <c r="T10" t="s">
-        <v>6404</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -97017,15 +97128,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6405</v>
+        <v>6410</v>
       </c>
       <c r="S11" t="s">
-        <v>6129</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6406</v>
+        <v>6411</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -97034,18 +97145,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6407</v>
+        <v>6412</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6408</v>
+        <v>6413</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6409</v>
+        <v>6414</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -97054,7 +97165,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6410</v>
+        <v>6415</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -97065,13 +97176,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6411</v>
+        <v>6416</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6412</v>
+        <v>6417</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -97082,7 +97193,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6413</v>
+        <v>6418</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -97091,10 +97202,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6296</v>
+        <v>6301</v>
       </c>
       <c r="T15" t="s">
-        <v>6414</v>
+        <v>6419</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -97105,12 +97216,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6415</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6416</v>
+        <v>6421</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -97118,22 +97229,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6417</v>
+        <v>6422</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6418</v>
+        <v>6423</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6419</v>
+        <v>6424</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6420</v>
+        <v>6425</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6421</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -97144,39 +97255,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6422</v>
+        <v>6427</v>
       </c>
       <c r="H32" t="s">
-        <v>6423</v>
+        <v>6428</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6424</v>
+        <v>6429</v>
       </c>
       <c r="K32" t="s">
-        <v>6425</v>
+        <v>6430</v>
       </c>
       <c r="N32" t="s">
-        <v>6426</v>
+        <v>6431</v>
       </c>
       <c r="Q32" t="s">
-        <v>6427</v>
+        <v>6432</v>
       </c>
       <c r="S32" t="s">
-        <v>6153</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -97185,13 +97296,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
       <c r="K33" t="s">
-        <v>6431</v>
+        <v>6436</v>
       </c>
       <c r="N33" t="s">
-        <v>6432</v>
+        <v>6437</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -97199,153 +97310,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6433</v>
+        <v>6438</v>
       </c>
       <c r="K34" t="s">
-        <v>6434</v>
+        <v>6439</v>
       </c>
       <c r="N34" t="s">
-        <v>6435</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6436</v>
+        <v>6441</v>
       </c>
       <c r="N35" t="s">
-        <v>6437</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6438</v>
+        <v>6443</v>
       </c>
       <c r="N36" t="s">
-        <v>6439</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6440</v>
+        <v>6445</v>
       </c>
       <c r="N37" t="s">
-        <v>6441</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6442</v>
+        <v>6447</v>
       </c>
       <c r="N38" t="s">
-        <v>6443</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6166</v>
+        <v>6171</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6444</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6445</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6446</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6447</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6448</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6449</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6450</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6451</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6452</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6453</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6343</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6454</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6455</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6341</v>
+        <v>6346</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6459</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6460</v>
+        <v>6465</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6461</v>
+        <v>6466</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97353,7 +97464,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6462</v>
+        <v>6467</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97369,7 +97480,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6463</v>
+        <v>6468</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97385,21 +97496,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6464</v>
+        <v>6469</v>
       </c>
       <c r="J68" t="s">
-        <v>6465</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6466</v>
+        <v>6471</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6467</v>
+        <v>6472</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97408,52 +97519,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6241</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6468</v>
+        <v>6473</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6098</v>
+        <v>6103</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6251</v>
+        <v>6256</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6274</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6469</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6470</v>
+        <v>6475</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6263</v>
+        <v>6268</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6471</v>
+        <v>6476</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6472</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97515,7 +97626,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6473</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97523,10 +97634,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6474</v>
+        <v>6479</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6475</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97534,7 +97645,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6476</v>
+        <v>6481</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97547,15 +97658,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6477</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6478</v>
+        <v>6483</v>
       </c>
       <c r="F17" t="s">
-        <v>6479</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3449</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3452</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13950" uniqueCount="6485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13963" uniqueCount="6489">
   <si>
     <t>名称</t>
   </si>
@@ -20918,6 +20918,18 @@
   </si>
   <si>
     <t>太难理解</t>
+  </si>
+  <si>
+    <t>反转一个字符串里的字母后反转特殊字符</t>
+  </si>
+  <si>
+    <t>打家劫舍 V</t>
+  </si>
+  <si>
+    <t>统计主导元素下标数</t>
+  </si>
+  <si>
+    <t>反向模拟</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -95457,13 +95469,76 @@
       </c>
     </row>
     <row r="3453" spans="1:8">
-      <c r="C3453" s="2"/>
+      <c r="A3453">
+        <v>3823</v>
+      </c>
+      <c r="B3453" t="s">
+        <v>6095</v>
+      </c>
+      <c r="C3453" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D3453" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3453" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3453">
+        <v>1250</v>
+      </c>
+      <c r="G3453" s="1" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="3454" spans="1:8">
-      <c r="C3454" s="2"/>
+      <c r="A3454">
+        <v>3840</v>
+      </c>
+      <c r="B3454" t="s">
+        <v>6096</v>
+      </c>
+      <c r="C3454" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D3454" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3454" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3454">
+        <v>1618</v>
+      </c>
+      <c r="G3454" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="3455" spans="1:8">
-      <c r="C3455" s="2"/>
+      <c r="A3455">
+        <v>3833</v>
+      </c>
+      <c r="B3455" t="s">
+        <v>6097</v>
+      </c>
+      <c r="C3455" s="2">
+        <v>46126</v>
+      </c>
+      <c r="D3455" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3455" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3455">
+        <v>1171</v>
+      </c>
+      <c r="G3455" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H3455" s="1" t="s">
+        <v>6098</v>
+      </c>
     </row>
     <row r="3456" spans="1:8">
       <c r="C3456" s="2"/>
@@ -95488,7 +95563,7 @@
         <v>3454</v>
       </c>
       <c r="B3463" t="s">
-        <v>6095</v>
+        <v>6099</v>
       </c>
       <c r="D3463" t="s">
         <v>138</v>
@@ -95508,7 +95583,7 @@
         <v>3562</v>
       </c>
       <c r="B3464" t="s">
-        <v>6096</v>
+        <v>6100</v>
       </c>
       <c r="D3464" t="s">
         <v>138</v>
@@ -95519,10 +95594,10 @@
     </row>
     <row r="3465" spans="1:7">
       <c r="A3465" t="s">
-        <v>6097</v>
+        <v>6101</v>
       </c>
       <c r="B3465" t="s">
-        <v>6098</v>
+        <v>6102</v>
       </c>
       <c r="D3465" t="s">
         <v>138</v>
@@ -95533,7 +95608,7 @@
         <v>3721</v>
       </c>
       <c r="B3466" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="D3466" t="s">
         <v>138</v>
@@ -95550,7 +95625,7 @@
         <v>3235</v>
       </c>
       <c r="B3467" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="C3467" s="2"/>
       <c r="D3467" t="s">
@@ -95561,7 +95636,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3449" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3452" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95608,10 +95683,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="D5" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95622,13 +95697,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95637,7 +95712,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95652,16 +95727,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95675,10 +95750,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="H14" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95693,16 +95768,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="W14" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95714,158 +95789,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="AL14" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="AO14" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AR14" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AU14" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AX14" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="T15" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="W15" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
       <c r="Z15" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AF15" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="AI15" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="AL15" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AU15" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AX15" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="H16" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="N16" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="T16" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
       <c r="W16" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="Z16" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="AC16" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AF16" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="AI16" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AL16" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="AR16" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="AU16" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AX16" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95873,43 +95948,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="D17" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="H17" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="N17" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="T17" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="W17" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="Z17" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="AC17" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="AF17" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="AI17" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AR17" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="AU17" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="BA17" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95917,37 +95992,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="H18" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="N18" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="T18" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="W18" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="Z18" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="AC18" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="AF18" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AI18" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="AU18" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="BA18" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -95955,37 +96030,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="H19" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="N19" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="T19" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="W19" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="Z19" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="AC19" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="AF19" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="AI19" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AU19" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="BA19" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -95993,37 +96068,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6185</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6186</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6187</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6188</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6189</v>
+      </c>
+      <c r="W20" t="s">
         <v>6181</v>
       </c>
-      <c r="D20" t="s">
-        <v>6182</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6183</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6184</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6185</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6177</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="AC20" t="s">
-        <v>6186</v>
+        <v>6190</v>
       </c>
       <c r="AF20" t="s">
-        <v>6187</v>
+        <v>6191</v>
       </c>
       <c r="AU20" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="BA20" t="s">
-        <v>6189</v>
+        <v>6193</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -96031,37 +96106,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="D21" t="s">
+        <v>6195</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6196</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6197</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6198</v>
+      </c>
+      <c r="W21" t="s">
         <v>6191</v>
       </c>
-      <c r="H21" t="s">
-        <v>6192</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6193</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6194</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6187</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="AC21" t="s">
-        <v>6195</v>
+        <v>6199</v>
       </c>
       <c r="AF21" t="s">
-        <v>6196</v>
+        <v>6200</v>
       </c>
       <c r="AU21" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="BA21" t="s">
-        <v>6198</v>
+        <v>6202</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -96072,13 +96147,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -96087,16 +96162,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="AC22" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="AF22" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="AU22" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -96104,25 +96179,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="H23" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="T23" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="Z23" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="AC23" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
       <c r="AF23" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="AU23" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="24" spans="3:54">
@@ -96130,89 +96205,89 @@
         <v>1786</v>
       </c>
       <c r="H24" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="T24" t="s">
-        <v>6211</v>
+        <v>6215</v>
       </c>
       <c r="Z24" t="s">
-        <v>6212</v>
+        <v>6216</v>
       </c>
       <c r="AC24" t="s">
-        <v>6213</v>
+        <v>6217</v>
       </c>
       <c r="AF24" t="s">
-        <v>6214</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="25" spans="3:54">
       <c r="C25" t="s">
-        <v>6215</v>
+        <v>6219</v>
       </c>
       <c r="D25" t="s">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="T25" t="s">
-        <v>6217</v>
+        <v>6221</v>
       </c>
       <c r="AC25" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AF25" t="s">
-        <v>6219</v>
+        <v>6223</v>
       </c>
     </row>
     <row r="26" spans="3:54">
       <c r="T26" t="s">
-        <v>6220</v>
+        <v>6224</v>
       </c>
       <c r="AC26" t="s">
-        <v>6221</v>
+        <v>6225</v>
       </c>
       <c r="AF26" t="s">
-        <v>6222</v>
+        <v>6226</v>
       </c>
     </row>
     <row r="27" spans="3:54">
       <c r="T27" t="s">
-        <v>6223</v>
+        <v>6227</v>
       </c>
       <c r="AC27" t="s">
-        <v>6224</v>
+        <v>6228</v>
       </c>
       <c r="AF27" t="s">
-        <v>6225</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="28" spans="3:54">
       <c r="T28" t="s">
-        <v>6226</v>
+        <v>6230</v>
       </c>
       <c r="AC28" t="s">
-        <v>6227</v>
+        <v>6231</v>
       </c>
       <c r="AF28" t="s">
-        <v>6228</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="29" spans="3:54">
       <c r="T29" t="s">
-        <v>6229</v>
+        <v>6233</v>
       </c>
     </row>
     <row r="30" spans="3:54">
       <c r="T30" t="s">
-        <v>6230</v>
+        <v>6234</v>
       </c>
     </row>
     <row r="31" spans="3:54">
       <c r="T31" t="s">
-        <v>6231</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="32" spans="3:54">
       <c r="T32" t="s">
-        <v>6232</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="33" spans="3:44">
@@ -96222,22 +96297,22 @@
     </row>
     <row r="34" spans="3:44">
       <c r="T34" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="35" spans="3:44">
       <c r="T35" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
     </row>
     <row r="36" spans="3:44">
       <c r="T36" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="37" spans="3:44">
       <c r="T37" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="38" spans="3:44">
@@ -96247,7 +96322,7 @@
     </row>
     <row r="39" ht="115.2" spans="3:44">
       <c r="I39" s="1" t="s">
-        <v>6237</v>
+        <v>6241</v>
       </c>
       <c r="T39" t="s">
         <v>2288</v>
@@ -96255,7 +96330,7 @@
     </row>
     <row r="40" s="3" customFormat="1" ht="13.8" spans="3:44">
       <c r="C40" s="3" t="s">
-        <v>6238</v>
+        <v>6242</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>109</v>
@@ -96270,7 +96345,7 @@
         <v>1914</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="W40" s="3" t="s">
         <v>67</v>
@@ -96288,227 +96363,227 @@
         <v>3909</v>
       </c>
       <c r="AL40" s="3" t="s">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="AO40" s="3" t="s">
-        <v>6241</v>
+        <v>6245</v>
       </c>
       <c r="AR40" s="3" t="s">
-        <v>6242</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="41" spans="3:44">
       <c r="C41" t="s">
-        <v>6243</v>
+        <v>6247</v>
       </c>
       <c r="F41">
         <v>1802</v>
       </c>
       <c r="G41" t="s">
-        <v>6244</v>
+        <v>6248</v>
       </c>
       <c r="K41">
         <v>1000</v>
       </c>
       <c r="N41" t="s">
-        <v>6245</v>
+        <v>6249</v>
       </c>
       <c r="Q41" t="s">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="T41" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="W41" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
       <c r="Z41">
         <v>834</v>
       </c>
       <c r="AC41" t="s">
-        <v>6247</v>
+        <v>6251</v>
       </c>
       <c r="AF41" t="s">
         <v>2233</v>
       </c>
       <c r="AI41" t="s">
-        <v>6248</v>
+        <v>6252</v>
       </c>
       <c r="AL41" t="s">
-        <v>6249</v>
+        <v>6253</v>
       </c>
       <c r="AO41" t="s">
-        <v>6250</v>
+        <v>6254</v>
       </c>
       <c r="AR41" t="s">
-        <v>6251</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="42" ht="26.4" spans="3:44">
       <c r="C42" s="4" t="s">
-        <v>6252</v>
+        <v>6256</v>
       </c>
       <c r="F42">
         <v>2517</v>
       </c>
       <c r="G42" t="s">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="K42">
         <v>1039</v>
       </c>
       <c r="N42" t="s">
-        <v>6254</v>
+        <v>6258</v>
       </c>
       <c r="Q42" t="s">
-        <v>6234</v>
+        <v>6238</v>
       </c>
       <c r="T42" t="s">
-        <v>6255</v>
+        <v>6259</v>
       </c>
       <c r="W42" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
       <c r="X42" s="2">
         <v>45181</v>
       </c>
       <c r="Z42" t="s">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="AC42" t="s">
-        <v>6258</v>
+        <v>6262</v>
       </c>
       <c r="AF42">
         <v>995</v>
       </c>
       <c r="AI42" t="s">
-        <v>6259</v>
+        <v>6263</v>
       </c>
       <c r="AL42" t="s">
-        <v>6260</v>
+        <v>6264</v>
       </c>
       <c r="AO42" t="s">
-        <v>6261</v>
+        <v>6265</v>
       </c>
       <c r="AR42" t="s">
-        <v>6262</v>
+        <v>6266</v>
       </c>
     </row>
     <row r="43" ht="26.4" spans="3:44">
       <c r="C43" s="4" t="s">
-        <v>6263</v>
+        <v>6267</v>
       </c>
       <c r="F43">
         <v>1379</v>
       </c>
       <c r="G43" t="s">
-        <v>6264</v>
+        <v>6268</v>
       </c>
       <c r="K43" t="s">
-        <v>6265</v>
+        <v>6269</v>
       </c>
       <c r="N43" t="s">
-        <v>6266</v>
+        <v>6270</v>
       </c>
       <c r="Q43" t="s">
-        <v>6235</v>
+        <v>6239</v>
       </c>
       <c r="T43" t="s">
-        <v>6267</v>
+        <v>6271</v>
       </c>
       <c r="W43" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
       <c r="Z43" t="s">
-        <v>6269</v>
+        <v>6273</v>
       </c>
       <c r="AC43" t="s">
-        <v>6270</v>
+        <v>6274</v>
       </c>
       <c r="AF43" t="s">
-        <v>6271</v>
+        <v>6275</v>
       </c>
       <c r="AG43" s="2">
         <v>45185</v>
       </c>
       <c r="AI43" t="s">
-        <v>6272</v>
+        <v>6276</v>
       </c>
       <c r="AL43" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="AO43" t="s">
-        <v>6273</v>
+        <v>6277</v>
       </c>
       <c r="AR43" t="s">
-        <v>6274</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="44" spans="3:44">
       <c r="C44" s="4" t="s">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="F44" t="s">
-        <v>6276</v>
+        <v>6280</v>
       </c>
       <c r="G44" s="2">
         <v>45078</v>
       </c>
       <c r="K44" t="s">
-        <v>6277</v>
+        <v>6281</v>
       </c>
       <c r="N44" t="s">
-        <v>6278</v>
+        <v>6282</v>
       </c>
       <c r="Q44" t="s">
-        <v>6236</v>
+        <v>6240</v>
       </c>
       <c r="W44" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
       <c r="Z44" t="s">
-        <v>6280</v>
+        <v>6284</v>
       </c>
       <c r="AC44" t="s">
-        <v>6281</v>
+        <v>6285</v>
       </c>
       <c r="AF44" t="s">
-        <v>6218</v>
+        <v>6222</v>
       </c>
       <c r="AG44" s="2">
         <v>45185</v>
       </c>
       <c r="AI44" t="s">
-        <v>6282</v>
+        <v>6286</v>
       </c>
       <c r="AL44" t="s">
-        <v>6283</v>
+        <v>6287</v>
       </c>
       <c r="AO44" t="s">
-        <v>6284</v>
+        <v>6288</v>
       </c>
       <c r="AR44" t="s">
-        <v>6285</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="45" ht="72" spans="3:44">
       <c r="C45" s="4" t="s">
-        <v>6286</v>
+        <v>6290</v>
       </c>
       <c r="F45" t="s">
-        <v>6287</v>
+        <v>6291</v>
       </c>
       <c r="G45" s="2">
         <v>45079</v>
       </c>
       <c r="K45" t="s">
-        <v>6288</v>
+        <v>6292</v>
       </c>
       <c r="N45" t="s">
-        <v>6289</v>
+        <v>6293</v>
       </c>
       <c r="Q45" t="s">
-        <v>6290</v>
+        <v>6294</v>
       </c>
       <c r="Z45">
         <v>2858</v>
@@ -96517,103 +96592,103 @@
         <v>2278</v>
       </c>
       <c r="AC45" t="s">
-        <v>6291</v>
+        <v>6295</v>
       </c>
       <c r="AF45" t="s">
-        <v>6292</v>
+        <v>6296</v>
       </c>
       <c r="AG45" s="2">
         <v>45187</v>
       </c>
       <c r="AI45" t="s">
-        <v>6293</v>
+        <v>6297</v>
       </c>
       <c r="AO45" t="s">
-        <v>6294</v>
+        <v>6298</v>
       </c>
       <c r="AR45" t="s">
-        <v>6295</v>
+        <v>6299</v>
       </c>
     </row>
     <row r="46" ht="26.4" spans="3:44">
       <c r="C46" s="4" t="s">
-        <v>6296</v>
+        <v>6300</v>
       </c>
       <c r="F46" t="s">
-        <v>6297</v>
+        <v>6301</v>
       </c>
       <c r="G46" s="2">
         <v>45082</v>
       </c>
       <c r="K46" t="s">
-        <v>6298</v>
+        <v>6302</v>
       </c>
       <c r="N46" t="s">
-        <v>6299</v>
+        <v>6303</v>
       </c>
       <c r="AC46" t="s">
-        <v>6300</v>
+        <v>6304</v>
       </c>
       <c r="AF46" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="AG46" s="2">
         <v>45188</v>
       </c>
       <c r="AI46" t="s">
-        <v>6302</v>
+        <v>6306</v>
       </c>
       <c r="AO46" t="s">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="AR46" t="s">
-        <v>6304</v>
+        <v>6308</v>
       </c>
     </row>
     <row r="47" ht="26.4" spans="3:44">
       <c r="C47" s="4" t="s">
-        <v>6305</v>
+        <v>6309</v>
       </c>
       <c r="F47" t="s">
-        <v>6306</v>
+        <v>6310</v>
       </c>
       <c r="G47" s="2">
         <v>45082</v>
       </c>
       <c r="K47" t="s">
-        <v>6307</v>
+        <v>6311</v>
       </c>
       <c r="N47">
         <v>1155</v>
       </c>
       <c r="O47" t="s">
-        <v>6308</v>
+        <v>6312</v>
       </c>
       <c r="AC47" t="s">
-        <v>6309</v>
+        <v>6313</v>
       </c>
       <c r="AF47" t="s">
-        <v>6310</v>
+        <v>6314</v>
       </c>
       <c r="AG47" s="2">
         <v>45190</v>
       </c>
       <c r="AI47" t="s">
-        <v>6311</v>
+        <v>6315</v>
       </c>
       <c r="AO47" t="s">
-        <v>6312</v>
+        <v>6316</v>
       </c>
       <c r="AR47" t="s">
-        <v>6313</v>
+        <v>6317</v>
       </c>
     </row>
     <row r="48" spans="3:44">
       <c r="C48" t="s">
-        <v>6314</v>
+        <v>6318</v>
       </c>
       <c r="F48" t="s">
-        <v>6315</v>
+        <v>6319</v>
       </c>
       <c r="G48" s="2">
         <v>45082</v>
@@ -96625,141 +96700,141 @@
         <v>2418</v>
       </c>
       <c r="AC48" t="s">
-        <v>6316</v>
+        <v>6320</v>
       </c>
       <c r="AF48" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
       <c r="AO48" t="s">
-        <v>6318</v>
+        <v>6322</v>
       </c>
       <c r="AR48" t="s">
-        <v>6319</v>
+        <v>6323</v>
       </c>
     </row>
     <row r="49" spans="3:44">
       <c r="C49" t="s">
-        <v>6320</v>
+        <v>6324</v>
       </c>
       <c r="D49" s="2">
         <v>45181</v>
       </c>
       <c r="F49" t="s">
-        <v>6321</v>
+        <v>6325</v>
       </c>
       <c r="G49" s="2">
         <v>45082</v>
       </c>
       <c r="AC49" t="s">
-        <v>6322</v>
+        <v>6326</v>
       </c>
       <c r="AF49" t="s">
-        <v>6323</v>
+        <v>6327</v>
       </c>
       <c r="AG49" s="2">
         <v>45189</v>
       </c>
       <c r="AO49" t="s">
-        <v>6324</v>
+        <v>6328</v>
       </c>
       <c r="AR49" t="s">
-        <v>6325</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="50" spans="3:44">
       <c r="C50" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="F50" t="s">
-        <v>6327</v>
+        <v>6331</v>
       </c>
       <c r="G50" s="2">
         <v>45082</v>
       </c>
       <c r="AF50" t="s">
-        <v>6328</v>
+        <v>6332</v>
       </c>
       <c r="AG50" s="2">
         <v>45186</v>
       </c>
       <c r="AO50" t="s">
-        <v>6329</v>
+        <v>6333</v>
       </c>
       <c r="AR50" t="s">
-        <v>6330</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="51" spans="3:44">
       <c r="C51" t="s">
-        <v>6331</v>
+        <v>6335</v>
       </c>
       <c r="F51" t="s">
-        <v>6332</v>
+        <v>6336</v>
       </c>
       <c r="G51" s="2">
         <v>45082</v>
       </c>
       <c r="AF51" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
       <c r="AR51" t="s">
-        <v>6334</v>
+        <v>6338</v>
       </c>
     </row>
     <row r="52" spans="3:44">
       <c r="C52" t="s">
-        <v>6335</v>
+        <v>6339</v>
       </c>
       <c r="D52" s="2">
         <v>45183</v>
       </c>
       <c r="F52" t="s">
-        <v>6336</v>
+        <v>6340</v>
       </c>
       <c r="G52" s="2">
         <v>45083</v>
       </c>
       <c r="AF52" t="s">
-        <v>6337</v>
+        <v>6341</v>
       </c>
       <c r="AR52" t="s">
-        <v>6338</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="53" spans="3:44">
       <c r="C53" t="s">
-        <v>6339</v>
+        <v>6343</v>
       </c>
       <c r="F53" t="s">
-        <v>6340</v>
+        <v>6344</v>
       </c>
       <c r="G53" s="2">
         <v>45083</v>
       </c>
       <c r="AR53" t="s">
-        <v>6341</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="54" spans="3:44">
       <c r="C54" t="s">
-        <v>6342</v>
+        <v>6346</v>
       </c>
       <c r="F54" t="s">
-        <v>6343</v>
+        <v>6347</v>
       </c>
       <c r="G54" s="2">
         <v>45083</v>
       </c>
       <c r="AR54" t="s">
-        <v>6344</v>
+        <v>6348</v>
       </c>
     </row>
     <row r="55" spans="3:44">
       <c r="C55" t="s">
-        <v>6345</v>
+        <v>6349</v>
       </c>
       <c r="F55" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
       <c r="G55" s="2">
         <v>45088</v>
@@ -96767,10 +96842,10 @@
     </row>
     <row r="56" spans="3:44">
       <c r="C56" t="s">
-        <v>6347</v>
+        <v>6351</v>
       </c>
       <c r="F56" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
       <c r="G56" s="2">
         <v>45100</v>
@@ -96778,18 +96853,18 @@
     </row>
     <row r="57" spans="3:44">
       <c r="C57" t="s">
-        <v>6349</v>
+        <v>6353</v>
       </c>
       <c r="F57" t="s">
-        <v>6350</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="58" spans="3:44">
       <c r="C58" t="s">
-        <v>6351</v>
+        <v>6355</v>
       </c>
       <c r="F58" t="s">
-        <v>6352</v>
+        <v>6356</v>
       </c>
       <c r="G58" s="2">
         <v>45099</v>
@@ -96797,42 +96872,42 @@
     </row>
     <row r="59" spans="3:44">
       <c r="C59" t="s">
-        <v>6353</v>
+        <v>6357</v>
       </c>
       <c r="F59" t="s">
-        <v>6354</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="60" spans="3:44">
       <c r="C60" t="s">
-        <v>6355</v>
+        <v>6359</v>
       </c>
       <c r="F60" t="s">
-        <v>6356</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="61" spans="3:44">
       <c r="C61" t="s">
-        <v>6357</v>
+        <v>6361</v>
       </c>
       <c r="F61" t="s">
-        <v>6358</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="62" spans="3:44">
       <c r="C62" t="s">
-        <v>6359</v>
+        <v>6363</v>
       </c>
       <c r="F62" t="s">
-        <v>6360</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="63" spans="3:44">
       <c r="C63" t="s">
-        <v>6361</v>
+        <v>6365</v>
       </c>
       <c r="F63" t="s">
-        <v>6362</v>
+        <v>6366</v>
       </c>
       <c r="G63" s="2">
         <v>45101</v>
@@ -96840,181 +96915,181 @@
     </row>
     <row r="64" spans="3:44">
       <c r="C64" t="s">
-        <v>6363</v>
+        <v>6367</v>
       </c>
       <c r="F64" t="s">
-        <v>6364</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="65" spans="3:7">
       <c r="C65" t="s">
-        <v>6326</v>
+        <v>6330</v>
       </c>
       <c r="F65" t="s">
-        <v>6317</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="66" spans="3:7">
       <c r="C66" t="s">
-        <v>6365</v>
+        <v>6369</v>
       </c>
       <c r="F66" t="s">
-        <v>6366</v>
+        <v>6370</v>
       </c>
       <c r="G66" s="1"/>
     </row>
     <row r="67" spans="3:7">
       <c r="C67" t="s">
-        <v>6367</v>
+        <v>6371</v>
       </c>
       <c r="F67" t="s">
-        <v>6368</v>
+        <v>6372</v>
       </c>
     </row>
     <row r="68" spans="3:7">
       <c r="C68" t="s">
-        <v>6369</v>
+        <v>6373</v>
       </c>
       <c r="F68" t="s">
-        <v>6333</v>
+        <v>6337</v>
       </c>
     </row>
     <row r="69" spans="3:7">
       <c r="C69" t="s">
-        <v>6370</v>
+        <v>6374</v>
       </c>
       <c r="F69" t="s">
-        <v>6371</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="70" spans="3:7">
       <c r="C70" t="s">
-        <v>6372</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="71" spans="3:7">
       <c r="C71" t="s">
-        <v>6373</v>
+        <v>6377</v>
       </c>
     </row>
     <row r="72" spans="3:7">
       <c r="C72" t="s">
-        <v>6374</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="73" spans="3:7">
       <c r="C73" t="s">
-        <v>6375</v>
+        <v>6379</v>
       </c>
     </row>
     <row r="74" spans="3:7">
       <c r="C74" t="s">
-        <v>6376</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" t="s">
-        <v>6377</v>
+        <v>6381</v>
       </c>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" t="s">
-        <v>6378</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="77" spans="3:7">
       <c r="C77" t="s">
-        <v>6379</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="78" spans="3:7">
       <c r="C78" t="s">
-        <v>6380</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="79" spans="3:7">
       <c r="C79" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="80" spans="3:7">
       <c r="C80" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="83" spans="3:3">
       <c r="C83" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="84" spans="3:3">
       <c r="C84" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="85" spans="3:3">
       <c r="C85" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="86" spans="3:3">
       <c r="C86" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="87" spans="3:3">
       <c r="C87" t="s">
-        <v>6389</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" t="s">
-        <v>6390</v>
+        <v>6394</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" t="s">
-        <v>6391</v>
+        <v>6395</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="91" spans="3:3">
       <c r="C91" t="s">
-        <v>6392</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="92" spans="3:3">
       <c r="C92" t="s">
-        <v>6393</v>
+        <v>6397</v>
       </c>
     </row>
     <row r="93" spans="3:3">
       <c r="C93" t="s">
-        <v>6394</v>
+        <v>6398</v>
       </c>
     </row>
     <row r="94" spans="3:3">
       <c r="C94" t="s">
-        <v>6395</v>
+        <v>6399</v>
       </c>
     </row>
     <row r="95" spans="3:3">
       <c r="C95" t="s">
-        <v>6396</v>
+        <v>6400</v>
       </c>
     </row>
   </sheetData>
@@ -97041,10 +97116,10 @@
   <sheetData>
     <row r="8" s="3" customFormat="1" ht="13.8" spans="4:23">
       <c r="D8" s="3" t="s">
-        <v>6397</v>
+        <v>6401</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6398</v>
+        <v>6402</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>152</v>
@@ -97053,13 +97128,13 @@
         <v>1662</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>6399</v>
+        <v>6403</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>6400</v>
+        <v>6404</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>6401</v>
+        <v>6405</v>
       </c>
     </row>
     <row r="9" spans="4:23">
@@ -97067,13 +97142,13 @@
         <v>1882</v>
       </c>
       <c r="H9" t="s">
-        <v>6402</v>
+        <v>6406</v>
       </c>
       <c r="I9">
         <v>2488</v>
       </c>
       <c r="J9" t="s">
-        <v>6403</v>
+        <v>6407</v>
       </c>
       <c r="K9">
         <v>1233</v>
@@ -97085,13 +97160,13 @@
         <v>892</v>
       </c>
       <c r="R9" t="s">
-        <v>6404</v>
+        <v>6408</v>
       </c>
       <c r="S9">
         <v>2589</v>
       </c>
       <c r="T9" t="s">
-        <v>6405</v>
+        <v>6409</v>
       </c>
       <c r="V9" t="s">
         <v>726</v>
@@ -97102,19 +97177,19 @@
     </row>
     <row r="10" spans="4:23">
       <c r="D10" t="s">
-        <v>6406</v>
+        <v>6410</v>
       </c>
       <c r="E10">
         <v>1955</v>
       </c>
       <c r="F10" t="s">
-        <v>6407</v>
+        <v>6411</v>
       </c>
       <c r="S10" t="s">
-        <v>6408</v>
+        <v>6412</v>
       </c>
       <c r="T10" t="s">
-        <v>6409</v>
+        <v>6413</v>
       </c>
     </row>
     <row r="11" ht="28.8" spans="4:23">
@@ -97128,15 +97203,15 @@
         <v>2262</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>6410</v>
+        <v>6414</v>
       </c>
       <c r="S11" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
     </row>
     <row r="12" spans="4:23">
       <c r="D12" t="s">
-        <v>6411</v>
+        <v>6415</v>
       </c>
       <c r="H12" t="s">
         <v>27</v>
@@ -97145,18 +97220,18 @@
         <v>2537</v>
       </c>
       <c r="S12" t="s">
-        <v>6412</v>
+        <v>6416</v>
       </c>
     </row>
     <row r="13" ht="28.8" spans="4:23">
       <c r="D13" t="s">
-        <v>6413</v>
+        <v>6417</v>
       </c>
       <c r="E13" s="1">
         <v>300</v>
       </c>
       <c r="F13" t="s">
-        <v>6414</v>
+        <v>6418</v>
       </c>
       <c r="H13" t="s">
         <v>543</v>
@@ -97165,7 +97240,7 @@
         <v>2522</v>
       </c>
       <c r="J13" t="s">
-        <v>6415</v>
+        <v>6419</v>
       </c>
       <c r="S13">
         <v>986</v>
@@ -97176,13 +97251,13 @@
     </row>
     <row r="14" spans="4:23">
       <c r="D14" t="s">
-        <v>6416</v>
+        <v>6420</v>
       </c>
       <c r="E14">
         <v>2484</v>
       </c>
       <c r="F14" t="s">
-        <v>6417</v>
+        <v>6421</v>
       </c>
       <c r="S14">
         <v>630</v>
@@ -97193,7 +97268,7 @@
     </row>
     <row r="15" spans="4:23">
       <c r="D15" t="s">
-        <v>6418</v>
+        <v>6422</v>
       </c>
       <c r="E15">
         <v>2407</v>
@@ -97202,10 +97277,10 @@
         <v>588</v>
       </c>
       <c r="S15" t="s">
-        <v>6301</v>
+        <v>6305</v>
       </c>
       <c r="T15" t="s">
-        <v>6419</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="16" spans="4:23">
@@ -97216,12 +97291,12 @@
         <v>1819</v>
       </c>
       <c r="F16" t="s">
-        <v>6420</v>
+        <v>6424</v>
       </c>
     </row>
     <row r="17" spans="4:19">
       <c r="D17" t="s">
-        <v>6421</v>
+        <v>6425</v>
       </c>
       <c r="E17">
         <v>2518</v>
@@ -97229,22 +97304,22 @@
     </row>
     <row r="31" s="3" customFormat="1" ht="13.8" spans="4:19">
       <c r="D31" s="3" t="s">
-        <v>6422</v>
+        <v>6426</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>6423</v>
+        <v>6427</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>6424</v>
+        <v>6428</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>6425</v>
+        <v>6429</v>
       </c>
       <c r="Q31" s="3" t="s">
         <v>1279</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>6426</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="32" spans="4:19">
@@ -97255,39 +97330,39 @@
         <v>2538</v>
       </c>
       <c r="F32" t="s">
-        <v>6427</v>
+        <v>6431</v>
       </c>
       <c r="H32" t="s">
-        <v>6428</v>
+        <v>6432</v>
       </c>
       <c r="I32">
         <v>2536</v>
       </c>
       <c r="J32" t="s">
-        <v>6429</v>
+        <v>6433</v>
       </c>
       <c r="K32" t="s">
-        <v>6430</v>
+        <v>6434</v>
       </c>
       <c r="N32" t="s">
-        <v>6431</v>
+        <v>6435</v>
       </c>
       <c r="Q32" t="s">
-        <v>6432</v>
+        <v>6436</v>
       </c>
       <c r="S32" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
     </row>
     <row r="33" ht="43.2" spans="4:14">
       <c r="D33" t="s">
-        <v>6433</v>
+        <v>6437</v>
       </c>
       <c r="E33">
         <v>310</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6434</v>
+        <v>6438</v>
       </c>
       <c r="H33" t="s">
         <v>35</v>
@@ -97296,13 +97371,13 @@
         <v>2503</v>
       </c>
       <c r="J33" t="s">
-        <v>6435</v>
+        <v>6439</v>
       </c>
       <c r="K33" t="s">
-        <v>6436</v>
+        <v>6440</v>
       </c>
       <c r="N33" t="s">
-        <v>6437</v>
+        <v>6441</v>
       </c>
     </row>
     <row r="34" spans="4:14">
@@ -97310,153 +97385,153 @@
         <v>2263</v>
       </c>
       <c r="J34" t="s">
-        <v>6438</v>
+        <v>6442</v>
       </c>
       <c r="K34" t="s">
-        <v>6439</v>
+        <v>6443</v>
       </c>
       <c r="N34" t="s">
-        <v>6440</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="35" spans="4:14">
       <c r="K35" t="s">
-        <v>6441</v>
+        <v>6445</v>
       </c>
       <c r="N35" t="s">
-        <v>6442</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="36" spans="4:14">
       <c r="K36" t="s">
-        <v>6443</v>
+        <v>6447</v>
       </c>
       <c r="N36" t="s">
-        <v>6444</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="37" spans="4:14">
       <c r="K37" t="s">
-        <v>6445</v>
+        <v>6449</v>
       </c>
       <c r="N37" t="s">
-        <v>6446</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="38" spans="4:14">
       <c r="K38" t="s">
-        <v>6447</v>
+        <v>6451</v>
       </c>
       <c r="N38" t="s">
-        <v>6448</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="39" spans="4:14">
       <c r="K39" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="L39" t="s">
         <v>946</v>
       </c>
       <c r="N39" t="s">
-        <v>6449</v>
+        <v>6453</v>
       </c>
     </row>
     <row r="40" spans="4:14">
       <c r="N40" t="s">
-        <v>6450</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="41" spans="4:14">
       <c r="N41" t="s">
-        <v>6451</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="42" spans="4:14">
       <c r="N42" t="s">
-        <v>6452</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="43" spans="4:14">
       <c r="N43" t="s">
-        <v>6453</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="44" spans="4:14">
       <c r="N44" t="s">
-        <v>6454</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="45" spans="4:14">
       <c r="N45" t="s">
-        <v>6455</v>
+        <v>6459</v>
       </c>
     </row>
     <row r="46" spans="4:14">
       <c r="N46" t="s">
-        <v>6456</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="47" spans="4:14">
       <c r="N47" t="s">
-        <v>6457</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="48" spans="4:14">
       <c r="N48" t="s">
-        <v>6458</v>
+        <v>6462</v>
       </c>
     </row>
     <row r="49" spans="4:14">
       <c r="N49" t="s">
-        <v>6348</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="50" spans="4:14">
       <c r="N50" t="s">
-        <v>6459</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="51" spans="4:14">
       <c r="N51" t="s">
-        <v>6460</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="52" spans="4:14">
       <c r="N52" t="s">
-        <v>6346</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="53" spans="4:14">
       <c r="N53" t="s">
-        <v>6461</v>
+        <v>6465</v>
       </c>
     </row>
     <row r="54" spans="4:14">
       <c r="N54" t="s">
-        <v>6462</v>
+        <v>6466</v>
       </c>
     </row>
     <row r="55" spans="4:14">
       <c r="D55" s="3" t="s">
-        <v>6463</v>
+        <v>6467</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>3808</v>
       </c>
       <c r="N55" t="s">
-        <v>6464</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="56" ht="43.2" spans="4:14">
       <c r="D56" t="s">
-        <v>6465</v>
+        <v>6469</v>
       </c>
       <c r="E56">
         <v>1819</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6466</v>
+        <v>6470</v>
       </c>
       <c r="I56">
         <v>753</v>
@@ -97464,7 +97539,7 @@
     </row>
     <row r="57" spans="4:14">
       <c r="D57" t="s">
-        <v>6467</v>
+        <v>6471</v>
       </c>
       <c r="E57">
         <v>2523</v>
@@ -97480,7 +97555,7 @@
     </row>
     <row r="59" spans="4:14">
       <c r="D59" t="s">
-        <v>6468</v>
+        <v>6472</v>
       </c>
       <c r="E59">
         <v>1250</v>
@@ -97496,21 +97571,21 @@
         <v>1279</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>6469</v>
+        <v>6473</v>
       </c>
       <c r="J68" t="s">
-        <v>6470</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="69" spans="4:10">
       <c r="D69" t="s">
-        <v>6471</v>
+        <v>6475</v>
       </c>
       <c r="E69">
         <v>1803</v>
       </c>
       <c r="F69" t="s">
-        <v>6472</v>
+        <v>6476</v>
       </c>
       <c r="H69" t="s">
         <v>201</v>
@@ -97519,52 +97594,52 @@
         <v>765</v>
       </c>
       <c r="J69" t="s">
-        <v>6246</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="70" spans="4:10">
       <c r="D70" t="s">
-        <v>6473</v>
+        <v>6477</v>
       </c>
       <c r="E70">
         <v>982</v>
       </c>
       <c r="H70" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="I70">
         <v>1703</v>
       </c>
       <c r="J70" t="s">
-        <v>6256</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="71" spans="4:10">
       <c r="J71" t="s">
-        <v>6279</v>
+        <v>6283</v>
       </c>
     </row>
     <row r="72" spans="4:10">
       <c r="J72" t="s">
-        <v>6474</v>
+        <v>6478</v>
       </c>
     </row>
     <row r="73" spans="4:10">
       <c r="J73" t="s">
-        <v>6475</v>
+        <v>6479</v>
       </c>
     </row>
     <row r="74" spans="4:10">
       <c r="J74" t="s">
-        <v>6268</v>
+        <v>6272</v>
       </c>
     </row>
     <row r="81" spans="4:9">
       <c r="D81" s="3" t="s">
-        <v>6476</v>
+        <v>6480</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>6477</v>
+        <v>6481</v>
       </c>
     </row>
     <row r="82" spans="4:9">
@@ -97626,7 +97701,7 @@
         <v>2462</v>
       </c>
       <c r="D7" t="s">
-        <v>6478</v>
+        <v>6482</v>
       </c>
     </row>
     <row r="8" ht="100.8" spans="3:5">
@@ -97634,10 +97709,10 @@
         <v>2476</v>
       </c>
       <c r="D8" t="s">
-        <v>6479</v>
+        <v>6483</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6480</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="9" spans="3:5">
@@ -97645,7 +97720,7 @@
         <v>2483</v>
       </c>
       <c r="D9" t="s">
-        <v>6481</v>
+        <v>6485</v>
       </c>
     </row>
     <row r="10" spans="3:5">
@@ -97658,15 +97733,15 @@
     </row>
     <row r="11" spans="3:5">
       <c r="E11" t="s">
-        <v>6482</v>
+        <v>6486</v>
       </c>
     </row>
     <row r="17" spans="3:8">
       <c r="C17" t="s">
-        <v>6483</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="s">
-        <v>6484</v>
+        <v>6488</v>
       </c>
     </row>
     <row r="18" spans="3:8">

--- a/Problems.xlsx
+++ b/Problems.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3452</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">题库!$A$1:$L$3455</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13963" uniqueCount="6489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13976" uniqueCount="6493">
   <si>
     <t>名称</t>
   </si>
@@ -20930,6 +20930,18 @@
   </si>
   <si>
     <t>反向模拟</t>
+  </si>
+  <si>
+    <t>二进制中恰好K个1的第N小整数</t>
+  </si>
+  <si>
+    <t>开始用了数位DP，发现性能不够</t>
+  </si>
+  <si>
+    <t>前缀连接组的数目</t>
+  </si>
+  <si>
+    <t>频率唯一的第一个元素</t>
   </si>
   <si>
     <t>分割正方形 II</t>
@@ -22598,16 +22610,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -95541,13 +95553,76 @@
       </c>
     </row>
     <row r="3456" spans="1:8">
-      <c r="C3456" s="2"/>
+      <c r="A3456">
+        <v>3821</v>
+      </c>
+      <c r="B3456" t="s">
+        <v>6099</v>
+      </c>
+      <c r="C3456" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D3456" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3456" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3456">
+        <v>2069</v>
+      </c>
+      <c r="G3456" s="1" t="s">
+        <v>5692</v>
+      </c>
+      <c r="H3456" s="1" t="s">
+        <v>6100</v>
+      </c>
     </row>
     <row r="3457" spans="1:7">
-      <c r="C3457" s="2"/>
+      <c r="A3457">
+        <v>3839</v>
+      </c>
+      <c r="B3457" t="s">
+        <v>6101</v>
+      </c>
+      <c r="C3457" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D3457" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3457" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3457">
+        <v>1401</v>
+      </c>
+      <c r="G3457" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3458" spans="1:7">
-      <c r="C3458" s="2"/>
+      <c r="A3458">
+        <v>3843</v>
+      </c>
+      <c r="B3458" t="s">
+        <v>6102</v>
+      </c>
+      <c r="C3458" s="2">
+        <v>46127</v>
+      </c>
+      <c r="D3458" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3458" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3458">
+        <v>1347</v>
+      </c>
+      <c r="G3458" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3459" spans="1:7">
       <c r="C3459" s="2"/>
@@ -95563,7 +95638,7 @@
         <v>3454</v>
       </c>
       <c r="B3463" t="s">
-        <v>6099</v>
+        <v>6103</v>
       </c>
       <c r="D3463" t="s">
         <v>138</v>
@@ -95583,7 +95658,7 @@
         <v>3562</v>
       </c>
       <c r="B3464" t="s">
-        <v>6100</v>
+        <v>6104</v>
       </c>
       <c r="D3464" t="s">
         <v>138</v>
@@ -95594,10 +95669,10 @@
     </row>
     <row r="3465" spans="1:7">
       <c r="A3465" t="s">
-        <v>6101</v>
+        <v>6105</v>
       </c>
       <c r="B3465" t="s">
-        <v>6102</v>
+        <v>6106</v>
       </c>
       <c r="D3465" t="s">
         <v>138</v>
@@ -95608,7 +95683,7 @@
         <v>3721</v>
       </c>
       <c r="B3466" t="s">
-        <v>6103</v>
+        <v>6107</v>
       </c>
       <c r="D3466" t="s">
         <v>138</v>
@@ -95625,7 +95700,7 @@
         <v>3235</v>
       </c>
       <c r="B3467" t="s">
-        <v>6104</v>
+        <v>6108</v>
       </c>
       <c r="C3467" s="2"/>
       <c r="D3467" t="s">
@@ -95636,7 +95711,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3452" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L3455" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -95683,10 +95758,10 @@
   <sheetData>
     <row r="5" spans="3:59">
       <c r="C5" t="s">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="D5" t="s">
-        <v>6106</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="13.8" spans="3:59">
@@ -95697,13 +95772,13 @@
         <v>791</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>6107</v>
+        <v>6111</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>1666</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>6108</v>
+        <v>6112</v>
       </c>
       <c r="T13" s="3" t="s">
         <v>125</v>
@@ -95712,7 +95787,7 @@
         <v>116</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>6109</v>
+        <v>6113</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>929</v>
@@ -95727,16 +95802,16 @@
         <v>767</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="AR13" s="3" t="s">
-        <v>6111</v>
+        <v>6115</v>
       </c>
       <c r="AU13" s="3" t="s">
         <v>3546</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>6112</v>
+        <v>6116</v>
       </c>
       <c r="BA13" s="3" t="s">
         <v>2963</v>
@@ -95750,10 +95825,10 @@
     </row>
     <row r="14" ht="43.2" spans="3:59">
       <c r="C14" t="s">
-        <v>6113</v>
+        <v>6117</v>
       </c>
       <c r="H14" t="s">
-        <v>6114</v>
+        <v>6118</v>
       </c>
       <c r="K14">
         <v>462</v>
@@ -95768,16 +95843,16 @@
         <v>2182</v>
       </c>
       <c r="T14" t="s">
-        <v>6115</v>
+        <v>6119</v>
       </c>
       <c r="W14" t="s">
-        <v>6116</v>
+        <v>6120</v>
       </c>
       <c r="X14" s="2">
         <v>45102</v>
       </c>
       <c r="Z14" t="s">
-        <v>6117</v>
+        <v>6121</v>
       </c>
       <c r="AA14" s="2">
         <v>45139</v>
@@ -95789,158 +95864,158 @@
         <v>2103</v>
       </c>
       <c r="AF14" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AG14" s="2">
         <v>45172</v>
       </c>
       <c r="AI14" t="s">
-        <v>6119</v>
+        <v>6123</v>
       </c>
       <c r="AL14" t="s">
-        <v>6120</v>
+        <v>6124</v>
       </c>
       <c r="AO14" t="s">
-        <v>6121</v>
+        <v>6125</v>
       </c>
       <c r="AR14" t="s">
-        <v>6122</v>
+        <v>6126</v>
       </c>
       <c r="AU14" t="s">
-        <v>6123</v>
+        <v>6127</v>
       </c>
       <c r="AX14" t="s">
-        <v>6124</v>
+        <v>6128</v>
       </c>
       <c r="AY14">
         <v>1762</v>
       </c>
       <c r="BA14" t="s">
-        <v>6125</v>
+        <v>6129</v>
       </c>
       <c r="BB14">
         <v>1985</v>
       </c>
       <c r="BD14" t="s">
-        <v>6126</v>
+        <v>6130</v>
       </c>
       <c r="BE14">
         <v>1897</v>
       </c>
       <c r="BG14" t="s">
-        <v>6127</v>
+        <v>6131</v>
       </c>
     </row>
     <row r="15" spans="3:59">
       <c r="C15" t="s">
-        <v>6128</v>
+        <v>6132</v>
       </c>
       <c r="H15" t="s">
         <v>1547</v>
       </c>
       <c r="N15" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="T15" t="s">
-        <v>6130</v>
+        <v>6134</v>
       </c>
       <c r="W15" t="s">
-        <v>6131</v>
+        <v>6135</v>
       </c>
       <c r="Z15" t="s">
-        <v>6132</v>
+        <v>6136</v>
       </c>
       <c r="AA15" s="2">
         <v>45141</v>
       </c>
       <c r="AC15" t="s">
-        <v>6133</v>
+        <v>6137</v>
       </c>
       <c r="AF15" t="s">
-        <v>6134</v>
+        <v>6138</v>
       </c>
       <c r="AI15" t="s">
-        <v>6135</v>
+        <v>6139</v>
       </c>
       <c r="AL15" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AO15" t="s">
         <v>2289</v>
       </c>
       <c r="AR15" t="s">
-        <v>6137</v>
+        <v>6141</v>
       </c>
       <c r="AU15" t="s">
-        <v>6138</v>
+        <v>6142</v>
       </c>
       <c r="AX15" t="s">
-        <v>6139</v>
+        <v>6143</v>
       </c>
       <c r="AY15">
         <v>1846</v>
       </c>
       <c r="BA15" t="s">
-        <v>6140</v>
+        <v>6144</v>
       </c>
       <c r="BB15">
         <v>1723</v>
       </c>
       <c r="BD15" t="s">
-        <v>6141</v>
+        <v>6145</v>
       </c>
       <c r="BE15">
         <v>2227</v>
       </c>
       <c r="BG15" t="s">
-        <v>6142</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="16" spans="3:59">
       <c r="C16" t="s">
-        <v>6143</v>
+        <v>6147</v>
       </c>
       <c r="H16" t="s">
-        <v>6144</v>
+        <v>6148</v>
       </c>
       <c r="N16" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="T16" t="s">
-        <v>6146</v>
+        <v>6150</v>
       </c>
       <c r="W16" t="s">
-        <v>6147</v>
+        <v>6151</v>
       </c>
       <c r="Z16" t="s">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="AC16" t="s">
-        <v>6136</v>
+        <v>6140</v>
       </c>
       <c r="AF16" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="AI16" t="s">
-        <v>6149</v>
+        <v>6153</v>
       </c>
       <c r="AL16" t="s">
-        <v>6150</v>
+        <v>6154</v>
       </c>
       <c r="AR16" t="s">
-        <v>6151</v>
+        <v>6155</v>
       </c>
       <c r="AU16" t="s">
-        <v>6152</v>
+        <v>6156</v>
       </c>
       <c r="AX16" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="AY16">
         <v>2039</v>
       </c>
       <c r="BA16" t="s">
-        <v>6154</v>
+        <v>6158</v>
       </c>
       <c r="BB16">
         <v>1751</v>
@@ -95948,43 +96023,43 @@
     </row>
     <row r="17" spans="3:54">
       <c r="C17" t="s">
-        <v>6155</v>
+        <v>6159</v>
       </c>
       <c r="D17" t="s">
-        <v>6156</v>
+        <v>6160</v>
       </c>
       <c r="H17" t="s">
-        <v>6157</v>
+        <v>6161</v>
       </c>
       <c r="N17" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="T17" t="s">
-        <v>6159</v>
+        <v>6163</v>
       </c>
       <c r="W17" t="s">
-        <v>6118</v>
+        <v>6122</v>
       </c>
       <c r="Z17" t="s">
-        <v>6129</v>
+        <v>6133</v>
       </c>
       <c r="AC17" t="s">
-        <v>6160</v>
+        <v>6164</v>
       </c>
       <c r="AF17" t="s">
-        <v>6161</v>
+        <v>6165</v>
       </c>
       <c r="AI17" t="s">
-        <v>6162</v>
+        <v>6166</v>
       </c>
       <c r="AR17" t="s">
-        <v>6163</v>
+        <v>6167</v>
       </c>
       <c r="AU17" t="s">
-        <v>6164</v>
+        <v>6168</v>
       </c>
       <c r="BA17" t="s">
-        <v>6165</v>
+        <v>6169</v>
       </c>
       <c r="BB17">
         <v>2070</v>
@@ -95992,37 +96067,37 @@
     </row>
     <row r="18" spans="3:54">
       <c r="C18" t="s">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="H18" t="s">
-        <v>6167</v>
+        <v>6171</v>
       </c>
       <c r="N18" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="T18" t="s">
-        <v>6169</v>
+        <v>6173</v>
       </c>
       <c r="W18" t="s">
-        <v>6170</v>
+        <v>6174</v>
       </c>
       <c r="Z18" t="s">
-        <v>6145</v>
+        <v>6149</v>
       </c>
       <c r="AC18" t="s">
-        <v>6171</v>
+        <v>6175</v>
       </c>
       <c r="AF18" t="s">
-        <v>6172</v>
+        <v>6176</v>
       </c>
       <c r="AI18" t="s">
-        <v>6173</v>
+        <v>6177</v>
       </c>
       <c r="AU18" t="s">
-        <v>6174</v>
+        <v>6178</v>
       </c>
       <c r="BA18" t="s">
-        <v>6175</v>
+        <v>6179</v>
       </c>
       <c r="BB18">
         <v>2080</v>
@@ -96030,37 +96105,37 @@
     </row>
     <row r="19" spans="3:54">
       <c r="C19" t="s">
-        <v>6176</v>
+        <v>6180</v>
       </c>
       <c r="H19" t="s">
-        <v>6177</v>
+        <v>6181</v>
       </c>
       <c r="N19" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="T19" t="s">
-        <v>6179</v>
+        <v>6183</v>
       </c>
       <c r="W19" t="s">
-        <v>6153</v>
+        <v>6157</v>
       </c>
       <c r="Z19" t="s">
-        <v>6158</v>
+        <v>6162</v>
       </c>
       <c r="AC19" t="s">
-        <v>6180</v>
+        <v>6184</v>
       </c>
       <c r="AF19" t="s">
-        <v>6181</v>
+        <v>6185</v>
       </c>
       <c r="AI19" t="s">
-        <v>6182</v>
+        <v>6186</v>
       </c>
       <c r="AU19" t="s">
-        <v>6183</v>
+        <v>6187</v>
       </c>
       <c r="BA19" t="s">
-        <v>6184</v>
+        <v>6188</v>
       </c>
       <c r="BB19">
         <v>2092</v>
@@ -96068,37 +96143,37 @@
     </row>
     <row r="20" spans="3:54">
       <c r="C20" t="s">
+        <v>6189</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6190</v>
+      </c>
+      <c r="H20" t="s">
+        <v>6191</v>
+      </c>
+      <c r="N20" t="s">
+        <v>6192</v>
+      </c>
+      <c r="T20" t="s">
+        <v>6193</v>
+      </c>
+      <c r="W20" t="s">
         <v>6185</v>
       </c>
-      <c r="D20" t="s">
-        <v>6186</v>
-      </c>
-      <c r="H20" t="s">
-        <v>6187</v>
-      </c>
-      <c r="N20" t="s">
-        <v>6188</v>
-      </c>
-      <c r="T20" t="s">
-        <v>6189</v>
-      </c>
-      <c r="W20" t="s">
-        <v>6181</v>
-      </c>
       <c r="Z20" t="s">
-        <v>6168</v>
+        <v>6172</v>
       </c>
       <c r="AC20" t="s">
-        <v>6190</v>
+        <v>6194</v>
       </c>
       <c r="AF20" t="s">
-        <v>6191</v>
+        <v>6195</v>
       </c>
       <c r="AU20" t="s">
-        <v>6192</v>
+        <v>6196</v>
       </c>
       <c r="BA20" t="s">
-        <v>6193</v>
+        <v>6197</v>
       </c>
       <c r="BB20">
         <v>2071</v>
@@ -96106,37 +96181,37 @@
     </row>
     <row r="21" spans="3:54">
       <c r="C21" t="s">
-        <v>6194</v>
+        <v>6198</v>
       </c>
       <c r="D21" t="s">
+        <v>6199</v>
+      </c>
+      <c r="H21" t="s">
+        <v>6200</v>
+      </c>
+      <c r="N21" t="s">
+        <v>6201</v>
+      </c>
+      <c r="T21" t="s">
+        <v>6202</v>
+      </c>
+      <c r="W21" t="s">
         <v>6195</v>
       </c>
-      <c r="H21" t="s">
-        <v>6196</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6197</v>
-      </c>
-      <c r="T21" t="s">
-        <v>6198</v>
-      </c>
-      <c r="W21" t="s">
-        <v>6191</v>
-      </c>
       <c r="Z21" t="s">
-        <v>6178</v>
+        <v>6182</v>
       </c>
       <c r="AC21" t="s">
-        <v>6199</v>
+        <v>6203</v>
       </c>
       <c r="AF21" t="s">
-        <v>6200</v>
+        <v>6204</v>
       </c>
       <c r="AU21" t="s">
-        <v>6201</v>
+        <v>6205</v>
       </c>
       <c r="BA21" t="s">
-        <v>6202</v>
+        <v>6206</v>
       </c>
       <c r="BB21">
         <v>1915</v>
@@ -96147,13 +96222,13 @@
         <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>6203</v>
+        <v>6207</v>
       </c>
       <c r="N22">
         <v>2741</v>
       </c>
       <c r="T22" t="s">
-        <v>6204</v>
+        <v>6208</v>
       </c>
       <c r="W22">
         <v>1444</v>
@@ -96162,16 +96237,16 @@
         <v>2154</v>
       </c>
       <c r="Z22" t="s">
-        <v>6188</v>
+        <v>6192</v>
       </c>
       <c r="AC22" t="s">
-        <v>6205</v>
+        <v>6209</v>
       </c>
       <c r="AF22" t="s">
-        <v>6206</v>
+        <v>6210</v>
       </c>
       <c r="AU22" t="s">
-        <v>6207</v>
+        <v>6211</v>
       </c>
     </row>
     <row r="23" spans="3:54">
@@ -96179,25 +96254,25 @@
         <v>1591</v>
       </c>
       <c r="D23" t="s">
-        <v>6208</v>
+        <v>6212</v>
       </c>
       <c r="H23" t="s">
-        <v>6209</v>
+        <v>6213</v>
       </c>
       <c r="T23" t="s">
-        <v>6210</v>
+        <v>6214</v>
       </c>
       <c r="Z23" t="s">
-        <v>6197</v>
+        <v>6201</v>
       </c>
       <c r="AC23" t="s">
-     